--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -3223,7 +3223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
     <col width="18" customWidth="1" style="30" min="1" max="1"/>
@@ -4399,26 +4399,24 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>广告执行调整</t>
-        </is>
-      </c>
-      <c r="C31" s="42" t="n">
+          <t>关键词与搜索词调整</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="42" t="n">
+      <c r="D31" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>小批量（≤5个Campaign）：2分。
-中批量（6—20个Campaign）：3分。
-大批量（21个及以上Campaign）：4分。
-按同次安排、同一调整目的计。</t>
+          <t>同次安排、同一调整目的的一批任务合计2分。
+涉及多项具体明细仍只计一次，不按数量分档。</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>固定1.0；按负责人明确指令执行并核验。分值按涉及Campaign数量分档选择。</t>
+          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
         </is>
       </c>
       <c r="G31" s="41">
@@ -4427,7 +4425,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>涵盖关键词与搜索词调整、否定投放调整、广告产品归组与补充、ASIN与商品投放调整、Bid与投放位置调整。同一次安排、同一调整目的合计基础分；不按对象或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分。</t>
+          <t>按指定要求新增、暂停或修改关键词及匹配方式。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4441,42 +4439,194 @@
     <row r="32" ht="55.5" customHeight="1" s="39">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>广告调整</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>否定投放调整</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>同次安排、同一调整目的的一批任务合计2分。
+涉及多项具体明细仍只计一次，不按数量分档。</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
+        </is>
+      </c>
+      <c r="G32" s="41">
+        <f>ROUND(C32*D32,1)</f>
+        <v/>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>按指定要求添加或调整否定关键词、否定ASIN。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>广告调整</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>广告产品归组与补充</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>同次安排、同一调整目的的一批任务合计2分。
+涉及多项具体明细仍只计一次，不按数量分档。</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
+        </is>
+      </c>
+      <c r="G33" s="41">
+        <f>ROUND(C33*D33,1)</f>
+        <v/>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>按指定要求补充、暂停或调整广告商品SKU及广告组归属。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="55.5" customHeight="1" s="39">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>广告调整</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>ASIN与商品投放调整</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>同次安排、同一调整目的的一批任务合计2分。
+涉及多项具体明细仍只计一次，不按数量分档。</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
+        </is>
+      </c>
+      <c r="G34" s="41">
+        <f>ROUND(C34*D34,1)</f>
+        <v/>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>按指定要求新增、暂停或修改ASIN及品类投放。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="55.5" customHeight="1" s="39">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>广告调整</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Bid与投放位置调整</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>同次安排、同一调整目的的一批任务合计2分。
+涉及多项具体明细仍只计一次，不按数量分档。</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
+        </is>
+      </c>
+      <c r="G35" s="41">
+        <f>ROUND(C35*D35,1)</f>
+        <v/>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>按指定要求调整竞价或广告位置竞价。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>Listing与账号异常</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Listing异常申诉与Case处理</t>
         </is>
       </c>
-      <c r="C32" s="40" t="n">
+      <c r="C36" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="D36" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>每个ASIN的一项独立异常处理：4分。
 处理5个ASIN计20分；不再采用ASIN数量分档。
 同一ASIN同一异常只计一次。</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>固定1.0；按ASIN及独立异常计分，不按Case数量或处理次数增加系数。</t>
         </is>
       </c>
-      <c r="G32" s="41">
-        <f>ROUND(C32*D32,1)</f>
-        <v/>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="G36" s="41">
+        <f>ROUND(C36*D36,1)</f>
+        <v/>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>包含异常核查、材料整理、Appeal或Case提交、回复跟进及结果核验。同一ASIN同一异常的多次申诉、多个Case或补充材料合并计4分。合并在一个Case中的多个ASIN按个数计分，但须逐个记录处理结果。恢复后验收；未恢复时提交完整记录，经负责人确认阶段结案后计分，后续同一异常恢复不重复领取。已归Buy Box、滞留库存或变体关系维护的同一问题不叠加本项。负责人安排计任务分，自主发起改善仅计主动分。</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>1个ASIN，多次Case处理同一异常：4分。
 5个ASIN合并一个Case，逐个完成核验：20分。
@@ -4484,240 +4634,240 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="37" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Brand Store维护</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>二级类目商品维护</t>
         </is>
       </c>
-      <c r="C33" s="40" t="n">
+      <c r="C37" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="D37" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>每个二级类目的一次商品更新：2分。
 在原有模块内添加、删除或替换商品；不按SKU数量增加。</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>固定1.0；按实际更新的二级类目数量计分。</t>
         </is>
       </c>
-      <c r="G33" s="41">
-        <f>ROUND(C33*D33,1)</f>
-        <v/>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="G37" s="41">
+        <f>ROUND(C37*D37,1)</f>
+        <v/>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>按实际二级类目及一次安排计分，例如Motorized Ball Valve下的1/2英寸尺寸类目。记录类目路径和页面标识；同类目多商品更新合并一次，不按SKU数量加分。同一二级类目既改商品又重建模块，只计5分，不计7分。正常提交、反馈修正及核验包含在原任务中；本人本次操作导致的报错修复不新增分。按发起来源选择任务分或主动分，不叠加。</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>更新1/2英寸类目商品：2分。
 同时更新1/2英寸和3/4英寸两个类目：4分。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="55.5" customHeight="1" s="39">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="38" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Brand Store维护</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>二级类目模块新增或重建</t>
         </is>
       </c>
-      <c r="C34" s="40" t="n">
+      <c r="C38" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="D38" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>每个二级类目的一次模块新增、替换或重建：5分。
 包含必要布局、商品配置及核验；不按模块数量增加。</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>固定1.0；按实际调整的二级类目数量计分。</t>
         </is>
       </c>
-      <c r="G34" s="41">
-        <f>ROUND(C34*D34,1)</f>
-        <v/>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="G38" s="41">
+        <f>ROUND(C38*D38,1)</f>
+        <v/>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>按实际二级类目及一次安排计分，例如Motorized Ball Valve下的1/2英寸尺寸类目。记录类目路径和页面标识；同类目多商品更新合并一次，不按SKU数量加分。同一二级类目既改商品又重建模块，只计5分，不计7分。正常提交、反馈修正及核验包含在原任务中；本人本次操作导致的报错修复不新增分。按发起来源选择任务分或主动分，不叠加。</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>1/2英寸类目重建模块并配置商品：5分。
 两个尺寸类目均需重建：10分。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="55.5" customHeight="1" s="39">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="39" ht="55.5" customHeight="1" s="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Brand Store维护</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>提交阻断问题处理</t>
         </is>
       </c>
-      <c r="C35" s="40" t="n">
+      <c r="C39" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="D39" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>每次独立提交任务：3分。
 仅限本次更新范围外其他板块的原有报错。</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>固定1.0；同次提交多个报错合并计分。</t>
         </is>
       </c>
-      <c r="G35" s="41">
-        <f>ROUND(C35*D35,1)</f>
-        <v/>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="G39" s="41">
+        <f>ROUND(C39*D39,1)</f>
+        <v/>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>仅处理本次更新范围之外、其他板块原有报错导致无法提交的问题。须保留报错截图、修复位置和提交成功记录。同一独立提交任务出现多个报错、反复尝试或涉及多个类目，只计一次3分，不按报错或类目数累加。本人本次更新造成的错误属于返工，不计本项。由同一人或不同人处理均按实际工作归属，不能重复领取。</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>两个尺寸类目商品更新4分＋修复其他板块历史报错3分＝7分。
 若报错由本人本次操作导致，仍只计4分。</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="40" ht="55.5" customHeight="1" s="39">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Review、Feedback与客户声音</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>VOC数据更新与AI分析</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n">
+      <c r="C40" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="D40" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>每周完成一次数据下载、数据库更新、AI分析及基本核验，计2分；不按数据条数分档。</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>固定1.0；按每周完整任务计分。</t>
         </is>
       </c>
-      <c r="G36" s="41">
-        <f>ROUND(C36*D36,1)</f>
-        <v/>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="G40" s="41">
+        <f>ROUND(C40*D40,1)</f>
+        <v/>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>下载本周所需数据并记录期间；保存到数据库，核对导入成功、无明显遗漏或重复；运行AI分析，保存结果并检查是否正常生成及有无明显错误。同一周任务中的多次下载、分文件导入、AI重跑和失败重试合并计分。AI分析不等于员工独立业务分析；后续核实问题、形成建议或推动处理，按独立交付及发起来源另行认定，相同工作不重复计分。</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>完成本周下载、入库、AI分析及核验：2分。
 同周分多个文件导入或重跑AI：仍计2分。</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="41" ht="41.65" customHeight="1" s="39">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Review、Feedback与客户声音</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Listing问题处理</t>
         </is>
       </c>
-      <c r="C37" s="40" t="n">
+      <c r="C41" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="D41" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>关联入口：0分
 按Listing纠错、优化或素材主任务计分
 相同修改不再重复获得任务分</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>不适用：本项不独立计任务分
 难度按关联主任务的等级选择</t>
         </is>
       </c>
-      <c r="G37" s="41">
-        <f>ROUND(C37*D37,1)</f>
-        <v/>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="G41" s="41">
+        <f>ROUND(C41*D41,1)</f>
+        <v/>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>VOC只是问题来源，不决定计分路径。负责人安排的修改按对应主任务计分；员工自主发现并发起的改善仅计主动分，同一交付不叠加。</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="I41" s="2" t="n"/>
+    </row>
+    <row r="42" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>Review、Feedback与客户声音</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>产品质量问题反馈</t>
         </is>
       </c>
-      <c r="C38" s="40" t="n">
+      <c r="C42" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="D42" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>1类产品共性问题：
 1个产品：2分
@@ -4726,378 +4876,322 @@
 含证据、转交及1个反馈节点</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>1.0：按标准范围和既定方案完成
 1.3：证据存在差异，需补充分类或核实范围。
 1.6：跨产品证据相互矛盾，需系统梳理及协调验证结论。</t>
         </is>
       </c>
-      <c r="G38" s="41">
-        <f>ROUND(C38*D38,1)</f>
-        <v/>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="G42" s="41">
+        <f>ROUND(C42*D42,1)</f>
+        <v/>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>与售后同类反馈合并为同一问题单；产品开发执行另计开发任务。</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n"/>
-    </row>
-    <row r="39" ht="55.5" customHeight="1" s="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="I42" s="2" t="n"/>
+    </row>
+    <row r="43" ht="41.65" customHeight="1" s="39">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>库存与配送</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>FBA货件问题处理</t>
         </is>
       </c>
-      <c r="C39" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="C43" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>每个货件问题计1分。</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G39" s="41">
-        <f>ROUND(C39*D39,1)</f>
-        <v/>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="G43" s="41">
+        <f>ROUND(C43*D43,1)</f>
+        <v/>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>查看问题并核对情况，按实际情况接受，或选择不接受并提交Appeal，完成处理记录。同一货件、同一问题后续查看、重复提交及跟进不重复计分。不以Appeal成功为计分条件，须完成必要操作并核验提交状态。</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>处理3个货件，每个货件各1个问题：3分。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="55.5" customHeight="1" s="39">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="44" ht="41.65" customHeight="1" s="39">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>库存与配送</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>库存冗余折扣上传</t>
         </is>
       </c>
-      <c r="C40" s="40" t="n">
+      <c r="C44" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="D44" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>同一次安排的一批上传任务计2分，不按SKU数量增加。</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>固定1.0；程序提供SKU及折扣方案，员工上传并核验。</t>
         </is>
       </c>
-      <c r="G40" s="41">
-        <f>ROUND(C40*D40,1)</f>
-        <v/>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="G44" s="41">
+        <f>ROUND(C44*D44,1)</f>
+        <v/>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>包含上传、检查处理结果及修正上传报错。同一批拆成多个文件、重复上传或重试不重复计分。不要求员工分析冗余原因或制定折扣方案，不以库存最终售出作为完成条件。与价格调整或促销创建属于同一次交付的，只计一次分。</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>程序生成50个SKU及折扣，完成上传并确认生效：2分。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="41.65" customHeight="1" s="39">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="45" ht="83.25" customHeight="1" s="39">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>库存管理</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>滞留库存—移除库存</t>
         </is>
       </c>
-      <c r="C41" s="40" t="n">
+      <c r="C45" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="D45" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>每批2分，不按SKU数量增加。</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G41" s="41">
-        <f>ROUND(C41*D41,1)</f>
-        <v/>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="G45" s="41">
+        <f>ROUND(C45*D45,1)</f>
+        <v/>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>成功创建移除订单，核对SKU、数量及处理方式，保存订单编号。
 同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>同批移除多个SKU：2分。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="46" ht="83.25" customHeight="1" s="39">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>库存管理</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>滞留库存—Relist重新发布</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n">
+      <c r="C46" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="D46" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>每批2分，不按SKU数量增加。</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G42" s="41">
-        <f>ROUND(C42*D42,1)</f>
-        <v/>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="G46" s="41">
+        <f>ROUND(C46*D46,1)</f>
+        <v/>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>完成重新发布，核验发布结果及滞留状态，保留处理记录。
 同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>同批Relist多个SKU：2分。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="41.65" customHeight="1" s="39">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="47" ht="97.15000000000001" customHeight="1" s="39">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>库存管理</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>滞留库存—申诉或Case处理</t>
         </is>
       </c>
-      <c r="C43" s="40" t="n">
+      <c r="C47" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="D43" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="D47" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>每个独立问题3分，不按Case或提交次数增加。</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G43" s="41">
-        <f>ROUND(C43*D43,1)</f>
-        <v/>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="G47" s="41">
+        <f>ROUND(C47*D47,1)</f>
+        <v/>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>核对原因、提交申诉或Case并跟进；问题解决，或材料及处理记录完整、由负责人确认阶段结案。
 同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>同一问题先Relist再申诉：合计3分。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="41.65" customHeight="1" s="39">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="48" ht="83.25" customHeight="1" s="39">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>库存管理</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>滞留库存—已有电池／化学品资料提交</t>
         </is>
       </c>
-      <c r="C44" s="40" t="n">
+      <c r="C48" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="D48" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>使用已有完整资料完成一批提交，计2分。</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G44" s="41">
-        <f>ROUND(C44*D44,1)</f>
-        <v/>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="G48" s="41">
+        <f>ROUND(C48*D48,1)</f>
+        <v/>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>核对资料与SKU的对应关系，提交并跟进审核结果，保存资料版本及处理记录。
 同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>已有完整资料完成一批提交：2分。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="83.25" customHeight="1" s="39">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="49" ht="97.15000000000001" customHeight="1" s="39">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>库存管理</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>滞留库存—电池／化学品资料协调与提交</t>
         </is>
       </c>
-      <c r="C45" s="42" t="n">
+      <c r="C49" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D45" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="D49" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>需协调获取资料、核对并完成一批提交，计3分。</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G45" s="41">
-        <f>ROUND(C45*D45,1)</f>
-        <v/>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="G49" s="41">
+        <f>ROUND(C49*D49,1)</f>
+        <v/>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不再加计2分。
 同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>协调取得资料并提交：合计3分。</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="83.25" customHeight="1" s="39">
-      <c r="A46" s="7" t="n"/>
-      <c r="B46" s="7" t="n"/>
-      <c r="C46" s="40" t="n"/>
-      <c r="D46" s="40" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
-      <c r="G46" s="41">
-        <f>ROUND(C46*D46,1)</f>
-        <v/>
-      </c>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="97.15000000000001" customHeight="1" s="39">
-      <c r="A47" s="7" t="n"/>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="40" t="n"/>
-      <c r="D47" s="40" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="41">
-        <f>ROUND(C47*D47,1)</f>
-        <v/>
-      </c>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="83.25" customHeight="1" s="39">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="40" t="n"/>
-      <c r="D48" s="40" t="n"/>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="7" t="n"/>
-      <c r="G48" s="41">
-        <f>ROUND(C48*D48,1)</f>
-        <v/>
-      </c>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="2" t="n"/>
-    </row>
-    <row r="49" ht="97.15000000000001" customHeight="1" s="39">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="40" t="n"/>
-      <c r="D49" s="40" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="41">
-        <f>ROUND(C49*D49,1)</f>
-        <v/>
-      </c>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="2" t="n"/>
     </row>
     <row r="50" ht="14.6" customHeight="1" s="39">
       <c r="A50" s="7" t="n"/>
@@ -5225,10 +5319,62 @@
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="2" t="n"/>
     </row>
-    <row r="59" ht="14.6" customHeight="1" s="39"/>
-    <row r="60" ht="14.6" customHeight="1" s="39"/>
-    <row r="61" ht="14.6" customHeight="1" s="39"/>
-    <row r="62" ht="14.6" customHeight="1" s="39"/>
+    <row r="59" ht="14.6" customHeight="1" s="39">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="40" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="41">
+        <f>ROUND(C59*D59,1)</f>
+        <v/>
+      </c>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="2" t="n"/>
+    </row>
+    <row r="60" ht="14.6" customHeight="1" s="39">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="41">
+        <f>ROUND(C60*D60,1)</f>
+        <v/>
+      </c>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="14.6" customHeight="1" s="39">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="40" t="n"/>
+      <c r="D61" s="40" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="41">
+        <f>ROUND(C61*D61,1)</f>
+        <v/>
+      </c>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="2" t="n"/>
+    </row>
+    <row r="62" ht="14.6" customHeight="1" s="39">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="40" t="n"/>
+      <c r="D62" s="40" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="41">
+        <f>ROUND(C62*D62,1)</f>
+        <v/>
+      </c>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="2" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="D8 D20 D24 D41 D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -9584,241 +9730,67 @@
       </c>
     </row>
     <row r="143" ht="30" customHeight="1" s="39">
-      <c r="A143" s="47" t="inlineStr">
-        <is>
-          <t>广告执行调整：按涉及Campaign数量分档计分</t>
-        </is>
-      </c>
+      <c r="A143" s="47" t="n"/>
     </row>
     <row r="144" ht="34" customHeight="1" s="39">
-      <c r="A144" s="48" t="inlineStr">
-        <is>
-          <t>工作项目</t>
-        </is>
-      </c>
-      <c r="B144" s="48" t="inlineStr">
-        <is>
-          <t>实际场景</t>
-        </is>
-      </c>
-      <c r="C144" s="48" t="inlineStr">
-        <is>
-          <t>累计基础分</t>
-        </is>
-      </c>
-      <c r="D144" s="48" t="inlineStr">
-        <is>
-          <t>难度系数</t>
-        </is>
-      </c>
-      <c r="E144" s="48" t="inlineStr">
-        <is>
-          <t>任务积分</t>
-        </is>
-      </c>
-      <c r="F144" s="48" t="inlineStr">
-        <is>
-          <t>计算依据</t>
-        </is>
-      </c>
-      <c r="G144" s="48" t="inlineStr">
-        <is>
-          <t>结算说明</t>
-        </is>
-      </c>
-      <c r="H144" s="48" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
+      <c r="A144" s="48" t="n"/>
+      <c r="B144" s="48" t="n"/>
+      <c r="C144" s="48" t="n"/>
+      <c r="D144" s="48" t="n"/>
+      <c r="E144" s="48" t="n"/>
+      <c r="F144" s="48" t="n"/>
+      <c r="G144" s="48" t="n"/>
+      <c r="H144" s="48" t="n"/>
     </row>
     <row r="145" ht="105" customHeight="1" s="39">
-      <c r="A145" s="0" t="inlineStr">
-        <is>
-          <t>广告执行调整</t>
-        </is>
-      </c>
-      <c r="B145" s="0" t="inlineStr">
-        <is>
-          <t>同次安排调整3个Campaign的Bid</t>
-        </is>
-      </c>
-      <c r="C145" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D145" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" s="0">
-        <f>ROUND(C145*D145,1)</f>
-        <v/>
-      </c>
-      <c r="F145" s="0" t="inlineStr">
-        <is>
-          <t>≤5个Campaign：2分</t>
-        </is>
-      </c>
-      <c r="G145" s="0" t="inlineStr">
-        <is>
-          <t>认领变化、关联任务、填写原因并核验后计分</t>
-        </is>
-      </c>
-      <c r="H145" s="0" t="inlineStr">
-        <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
-        </is>
-      </c>
+      <c r="A145" s="0" t="n"/>
+      <c r="B145" s="0" t="n"/>
+      <c r="C145" s="0" t="n"/>
+      <c r="D145" s="0" t="n"/>
+      <c r="E145" s="0" t="n"/>
+      <c r="F145" s="0" t="n"/>
+      <c r="G145" s="0" t="n"/>
+      <c r="H145" s="0" t="n"/>
     </row>
     <row r="146" ht="105" customHeight="1" s="39">
-      <c r="A146" s="0" t="inlineStr">
-        <is>
-          <t>广告执行调整</t>
-        </is>
-      </c>
-      <c r="B146" s="0" t="inlineStr">
-        <is>
-          <t>同次安排调整15个Campaign的否定词</t>
-        </is>
-      </c>
-      <c r="C146" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D146" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" s="0">
-        <f>ROUND(C146*D146,1)</f>
-        <v/>
-      </c>
-      <c r="F146" s="0" t="inlineStr">
-        <is>
-          <t>6—20个Campaign：3分</t>
-        </is>
-      </c>
-      <c r="G146" s="0" t="inlineStr">
-        <is>
-          <t>同一调整目的的多项明细只计一次</t>
-        </is>
-      </c>
-      <c r="H146" s="0" t="inlineStr">
-        <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
-        </is>
-      </c>
+      <c r="A146" s="0" t="n"/>
+      <c r="B146" s="0" t="n"/>
+      <c r="C146" s="0" t="n"/>
+      <c r="D146" s="0" t="n"/>
+      <c r="E146" s="0" t="n"/>
+      <c r="F146" s="0" t="n"/>
+      <c r="G146" s="0" t="n"/>
+      <c r="H146" s="0" t="n"/>
     </row>
     <row r="147" ht="105" customHeight="1" s="39">
-      <c r="A147" s="0" t="inlineStr">
-        <is>
-          <t>广告执行调整</t>
-        </is>
-      </c>
-      <c r="B147" s="0" t="inlineStr">
-        <is>
-          <t>同次安排调整30个Campaign的关键词与Bid</t>
-        </is>
-      </c>
-      <c r="C147" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D147" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" s="0">
-        <f>ROUND(C147*D147,1)</f>
-        <v/>
-      </c>
-      <c r="F147" s="0" t="inlineStr">
-        <is>
-          <t>21个及以上Campaign：4分</t>
-        </is>
-      </c>
-      <c r="G147" s="0" t="inlineStr">
-        <is>
-          <t>不按调整类型拆分，同一目的合并</t>
-        </is>
-      </c>
-      <c r="H147" s="0" t="inlineStr">
-        <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
-        </is>
-      </c>
+      <c r="A147" s="0" t="n"/>
+      <c r="B147" s="0" t="n"/>
+      <c r="C147" s="0" t="n"/>
+      <c r="D147" s="0" t="n"/>
+      <c r="E147" s="0" t="n"/>
+      <c r="F147" s="0" t="n"/>
+      <c r="G147" s="0" t="n"/>
+      <c r="H147" s="0" t="n"/>
     </row>
     <row r="148" ht="105" customHeight="1" s="39">
-      <c r="A148" s="0" t="inlineStr">
-        <is>
-          <t>广告执行调整</t>
-        </is>
-      </c>
-      <c r="B148" s="0" t="inlineStr">
-        <is>
-          <t>同次安排同时调整否定词和Bid，涉及8个Campaign</t>
-        </is>
-      </c>
-      <c r="C148" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D148" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="0">
-        <f>ROUND(C148*D148,1)</f>
-        <v/>
-      </c>
-      <c r="F148" s="0" t="inlineStr">
-        <is>
-          <t>同一调整目的关联一个任务</t>
-        </is>
-      </c>
-      <c r="G148" s="0" t="inlineStr">
-        <is>
-          <t>不按调整类型分别计分</t>
-        </is>
-      </c>
-      <c r="H148" s="0" t="inlineStr">
-        <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
-        </is>
-      </c>
+      <c r="A148" s="0" t="n"/>
+      <c r="B148" s="0" t="n"/>
+      <c r="C148" s="0" t="n"/>
+      <c r="D148" s="0" t="n"/>
+      <c r="E148" s="0" t="n"/>
+      <c r="F148" s="0" t="n"/>
+      <c r="G148" s="0" t="n"/>
+      <c r="H148" s="0" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="0" t="inlineStr">
-        <is>
-          <t>广告执行调整</t>
-        </is>
-      </c>
-      <c r="B149" s="0" t="inlineStr">
-        <is>
-          <t>两个独立目的分别调整不同Campaign</t>
-        </is>
-      </c>
-      <c r="C149" s="0" t="inlineStr">
-        <is>
-          <t>各自分档</t>
-        </is>
-      </c>
-      <c r="D149" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="0" t="inlineStr">
-        <is>
-          <t>各自分档</t>
-        </is>
-      </c>
-      <c r="F149" s="0" t="inlineStr">
-        <is>
-          <t>按独立目的分别计分</t>
-        </is>
-      </c>
-      <c r="G149" s="0" t="inlineStr">
-        <is>
-          <t>每个目的按各自Campaign数量分档</t>
-        </is>
-      </c>
-      <c r="H149" s="0" t="inlineStr">
-        <is>
-          <t>各自独立按≤5/6-20/21+选档</t>
-        </is>
-      </c>
+      <c r="A149" s="0" t="n"/>
+      <c r="B149" s="0" t="n"/>
+      <c r="C149" s="0" t="n"/>
+      <c r="D149" s="0" t="n"/>
+      <c r="E149" s="0" t="n"/>
+      <c r="F149" s="0" t="n"/>
+      <c r="G149" s="0" t="n"/>
+      <c r="H149" s="0" t="n"/>
     </row>
     <row r="151" ht="30" customHeight="1" s="39"/>
     <row r="152" ht="34" customHeight="1" s="39"/>
@@ -11113,9 +11085,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A143:H143"/>
     <mergeCell ref="A109:H109"/>
     <mergeCell ref="A87:H87"/>
     <mergeCell ref="A134:H134"/>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="43">
     <font>
       <name val="Carlito"/>
       <charset val="134"/>
@@ -270,8 +270,28 @@
       <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -494,8 +514,26 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -634,6 +672,40 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -787,7 +859,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -910,6 +982,51 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="38" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="39" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="40" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -3223,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
     <col width="18" customWidth="1" style="30" min="1" max="1"/>
@@ -4392,40 +4509,41 @@
       </c>
     </row>
     <row r="31" ht="55.5" customHeight="1" s="39">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>广告调整</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>关键词与搜索词调整</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="n">
+      <c r="B31" s="60" t="inlineStr">
+        <is>
+          <t>广告执行调整</t>
+        </is>
+      </c>
+      <c r="C31" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>同次安排、同一调整目的的一批任务合计2分。
-涉及多项具体明细仍只计一次，不按数量分档。</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
-        </is>
-      </c>
-      <c r="G31" s="41">
+      <c r="D31" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="60" t="inlineStr">
+        <is>
+          <t>每个Campaign每次有效调整：2分。
+每个自然周（周一至周日）每个Campaign最多计2次，即每个Campaign每周最高4分。
+不同Campaign分别计分。</t>
+        </is>
+      </c>
+      <c r="F31" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；按负责人明确指令或主动发起的有效调整执行并核验。</t>
+        </is>
+      </c>
+      <c r="G31" s="63">
         <f>ROUND(C31*D31,1)</f>
         <v/>
       </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>按指定要求新增、暂停或修改关键词及匹配方式。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
+      <c r="H31" s="60" t="inlineStr">
+        <is>
+          <t>涵盖关键词与搜索词调整、否定投放调整、广告产品归组与补充、ASIN与商品投放调整、Bid与投放位置调整。同一次调整包含多种动作合计只算1次。第二次计分须有第一次调整后的复查依据或新问题依据，并实际完成新的调整；拆分操作、重复提交、修复本人错误不另算。每次关联Ads Change，记录原因并完成核验。主动倍率×1。</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4439,194 +4557,42 @@
     <row r="32" ht="55.5" customHeight="1" s="39">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>广告调整</t>
+          <t>Listing与账号异常</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>否定投放调整</t>
+          <t>Listing异常申诉与Case处理</t>
         </is>
       </c>
       <c r="C32" s="40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>同次安排、同一调整目的的一批任务合计2分。
-涉及多项具体明细仍只计一次，不按数量分档。</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
-        </is>
-      </c>
-      <c r="G32" s="41">
-        <f>ROUND(C32*D32,1)</f>
-        <v/>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>按指定要求添加或调整否定关键词、否定ASIN。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>广告调整</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>广告产品归组与补充</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>同次安排、同一调整目的的一批任务合计2分。
-涉及多项具体明细仍只计一次，不按数量分档。</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
-        </is>
-      </c>
-      <c r="G33" s="41">
-        <f>ROUND(C33*D33,1)</f>
-        <v/>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>按指定要求补充、暂停或调整广告商品SKU及广告组归属。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="55.5" customHeight="1" s="39">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>广告调整</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>ASIN与商品投放调整</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>同次安排、同一调整目的的一批任务合计2分。
-涉及多项具体明细仍只计一次，不按数量分档。</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
-        </is>
-      </c>
-      <c r="G34" s="41">
-        <f>ROUND(C34*D34,1)</f>
-        <v/>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>按指定要求新增、暂停或修改ASIN及品类投放。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="55.5" customHeight="1" s="39">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>广告调整</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Bid与投放位置调整</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>同次安排、同一调整目的的一批任务合计2分。
-涉及多项具体明细仍只计一次，不按数量分档。</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按明确指令执行，负责人已明确调整对象及具体操作要求，员工执行并核验。</t>
-        </is>
-      </c>
-      <c r="G35" s="41">
-        <f>ROUND(C35*D35,1)</f>
-        <v/>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>按指定要求调整竞价或广告位置竞价。 仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计2分，多个明细关联同一任务，不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Listing与账号异常</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Listing异常申诉与Case处理</t>
-        </is>
-      </c>
-      <c r="C36" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>每个ASIN的一项独立异常处理：4分。
 处理5个ASIN计20分；不再采用ASIN数量分档。
 同一ASIN同一异常只计一次。</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>固定1.0；按ASIN及独立异常计分，不按Case数量或处理次数增加系数。</t>
         </is>
       </c>
-      <c r="G36" s="41">
-        <f>ROUND(C36*D36,1)</f>
-        <v/>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="G32" s="41">
+        <f>ROUND(C32*D32,1)</f>
+        <v/>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>包含异常核查、材料整理、Appeal或Case提交、回复跟进及结果核验。同一ASIN同一异常的多次申诉、多个Case或补充材料合并计4分。合并在一个Case中的多个ASIN按个数计分，但须逐个记录处理结果。恢复后验收；未恢复时提交完整记录，经负责人确认阶段结案后计分，后续同一异常恢复不重复领取。已归Buy Box、滞留库存或变体关系维护的同一问题不叠加本项。负责人安排计任务分，自主发起改善仅计主动分。</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>1个ASIN，多次Case处理同一异常：4分。
 5个ASIN合并一个Case，逐个完成核验：20分。
@@ -4634,240 +4600,240 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Brand Store维护</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>二级类目商品维护</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>每个二级类目的一次商品更新：2分。
+在原有模块内添加、删除或替换商品；不按SKU数量增加。</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际更新的二级类目数量计分。</t>
+        </is>
+      </c>
+      <c r="G33" s="41">
+        <f>ROUND(C33*D33,1)</f>
+        <v/>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>按实际二级类目及一次安排计分，例如Motorized Ball Valve下的1/2英寸尺寸类目。记录类目路径和页面标识；同类目多商品更新合并一次，不按SKU数量加分。同一二级类目既改商品又重建模块，只计5分，不计7分。正常提交、反馈修正及核验包含在原任务中；本人本次操作导致的报错修复不新增分。按发起来源选择任务分或主动分，不叠加。</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>更新1/2英寸类目商品：2分。
+同时更新1/2英寸和3/4英寸两个类目：4分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="55.5" customHeight="1" s="39">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Brand Store维护</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>二级类目模块新增或重建</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>每个二级类目的一次模块新增、替换或重建：5分。
+包含必要布局、商品配置及核验；不按模块数量增加。</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际调整的二级类目数量计分。</t>
+        </is>
+      </c>
+      <c r="G34" s="41">
+        <f>ROUND(C34*D34,1)</f>
+        <v/>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>按实际二级类目及一次安排计分，例如Motorized Ball Valve下的1/2英寸尺寸类目。记录类目路径和页面标识；同类目多商品更新合并一次，不按SKU数量加分。同一二级类目既改商品又重建模块，只计5分，不计7分。正常提交、反馈修正及核验包含在原任务中；本人本次操作导致的报错修复不新增分。按发起来源选择任务分或主动分，不叠加。</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1/2英寸类目重建模块并配置商品：5分。
+两个尺寸类目均需重建：10分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="55.5" customHeight="1" s="39">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Brand Store维护</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>提交阻断问题处理</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>每次独立提交任务：3分。
+仅限本次更新范围外其他板块的原有报错。</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；同次提交多个报错合并计分。</t>
+        </is>
+      </c>
+      <c r="G35" s="41">
+        <f>ROUND(C35*D35,1)</f>
+        <v/>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>仅处理本次更新范围之外、其他板块原有报错导致无法提交的问题。须保留报错截图、修复位置和提交成功记录。同一独立提交任务出现多个报错、反复尝试或涉及多个类目，只计一次3分，不按报错或类目数累加。本人本次更新造成的错误属于返工，不计本项。由同一人或不同人处理均按实际工作归属，不能重复领取。</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>两个尺寸类目商品更新4分＋修复其他板块历史报错3分＝7分。
+若报错由本人本次操作导致，仍只计4分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Review、Feedback与客户声音</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>VOC数据更新与AI分析</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>每周完成一次数据下载、数据库更新、AI分析及基本核验，计2分；不按数据条数分档。</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；按每周完整任务计分。</t>
+        </is>
+      </c>
+      <c r="G36" s="41">
+        <f>ROUND(C36*D36,1)</f>
+        <v/>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>下载本周所需数据并记录期间；保存到数据库，核对导入成功、无明显遗漏或重复；运行AI分析，保存结果并检查是否正常生成及有无明显错误。同一周任务中的多次下载、分文件导入、AI重跑和失败重试合并计分。AI分析不等于员工独立业务分析；后续核实问题、形成建议或推动处理，按独立交付及发起来源另行认定，相同工作不重复计分。</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>完成本周下载、入库、AI分析及核验：2分。
+同周分多个文件导入或重跑AI：仍计2分。</t>
+        </is>
+      </c>
+    </row>
     <row r="37" ht="69.40000000000001" customHeight="1" s="39">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Brand Store维护</t>
+          <t>Review、Feedback与客户声音</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>二级类目商品维护</t>
+          <t>Listing问题处理</t>
         </is>
       </c>
       <c r="C37" s="40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D37" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>每个二级类目的一次商品更新：2分。
-在原有模块内添加、删除或替换商品；不按SKU数量增加。</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按实际更新的二级类目数量计分。</t>
-        </is>
-      </c>
-      <c r="G37" s="41">
-        <f>ROUND(C37*D37,1)</f>
-        <v/>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>按实际二级类目及一次安排计分，例如Motorized Ball Valve下的1/2英寸尺寸类目。记录类目路径和页面标识；同类目多商品更新合并一次，不按SKU数量加分。同一二级类目既改商品又重建模块，只计5分，不计7分。正常提交、反馈修正及核验包含在原任务中；本人本次操作导致的报错修复不新增分。按发起来源选择任务分或主动分，不叠加。</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>更新1/2英寸类目商品：2分。
-同时更新1/2英寸和3/4英寸两个类目：4分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Brand Store维护</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>二级类目模块新增或重建</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>每个二级类目的一次模块新增、替换或重建：5分。
-包含必要布局、商品配置及核验；不按模块数量增加。</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按实际调整的二级类目数量计分。</t>
-        </is>
-      </c>
-      <c r="G38" s="41">
-        <f>ROUND(C38*D38,1)</f>
-        <v/>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>按实际二级类目及一次安排计分，例如Motorized Ball Valve下的1/2英寸尺寸类目。记录类目路径和页面标识；同类目多商品更新合并一次，不按SKU数量加分。同一二级类目既改商品又重建模块，只计5分，不计7分。正常提交、反馈修正及核验包含在原任务中；本人本次操作导致的报错修复不新增分。按发起来源选择任务分或主动分，不叠加。</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>1/2英寸类目重建模块并配置商品：5分。
-两个尺寸类目均需重建：10分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="55.5" customHeight="1" s="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Brand Store维护</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>提交阻断问题处理</t>
-        </is>
-      </c>
-      <c r="C39" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>每次独立提交任务：3分。
-仅限本次更新范围外其他板块的原有报错。</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；同次提交多个报错合并计分。</t>
-        </is>
-      </c>
-      <c r="G39" s="41">
-        <f>ROUND(C39*D39,1)</f>
-        <v/>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>仅处理本次更新范围之外、其他板块原有报错导致无法提交的问题。须保留报错截图、修复位置和提交成功记录。同一独立提交任务出现多个报错、反复尝试或涉及多个类目，只计一次3分，不按报错或类目数累加。本人本次更新造成的错误属于返工，不计本项。由同一人或不同人处理均按实际工作归属，不能重复领取。</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>两个尺寸类目商品更新4分＋修复其他板块历史报错3分＝7分。
-若报错由本人本次操作导致，仍只计4分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="55.5" customHeight="1" s="39">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Review、Feedback与客户声音</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>VOC数据更新与AI分析</t>
-        </is>
-      </c>
-      <c r="C40" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>每周完成一次数据下载、数据库更新、AI分析及基本核验，计2分；不按数据条数分档。</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0；按每周完整任务计分。</t>
-        </is>
-      </c>
-      <c r="G40" s="41">
-        <f>ROUND(C40*D40,1)</f>
-        <v/>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>下载本周所需数据并记录期间；保存到数据库，核对导入成功、无明显遗漏或重复；运行AI分析，保存结果并检查是否正常生成及有无明显错误。同一周任务中的多次下载、分文件导入、AI重跑和失败重试合并计分。AI分析不等于员工独立业务分析；后续核实问题、形成建议或推动处理，按独立交付及发起来源另行认定，相同工作不重复计分。</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>完成本周下载、入库、AI分析及核验：2分。
-同周分多个文件导入或重跑AI：仍计2分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="41.65" customHeight="1" s="39">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Review、Feedback与客户声音</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Listing问题处理</t>
-        </is>
-      </c>
-      <c r="C41" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>关联入口：0分
 按Listing纠错、优化或素材主任务计分
 相同修改不再重复获得任务分</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>不适用：本项不独立计任务分
 难度按关联主任务的等级选择</t>
         </is>
       </c>
-      <c r="G41" s="41">
-        <f>ROUND(C41*D41,1)</f>
-        <v/>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="G37" s="41">
+        <f>ROUND(C37*D37,1)</f>
+        <v/>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>VOC只是问题来源，不决定计分路径。负责人安排的修改按对应主任务计分；员工自主发现并发起的改善仅计主动分，同一交付不叠加。</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="I37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Review、Feedback与客户声音</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>产品质量问题反馈</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n">
+      <c r="C38" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="D38" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>1类产品共性问题：
 1个产品：2分
@@ -4876,44 +4842,214 @@
 含证据、转交及1个反馈节点</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>1.0：按标准范围和既定方案完成
 1.3：证据存在差异，需补充分类或核实范围。
 1.6：跨产品证据相互矛盾，需系统梳理及协调验证结论。</t>
         </is>
       </c>
+      <c r="G38" s="41">
+        <f>ROUND(C38*D38,1)</f>
+        <v/>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>与售后同类反馈合并为同一问题单；产品开发执行另计开发任务。</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n"/>
+    </row>
+    <row r="39" ht="55.5" customHeight="1" s="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>库存与配送</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>FBA货件问题处理</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>每个货件问题计1分。</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0。</t>
+        </is>
+      </c>
+      <c r="G39" s="41">
+        <f>ROUND(C39*D39,1)</f>
+        <v/>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>查看问题并核对情况，按实际情况接受，或选择不接受并提交Appeal，完成处理记录。同一货件、同一问题后续查看、重复提交及跟进不重复计分。不以Appeal成功为计分条件，须完成必要操作并核验提交状态。</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>处理3个货件，每个货件各1个问题：3分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="55.5" customHeight="1" s="39">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>库存与配送</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>库存冗余折扣上传</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>同一次安排的一批上传任务计2分，不按SKU数量增加。</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0；程序提供SKU及折扣方案，员工上传并核验。</t>
+        </is>
+      </c>
+      <c r="G40" s="41">
+        <f>ROUND(C40*D40,1)</f>
+        <v/>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>包含上传、检查处理结果及修正上传报错。同一批拆成多个文件、重复上传或重试不重复计分。不要求员工分析冗余原因或制定折扣方案，不以库存最终售出作为完成条件。与价格调整或促销创建属于同一次交付的，只计一次分。</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>程序生成50个SKU及折扣，完成上传并确认生效：2分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="41.65" customHeight="1" s="39">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>库存管理</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>滞留库存—移除库存</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>每批2分，不按SKU数量增加。</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0。</t>
+        </is>
+      </c>
+      <c r="G41" s="41">
+        <f>ROUND(C41*D41,1)</f>
+        <v/>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>成功创建移除订单，核对SKU、数量及处理方式，保存订单编号。
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>同批移除多个SKU：2分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="69.40000000000001" customHeight="1" s="39">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>库存管理</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>滞留库存—Relist重新发布</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>每批2分，不按SKU数量增加。</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>固定1.0。</t>
+        </is>
+      </c>
       <c r="G42" s="41">
         <f>ROUND(C42*D42,1)</f>
         <v/>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>与售后同类反馈合并为同一问题单；产品开发执行另计开发任务。</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n"/>
+          <t>完成重新发布，核验发布结果及滞留状态，保留处理记录。
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>同批Relist多个SKU：2分。</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="41.65" customHeight="1" s="39">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>库存与配送</t>
+          <t>库存管理</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>FBA货件问题处理</t>
+          <t>滞留库存—申诉或Case处理</t>
         </is>
       </c>
       <c r="C43" s="40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>每个货件问题计1分。</t>
+          <t>每个独立问题3分，不按Case或提交次数增加。</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -4927,24 +5063,25 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>查看问题并核对情况，按实际情况接受，或选择不接受并提交Appeal，完成处理记录。同一货件、同一问题后续查看、重复提交及跟进不重复计分。不以Appeal成功为计分条件，须完成必要操作并核验提交状态。</t>
+          <t>核对原因、提交申诉或Case并跟进；问题解决，或材料及处理记录完整、由负责人确认阶段结案。
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>处理3个货件，每个货件各1个问题：3分。</t>
+          <t>同一问题先Relist再申诉：合计3分。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="41.65" customHeight="1" s="39">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>库存与配送</t>
+          <t>库存管理</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>库存冗余折扣上传</t>
+          <t>滞留库存—已有电池／化学品资料提交</t>
         </is>
       </c>
       <c r="C44" s="40" t="n">
@@ -4955,12 +5092,12 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>同一次安排的一批上传任务计2分，不按SKU数量增加。</t>
+          <t>使用已有完整资料完成一批提交，计2分。</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>固定1.0；程序提供SKU及折扣方案，员工上传并核验。</t>
+          <t>固定1.0。</t>
         </is>
       </c>
       <c r="G44" s="41">
@@ -4969,12 +5106,13 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>包含上传、检查处理结果及修正上传报错。同一批拆成多个文件、重复上传或重试不重复计分。不要求员工分析冗余原因或制定折扣方案，不以库存最终售出作为完成条件。与价格调整或促销创建属于同一次交付的，只计一次分。</t>
+          <t>核对资料与SKU的对应关系，提交并跟进审核结果，保存资料版本及处理记录。
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>程序生成50个SKU及折扣，完成上传并确认生效：2分。</t>
+          <t>已有完整资料完成一批提交：2分。</t>
         </is>
       </c>
     </row>
@@ -4986,18 +5124,18 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>滞留库存—移除库存</t>
-        </is>
-      </c>
-      <c r="C45" s="40" t="n">
-        <v>2</v>
+          <t>滞留库存—电池／化学品资料协调与提交</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="D45" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>每批2分，不按SKU数量增加。</t>
+          <t>需协调获取资料、核对并完成一批提交，计3分。</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -5011,187 +5149,71 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>成功创建移除订单，核对SKU、数量及处理方式，保存订单编号。
+          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不再加计2分。
 同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>同批移除多个SKU：2分。</t>
+          <t>协调取得资料并提交：合计3分。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="83.25" customHeight="1" s="39">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>库存管理</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>滞留库存—Relist重新发布</t>
-        </is>
-      </c>
-      <c r="C46" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>每批2分，不按SKU数量增加。</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0。</t>
-        </is>
-      </c>
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="40" t="n"/>
+      <c r="D46" s="40" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
       <c r="G46" s="41">
         <f>ROUND(C46*D46,1)</f>
         <v/>
       </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>完成重新发布，核验发布结果及滞留状态，保留处理记录。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>同批Relist多个SKU：2分。</t>
-        </is>
-      </c>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="2" t="n"/>
     </row>
     <row r="47" ht="97.15000000000001" customHeight="1" s="39">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>库存管理</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>滞留库存—申诉或Case处理</t>
-        </is>
-      </c>
-      <c r="C47" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D47" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>每个独立问题3分，不按Case或提交次数增加。</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0。</t>
-        </is>
-      </c>
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
       <c r="G47" s="41">
         <f>ROUND(C47*D47,1)</f>
         <v/>
       </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>核对原因、提交申诉或Case并跟进；问题解决，或材料及处理记录完整、由负责人确认阶段结案。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>同一问题先Relist再申诉：合计3分。</t>
-        </is>
-      </c>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="2" t="n"/>
     </row>
     <row r="48" ht="83.25" customHeight="1" s="39">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>库存管理</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>滞留库存—已有电池／化学品资料提交</t>
-        </is>
-      </c>
-      <c r="C48" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>使用已有完整资料完成一批提交，计2分。</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0。</t>
-        </is>
-      </c>
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
       <c r="G48" s="41">
         <f>ROUND(C48*D48,1)</f>
         <v/>
       </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>核对资料与SKU的对应关系，提交并跟进审核结果，保存资料版本及处理记录。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>已有完整资料完成一批提交：2分。</t>
-        </is>
-      </c>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="2" t="n"/>
     </row>
     <row r="49" ht="97.15000000000001" customHeight="1" s="39">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>库存管理</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>滞留库存—电池／化学品资料协调与提交</t>
-        </is>
-      </c>
-      <c r="C49" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>需协调获取资料、核对并完成一批提交，计3分。</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>固定1.0。</t>
-        </is>
-      </c>
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="40" t="n"/>
+      <c r="D49" s="40" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
       <c r="G49" s="41">
         <f>ROUND(C49*D49,1)</f>
         <v/>
       </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不再加计2分。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>协调取得资料并提交：合计3分。</t>
-        </is>
-      </c>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="2" t="n"/>
     </row>
     <row r="50" ht="14.6" customHeight="1" s="39">
       <c r="A50" s="7" t="n"/>
@@ -5319,63 +5341,253 @@
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="2" t="n"/>
     </row>
-    <row r="59" ht="14.6" customHeight="1" s="39">
-      <c r="A59" s="7" t="n"/>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="40" t="n"/>
-      <c r="D59" s="40" t="n"/>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
-      <c r="G59" s="41">
-        <f>ROUND(C59*D59,1)</f>
-        <v/>
-      </c>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="14.6" customHeight="1" s="39">
-      <c r="A60" s="7" t="n"/>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="40" t="n"/>
-      <c r="D60" s="40" t="n"/>
-      <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
-      <c r="G60" s="41">
-        <f>ROUND(C60*D60,1)</f>
-        <v/>
-      </c>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="2" t="n"/>
-    </row>
+    <row r="59" ht="14.6" customHeight="1" s="39"/>
+    <row r="60" ht="14.6" customHeight="1" s="39"/>
     <row r="61" ht="14.6" customHeight="1" s="39">
-      <c r="A61" s="7" t="n"/>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="40" t="n"/>
-      <c r="D61" s="40" t="n"/>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="41">
-        <f>ROUND(C61*D61,1)</f>
-        <v/>
-      </c>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="2" t="n"/>
+      <c r="A61" s="51" t="inlineStr">
+        <is>
+          <t>主动执行倍率规则</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="14.6" customHeight="1" s="39">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="40" t="n"/>
-      <c r="D62" s="40" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="41">
-        <f>ROUND(C62*D62,1)</f>
-        <v/>
-      </c>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="2" t="n"/>
-    </row>
+      <c r="A62" s="52" t="inlineStr">
+        <is>
+          <t>主动任务积分 ＝ 正常任务积分 × 主动倍率。主动执行指员工自主发现问题或机会并发起处理，非负责人安排。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="53" t="inlineStr">
+        <is>
+          <t>工作分类</t>
+        </is>
+      </c>
+      <c r="B64" s="53" t="inlineStr">
+        <is>
+          <t>对应项目</t>
+        </is>
+      </c>
+      <c r="C64" s="64" t="n"/>
+      <c r="D64" s="53" t="inlineStr">
+        <is>
+          <t>主动倍率</t>
+        </is>
+      </c>
+      <c r="E64" s="53" t="inlineStr">
+        <is>
+          <t>认定条件</t>
+        </is>
+      </c>
+      <c r="F64" s="65" t="n"/>
+      <c r="G64" s="65" t="n"/>
+      <c r="H64" s="64" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="55" t="inlineStr">
+        <is>
+          <t>Listing内容优化</t>
+        </is>
+      </c>
+      <c r="B65" s="56" t="inlineStr">
+        <is>
+          <t>重新编写标题／五点／描述／关键词、全新制作或完全重做A+、A+内容增删修改</t>
+        </is>
+      </c>
+      <c r="C65" s="64" t="n"/>
+      <c r="D65" s="58" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E65" s="56" t="inlineStr">
+        <is>
+          <t>主动分析问题、提出方案，实际重写或重做并完成复盘。单纯纠错、翻译、上传已有内容不属于此档。</t>
+        </is>
+      </c>
+      <c r="F65" s="65" t="n"/>
+      <c r="G65" s="65" t="n"/>
+      <c r="H65" s="64" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="55" t="inlineStr">
+        <is>
+          <t>广告新建</t>
+        </is>
+      </c>
+      <c r="B66" s="56" t="inlineStr">
+        <is>
+          <t>SP／SB／SBV／SD广告创建</t>
+        </is>
+      </c>
+      <c r="C66" s="64" t="n"/>
+      <c r="D66" s="58" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E66" s="56" t="inlineStr">
+        <is>
+          <t>主动提出投放机会，说明产品、投放方向及测试目标，完成创建和复盘。复制已有Campaign不能仅凭新建数量拿双倍。</t>
+        </is>
+      </c>
+      <c r="F66" s="65" t="n"/>
+      <c r="G66" s="65" t="n"/>
+      <c r="H66" s="64" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="55" t="inlineStr">
+        <is>
+          <t>广告调整</t>
+        </is>
+      </c>
+      <c r="B67" s="56" t="inlineStr">
+        <is>
+          <t>广告执行调整（涵盖关键词、否定词、产品归组、ASIN投放、Bid调整）</t>
+        </is>
+      </c>
+      <c r="C67" s="64" t="n"/>
+      <c r="D67" s="58" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E67" s="56" t="inlineStr">
+        <is>
+          <t>有依据并完成核验。同一次调整包含多种动作合计只算1次。每个Campaign每周最多计2次（2×2＝4分/Campaign/周）。第二次须有复查依据或新问题依据；拆分操作、重复提交、修复本人错误不另算。</t>
+        </is>
+      </c>
+      <c r="F67" s="65" t="n"/>
+      <c r="G67" s="65" t="n"/>
+      <c r="H67" s="64" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="55" t="inlineStr">
+        <is>
+          <t>异常处理／申诉</t>
+        </is>
+      </c>
+      <c r="B68" s="56" t="inlineStr">
+        <is>
+          <t>Listing异常申诉与Case处理、Buy Box异常处理、Brand Store提交阻断问题处理</t>
+        </is>
+      </c>
+      <c r="C68" s="64" t="n"/>
+      <c r="D68" s="58" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E68" s="56" t="inlineStr">
+        <is>
+          <t>主动发现、及时记录并推动处理；同一问题反复提交只计一次。</t>
+        </is>
+      </c>
+      <c r="F68" s="65" t="n"/>
+      <c r="G68" s="65" t="n"/>
+      <c r="H68" s="64" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="55" t="inlineStr">
+        <is>
+          <t>其他执行类</t>
+        </is>
+      </c>
+      <c r="B69" s="56" t="inlineStr">
+        <is>
+          <t>价格调整、Coupon与Promotion创建、Deal活动提报、库存相关处理、VOC数据更新等</t>
+        </is>
+      </c>
+      <c r="C69" s="64" t="n"/>
+      <c r="D69" s="58" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E69" s="56" t="inlineStr">
+        <is>
+          <t>主动发现具体问题或机会，提出合理措施并完成处理；固定例行工作仍按正常积分（×1）。</t>
+        </is>
+      </c>
+      <c r="F69" s="65" t="n"/>
+      <c r="G69" s="65" t="n"/>
+      <c r="H69" s="64" t="n"/>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="59" t="inlineStr">
+        <is>
+          <t>边界规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="52" t="inlineStr">
+        <is>
+          <t>① 主动发现后及时登记即可，不要求处理完才申报。提出方案后经负责人批准执行，仍算主动；隐瞒或拖延已知问题不享受倍率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="52" t="inlineStr">
+        <is>
+          <t>② 固定巡检、例行维护、已被安排的任务，以及修复本人错误，不享受主动倍率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="52" t="inlineStr">
+        <is>
+          <t>③ 同一工作只计算一次乘倍率后的积分，不再另加正常积分。未完成处理及必要核验的，先保留记录，不提前领取完整积分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="59" t="inlineStr">
+        <is>
+          <t>广告调整频次限制</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="52" t="inlineStr">
+        <is>
+          <t>每个Campaign每自然周（周一至周日）最多计2次广告调整积分，不区分调整类型。不同Campaign分别计分，可以采取不同调整措施。超出频次的调整仍须执行，但不再计分。
+示例：同一周，Campaign A有效调整2次、B调整1次、C调整3次，分别计 4＋2＋4＝10积分（C的第3次不计分）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="80"/>
+    <row r="81"/>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="A81:H81"/>
+  </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="D8 D20 D24 D41 D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"1,1.3,1.6"</formula1>
@@ -9730,75 +9942,504 @@
       </c>
     </row>
     <row r="143" ht="30" customHeight="1" s="39">
-      <c r="A143" s="47" t="n"/>
+      <c r="A143" s="47" t="inlineStr">
+        <is>
+          <t>广告执行调整：按Campaign×调整次数计分</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="34" customHeight="1" s="39">
-      <c r="A144" s="48" t="n"/>
-      <c r="B144" s="48" t="n"/>
-      <c r="C144" s="48" t="n"/>
-      <c r="D144" s="48" t="n"/>
-      <c r="E144" s="48" t="n"/>
-      <c r="F144" s="48" t="n"/>
-      <c r="G144" s="48" t="n"/>
-      <c r="H144" s="48" t="n"/>
+      <c r="A144" s="66" t="inlineStr">
+        <is>
+          <t>工作项目</t>
+        </is>
+      </c>
+      <c r="B144" s="66" t="inlineStr">
+        <is>
+          <t>实际场景</t>
+        </is>
+      </c>
+      <c r="C144" s="66" t="inlineStr">
+        <is>
+          <t>累计基础分</t>
+        </is>
+      </c>
+      <c r="D144" s="66" t="inlineStr">
+        <is>
+          <t>难度系数</t>
+        </is>
+      </c>
+      <c r="E144" s="66" t="inlineStr">
+        <is>
+          <t>任务积分</t>
+        </is>
+      </c>
+      <c r="F144" s="66" t="inlineStr">
+        <is>
+          <t>计算依据</t>
+        </is>
+      </c>
+      <c r="G144" s="66" t="inlineStr">
+        <is>
+          <t>结算说明</t>
+        </is>
+      </c>
+      <c r="H144" s="66" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="105" customHeight="1" s="39">
-      <c r="A145" s="0" t="n"/>
-      <c r="B145" s="0" t="n"/>
-      <c r="C145" s="0" t="n"/>
-      <c r="D145" s="0" t="n"/>
-      <c r="E145" s="0" t="n"/>
-      <c r="F145" s="0" t="n"/>
-      <c r="G145" s="0" t="n"/>
-      <c r="H145" s="0" t="n"/>
+      <c r="A145" s="67" t="inlineStr">
+        <is>
+          <t>广告执行调整</t>
+        </is>
+      </c>
+      <c r="B145" s="67" t="inlineStr">
+        <is>
+          <t>同一周对Campaign A调整Bid 1次</t>
+        </is>
+      </c>
+      <c r="C145" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" s="68">
+        <f>ROUND(C145*D145,1)</f>
+        <v/>
+      </c>
+      <c r="F145" s="67" t="inlineStr">
+        <is>
+          <t>1个Campaign×1次＝2分</t>
+        </is>
+      </c>
+      <c r="G145" s="67" t="inlineStr">
+        <is>
+          <t>关联Ads Change，记录原因并核验</t>
+        </is>
+      </c>
+      <c r="H145" s="67" t="inlineStr">
+        <is>
+          <t>周内还可再计1次</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="105" customHeight="1" s="39">
-      <c r="A146" s="0" t="n"/>
-      <c r="B146" s="0" t="n"/>
-      <c r="C146" s="0" t="n"/>
-      <c r="D146" s="0" t="n"/>
-      <c r="E146" s="0" t="n"/>
-      <c r="F146" s="0" t="n"/>
-      <c r="G146" s="0" t="n"/>
-      <c r="H146" s="0" t="n"/>
+      <c r="A146" s="67" t="inlineStr">
+        <is>
+          <t>广告执行调整</t>
+        </is>
+      </c>
+      <c r="B146" s="67" t="inlineStr">
+        <is>
+          <t>同一周对Campaign A先调否定词，复查后再调Bid（2次）</t>
+        </is>
+      </c>
+      <c r="C146" s="68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D146" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="68">
+        <f>ROUND(C146*D146,1)</f>
+        <v/>
+      </c>
+      <c r="F146" s="67" t="inlineStr">
+        <is>
+          <t>1个Campaign×2次＝4分</t>
+        </is>
+      </c>
+      <c r="G146" s="67" t="inlineStr">
+        <is>
+          <t>第2次须有复查依据或新问题依据</t>
+        </is>
+      </c>
+      <c r="H146" s="67" t="inlineStr">
+        <is>
+          <t>已达周上限，本周不再计分</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="105" customHeight="1" s="39">
-      <c r="A147" s="0" t="n"/>
-      <c r="B147" s="0" t="n"/>
-      <c r="C147" s="0" t="n"/>
-      <c r="D147" s="0" t="n"/>
-      <c r="E147" s="0" t="n"/>
-      <c r="F147" s="0" t="n"/>
-      <c r="G147" s="0" t="n"/>
-      <c r="H147" s="0" t="n"/>
+      <c r="A147" s="67" t="inlineStr">
+        <is>
+          <t>广告执行调整</t>
+        </is>
+      </c>
+      <c r="B147" s="67" t="inlineStr">
+        <is>
+          <t>同一次调整同时改否定词＋Bid＋商品投放</t>
+        </is>
+      </c>
+      <c r="C147" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="68">
+        <f>ROUND(C147*D147,1)</f>
+        <v/>
+      </c>
+      <c r="F147" s="67" t="inlineStr">
+        <is>
+          <t>同一次多种动作合计1次＝2分</t>
+        </is>
+      </c>
+      <c r="G147" s="67" t="inlineStr">
+        <is>
+          <t>不按调整类型拆分</t>
+        </is>
+      </c>
+      <c r="H147" s="67" t="inlineStr">
+        <is>
+          <t>关联一条Ads Change记录</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="105" customHeight="1" s="39">
-      <c r="A148" s="0" t="n"/>
-      <c r="B148" s="0" t="n"/>
-      <c r="C148" s="0" t="n"/>
-      <c r="D148" s="0" t="n"/>
-      <c r="E148" s="0" t="n"/>
-      <c r="F148" s="0" t="n"/>
-      <c r="G148" s="0" t="n"/>
-      <c r="H148" s="0" t="n"/>
+      <c r="A148" s="67" t="inlineStr">
+        <is>
+          <t>广告执行调整</t>
+        </is>
+      </c>
+      <c r="B148" s="67" t="inlineStr">
+        <is>
+          <t>同一周：A调整2次、B调整1次、C调整3次</t>
+        </is>
+      </c>
+      <c r="C148" s="68" t="n">
+        <v>10</v>
+      </c>
+      <c r="D148" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="68">
+        <f>ROUND(C148*D148,1)</f>
+        <v/>
+      </c>
+      <c r="F148" s="67" t="inlineStr">
+        <is>
+          <t>A=4＋B=2＋C=4＝10分</t>
+        </is>
+      </c>
+      <c r="G148" s="67" t="inlineStr">
+        <is>
+          <t>C的第3次超出周上限不计分</t>
+        </is>
+      </c>
+      <c r="H148" s="67" t="inlineStr">
+        <is>
+          <t>不同Campaign分别计分，各自2次上限</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="0" t="n"/>
-      <c r="B149" s="0" t="n"/>
-      <c r="C149" s="0" t="n"/>
-      <c r="D149" s="0" t="n"/>
-      <c r="E149" s="0" t="n"/>
-      <c r="F149" s="0" t="n"/>
-      <c r="G149" s="0" t="n"/>
-      <c r="H149" s="0" t="n"/>
-    </row>
-    <row r="151" ht="30" customHeight="1" s="39"/>
-    <row r="152" ht="34" customHeight="1" s="39"/>
-    <row r="153" ht="105" customHeight="1" s="39"/>
-    <row r="154" ht="105" customHeight="1" s="39"/>
-    <row r="155" ht="105" customHeight="1" s="39"/>
-    <row r="156" ht="105" customHeight="1" s="39"/>
-    <row r="157" ht="105" customHeight="1" s="39"/>
+      <c r="A149" s="67" t="inlineStr">
+        <is>
+          <t>广告执行调整</t>
+        </is>
+      </c>
+      <c r="B149" s="67" t="inlineStr">
+        <is>
+          <t>拆分同一次调整为多条提交</t>
+        </is>
+      </c>
+      <c r="C149" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="68">
+        <f>ROUND(C149*D149,1)</f>
+        <v/>
+      </c>
+      <c r="F149" s="67" t="inlineStr">
+        <is>
+          <t>拆分操作不另算</t>
+        </is>
+      </c>
+      <c r="G149" s="67" t="inlineStr">
+        <is>
+          <t>按实际有效调整次数计，不按提交次数</t>
+        </is>
+      </c>
+      <c r="H149" s="67" t="inlineStr">
+        <is>
+          <t>修复本人错误也不另算</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="30" customHeight="1" s="39">
+      <c r="A151" s="47" t="inlineStr">
+        <is>
+          <t>主动执行倍率计分示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="34" customHeight="1" s="39">
+      <c r="A152" s="66" t="inlineStr">
+        <is>
+          <t>工作项目</t>
+        </is>
+      </c>
+      <c r="B152" s="66" t="inlineStr">
+        <is>
+          <t>实际场景</t>
+        </is>
+      </c>
+      <c r="C152" s="66" t="inlineStr">
+        <is>
+          <t>正常积分</t>
+        </is>
+      </c>
+      <c r="D152" s="66" t="inlineStr">
+        <is>
+          <t>主动倍率</t>
+        </is>
+      </c>
+      <c r="E152" s="66" t="inlineStr">
+        <is>
+          <t>主动积分</t>
+        </is>
+      </c>
+      <c r="F152" s="66" t="inlineStr">
+        <is>
+          <t>计算依据</t>
+        </is>
+      </c>
+      <c r="G152" s="66" t="inlineStr">
+        <is>
+          <t>认定说明</t>
+        </is>
+      </c>
+      <c r="H152" s="66" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="105" customHeight="1" s="39">
+      <c r="A153" s="56" t="inlineStr">
+        <is>
+          <t>重新编写标题</t>
+        </is>
+      </c>
+      <c r="B153" s="56" t="inlineStr">
+        <is>
+          <t>主动分析搜索词数据，发现标题缺少核心关键词，重写并完成复盘</t>
+        </is>
+      </c>
+      <c r="C153" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" s="69" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E153" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F153" s="56" t="inlineStr">
+        <is>
+          <t>2×2＝4分</t>
+        </is>
+      </c>
+      <c r="G153" s="56" t="inlineStr">
+        <is>
+          <t>符合Listing内容优化认定：有数据分析、有方案、实际重写、完成复盘</t>
+        </is>
+      </c>
+      <c r="H153" s="56" t="inlineStr"/>
+    </row>
+    <row r="154" ht="105" customHeight="1" s="39">
+      <c r="A154" s="56" t="inlineStr">
+        <is>
+          <t>SP广告创建</t>
+        </is>
+      </c>
+      <c r="B154" s="56" t="inlineStr">
+        <is>
+          <t>主动发现产品缺少某品类投放，提出测试目标，创建1个SP Campaign</t>
+        </is>
+      </c>
+      <c r="C154" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" s="69" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E154" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F154" s="56" t="inlineStr">
+        <is>
+          <t>3×2＝6分</t>
+        </is>
+      </c>
+      <c r="G154" s="56" t="inlineStr">
+        <is>
+          <t>符合广告新建认定：有投放机会分析、投放方向、测试目标</t>
+        </is>
+      </c>
+      <c r="H154" s="56" t="inlineStr">
+        <is>
+          <t>复制已有Campaign结构不适用×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="105" customHeight="1" s="39">
+      <c r="A155" s="56" t="inlineStr">
+        <is>
+          <t>Buy Box异常处理</t>
+        </is>
+      </c>
+      <c r="B155" s="56" t="inlineStr">
+        <is>
+          <t>主动发现Buy Box丢失，及时截图取证并开Case处理</t>
+        </is>
+      </c>
+      <c r="C155" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D155" s="69" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E155" s="69" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F155" s="56" t="inlineStr">
+        <is>
+          <t>3×1.5＝4.5分</t>
+        </is>
+      </c>
+      <c r="G155" s="56" t="inlineStr">
+        <is>
+          <t>符合异常处理认定：主动发现、及时记录、推动处理</t>
+        </is>
+      </c>
+      <c r="H155" s="56" t="inlineStr"/>
+    </row>
+    <row r="156" ht="105" customHeight="1" s="39">
+      <c r="A156" s="56" t="inlineStr">
+        <is>
+          <t>价格调整</t>
+        </is>
+      </c>
+      <c r="B156" s="56" t="inlineStr">
+        <is>
+          <t>主动发现竞品降价导致转化下降，提出调价方案并执行</t>
+        </is>
+      </c>
+      <c r="C156" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" s="69" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E156" s="69" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F156" s="56" t="inlineStr">
+        <is>
+          <t>3×1.5＝4.5分</t>
+        </is>
+      </c>
+      <c r="G156" s="56" t="inlineStr">
+        <is>
+          <t>符合其他执行类认定：发现问题、有合理措施、完成处理</t>
+        </is>
+      </c>
+      <c r="H156" s="56" t="inlineStr">
+        <is>
+          <t>例行巡检调价不享受倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="105" customHeight="1" s="39">
+      <c r="A157" s="56" t="inlineStr">
+        <is>
+          <t>广告执行调整</t>
+        </is>
+      </c>
+      <c r="B157" s="56" t="inlineStr">
+        <is>
+          <t>主动分析广告报表，调整Campaign A的否定词和Bid</t>
+        </is>
+      </c>
+      <c r="C157" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" s="69" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E157" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" s="56" t="inlineStr">
+        <is>
+          <t>2×1＝2分</t>
+        </is>
+      </c>
+      <c r="G157" s="56" t="inlineStr">
+        <is>
+          <t>广告调整主动倍率固定×1</t>
+        </is>
+      </c>
+      <c r="H157" s="56" t="inlineStr">
+        <is>
+          <t>有依据并核验；周内可再计1次</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="56" t="inlineStr">
+        <is>
+          <t>重新编写标题</t>
+        </is>
+      </c>
+      <c r="B158" s="56" t="inlineStr">
+        <is>
+          <t>上传翻译好的标题（非自主分析优化）</t>
+        </is>
+      </c>
+      <c r="C158" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" s="69" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E158" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" s="56" t="inlineStr">
+        <is>
+          <t>不满足×2认定条件</t>
+        </is>
+      </c>
+      <c r="G158" s="56" t="inlineStr">
+        <is>
+          <t>单纯翻译上传不属于内容优化档，按正常积分</t>
+        </is>
+      </c>
+      <c r="H158" s="56" t="inlineStr"/>
+    </row>
     <row r="160" ht="30" customHeight="1" s="39">
       <c r="A160" s="0" t="inlineStr">
         <is>
@@ -11085,8 +11726,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A143:H143"/>
     <mergeCell ref="A109:H109"/>
     <mergeCell ref="A87:H87"/>
     <mergeCell ref="A134:H134"/>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <name val="Carlito"/>
       <charset val="134"/>
@@ -289,6 +289,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="41">
@@ -859,7 +865,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1028,6 +1034,7 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2396,7 +2403,7 @@
       </c>
       <c r="D18" s="38" t="inlineStr">
         <is>
-          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善2/4/6分档认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。</t>
+          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善按正常积分×主动倍率认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。</t>
         </is>
       </c>
       <c r="E18" s="38" t="inlineStr">
@@ -2674,7 +2681,7 @@
       </c>
       <c r="G25" s="38" t="inlineStr">
         <is>
-          <t>具体调整完成并核验；同一任务仅结算一次。按实际涉及Campaign数量选择分档。自行分析的安排任务按Campaign优化计分，自主发起只计主动分。</t>
+          <t>具体调整完成并核验；同一任务仅结算一次。按实际涉及Campaign数量选择分档。自行分析的安排任务按Campaign优化计分，自主发起按正常积分×主动倍率计算。</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3418,7 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>计分来源互斥：负责人安排计任务积分（折算最高80分）；员工自主发起改善计主动分（2/4/6分档，月度最高20分）。同一工作不同时计入两部分，主动提出后获批或补建任务仍属主动改善。</t>
+          <t>计分来源互斥：负责人安排计正常任务积分；员工自主发起计主动任务积分（正常任务积分×主动倍率）。同一工作只计算一次乘倍率后的积分，不再另加正常积分。主动提出后获批或补建任务仍属主动。详见本表"主动执行倍率规则"。</t>
         </is>
       </c>
       <c r="B5" s="31" t="n"/>
@@ -3469,7 +3476,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>默认单位积分</t>
+          <t>默认示例积分（非结算分）</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -3985,9 +3992,8 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>每个实际修改的模块：2分。
-新增或删除整个模块也按2分/模块计。
-同一份A+同一轮累计最高10分。</t>
+          <t>同一份A+同一轮局部修改：2分。
+不按模块数量累加；全新制作或完全重做按10分/份。</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -4001,7 +4007,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>同一模块内增加、删除或修改多处信息只计一次2分；同一轮反复调整不重复计分。全新制作或完全重做按10分/份，不叠加局部修改分。仅增加绑定SKU归A+制作发布，按1分/SKU。单纯事实纠错按Listing纠错计分。以优化为目的的修改执行优化登记与复盘规则。</t>
+          <t>同一份A+同一轮内所有局部增加、删除或修改合计2分，不按模块数量累加；同一轮反复调整不重复计分。全新制作或完全重做按10分/份，不叠加局部修改分。仅增加绑定SKU归A+制作发布，按1分/SKU。单纯事实纠错按Listing纠错计分。以优化为目的的修改执行优化登记与复盘规则。</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -4218,7 +4224,7 @@
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>主动改善关联入口：任务积分0分。
-仅按主动改善2/4/6分档认定，同案取最高档。</t>
+自主发起按主动倍率计算，同案取最高适用倍率。</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -4233,7 +4239,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善2/4/6分档认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。 本行0分表示不计任务积分，不表示主动改善没有得分。</t>
+          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计正常任务积分；员工自主发现并发起的改善按正常任务积分×主动倍率计算，同一工作只计一次。员工先提出建议、经负责人批准后执行，仍属主动。补建任务或认领变化不改变来源。本行0分表示不计正常任务积分，不表示主动改善没有得分。</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -4362,7 +4368,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排计任务分，自主发起只计主动改善分，两者不叠加。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
+          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -4407,7 +4413,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排计任务分，自主发起只计主动改善分，两者不叠加。 SBV只按SBV项目计分，不再同时计SB创建分。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
+          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。 SBV只按SBV项目计分，不再同时计SB创建分。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -4452,7 +4458,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排计任务分，自主发起只计主动改善分，两者不叠加。 SBV只按SBV项目计分，不再同时计SB创建分。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
+          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。 SBV只按SBV项目计分，不再同时计SB创建分。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -4497,7 +4503,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排计任务分，自主发起只计主动改善分，两者不叠加。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
+          <t>创建后在Ads Change中认领对应变化，创建或关联任务，填写创建原因并完成核验。以Campaign ID去重，同一Campaign只领取一次创建分；多条变化记录不重复计分。初始广告组、商品、目标、素材、预算、竞价及否定设置均包含在创建分中。不得人为拆分Campaign增加积分；认领变化不改变发起来源；负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。 新建Campaign必要的命名和归组包含在创建分中，不单独计分。</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4543,7 +4549,7 @@
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>涵盖关键词与搜索词调整、否定投放调整、广告产品归组与补充、ASIN与商品投放调整、Bid与投放位置调整。同一次调整包含多种动作合计只算1次。第二次计分须有第一次调整后的复查依据或新问题依据，并实际完成新的调整；拆分操作、重复提交、修复本人错误不另算。每次关联Ads Change，记录原因并完成核验。主动倍率×1。</t>
+          <t>涵盖关键词与搜索词调整、否定投放调整、广告产品归组与补充、ASIN与商品投放调整、Bid与投放位置调整。同一次调整包含多种动作合计只算1次，可关联多条Ads Change。第二次计分须有第一次调整后的复查依据或新问题依据，并实际完成新的调整；拆分操作、重复提交、修复本人错误不另算。同一广告账户、同一站点、同一Campaign，每自然周最多计2次；负责人安排和员工主动执行合并统计，多人参与不增加次数。主动倍率×1。</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4589,7 +4595,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>包含异常核查、材料整理、Appeal或Case提交、回复跟进及结果核验。同一ASIN同一异常的多次申诉、多个Case或补充材料合并计4分。合并在一个Case中的多个ASIN按个数计分，但须逐个记录处理结果。恢复后验收；未恢复时提交完整记录，经负责人确认阶段结案后计分，后续同一异常恢复不重复领取。已归Buy Box、滞留库存或变体关系维护的同一问题不叠加本项。负责人安排计任务分，自主发起改善仅计主动分。</t>
+          <t>包含异常核查、材料整理、Appeal或Case提交、回复跟进及结果核验。同一ASIN同一异常的多次申诉、多个Case或补充材料合并计4分。合并在一个Case中的多个ASIN按个数计分，但须逐个记录处理结果。恢复后验收；未恢复时提交完整记录，经负责人确认阶段结案后计分，后续同一异常恢复不重复领取。已归Buy Box、滞留库存或变体关系维护的同一问题不叠加本项。负责人安排按正常积分；自主发起按正常积分×主动倍率计算。</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4978,7 +4984,7 @@
       <c r="H41" s="7" t="inlineStr">
         <is>
           <t>成功创建移除订单，核对SKU、数量及处理方式，保存订单编号。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5021,7 +5027,7 @@
       <c r="H42" s="7" t="inlineStr">
         <is>
           <t>完成重新发布，核验发布结果及滞留状态，保留处理记录。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5064,7 +5070,7 @@
       <c r="H43" s="7" t="inlineStr">
         <is>
           <t>核对原因、提交申诉或Case并跟进；问题解决，或材料及处理记录完整、由负责人确认阶段结案。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5107,7 +5113,7 @@
       <c r="H44" s="7" t="inlineStr">
         <is>
           <t>核对资料与SKU的对应关系，提交并跟进审核结果，保存资料版本及处理记录。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5128,14 +5134,14 @@
         </is>
       </c>
       <c r="C45" s="42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>需协调获取资料、核对并完成一批提交，计3分。</t>
+          <t>需协调获取资料、核对并完成一批提交，计2分。</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -5150,7 +5156,7 @@
       <c r="H45" s="7" t="inlineStr">
         <is>
           <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不再加计2分。
-同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排计任务分，员工自主发起计主动改善分，二者不叠加。</t>
+同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5216,31 +5222,80 @@
       <c r="I49" s="2" t="n"/>
     </row>
     <row r="50" ht="14.6" customHeight="1" s="39">
-      <c r="A50" s="7" t="n"/>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="40" t="n"/>
-      <c r="D50" s="40" t="n"/>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="A50" s="60" t="inlineStr">
+        <is>
+          <t>数据与报表</t>
+        </is>
+      </c>
+      <c r="B50" s="60" t="inlineStr">
+        <is>
+          <t>Category Report下载</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>每周完成一次下载并归档：1分/周。
+按天折算时按实际完成天数比例计算。</t>
+        </is>
+      </c>
+      <c r="F50" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；按每周完整任务计分。</t>
+        </is>
+      </c>
       <c r="G50" s="41">
         <f>ROUND(C50*D50,1)</f>
         <v/>
       </c>
-      <c r="H50" s="7" t="n"/>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>固定例行工作，主动倍率×1。下载并归档后验收；同一周多次下载合并计分。</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="n"/>
     </row>
     <row r="51" ht="14.6" customHeight="1" s="39">
-      <c r="A51" s="7" t="n"/>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="40" t="n"/>
-      <c r="D51" s="40" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
+      <c r="A51" s="60" t="inlineStr">
+        <is>
+          <t>数据与报表</t>
+        </is>
+      </c>
+      <c r="B51" s="60" t="inlineStr">
+        <is>
+          <t>关键词市场占有率统计及竞品检查</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="60" t="inlineStr">
+        <is>
+          <t>每个关键词每月完成一次统计及竞品检查：2分/关键词/月。</t>
+        </is>
+      </c>
+      <c r="F51" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；按关键词数量及月度任务计分。</t>
+        </is>
+      </c>
       <c r="G51" s="41">
         <f>ROUND(C51*D51,1)</f>
         <v/>
       </c>
-      <c r="H51" s="7" t="n"/>
+      <c r="H51" s="60" t="inlineStr">
+        <is>
+          <t>固定例行工作，主动倍率×1。完成统计数据整理及竞品对比后验收。同一关键词同月不重复计分。</t>
+        </is>
+      </c>
       <c r="I51" s="2" t="n"/>
     </row>
     <row r="52" ht="14.6" customHeight="1" s="39">
@@ -5386,12 +5441,12 @@
     <row r="65">
       <c r="A65" s="55" t="inlineStr">
         <is>
-          <t>Listing内容优化</t>
+          <t>Listing内容实质重写</t>
         </is>
       </c>
       <c r="B65" s="56" t="inlineStr">
         <is>
-          <t>重新编写标题／五点／描述／关键词、全新制作或完全重做A+、A+内容增删修改</t>
+          <t>重新编写标题、重新编写五点、重新编写描述、重新整理Generic Keywords、全新制作或完全重做A+</t>
         </is>
       </c>
       <c r="C65" s="64" t="n"/>
@@ -5417,7 +5472,7 @@
       </c>
       <c r="B66" s="56" t="inlineStr">
         <is>
-          <t>SP／SB／SBV／SD广告创建</t>
+          <t>SP广告创建、SB广告创建、SBV广告创建、SD广告创建</t>
         </is>
       </c>
       <c r="C66" s="64" t="n"/>
@@ -5454,7 +5509,7 @@
       </c>
       <c r="E67" s="56" t="inlineStr">
         <is>
-          <t>有依据并完成核验。同一次调整包含多种动作合计只算1次。每个Campaign每周最多计2次（2×2＝4分/Campaign/周）。第二次须有复查依据或新问题依据；拆分操作、重复提交、修复本人错误不另算。</t>
+          <t>有依据并完成核验。每Campaign每自然周最多计2次，跨人员、跨发起来源合并统计。可关联多条Ads Change。</t>
         </is>
       </c>
       <c r="F67" s="65" t="n"/>
@@ -5490,12 +5545,12 @@
     <row r="69">
       <c r="A69" s="55" t="inlineStr">
         <is>
-          <t>其他执行类</t>
+          <t>Listing事实纠错及局部维护</t>
         </is>
       </c>
       <c r="B69" s="56" t="inlineStr">
         <is>
-          <t>价格调整、Coupon与Promotion创建、Deal活动提报、库存相关处理、VOC数据更新等</t>
+          <t>Listing纠错、A+内容增删修改、图片维护、视频上传与信息维护、变体关系维护</t>
         </is>
       </c>
       <c r="C69" s="64" t="n"/>
@@ -5506,63 +5561,162 @@
       </c>
       <c r="E69" s="56" t="inlineStr">
         <is>
-          <t>主动发现具体问题或机会，提出合理措施并完成处理；固定例行工作仍按正常积分（×1）。</t>
+          <t>主动发现并完成纠正或维护。事实纠错≠内容实质重写，不适用×2。</t>
         </is>
       </c>
       <c r="F69" s="65" t="n"/>
       <c r="G69" s="65" t="n"/>
       <c r="H69" s="64" t="n"/>
     </row>
-    <row r="70"/>
+    <row r="70">
+      <c r="A70" s="55" t="inlineStr">
+        <is>
+          <t>价格／促销／库存等执行类</t>
+        </is>
+      </c>
+      <c r="B70" s="56" t="inlineStr">
+        <is>
+          <t>价格调整、Coupon与Promotion创建、Deal活动提报、库存移除／Relist／申诉／资料提交</t>
+        </is>
+      </c>
+      <c r="C70" s="64" t="n"/>
+      <c r="D70" s="58" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E70" s="56" t="inlineStr">
+        <is>
+          <t>主动发现具体问题或机会，提出合理措施并完成处理。</t>
+        </is>
+      </c>
+      <c r="F70" s="65" t="n"/>
+      <c r="G70" s="65" t="n"/>
+      <c r="H70" s="64" t="n"/>
+    </row>
     <row r="71">
-      <c r="A71" s="59" t="inlineStr">
+      <c r="A71" s="55" t="inlineStr">
+        <is>
+          <t>Brand Store维护</t>
+        </is>
+      </c>
+      <c r="B71" s="56" t="inlineStr">
+        <is>
+          <t>二级类目商品维护、二级类目模块新增或重建</t>
+        </is>
+      </c>
+      <c r="C71" s="64" t="n"/>
+      <c r="D71" s="58" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E71" s="56" t="inlineStr">
+        <is>
+          <t>主动发现维护需求并完成更新。</t>
+        </is>
+      </c>
+      <c r="F71" s="65" t="n"/>
+      <c r="G71" s="65" t="n"/>
+      <c r="H71" s="64" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="55" t="inlineStr">
+        <is>
+          <t>固定例行工作</t>
+        </is>
+      </c>
+      <c r="B72" s="56" t="inlineStr">
+        <is>
+          <t>VOC数据更新与AI分析、Category Report下载、关键词市场占有率统计及竞品检查</t>
+        </is>
+      </c>
+      <c r="C72" s="64" t="n"/>
+      <c r="D72" s="58" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E72" s="56" t="inlineStr">
+        <is>
+          <t>固定周期任务，不享受主动倍率。</t>
+        </is>
+      </c>
+      <c r="F72" s="65" t="n"/>
+      <c r="G72" s="65" t="n"/>
+      <c r="H72" s="64" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="55" t="inlineStr">
+        <is>
+          <t>未明确列入的项目</t>
+        </is>
+      </c>
+      <c r="B73" s="56" t="inlineStr">
+        <is>
+          <t>（暂按×1，不自行套用高倍率）</t>
+        </is>
+      </c>
+      <c r="C73" s="64" t="n"/>
+      <c r="D73" s="58" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E73" s="56" t="inlineStr">
+        <is>
+          <t>如有争议，由负责人认定适用分类。</t>
+        </is>
+      </c>
+      <c r="F73" s="65" t="n"/>
+      <c r="G73" s="65" t="n"/>
+      <c r="H73" s="64" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="59" t="inlineStr">
         <is>
           <t>边界规则</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="52" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="52" t="inlineStr">
         <is>
           <t>① 主动发现后及时登记即可，不要求处理完才申报。提出方案后经负责人批准执行，仍算主动；隐瞒或拖延已知问题不享受倍率。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="52" t="inlineStr">
-        <is>
-          <t>② 固定巡检、例行维护、已被安排的任务，以及修复本人错误，不享受主动倍率。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="52" t="inlineStr">
-        <is>
-          <t>③ 同一工作只计算一次乘倍率后的积分，不再另加正常积分。未完成处理及必要核验的，先保留记录，不提前领取完整积分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="59" t="inlineStr">
-        <is>
-          <t>广告调整频次限制</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="52" t="inlineStr">
         <is>
-          <t>每个Campaign每自然周（周一至周日）最多计2次广告调整积分，不区分调整类型。不同Campaign分别计分，可以采取不同调整措施。超出频次的调整仍须执行，但不再计分。
+          <t>② 固定巡检、例行维护、已被安排的任务，以及修复本人错误，不享受主动倍率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="52" t="inlineStr">
+        <is>
+          <t>③ 同一工作只计算一次乘倍率后的积分，不再另加正常积分。未完成处理及必要核验的，先保留记录，不提前领取完整积分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="59" t="inlineStr">
+        <is>
+          <t>广告调整频次限制</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="52" t="inlineStr">
+        <is>
+          <t>同一广告账户、同一站点、同一Campaign，每自然周（周一至周日）最多计2次广告调整积分，不区分调整类型。负责人安排和员工主动执行合并统计，多人参与不增加次数。同一次调整可关联多条Ads Change。超出频次的调整仍须执行，但不再计分。
 示例：同一周，Campaign A有效调整2次、B调整1次、C调整3次，分别计 4＋2＋4＝10积分（C的第3次不计分）。</t>
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="80"/>
-    <row r="81"/>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="A77:H77"/>
     <mergeCell ref="E70:H70"/>
     <mergeCell ref="B72:C72"/>
@@ -5580,10 +5734,12 @@
     <mergeCell ref="E67:H67"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E64:H64"/>
     <mergeCell ref="E73:H73"/>
     <mergeCell ref="A76:H76"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B64:C64"/>
     <mergeCell ref="E69:H69"/>
     <mergeCell ref="E65:H65"/>
     <mergeCell ref="A81:H81"/>
@@ -5646,9 +5802,9 @@
       <c r="E2" s="22" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="39">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>月度绩效＝任务完成得分（最高80分）＋主动改善得分（最高20分），总分100分；主动改善不再额外加在100分之外。</t>
+      <c r="A3" s="70" t="inlineStr">
+        <is>
+          <t>【已重构】主动改善不再使用2/4/6分档和20分上限。新规则：主动任务积分＝正常任务积分×主动倍率（见"任务评分"主动执行倍率规则）。下方评价框架保留用于认定主动行为是否成立，分值按新倍率计算。</t>
         </is>
       </c>
       <c r="B3" s="22" t="n"/>
@@ -5659,7 +5815,7 @@
     <row r="4" ht="75" customHeight="1" s="39">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善2/4/6分档认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。 案例继续在现有主动改善页面记录，并关联任务编号。</t>
+          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善按正常任务积分×主动倍率计算，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。 案例继续在现有主动改善页面记录，并关联任务编号。</t>
         </is>
       </c>
       <c r="B4" s="22" t="n"/>
@@ -5940,7 +6096,7 @@
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>员工先提出问题及建议，再获批准并建立任务，仍属主动改善；只计主动分，不计对应任务分。</t>
+          <t>员工先提出问题及建议，再获批准并建立任务，仍属主动改善；按主动倍率计算，不计对应任务分。</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6427,7 @@
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
-          <t>主动改善得分＝MIN（当月案例核定分及升级补差合计，月度上限20分）；总绩效最高100分。任务完成部分须折算至最高80分，不把原始任务积分直接相加。</t>
+          <t>主动改善得分＝MIN（当月案例核定分及升级补差合计，月度上限20分）；总绩效最高100分。任务完成部分须折算至正常积分，不把原始任务积分直接相加。</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6626,7 @@
     <row r="4" ht="25" customHeight="1" s="39">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>本页普通任务积分示例以负责人安排为前提；自主发起改善只按主动改善案例等级计分，不叠加示例任务积分。同一工作只选一条路径。</t>
+          <t>本页普通任务积分示例以负责人安排为前提；自主发起按正常任务积分×主动倍率计算（见"任务评分"主动执行倍率规则），同一工作只计一次。</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9441,7 @@
     <row r="114" ht="105" customHeight="1" s="39">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>主动改善</t>
+          <t>主动发起</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
@@ -9310,7 +9466,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>计入最高20分部分；不乘任务难度系数</t>
+          <t>按正常积分×主动倍率计算</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr"/>
@@ -9789,7 +9945,7 @@
       </c>
       <c r="H136" s="0" t="inlineStr">
         <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
+          <t>自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9982,7 @@
       </c>
       <c r="H137" s="0" t="inlineStr">
         <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
+          <t>自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -9863,7 +10019,7 @@
       </c>
       <c r="H138" s="0" t="inlineStr">
         <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
+          <t>自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -9900,7 +10056,7 @@
       </c>
       <c r="H139" s="0" t="inlineStr">
         <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
+          <t>自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -9937,7 +10093,7 @@
       </c>
       <c r="H140" s="0" t="inlineStr">
         <is>
-          <t>自主发起只计主动分，不叠加本例任务分</t>
+          <t>自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10823,7 @@
       </c>
       <c r="H170" s="0" t="inlineStr">
         <is>
-          <t>示例为负责人安排；自主发起仅计主动分</t>
+          <t>示例为负责人安排；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10860,7 @@
       </c>
       <c r="H171" s="0" t="inlineStr">
         <is>
-          <t>示例为负责人安排；自主发起仅计主动分</t>
+          <t>示例为负责人安排；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10741,7 +10897,7 @@
       </c>
       <c r="H172" s="0" t="inlineStr">
         <is>
-          <t>示例为负责人安排；自主发起仅计主动分</t>
+          <t>示例为负责人安排；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10934,7 @@
       </c>
       <c r="H173" s="0" t="inlineStr">
         <is>
-          <t>示例为负责人安排；自主发起仅计主动分</t>
+          <t>示例为负责人安排；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10950,7 @@
         </is>
       </c>
       <c r="C174" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D174" s="0" t="n">
         <v>1</v>
@@ -10815,7 +10971,7 @@
       </c>
       <c r="H174" s="0" t="inlineStr">
         <is>
-          <t>示例为负责人安排；自主发起仅计主动分</t>
+          <t>示例为负责人安排；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10852,7 +11008,7 @@
       </c>
       <c r="H175" s="0" t="inlineStr">
         <is>
-          <t>示例为负责人安排；自主发起仅计主动分</t>
+          <t>示例为负责人安排；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10938,7 +11094,7 @@
       </c>
       <c r="H180" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起仅计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -10975,7 +11131,7 @@
       </c>
       <c r="H181" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起仅计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11168,7 @@
       </c>
       <c r="H182" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起仅计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11205,7 @@
       </c>
       <c r="H183" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起仅计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11291,7 @@
       </c>
       <c r="H188" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起只计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11328,7 @@
       </c>
       <c r="H189" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起只计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11365,7 @@
       </c>
       <c r="H190" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起只计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11402,7 @@
       </c>
       <c r="H191" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起只计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11439,7 @@
       </c>
       <c r="H192" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起只计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11476,7 @@
       </c>
       <c r="H193" s="0" t="inlineStr">
         <is>
-          <t>负责人安排的任务示例；自主发起只计主动分</t>
+          <t>负责人安排的任务示例；自主发起按正常积分×主动倍率计算</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11537,7 @@
       </c>
       <c r="D198" s="49" t="inlineStr">
         <is>
-          <t>叠加计20分</t>
+          <t>按各自正常积分×主动倍率分别计算</t>
         </is>
       </c>
       <c r="E198" s="49" t="inlineStr">
@@ -11436,17 +11592,17 @@
       </c>
       <c r="C200" s="49" t="inlineStr">
         <is>
-          <t>只计主动改善分（2/4/6分档）</t>
+          <t>按正常积分×主动倍率</t>
         </is>
       </c>
       <c r="D200" s="49" t="inlineStr">
         <is>
-          <t>任务分3分＋主动分4分</t>
+          <t>正常积分＋另加主动积分</t>
         </is>
       </c>
       <c r="E200" s="49" t="inlineStr">
         <is>
-          <t>发起来源互斥：自主发起只走主动分</t>
+          <t>发起来源互斥：自主发起按倍率，不另加正常积分</t>
         </is>
       </c>
       <c r="F200" s="49" t="inlineStr">
@@ -11466,7 +11622,7 @@
       </c>
       <c r="C201" s="49" t="inlineStr">
         <is>
-          <t>只计主动改善分</t>
+          <t>按正常积分×主动倍率</t>
         </is>
       </c>
       <c r="D201" s="49" t="inlineStr">
@@ -11834,7 +11990,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>标题2分/个；五点2分/套（改1点或全部五点均2分）；描述2分/份；Generic Keywords 2分/套；独立全新或完全重做A+10分/份；部分A+2分/模块、每份每轮最高10分。系数均固定1.0。</t>
+          <t>标题2分/个；五点3分/套（改1点或全部五点均3分）；描述3分/份；Generic Keywords 2分/套；独立全新或完全重做A+10分/份；同一份A+同一轮局部修改2分。系数均固定1.0。</t>
         </is>
       </c>
     </row>
@@ -11942,7 +12098,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善2/4/6分档认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。 月度绩效仍为任务完成最高80分＋主动改善最高20分。</t>
+          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善主动倍率认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。 月度绩效仍为任务完成正常积分×主动倍率＋主动改善正常积分×主动倍率。</t>
         </is>
       </c>
     </row>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -865,7 +865,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1035,6 +1035,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3432,7 +3433,7 @@
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
         <is>
-          <t>上架执行组＝同一次安排、同一执行人、同一站点、能共用一张上架表的SKU集合。OA仍一条一个SKU，以组编号关联。难度按本次需处理关系的不同父体数判断；详见“场景示例”。</t>
+          <t>上架执行组＝同一次安排、同一执行人、同一站点、能共用一张上架表的SKU集合。OA仍一条一个SKU，以组编号关联。难度按本次需处理关系的不同父体数判断；详见"场景示例"。跨站点上架按目标站点分别计算执行组（CA、MX、BR等各自独立）。</t>
         </is>
       </c>
       <c r="B6" s="31" t="n"/>
@@ -5299,45 +5300,123 @@
       <c r="I51" s="2" t="n"/>
     </row>
     <row r="52" ht="14.6" customHeight="1" s="39">
-      <c r="A52" s="7" t="n"/>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="40" t="n"/>
-      <c r="D52" s="40" t="n"/>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
+      <c r="A52" s="60" t="inlineStr">
+        <is>
+          <t>跨站点执行</t>
+        </is>
+      </c>
+      <c r="B52" s="60" t="inlineStr">
+        <is>
+          <t>跨站点Listing创建</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="60" t="inlineStr">
+        <is>
+          <t>按目标站点分别计算上架执行组，与美国站相同规则：
+1个SKU：5分；2个及以上可共用上架表：8分。
+CA、MX、BR等各站点分别制作上架表并完成发布，按各自站点独立计分。</t>
+        </is>
+      </c>
+      <c r="F52" s="60" t="inlineStr">
+        <is>
+          <t>1.0：本组不新增或调整任何父子关系
+1.3：本组需处理父子关系，仅涉及1个父体
+1.6：本组需处理父子关系，涉及2个及以上不同父体</t>
+        </is>
+      </c>
       <c r="G52" s="41">
         <f>ROUND(C52*D52,1)</f>
         <v/>
       </c>
-      <c r="H52" s="7" t="n"/>
+      <c r="H52" s="60" t="inlineStr">
+        <is>
+          <t>与美国站上架执行组规则一致，按目标站点独立分组。不同站点的上架表不共用，因此分别计分。同一SKU在多个站点上架，按各站点分别计算。</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="n"/>
     </row>
     <row r="53" ht="14.6" customHeight="1" s="39">
-      <c r="A53" s="7" t="n"/>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="40" t="n"/>
-      <c r="D53" s="40" t="n"/>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="A53" s="60" t="inlineStr">
+        <is>
+          <t>跨站点执行</t>
+        </is>
+      </c>
+      <c r="B53" s="60" t="inlineStr">
+        <is>
+          <t>A+翻译后发布（非新策划）</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="60" t="inlineStr">
+        <is>
+          <t>将已有A+翻译后发布到其他站点：2分/批。
+同一次安排、同一份A+内容发布到多个站点，按批计分，不按站点数量累加。</t>
+        </is>
+      </c>
+      <c r="F53" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；已有内容的翻译与发布。</t>
+        </is>
+      </c>
       <c r="G53" s="41">
         <f>ROUND(C53*D53,1)</f>
         <v/>
       </c>
-      <c r="H53" s="7" t="n"/>
+      <c r="H53" s="60" t="inlineStr">
+        <is>
+          <t>仅限将美国站等已有A+翻译后发布，不涉及内容策划或重新设计。全新策划制作的A+按10分/份计分（A+制作发布），不按本项。翻译＋发布合并计分，不拆分翻译和发布分别领取。主动倍率按"固定例行工作"×1。</t>
+        </is>
+      </c>
       <c r="I53" s="2" t="n"/>
     </row>
     <row r="54" ht="14.6" customHeight="1" s="39">
-      <c r="A54" s="7" t="n"/>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="40" t="n"/>
-      <c r="D54" s="40" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="A54" s="60" t="inlineStr">
+        <is>
+          <t>跨站点执行</t>
+        </is>
+      </c>
+      <c r="B54" s="60" t="inlineStr">
+        <is>
+          <t>翻译后批量更新Listing文案</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="60" t="inlineStr">
+        <is>
+          <t>已提供文案，翻译后批量更新标题、五点、描述等：2分/批。
+按同一次安排的一批任务计分，不按SKU数量增加。</t>
+        </is>
+      </c>
+      <c r="F54" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；按批次计分。</t>
+        </is>
+      </c>
       <c r="G54" s="41">
         <f>ROUND(C54*D54,1)</f>
         <v/>
       </c>
-      <c r="H54" s="7" t="n"/>
+      <c r="H54" s="60" t="inlineStr">
+        <is>
+          <t>与独立重写标题/五点/描述区分：本项为已有文案的翻译更新，非自主分析优化。独立重写按各自工作项目计分（标题3分、五点3分、描述3分等）。同一批翻译更新拆文件、重复上传不增加批次。主动倍率按"固定例行工作"×1。</t>
+        </is>
+      </c>
       <c r="I54" s="2" t="n"/>
     </row>
     <row r="55" ht="14.6" customHeight="1" s="39">
@@ -5628,7 +5707,7 @@
       </c>
       <c r="B72" s="56" t="inlineStr">
         <is>
-          <t>VOC数据更新与AI分析、Category Report下载、关键词市场占有率统计及竞品检查</t>
+          <t>VOC数据更新与AI分析、Category Report下载、关键词市场占有率统计及竞品检查、A+翻译后发布、翻译后批量更新Listing文案</t>
         </is>
       </c>
       <c r="C72" s="64" t="n"/>
@@ -5639,7 +5718,7 @@
       </c>
       <c r="E72" s="56" t="inlineStr">
         <is>
-          <t>固定周期任务，不享受主动倍率。</t>
+          <t>固定周期或已有内容的翻译发布任务，不享受主动倍率。</t>
         </is>
       </c>
       <c r="F72" s="65" t="n"/>
@@ -10597,149 +10676,238 @@
       <c r="H158" s="56" t="inlineStr"/>
     </row>
     <row r="160" ht="30" customHeight="1" s="39">
-      <c r="A160" s="0" t="inlineStr">
-        <is>
-          <t>按发起来源选择唯一计分路径</t>
+      <c r="A160" s="71" t="inlineStr">
+        <is>
+          <t>跨站点执行计分示例</t>
         </is>
       </c>
     </row>
     <row r="161" ht="34" customHeight="1" s="39">
-      <c r="A161" s="19" t="inlineStr">
-        <is>
-          <t>发起来源</t>
-        </is>
-      </c>
-      <c r="B161" s="19" t="inlineStr">
-        <is>
-          <t>实际工作</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="inlineStr">
+      <c r="A161" s="66" t="inlineStr">
+        <is>
+          <t>工作项目</t>
+        </is>
+      </c>
+      <c r="B161" s="66" t="inlineStr">
+        <is>
+          <t>实际场景</t>
+        </is>
+      </c>
+      <c r="C161" s="66" t="inlineStr">
+        <is>
+          <t>累计基础分</t>
+        </is>
+      </c>
+      <c r="D161" s="66" t="inlineStr">
+        <is>
+          <t>难度系数</t>
+        </is>
+      </c>
+      <c r="E161" s="66" t="inlineStr">
         <is>
           <t>任务积分</t>
         </is>
       </c>
-      <c r="D161" s="19" t="inlineStr">
-        <is>
-          <t>主动改善分</t>
-        </is>
-      </c>
-      <c r="E161" s="19" t="inlineStr">
-        <is>
-          <t>唯一计分路径</t>
-        </is>
-      </c>
-      <c r="F161" s="19" t="inlineStr">
-        <is>
-          <t>认定条件</t>
-        </is>
-      </c>
-      <c r="G161" s="19" t="inlineStr">
-        <is>
-          <t>归属说明</t>
-        </is>
-      </c>
-      <c r="H161" s="19" t="inlineStr">
-        <is>
-          <t>防重复规则</t>
+      <c r="F161" s="66" t="inlineStr">
+        <is>
+          <t>计算依据</t>
+        </is>
+      </c>
+      <c r="G161" s="66" t="inlineStr">
+        <is>
+          <t>结算说明</t>
+        </is>
+      </c>
+      <c r="H161" s="66" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="162" ht="105" customHeight="1" s="39">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="2" t="n"/>
-      <c r="F162" s="2" t="n"/>
-      <c r="G162" s="2" t="n"/>
-      <c r="H162" s="2" t="n"/>
+      <c r="A162" s="56" t="inlineStr">
+        <is>
+          <t>跨站点Listing创建</t>
+        </is>
+      </c>
+      <c r="B162" s="56" t="inlineStr">
+        <is>
+          <t>美国站3个SKU已上架，现需在CA站上架同3个SKU</t>
+        </is>
+      </c>
+      <c r="C162" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D162" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="69">
+        <f>ROUND(C162*D162,1)</f>
+        <v/>
+      </c>
+      <c r="F162" s="56" t="inlineStr">
+        <is>
+          <t>CA站独立分组，3个SKU可共用上架表＝8分</t>
+        </is>
+      </c>
+      <c r="G162" s="56" t="inlineStr">
+        <is>
+          <t>与US站分别计分</t>
+        </is>
+      </c>
+      <c r="H162" s="56" t="inlineStr">
+        <is>
+          <t>按目标站点独立上架执行组</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="105" customHeight="1" s="39">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>员工自主发起</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>自行发现无效花费，处理并核验解决</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="2" t="n">
+      <c r="A163" s="56" t="inlineStr">
+        <is>
+          <t>跨站点Listing创建</t>
+        </is>
+      </c>
+      <c r="B163" s="56" t="inlineStr">
+        <is>
+          <t>MX和BR各上架1个SKU</t>
+        </is>
+      </c>
+      <c r="C163" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D163" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" s="69">
+        <f>ROUND(C163*D163,1)</f>
+        <v/>
+      </c>
+      <c r="F163" s="56" t="inlineStr">
+        <is>
+          <t>MX站1个SKU＝5分 ＋ BR站1个SKU＝5分</t>
+        </is>
+      </c>
+      <c r="G163" s="56" t="inlineStr">
+        <is>
+          <t>不同站点分别计分</t>
+        </is>
+      </c>
+      <c r="H163" s="56" t="inlineStr">
+        <is>
+          <t>各站点不共用上架表</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="105" customHeight="1" s="39">
+      <c r="A164" s="56" t="inlineStr">
+        <is>
+          <t>A+翻译后发布</t>
+        </is>
+      </c>
+      <c r="B164" s="56" t="inlineStr">
+        <is>
+          <t>将US站A+翻译后发布到CA和MX</t>
+        </is>
+      </c>
+      <c r="C164" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="69">
+        <f>ROUND(C164*D164,1)</f>
+        <v/>
+      </c>
+      <c r="F164" s="56" t="inlineStr">
+        <is>
+          <t>同一份内容同一批＝2分</t>
+        </is>
+      </c>
+      <c r="G164" s="56" t="inlineStr">
+        <is>
+          <t>不按站点数量累加</t>
+        </is>
+      </c>
+      <c r="H164" s="56" t="inlineStr">
+        <is>
+          <t>非新策划，仅翻译发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="105" customHeight="1" s="39">
+      <c r="A165" s="56" t="inlineStr">
+        <is>
+          <t>A+翻译后发布</t>
+        </is>
+      </c>
+      <c r="B165" s="56" t="inlineStr">
+        <is>
+          <t>将US站2份不同A+分别翻译后发布到CA</t>
+        </is>
+      </c>
+      <c r="C165" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>主动改善部分</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>符合推动解决认定</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>同案取最高档</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>不叠加2分任务积分</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="105" customHeight="1" s="39">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>员工先建议、后获批</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>先提出问题方案，再获批准并执行解决</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>主动改善部分</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>保留首次提议及审批记录</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>补建任务不改变自主来源</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>不重复领取任务分</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="105" customHeight="1" s="39">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="2" t="n"/>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="2" t="n"/>
-      <c r="F165" s="2" t="n"/>
-      <c r="G165" s="2" t="n"/>
-      <c r="H165" s="2" t="n"/>
+      <c r="D165" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="69">
+        <f>ROUND(C165*D165,1)</f>
+        <v/>
+      </c>
+      <c r="F165" s="56" t="inlineStr">
+        <is>
+          <t>2份不同内容各2分＝4分</t>
+        </is>
+      </c>
+      <c r="G165" s="56" t="inlineStr">
+        <is>
+          <t>不同内容按份数计</t>
+        </is>
+      </c>
+      <c r="H165" s="56" t="inlineStr">
+        <is>
+          <t>每份A+独立计分</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="56" t="inlineStr">
+        <is>
+          <t>翻译后批量更新</t>
+        </is>
+      </c>
+      <c r="B166" s="56" t="inlineStr">
+        <is>
+          <t>已有中文文案，翻译后批量更新10个SKU的标题和五点</t>
+        </is>
+      </c>
+      <c r="C166" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="69">
+        <f>ROUND(C166*D166,1)</f>
+        <v/>
+      </c>
+      <c r="F166" s="56" t="inlineStr">
+        <is>
+          <t>同一批翻译更新＝2分</t>
+        </is>
+      </c>
+      <c r="G166" s="56" t="inlineStr">
+        <is>
+          <t>不按SKU数量增加</t>
+        </is>
+      </c>
+      <c r="H166" s="56" t="inlineStr">
+        <is>
+          <t>与独立重写区分：翻译更新按批，独立重写按项</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="30" customHeight="1" s="39">
       <c r="A168" s="0" t="inlineStr">

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -2215,14 +2215,13 @@
       </c>
       <c r="D13" s="38" t="inlineStr">
         <is>
-          <t>同一模块内增加、删除或修改多处信息只计一次2分；同一轮反复调整不重复计分。全新制作或完全重做按10分/份，不叠加局部修改分。仅增加绑定SKU归A+制作发布，按1分/SKU。单纯事实纠错按Listing纠错计分。以优化为目的的修改执行优化登记与复盘规则。</t>
+          <t>同一份A+同一轮内所有局部增加、删除或修改合计2分，不按模块数量累加；同一轮反复调整不重复计分。全新制作或完全重做按10分/份，不叠加局部修改分。仅增加绑定SKU归A+制作发布，按1分/SKU。单纯事实纠错按Listing纠错计分。以优化为目的的修改执行优化登记与复盘规则。</t>
         </is>
       </c>
       <c r="E13" s="38" t="inlineStr">
         <is>
-          <t>每个实际修改的模块：2分。
-新增或删除整个模块也按2分/模块计。
-同一份A+同一轮累计最高10分。</t>
+          <t>同一份A+同一轮局部修改合计2分。
+不按模块数量累加；全新制作或完全重做按10分/份。</t>
         </is>
       </c>
       <c r="F13" s="38" t="inlineStr">
@@ -2404,7 +2403,7 @@
       </c>
       <c r="D18" s="38" t="inlineStr">
         <is>
-          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善按正常积分×主动倍率认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。</t>
+          <t>本行为说明项，不产生独立计分。员工自主发现价格异常并完成修正时，使用"价格调整"的基础分3分×难度系数×主动倍率1.5结算。负责人安排的改价直接按"价格调整"计任务积分。员工先提出建议、经负责人批准后执行，仍属主动；补建任务或认领变化不改变来源。</t>
         </is>
       </c>
       <c r="E18" s="38" t="inlineStr">
@@ -2664,15 +2663,14 @@
       </c>
       <c r="D25" s="38" t="inlineStr">
         <is>
-          <t>仅用于负责人已明确具体要求的执行工作。同一次安排、同一调整目的合计基础分，多个明细关联同一任务不逐行叠加；独立目的的任务分别计分。不按对象、Campaign或Ads Change数量加分。认领变化、关联任务、填写原因并核验。员工自主发起改善仅计主动分，同一工作不重复计分。</t>
+          <t>仅用于负责人已明确具体要求的执行工作。以Campaign为计分单位，每个Campaign每次有效调整计2分。同一次调整包含多种动作（否定词＋Bid＋商品投放）合计只算1次。每个自然周（周一至周日）每个Campaign最多计2次，不同Campaign分别计分。负责人安排和员工主动执行合并统计，多人参与不增加次数。认领变化、关联任务、填写原因并核验。员工自主发起改善按正常积分×主动倍率计算，同一工作不重复计分。</t>
         </is>
       </c>
       <c r="E25" s="38" t="inlineStr">
         <is>
-          <t>小批量（≤5个Campaign）：2分。
-中批量（6—20个Campaign）：3分。
-大批量（21个及以上Campaign）：4分。
-按同次安排、同一调整目的计。</t>
+          <t>每个Campaign每次有效调整：2分。
+每个自然周（周一至周日）每个Campaign最多计2次。
+不同Campaign分别计分。</t>
         </is>
       </c>
       <c r="F25" s="38" t="inlineStr">
@@ -2682,7 +2680,7 @@
       </c>
       <c r="G25" s="38" t="inlineStr">
         <is>
-          <t>具体调整完成并核验；同一任务仅结算一次。按实际涉及Campaign数量选择分档。自行分析的安排任务按Campaign优化计分，自主发起按正常积分×主动倍率计算。</t>
+          <t>具体调整完成并核验；以Campaign为单位按周统计。第二次计分须有第一次调整后的复查依据或新问题依据。自主发起按正常积分×主动倍率计算。</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3186,7 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不再加计2分。</t>
+          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不另加分。</t>
         </is>
       </c>
       <c r="D39" s="38" t="inlineStr">
@@ -3198,7 +3196,7 @@
       </c>
       <c r="E39" s="38" t="inlineStr">
         <is>
-          <t>需协调获取资料、核对并完成一批提交，计3分。</t>
+          <t>需协调获取资料、核对并完成一批提交，计2分。</t>
         </is>
       </c>
       <c r="F39" s="38" t="inlineStr">
@@ -3208,54 +3206,199 @@
       </c>
       <c r="G39" s="38" t="inlineStr">
         <is>
-          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不再加计2分。</t>
+          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不另加分。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A40" s="37" t="n"/>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="38" t="n"/>
-      <c r="F40" s="38" t="n"/>
-      <c r="G40" s="38" t="n"/>
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t>数据与报表</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Category Report下载</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>按要求每天下载、归档并核验，每周合并结算。</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="inlineStr">
+        <is>
+          <t>固定例行工作，主动倍率×1。按天核验，按周结算。因假期、系统故障等不可控原因未下载的天数不计入应完成天数。同一天多次下载合并计分。</t>
+        </is>
+      </c>
+      <c r="E40" s="38" t="inlineStr">
+        <is>
+          <t>积分＝1×合格完成天数÷当周应完成天数。
+当周无任务则不计分。</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="inlineStr">
+        <is>
+          <t>每天下载文件、归档记录及核验结果。</t>
+        </is>
+      </c>
+      <c r="G40" s="38" t="inlineStr">
+        <is>
+          <t>每天按时下载、归档并核验；按周统计合格完成天数，计算当周积分。</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A41" s="37" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="38" t="n"/>
-      <c r="E41" s="38" t="n"/>
-      <c r="F41" s="38" t="n"/>
-      <c r="G41" s="38" t="n"/>
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>数据与报表</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>关键词市场占有率统计及竞品检查</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>按要求完成关键词的市场占有率数据统计及竞品检查。</t>
+        </is>
+      </c>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>每个关键词每月结算一次。同一关键词同一月份不重复计分。数据采集、统计、竞品检查及结果记录包含在分值内。</t>
+        </is>
+      </c>
+      <c r="E41" s="38" t="inlineStr">
+        <is>
+          <t>每个关键词每月：2分。
+不按数据条数分档。</t>
+        </is>
+      </c>
+      <c r="F41" s="38" t="inlineStr">
+        <is>
+          <t>关键词、数据期间、统计结果及竞品检查记录。</t>
+        </is>
+      </c>
+      <c r="G41" s="38" t="inlineStr">
+        <is>
+          <t>完成指定关键词的市场占有率统计及竞品检查，结果记录完整并核验。</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A42" s="37" t="n"/>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="38" t="n"/>
-      <c r="E42" s="38" t="n"/>
-      <c r="F42" s="38" t="n"/>
-      <c r="G42" s="38" t="n"/>
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>跨站点执行</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>跨站点Listing创建</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>将已有站点的商品信息翻译后在新站点创建Listing，完成SKU、价格、库存和配送方式设置。</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="inlineStr">
+        <is>
+          <t>按目标站点计分，每个目标站点视为一个独立上架执行。执行标准与US站Listing创建一致。与US站同一商品的首次Listing创建不重复计分。</t>
+        </is>
+      </c>
+      <c r="E42" s="38" t="inlineStr">
+        <is>
+          <t>每个目标站点的一个上架执行组：5分。
+执行标准与US站Listing创建一致。</t>
+        </is>
+      </c>
+      <c r="F42" s="38" t="inlineStr">
+        <is>
+          <t>上架清单、翻译记录、上传文件、父子关系及核验结果。</t>
+        </is>
+      </c>
+      <c r="G42" s="38" t="inlineStr">
+        <is>
+          <t>按US站Listing创建标准验收。目标站点Listing创建结果核验完成。</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="69.40000000000001" customHeight="1" s="39">
-      <c r="A43" s="37" t="n"/>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="38" t="n"/>
-      <c r="E43" s="38" t="n"/>
-      <c r="F43" s="38" t="n"/>
-      <c r="G43" s="38" t="n"/>
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>跨站点执行</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>A+翻译后发布（非新策划）</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>将已有A+内容翻译为目标站点语言，提交发布并核验。</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>与全新制作A+（10分/份）区分：本项为已有A+的翻译发布。同一批翻译发布拆文件、重复提交不增加批次。</t>
+        </is>
+      </c>
+      <c r="E43" s="38" t="inlineStr">
+        <is>
+          <t>每批翻译后发布：2分。
+同一批多个SKU的A+合计2分/批。</t>
+        </is>
+      </c>
+      <c r="F43" s="38" t="inlineStr">
+        <is>
+          <t>原A+内容编号、翻译记录、提交结果及核验记录。</t>
+        </is>
+      </c>
+      <c r="G43" s="38" t="inlineStr">
+        <is>
+          <t>翻译后A+已发布并核验。同一批翻译不重复计分。</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="14.6" customHeight="1" s="39">
-      <c r="A44" s="37" t="n"/>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="38" t="n"/>
-      <c r="E44" s="38" t="n"/>
-      <c r="F44" s="38" t="n"/>
-      <c r="G44" s="38" t="n"/>
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>跨站点执行</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>翻译后批量更新Listing文案</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>已提供文案，翻译后批量更新标题、五点、描述等。</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="inlineStr">
+        <is>
+          <t>与独立重写区分：本项为已有文案的翻译更新。同一批翻译更新拆文件、重复上传不增加批次。</t>
+        </is>
+      </c>
+      <c r="E44" s="38" t="inlineStr">
+        <is>
+          <t>每批翻译更新：2分。
+按同一次安排的一批任务计分。</t>
+        </is>
+      </c>
+      <c r="F44" s="38" t="inlineStr">
+        <is>
+          <t>文案来源、翻译记录、上传结果及核验记录。</t>
+        </is>
+      </c>
+      <c r="G44" s="38" t="inlineStr">
+        <is>
+          <t>翻译文案已更新并核验。同一批不重复计分。</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="14.6" customHeight="1" s="39">
       <c r="A45" s="37" t="n"/>
@@ -4013,9 +4156,9 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>同一模块增加两项参数：2分。
-另一模块删除过时信息：再计2分，共4分。
-同份同轮修改6个模块：封顶10分。</t>
+          <t>同一份A+本轮增加两项参数、删除过时信息、调整模块：合计2分。
+无论修改几个模块，同一份同一轮合计2分。
+全新制作或完全重做：按10分/份。</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4356,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>主动价格优化</t>
+          <t>主动价格优化（说明项，不独立计分）</t>
         </is>
       </c>
       <c r="C24" s="40" t="n">
@@ -4224,8 +4367,8 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>主动改善关联入口：任务积分0分。
-自主发起按主动倍率计算，同案取最高适用倍率。</t>
+          <t>本行不独立计分。
+员工自主发现价格异常并修正，使用"价格调整"基础分3分×主动倍率1.5＝4.5分。</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -4240,7 +4383,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计正常任务积分；员工自主发现并发起的改善按正常任务积分×主动倍率计算，同一工作只计一次。员工先提出建议、经负责人批准后执行，仍属主动。补建任务或认领变化不改变来源。本行0分表示不计正常任务积分，不表示主动改善没有得分。</t>
+          <t>本行为说明项，不产生独立任务积分。员工自主发现价格异常并完成修正时，使用"价格调整"的基础分3分×难度系数×主动倍率1.5结算，不另设独立计分项目。员工先提出建议、经负责人批准后执行，仍属主动。补建任务或认领变化不改变来源。</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -4555,9 +4698,10 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>同次安排调整3个Campaign的Bid：2分。
-同次安排调整15个Campaign的否定词：3分。
-同次安排调整30个Campaign的关键词：4分。</t>
+          <t>调整3个Campaign各1次有效调整：6分。
+调整15个Campaign各1次有效调整：30分。
+调整30个Campaign各1次有效调整：60分。
+1个Campaign本周已调整2次：不再计分。</t>
         </is>
       </c>
     </row>
@@ -5156,13 +5300,13 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不再加计2分。
+          <t>协调取得可用资料，核对SKU对应关系，完成提交并跟进审核结果；已包含资料提交，不另加分。
 同一次安排、同一处理方式且可一起完成的SKU合并为一批，不按SKU数量增加；拆文件、重复提交或重试不重复计分。同一问题连续处理只取最高分，例如先Relist再申诉合计3分；资料协调已含提交，不叠加。待资料或审核中不自动结案，未解决由负责人确认阶段结案。与Listing修复、其他库存处置的相同交付不重复计分。负责人安排按正常积分；自主发起按正常积分×主动倍率计算，同一工作只计一次。</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>协调取得资料并提交：合计3分。</t>
+          <t>协调取得资料并提交：合计2分。</t>
         </is>
       </c>
     </row>
@@ -5241,13 +5385,14 @@
       </c>
       <c r="E50" s="60" t="inlineStr">
         <is>
-          <t>每周完成一次下载并归档：1分/周。
-按天折算时按实际完成天数比例计算。</t>
+          <t>按要求每天下载、归档并核验，每周合并结算。
+积分＝1×合格完成天数÷当周应完成天数。
+当周无任务则不计分。</t>
         </is>
       </c>
       <c r="F50" s="60" t="inlineStr">
         <is>
-          <t>固定1.0；按每周完整任务计分。</t>
+          <t>固定1.0；按每天完成，每周结算。</t>
         </is>
       </c>
       <c r="G50" s="41">
@@ -5256,7 +5401,7 @@
       </c>
       <c r="H50" s="60" t="inlineStr">
         <is>
-          <t>固定例行工作，主动倍率×1。下载并归档后验收；同一周多次下载合并计分。</t>
+          <t>固定例行工作，主动倍率×1。每天按要求下载、归档并核验Category Report。每周合并结算：积分＝1×合格完成天数÷当周应完成天数。因假期、系统故障等不可控原因未下载的天数不计入应完成天数。当周无任务则不计分。同一天多次下载合并计分。</t>
         </is>
       </c>
       <c r="I50" s="2" t="n"/>
@@ -5414,7 +5559,7 @@
       </c>
       <c r="H54" s="60" t="inlineStr">
         <is>
-          <t>与独立重写标题/五点/描述区分：本项为已有文案的翻译更新，非自主分析优化。独立重写按各自工作项目计分（标题3分、五点3分、描述3分等）。同一批翻译更新拆文件、重复上传不增加批次。主动倍率按"固定例行工作"×1。</t>
+          <t>与独立重写标题/五点/描述区分：本项为已有文案的翻译更新，非自主分析优化。独立重写按各自工作项目计分（标题2分、五点3分、描述3分等）。同一批翻译更新拆文件、重复上传不增加批次。主动倍率按"固定例行工作"×1。</t>
         </is>
       </c>
       <c r="I54" s="2" t="n"/>
@@ -5883,7 +6028,7 @@
     <row r="3" ht="24" customHeight="1" s="39">
       <c r="A3" s="70" t="inlineStr">
         <is>
-          <t>【已重构】主动改善不再使用2/4/6分档和20分上限。新规则：主动任务积分＝正常任务积分×主动倍率（见"任务评分"主动执行倍率规则）。下方评价框架保留用于认定主动行为是否成立，分值按新倍率计算。</t>
+          <t>【已重构】主动改善不再使用独立的案例分值（原2/4/6分档）和月度20分上限。新规则：主动任务积分＝正常任务积分×主动倍率（见"任务评分"主动执行倍率规则）。下方评价框架仅用于认定主动行为是否成立及行为层次，不再产生独立分值。</t>
         </is>
       </c>
       <c r="B3" s="22" t="n"/>
@@ -5905,7 +6050,7 @@
     <row r="5" ht="24" customHeight="1" s="39">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>黄色案例分可调整；默认有效发现2分、推动解决4分、形成持续改善6分。同案只取最高档，主动分不乘任务难度系数。</t>
+          <t>下表定义行为层次，仅用于判断主动行为是否成立及深度（发现→解决→持续改善），不产生独立分值。认定成立后，按对应工作项目的正常任务积分×主动倍率结算。</t>
         </is>
       </c>
       <c r="B5" s="22" t="n"/>
@@ -5937,7 +6082,7 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>案例分</t>
+          <t>行为层次</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
@@ -5962,8 +6107,10 @@
           <t>员工自主发现真实问题，提供证据及可执行建议；问题经确认，建议被采纳。</t>
         </is>
       </c>
-      <c r="C8" s="43" t="n">
-        <v>2</v>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>第一层</t>
+        </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
@@ -5972,7 +6119,7 @@
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>尚未实施也可认定本档；只指出问题、无可执行建议，或未获确认采纳的，暂不计分。</t>
+          <t>尚未实施也可认定本层；只指出问题、无可执行建议，或未获确认采纳的，暂不认定。</t>
         </is>
       </c>
     </row>
@@ -5987,8 +6134,10 @@
           <t>在有效发现基础上，完成职责范围内的处理、协调及结果核验。</t>
         </is>
       </c>
-      <c r="C9" s="43" t="n">
-        <v>4</v>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>第二层</t>
+        </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
@@ -6012,8 +6161,10 @@
           <t>在解决问题基础上，形成可复用规则、预警或流程，减少同类问题再次发生，并有验证记录。</t>
         </is>
       </c>
-      <c r="C10" s="43" t="n">
-        <v>6</v>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>第三层</t>
+        </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
@@ -6022,7 +6173,7 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>只有建议或文档、尚未实施验证的，不认定本档；同一问题的发现、解决和持续改善不逐档累加。</t>
+          <t>只有建议或文档、尚未实施验证的，不认定本层；同一问题的发现、解决和持续改善取最深层次，不逐层累加。</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6299,7 @@
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>自主发现并发起的改善只按本页等级认定，不再领取对应执行工作的任务积分。</t>
+          <t>自主发现并发起的改善按正常任务积分×主动倍率结算，不再领取对应执行工作的任务积分。</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6506,7 @@
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
-          <t>按主动改善案例认定：有效发现2分、推动解决4分、形成持续改善6分，同案取最高档。对应执行及复盘不再计任务积分；审批或补建任务不改变自主发起来源。</t>
+          <t>按正常任务积分×主动倍率计算。对应执行及复盘不再另计任务积分；审批或补建任务不改变自主发起来源。</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6533,7 @@
       </c>
       <c r="E26" s="25" t="inlineStr">
         <is>
-          <t>按主动改善案例认定：有效发现2分、推动解决4分、形成持续改善6分，同案取最高档。对应执行及复盘不再计任务积分；审批或补建任务不改变自主发起来源。</t>
+          <t>按正常任务积分×主动倍率计算。对应执行及复盘不再另计任务积分；审批或补建任务不改变自主发起来源。</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6560,7 @@
       </c>
       <c r="E27" s="25" t="inlineStr">
         <is>
-          <t>按主动改善案例认定：有效发现2分、推动解决4分、形成持续改善6分，同案取最高档。对应执行及复盘不再计任务积分；审批或补建任务不改变自主发起来源。</t>
+          <t>按正常任务积分×主动倍率计算。对应执行及复盘不再另计任务积分；审批或补建任务不改变自主发起来源。</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6587,7 @@
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>按主动改善案例认定：有效发现2分、推动解决4分、形成持续改善6分，同案取最高档。对应执行及复盘不再计任务积分；审批或补建任务不改变自主发起来源。</t>
+          <t>按正常任务积分×主动倍率计算。对应执行及复盘不再另计任务积分；审批或补建任务不改变自主发起来源。</t>
         </is>
       </c>
     </row>
@@ -6488,25 +6639,27 @@
     <row r="32" ht="78" customHeight="1" s="39">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>月度上限</t>
+          <t>月度结算公式</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>按个人汇总当月通过认定的案例分或升级补差，主动改善得分不得超过本行上限。</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="n">
-        <v>20</v>
+          <t>正常任务积分＝按计分单位累计的基础分×难度系数。最终任务积分＝正常任务积分×适用主动倍率。负责人安排或固定例行工作，倍率为1；每项任务只计一次。月度积分为当月已验收任务最终积分之和。</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>见公式</t>
+        </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>现有页面导出的个人案例明细、核定分值及认定日期。</t>
+          <t>当月全部已验收任务的最终积分汇总。</t>
         </is>
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
-          <t>主动改善得分＝MIN（当月案例核定分及升级补差合计，月度上限20分）；总绩效最高100分。任务完成部分须折算至正常积分，不把原始任务积分直接相加。</t>
+          <t>不设月度上限；总绩效上限仍按公司规定。</t>
         </is>
       </c>
     </row>
@@ -6540,27 +6693,27 @@
     <row r="34" ht="78" customHeight="1" s="39">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>升级及跨月</t>
+          <t>跨月任务</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>已计分案例后续达到更高档，只计新档分值减去历次已认定分值的正差额。</t>
+          <t>跨月任务在验收完成的月份计入当月积分。</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>只补差额</t>
+          <t>按验收月</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>历史等级、历史已认定分、升级证据及本次差额。</t>
+          <t>验收日期、结算月及任务编号。</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>月度封顶被截去的部分不顺延补领，也不能通过升级重新领取；待验收案例于通过认定月份计分。</t>
+          <t>未验收任务不计入当月；待验收任务于通过验收月份计分。</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10485,7 @@
       </c>
       <c r="H147" s="67" t="inlineStr">
         <is>
-          <t>关联一条Ads Change记录</t>
+          <t>可关联多条Ads Change记录</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11282,7 @@
       </c>
       <c r="F174" s="0" t="inlineStr">
         <is>
-          <t>协调获取资料档：3分</t>
+          <t>协调获取资料：2分</t>
         </is>
       </c>
       <c r="G174" s="0" t="inlineStr">
@@ -11910,7 +12063,7 @@
       </c>
       <c r="C205" s="49" t="inlineStr">
         <is>
-          <t>封顶10分</t>
+          <t>合计2分</t>
         </is>
       </c>
       <c r="D205" s="49" t="inlineStr">
@@ -11920,7 +12073,7 @@
       </c>
       <c r="E205" s="49" t="inlineStr">
         <is>
-          <t>同份同轮累计最高10分</t>
+          <t>同份同轮合计2分，不按模块数量累加</t>
         </is>
       </c>
       <c r="F205" s="49" t="inlineStr">
@@ -12218,7 +12371,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>负责人安排的优化先登记预计任务积分，内容发布核验且复盘形成结论后结算；自主发起改善只按主动改善等级认定。结果未增长不自动判零分，按依据、实际交付及复盘验收；同一工作不跨两条路径重复计分。</t>
+          <t>负责人安排的优化先登记预计任务积分，内容发布核验且复盘形成结论后结算。自主发起改善按正常任务积分×主动倍率结算（见"任务评分"主动执行倍率规则），不再使用主动改善等级分值。结果未增长不自动判零分，按依据、实际交付及复盘验收；同一工作不跨两条路径重复计分。</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12419,8 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善仅按主动改善主动倍率认定，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。 月度绩效仍为任务完成正常积分×主动倍率＋主动改善正常积分×主动倍率。</t>
+          <t>按实际发起来源选择唯一计分路径：负责人安排的工作计任务积分；员工自主发现并发起的改善按正常任务积分×主动倍率结算，不再叠加任务积分。员工先提出建议、经负责人批准后执行，仍属主动改善；补建任务或认领变化不改变来源。
+正常任务积分＝按计分单位累计的基础分×难度系数。最终任务积分＝正常任务积分×适用主动倍率。负责人安排或固定例行工作，倍率为1；每项任务只计一次。月度积分为当月已验收任务最终积分之和。</t>
         </is>
       </c>
     </row>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -1376,7 +1376,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmazonOpsWorkOptimized" displayName="AmazonOpsWorkOptimized" ref="A1:G43" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmazonOpsWorkOptimized" displayName="AmazonOpsWorkOptimized" ref="A1:G44" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="一级模块"/>
     <tableColumn id="2" name="二级模块"/>
@@ -1417,7 +1417,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AmazonOpsScoring" displayName="AmazonOpsScoring" ref="A7:I49" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AmazonOpsScoring" displayName="AmazonOpsScoring" ref="A7:I54" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" name="一级模块"/>
     <tableColumn id="2" name="工作项目"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="D25" s="38" t="inlineStr">
         <is>
-          <t>仅用于负责人已明确具体要求的执行工作。以Campaign为计分单位，每个Campaign每次有效调整计2分。同一次调整包含多种动作（否定词＋Bid＋商品投放）合计只算1次。每个自然周（周一至周日）每个Campaign最多计2次，不同Campaign分别计分。负责人安排和员工主动执行合并统计，多人参与不增加次数。认领变化、关联任务、填写原因并核验。员工自主发起改善按正常积分×主动倍率计算，同一工作不重复计分。</t>
+          <t>适用于负责人安排或员工自主发起、完成有效调整并核验的工作。以Campaign为计分单位，每个Campaign每次有效调整计2分。同一次调整包含多种动作（否定词＋Bid＋商品投放）合计只算1次。每个自然周（周一至周日）每个Campaign最多计2次，不同Campaign分别计分。负责人安排和员工主动执行合并统计，多人参与不增加次数。认领变化、关联任务、填写原因并核验。员工自主发起按正常积分×主动倍率计算，同一工作不重复计分。</t>
         </is>
       </c>
       <c r="E25" s="38" t="inlineStr">
@@ -3304,13 +3304,14 @@
       </c>
       <c r="D42" s="38" t="inlineStr">
         <is>
-          <t>按目标站点计分，每个目标站点视为一个独立上架执行。执行标准与US站Listing创建一致。与US站同一商品的首次Listing创建不重复计分。</t>
+          <t>按目标站点计分，每个目标站点视为一个独立上架执行组。执行标准与US站Listing创建一致（含基础分和难度系数）。不同站点分别计分；同一目标站点的同一次上架，只选一个上架项目计分。</t>
         </is>
       </c>
       <c r="E42" s="38" t="inlineStr">
         <is>
-          <t>每个目标站点的一个上架执行组：5分。
-执行标准与US站Listing创建一致。</t>
+          <t>按目标站点分别计算上架执行组，与US站相同规则：
+1个SKU：5分；2个及以上可共用上架表：8分。
+各站点独立计分，再乘难度系数。</t>
         </is>
       </c>
       <c r="F42" s="38" t="inlineStr">
@@ -3320,7 +3321,7 @@
       </c>
       <c r="G42" s="38" t="inlineStr">
         <is>
-          <t>按US站Listing创建标准验收。目标站点Listing创建结果核验完成。</t>
+          <t>按US站Listing创建标准验收。目标站点Listing创建结果核验完成。不同站点分别计分。</t>
         </is>
       </c>
     </row>
@@ -3342,13 +3343,14 @@
       </c>
       <c r="D43" s="38" t="inlineStr">
         <is>
-          <t>与全新制作A+（10分/份）区分：本项为已有A+的翻译发布。同一批翻译发布拆文件、重复提交不增加批次。</t>
+          <t>与全新制作A+（10分/份）区分：本项为已有A+的翻译发布。同一次安排、同一份原A+内容为一批，不按站点数量或SKU数量累加。不同原A+内容分别计分。同一批翻译发布拆文件、重复提交不增加批次。</t>
         </is>
       </c>
       <c r="E43" s="38" t="inlineStr">
         <is>
           <t>每批翻译后发布：2分。
-同一批多个SKU的A+合计2分/批。</t>
+同一次安排、同一份原A+内容为一批；
+不同原A+内容分别计分。</t>
         </is>
       </c>
       <c r="F43" s="38" t="inlineStr">
@@ -6119,7 +6121,7 @@
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>尚未实施也可认定本层；只指出问题、无可执行建议，或未获确认采纳的，暂不认定。</t>
+          <t>尚未实施也可认定本层；只指出问题、无可执行建议，或未获确认采纳的，暂不认定。认定为"有效发现"只确认主动来源，不代表可以结算；完成对应工作及必要核验后，才按倍率计分。</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6668,7 @@
     <row r="33" ht="78" customHeight="1" s="39">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>同案只取最高档</t>
+          <t>同一任务不重复计分</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
@@ -6676,7 +6678,7 @@
       </c>
       <c r="C33" s="27" t="inlineStr">
         <is>
-          <t>取最高档</t>
+          <t>不重复</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
@@ -6725,7 +6727,7 @@
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>按实际发现、分析、执行、协调及验证贡献，在案例总分内分配个人份额。</t>
+          <t>按实际发现、分析、执行、协调及验证贡献，在该任务最终积分内分配个人份额。</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -6740,7 +6742,7 @@
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>参与者分数之和不得超过该案例档位分；升级后只分配新增差额，保留原已认定贡献。</t>
+          <t>参与者分数之和不得超过该任务最终积分；后续追加人员只分配新增工作量对应的份额，保留原已认定贡献。</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8915,7 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>1</v>
@@ -8924,12 +8926,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>3×2＝6分</t>
+          <t>同一份同一轮合计2分</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>同一份同一轮最高10分。</t>
+          <t>不按模块数量累加</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -9314,12 +9316,12 @@
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t>同模块多处修改只计2分</t>
+          <t>同模块多处修改计入本轮2分</t>
         </is>
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>同一轮反复修改合并计分</t>
+          <t>同一份同一轮合计2分，不按模块数量累加</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr"/>
@@ -9336,7 +9338,7 @@
         </is>
       </c>
       <c r="C101" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D101" s="0" t="n">
         <v>1</v>
@@ -9347,12 +9349,12 @@
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t>2个模块×2分</t>
+          <t>同一份同一轮合计2分</t>
         </is>
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>同份同轮最高10分</t>
+          <t>不按模块数量累加</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr"/>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -10682,7 +10682,7 @@
       </c>
       <c r="H154" s="56" t="inlineStr">
         <is>
-          <t>复制已有Campaign结构不适用×2</t>
+          <t>仅复制、没有独立投放分析和测试目标，不适用×2；复用结构本身不影响认定。完成创建及复盘后结算。</t>
         </is>
       </c>
     </row>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -4695,7 +4695,7 @@
       </c>
       <c r="H31" s="60" t="inlineStr">
         <is>
-          <t>涵盖关键词与搜索词调整、否定投放调整、广告产品归组与补充、ASIN与商品投放调整、Bid与投放位置调整。同一次调整包含多种动作合计只算1次，可关联多条Ads Change。第二次计分须有第一次调整后的复查依据或新问题依据，并实际完成新的调整；拆分操作、重复提交、修复本人错误不另算。同一广告账户、同一站点、同一Campaign，每自然周最多计2次；负责人安排和员工主动执行合并统计，多人参与不增加次数。主动倍率×1。</t>
+          <t>涵盖关键词与搜索词调整、否定投放调整、广告产品归组与补充、ASIN与商品投放调整、Bid与投放位置调整。同一次调整包含多种动作合计只算1次，可关联多条Ads Change。第二次计分须有第一次调整后的复查依据或新问题依据，并实际完成新的调整；拆分操作、重复提交、修复本人错误不另算。同一广告账户、同一站点、同一Campaign，每自然周最多计2次；负责人安排和员工主动执行合并统计，多人参与不增加次数。主动倍率×1。每周次数按实际调整日期归属，积分按验收月份结算。</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H51" s="60" t="inlineStr">
         <is>
-          <t>固定例行工作，主动倍率×1。完成统计数据整理及竞品对比后验收。同一关键词同月不重复计分。</t>
+          <t>固定例行工作，主动倍率×1。完成统计数据整理及竞品对比后验收。同一关键词同月不重复计分。验收须固定站点、关键词范围和采集口径，以可复核的计算分母为准。</t>
         </is>
       </c>
       <c r="I51" s="2" t="n"/>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>参与者分数之和不得超过该任务最终积分；后续追加人员只分配新增工作量对应的份额，保留原已认定贡献。</t>
+          <t>同一任务增加参与人员不增加总积分；各参与者分数之和不得超过该任务最终积分。每人须有独立可验收的工作产出，仅协助或旁观不计分。后续追加人员只分配新增工作量对应的份额，保留原已认定贡献。</t>
         </is>
       </c>
     </row>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -865,7 +865,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1036,6 +1036,12 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1376,7 +1382,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmazonOpsWorkOptimized" displayName="AmazonOpsWorkOptimized" ref="A1:G44" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmazonOpsWorkOptimized" displayName="AmazonOpsWorkOptimized" ref="A1:G47" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="一级模块"/>
     <tableColumn id="2" name="二级模块"/>
@@ -1417,7 +1423,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AmazonOpsScoring" displayName="AmazonOpsScoring" ref="A7:I54" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AmazonOpsScoring" displayName="AmazonOpsScoring" ref="A7:I57" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" name="一级模块"/>
     <tableColumn id="2" name="工作项目"/>
@@ -3403,31 +3409,115 @@
       </c>
     </row>
     <row r="45" ht="14.6" customHeight="1" s="39">
-      <c r="A45" s="37" t="n"/>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="38" t="n"/>
-      <c r="E45" s="38" t="n"/>
-      <c r="F45" s="38" t="n"/>
-      <c r="G45" s="38" t="n"/>
+      <c r="A45" s="72" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B45" s="60" t="inlineStr">
+        <is>
+          <t>市场调研报告</t>
+        </is>
+      </c>
+      <c r="C45" s="60" t="inlineStr">
+        <is>
+          <t>竞品分析、关键词与搜索量、市场容量初判、利润空间测算。调研阶段利润可用估算值。</t>
+        </is>
+      </c>
+      <c r="D45" s="60" t="inlineStr">
+        <is>
+          <t>验收重点是内容是否足以支持选品判断，不硬性要求竞品条数或供应商数量。员工主动提出选品方向并获批后完成，开发阶段按×1.5计算；同一份不重复计分。</t>
+        </is>
+      </c>
+      <c r="E45" s="60" t="inlineStr">
+        <is>
+          <t>每份调研报告：5分。</t>
+        </is>
+      </c>
+      <c r="F45" s="60" t="inlineStr">
+        <is>
+          <t>调研报告文档、数据来源及结论记录。</t>
+        </is>
+      </c>
+      <c r="G45" s="60" t="inlineStr">
+        <is>
+          <t>调研报告完整提交并核验。利润测算拿到报价后须更新。</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="14.6" customHeight="1" s="39">
-      <c r="A46" s="37" t="n"/>
-      <c r="B46" s="7" t="n"/>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="38" t="n"/>
-      <c r="E46" s="38" t="n"/>
-      <c r="F46" s="38" t="n"/>
-      <c r="G46" s="38" t="n"/>
+      <c r="A46" s="72" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B46" s="60" t="inlineStr">
+        <is>
+          <t>供应商开发</t>
+        </is>
+      </c>
+      <c r="C46" s="60" t="inlineStr">
+        <is>
+          <t>寻找供应商、询价比价、确认合作条件（价格、MOQ、交期）。</t>
+        </is>
+      </c>
+      <c r="D46" s="60" t="inlineStr">
+        <is>
+          <t>不硬性要求供应商数量，验收看比价信息是否足以支持决策。样品采购、交接已包含在开发任务中，不叠加运营表中的相同协调分。</t>
+        </is>
+      </c>
+      <c r="E46" s="60" t="inlineStr">
+        <is>
+          <t>每个产品的供应商开发：5分。</t>
+        </is>
+      </c>
+      <c r="F46" s="60" t="inlineStr">
+        <is>
+          <t>供应商信息、报价对比、合作条件确认记录。</t>
+        </is>
+      </c>
+      <c r="G46" s="60" t="inlineStr">
+        <is>
+          <t>比价信息和合作条件确认完成。</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="14.6" customHeight="1" s="39">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
+      <c r="A47" s="73" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B47" s="73" t="inlineStr">
+        <is>
+          <t>样品验证</t>
+        </is>
+      </c>
+      <c r="C47" s="73" t="inlineStr">
+        <is>
+          <t>样品评估、外观与功能检查、与竞品对比、问题记录与反馈。</t>
+        </is>
+      </c>
+      <c r="D47" s="73" t="inlineStr">
+        <is>
+          <t>同一轮验证中的催办、补测和针对原问题的修改，合并计分。新增独立验证范围经确认后另建任务。样品采购交接已含在开发任务中，不叠加。</t>
+        </is>
+      </c>
+      <c r="E47" s="73" t="inlineStr">
+        <is>
+          <t>每轮样品验证：5分。</t>
+        </is>
+      </c>
+      <c r="F47" s="73" t="inlineStr">
+        <is>
+          <t>样品评估报告、检测记录、问题反馈记录。</t>
+        </is>
+      </c>
+      <c r="G47" s="73" t="inlineStr">
+        <is>
+          <t>样品评估完成，问题记录并反馈。同一轮合并计分。</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="14.6" customHeight="1" s="39">
       <c r="A48" s="2" t="n"/>
@@ -3493,7 +3583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
     <col width="18" customWidth="1" style="30" min="1" max="1"/>
@@ -5567,46 +5657,122 @@
       <c r="I54" s="2" t="n"/>
     </row>
     <row r="55" ht="14.6" customHeight="1" s="39">
-      <c r="A55" s="7" t="n"/>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="40" t="n"/>
-      <c r="D55" s="40" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="41">
+      <c r="A55" s="60" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B55" s="60" t="inlineStr">
+        <is>
+          <t>市场调研报告</t>
+        </is>
+      </c>
+      <c r="C55" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="60" t="inlineStr">
+        <is>
+          <t>每份调研报告：5分。
+覆盖竞品分析、关键词与搜索量、市场容量初判、利润空间测算。
+调研阶段利润可用估算值，拿到供应商报价后须更新。</t>
+        </is>
+      </c>
+      <c r="F55" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；后续如需按品类定制档位，另行制定。</t>
+        </is>
+      </c>
+      <c r="G55" s="63">
         <f>ROUND(C55*D55,1)</f>
         <v/>
       </c>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="2" t="n"/>
+      <c r="H55" s="60" t="inlineStr">
+        <is>
+          <t>验收重点是调研内容是否足以支持选品判断，不硬性要求竞品条数或供应商数量。利润测算在调研阶段可以采用估算，拿到报价后更新为实际数据。员工主动提出选品方向并获批后完成本报告，开发阶段任务按主动倍率×1.5计算；同一份分析不能既算选品提案又算市场调研，只计一次。后续Listing、A+、广告等按各自任务规则计分，不因产品最初由主动提出而自动享受倍率。</t>
+        </is>
+      </c>
+      <c r="I55" s="73" t="n"/>
     </row>
     <row r="56" ht="14.6" customHeight="1" s="39">
-      <c r="A56" s="7" t="n"/>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="40" t="n"/>
-      <c r="D56" s="40" t="n"/>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
-      <c r="G56" s="41">
+      <c r="A56" s="60" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B56" s="60" t="inlineStr">
+        <is>
+          <t>供应商开发</t>
+        </is>
+      </c>
+      <c r="C56" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="60" t="inlineStr">
+        <is>
+          <t>每个产品的供应商开发：5分。
+含寻找供应商、询价比价、确认合作条件（价格、MOQ、交期）。</t>
+        </is>
+      </c>
+      <c r="F56" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；后续如需按品类定制档位，另行制定。</t>
+        </is>
+      </c>
+      <c r="G56" s="63">
         <f>ROUND(C56*D56,1)</f>
         <v/>
       </c>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="2" t="n"/>
+      <c r="H56" s="60" t="inlineStr">
+        <is>
+          <t>不硬性要求供应商数量，验收重点是比价信息是否足以支持决策。有些产品合格供应商少，不能为凑数提交无效报价。供应商开发与样品验证分别计分；样品采购、交接等环节已包含在本项及样品验证中，不再叠加运营表中的相同协调分。</t>
+        </is>
+      </c>
+      <c r="I56" s="73" t="n"/>
     </row>
     <row r="57" ht="14.6" customHeight="1" s="39">
-      <c r="A57" s="7" t="n"/>
-      <c r="B57" s="7" t="n"/>
-      <c r="C57" s="40" t="n"/>
-      <c r="D57" s="40" t="n"/>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="41">
+      <c r="A57" s="60" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B57" s="60" t="inlineStr">
+        <is>
+          <t>样品验证</t>
+        </is>
+      </c>
+      <c r="C57" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="60" t="inlineStr">
+        <is>
+          <t>每轮样品验证：5分。
+含样品评估、外观与功能检查、与竞品实物对比、问题记录与反馈。</t>
+        </is>
+      </c>
+      <c r="F57" s="60" t="inlineStr">
+        <is>
+          <t>固定1.0；后续如需按品类定制档位，另行制定。</t>
+        </is>
+      </c>
+      <c r="G57" s="63">
         <f>ROUND(C57*D57,1)</f>
         <v/>
       </c>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="2" t="n"/>
+      <c r="H57" s="60" t="inlineStr">
+        <is>
+          <t>同一轮验证中的催办、补测和针对原问题的修改，合并计分，不按每次修改重复领取5分。新增独立验证范围（如新功能版本、完全不同规格），经确认后另建任务，按新一轮计分。样品采购、交接等若已包含在供应商开发任务中，不再叠加。</t>
+        </is>
+      </c>
+      <c r="I57" s="73" t="n"/>
     </row>
     <row r="58" ht="14.6" customHeight="1" s="39">
       <c r="A58" s="7" t="n"/>
@@ -5847,40 +6013,41 @@
       <c r="H71" s="64" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="55" t="inlineStr">
-        <is>
-          <t>固定例行工作</t>
-        </is>
-      </c>
-      <c r="B72" s="56" t="inlineStr">
-        <is>
-          <t>VOC数据更新与AI分析、Category Report下载、关键词市场占有率统计及竞品检查、A+翻译后发布、翻译后批量更新Listing文案</t>
-        </is>
-      </c>
-      <c r="C72" s="64" t="n"/>
-      <c r="D72" s="58" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="E72" s="56" t="inlineStr">
-        <is>
-          <t>固定周期或已有内容的翻译发布任务，不享受主动倍率。</t>
-        </is>
-      </c>
-      <c r="F72" s="65" t="n"/>
-      <c r="G72" s="65" t="n"/>
-      <c r="H72" s="64" t="n"/>
+      <c r="A72" s="49" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B72" s="49" t="inlineStr">
+        <is>
+          <t>市场调研报告、供应商开发、样品验证</t>
+        </is>
+      </c>
+      <c r="C72" s="49" t="n"/>
+      <c r="D72" s="49" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E72" s="49" t="inlineStr">
+        <is>
+          <t>员工主动提出选品方向并获批后完成的开发任务，按×1.5计算。仅开发阶段（调研、找厂、样品）适用；后续Listing、A+、广告按各自任务规则，不自动继承倍率。负责人安排的产品按×1计算。</t>
+        </is>
+      </c>
+      <c r="F72" s="49" t="n"/>
+      <c r="G72" s="49" t="n"/>
+      <c r="H72" s="49" t="n"/>
+      <c r="I72" s="49" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="55" t="inlineStr">
         <is>
-          <t>未明确列入的项目</t>
+          <t>固定例行工作</t>
         </is>
       </c>
       <c r="B73" s="56" t="inlineStr">
         <is>
-          <t>（暂按×1，不自行套用高倍率）</t>
+          <t>VOC数据更新与AI分析、Category Report下载、关键词市场占有率统计及竞品检查、A+翻译后发布、翻译后批量更新Listing文案</t>
         </is>
       </c>
       <c r="C73" s="64" t="n"/>
@@ -5891,50 +6058,78 @@
       </c>
       <c r="E73" s="56" t="inlineStr">
         <is>
-          <t>如有争议，由负责人认定适用分类。</t>
+          <t>固定周期或已有内容的翻译发布任务，不享受主动倍率。</t>
         </is>
       </c>
       <c r="F73" s="65" t="n"/>
       <c r="G73" s="65" t="n"/>
       <c r="H73" s="64" t="n"/>
     </row>
-    <row r="75">
-      <c r="A75" s="59" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="55" t="inlineStr">
+        <is>
+          <t>未明确列入的项目</t>
+        </is>
+      </c>
+      <c r="B74" s="56" t="inlineStr">
+        <is>
+          <t>（暂按×1，不自行套用高倍率）</t>
+        </is>
+      </c>
+      <c r="C74" s="64" t="n"/>
+      <c r="D74" s="58" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E74" s="56" t="inlineStr">
+        <is>
+          <t>如有争议，由负责人认定适用分类。</t>
+        </is>
+      </c>
+      <c r="F74" s="65" t="n"/>
+      <c r="G74" s="65" t="n"/>
+      <c r="H74" s="64" t="n"/>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="59" t="inlineStr">
         <is>
           <t>边界规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="52" t="inlineStr">
-        <is>
-          <t>① 主动发现后及时登记即可，不要求处理完才申报。提出方案后经负责人批准执行，仍算主动；隐瞒或拖延已知问题不享受倍率。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="52" t="inlineStr">
         <is>
-          <t>② 固定巡检、例行维护、已被安排的任务，以及修复本人错误，不享受主动倍率。</t>
+          <t>① 主动发现后及时登记即可，不要求处理完才申报。提出方案后经负责人批准执行，仍算主动；隐瞒或拖延已知问题不享受倍率。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="52" t="inlineStr">
         <is>
+          <t>② 固定巡检、例行维护、已被安排的任务，以及修复本人错误，不享受主动倍率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="52" t="inlineStr">
+        <is>
           <t>③ 同一工作只计算一次乘倍率后的积分，不再另加正常积分。未完成处理及必要核验的，先保留记录，不提前领取完整积分。</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="59" t="inlineStr">
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="59" t="inlineStr">
         <is>
           <t>广告调整频次限制</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="52" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="52" t="inlineStr">
         <is>
           <t>同一广告账户、同一站点、同一Campaign，每自然周（周一至周日）最多计2次广告调整积分，不区分调整类型。负责人安排和员工主动执行合并统计，多人参与不增加次数。同一次调整可关联多条Ads Change。超出频次的调整仍须执行，但不再计分。
 示例：同一周，Campaign A有效调整2次、B调整1次、C调整3次，分别计 4＋2＋4＝10积分（C的第3次不计分）。</t>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00&quot;元&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="46">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -262,8 +262,13 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="45">
     <fill>
       <patternFill/>
     </fill>
@@ -468,7 +473,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EFF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -783,7 +802,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1036,6 +1055,59 @@
     </xf>
     <xf numFmtId="165" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1342,7 +1414,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmazonOpsWorkOptimized" displayName="AmazonOpsWorkOptimized" ref="A1:G50" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AmazonOpsWorkOptimized" displayName="AmazonOpsWorkOptimized" ref="A1:G59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="一级模块"/>
     <tableColumn id="2" name="二级模块"/>
@@ -1383,7 +1455,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AmazonOpsScoring" displayName="AmazonOpsScoring" ref="A7:I56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AmazonOpsScoring" displayName="AmazonOpsScoring" ref="A7:I65" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" name="一级模块"/>
     <tableColumn id="2" name="工作项目"/>
@@ -1697,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -1709,7 +1781,7 @@
     <col width="65" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1" s="1">
+    <row r="1" ht="32" customHeight="1" s="1">
       <c r="A1" s="57" t="inlineStr">
         <is>
           <t>一级模块</t>
@@ -2333,23 +2405,22 @@
       </c>
       <c r="D17" s="61" t="inlineStr">
         <is>
-          <t>包含售价及运费核查、截图取证、整理材料、开Case及后续跟进。同一任务不按Case数量、重试次数或处理时长增加金额；已包含的改价不另计费。恢复后核验验收；未恢复时提交取证截图、Case编号及最终回复，经负责人确认阶段结案后也计15元。处理中暂不结算，阶段结案后恢复不再重复计费。</t>
+          <t>包含售价及运费核查、截图取证、材料整理、开Case及后续跟进。按站点＋ASIN＋同一异常识别任务，不按SKU、Case、重试次数或处理时长增加金额；已含改价不另计费。每个ASIN须记录处理及核验结果。恢复后核验验收；未恢复时凭证齐全并经负责人确认阶段结案可结算。处理中暂不结算，阶段结案后同一异常恢复不重复计费。本人责任纠错不另计酬，主动任务按适用倍率结算。</t>
         </is>
       </c>
       <c r="E17" s="61" t="inlineStr">
         <is>
-          <t>每个独立Buy Box异常处理任务：15元。
-同站点、同ASIN、同原因的连续异常算一个任务；多个ASIN共用同一套证据与处理过程时合并计费。</t>
+          <t>15元/ASIN（基础金额）。同一站点、同一ASIN、同一原因的连续异常只计一次；同一ASIN对应多个SKU不重复计费。不同ASIN分别计费，即使共用证据或同一个Case，也按实际处理并逐个验收的ASIN数量计算。</t>
         </is>
       </c>
       <c r="F17" s="61" t="inlineStr">
         <is>
-          <t>取证截图、商品及站点标识、Case编号或链接、平台最终回复、Buy Box核验结果；未恢复需附负责人阶段结案确认。</t>
+          <t>按ASIN记录站点、取证截图、Case编号或链接、平台最终回复及Buy Box核验结果；SKU仅作辅助关联。未恢复须附负责人阶段结案确认。</t>
         </is>
       </c>
       <c r="G17" s="61" t="inlineStr">
         <is>
-          <t>工作完成状态与Buy Box结果分开记录。恢复后核验通过，或未恢复但凭证齐全并经负责人确认阶段结案，计15元。仍处理中暂不结算；同一任务累计不超过15元。</t>
+          <t>工作完成状态与Buy Box结果分开记录。每个ASIN恢复后核验通过，或凭证齐全且负责人确认阶段结案后，按15元基础金额及适用倍率结算。同一站点同一ASIN同一异常只计一次；仍处理中暂不结算。</t>
         </is>
       </c>
     </row>
@@ -3596,29 +3667,440 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="13.85000038146973" customHeight="1" s="1">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
-    </row>
-    <row r="52" ht="13.85000038146973" customHeight="1" s="1">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
-    </row>
-    <row r="53" s="1"/>
-    <row r="54" s="1"/>
-    <row r="55" s="1"/>
-    <row r="56" s="1"/>
+    <row r="51" ht="320" customHeight="1" s="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>数据与经营分析</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>利润或亏损原因分析与优化建议</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>核查收入、售价与折扣、采购成本、运输及平台费用、广告、退货损失等相关因素，明确利润口径及对比期间，找出主要变化原因。必须给出有依据的优化建议，说明建议动作、预期作用、优先级及必要验证；不要求建议已执行或利润已改善。</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>按需指派，不设固定频次。完整分析30元；有数据证据但关键判断未核实，经负责人确认按初步成果结案计15元；仅转发报表或AI原文、无证据或无具体建议，退回补充，暂不结算。初步15元后补成完整分析只补15元，同一任务累计基础金额30元。不以篇幅长短判定；关键数据不可得须说明原因，不自动减半。独立分析与后续独立执行分别验收，相同分析若已包含在其他任务中不重复计酬。同一范围及期间的销量、利润和活动分析使用同一交付时只选一项，不按报告名称重复计费。本人责任纠错不另计酬。负责人安排倍率1；自主发起按未明确项目暂为1，不自行套用高倍率。</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>同一站点、一个ASIN、同一次独立利润问题分析：完整30元，初步15元。多个SKU对应同一ASIN不重复计费；多个ASIN共用同一份分析合并，分别独立分析并验收才分别计费。</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>数据来源与期间、利润测算口径、变化拆解、原因证据、优化建议及负责人验收。</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>核实数据，提交原因判断、证据和可执行建议，经负责人按完整或初步档位验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="320" customHeight="1" s="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>数据与经营分析</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>活动效果复盘</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>对比活动前、活动期间及适当的后续期间，核查销量、流量、转化、优惠成本、活动费用、广告投入、利润及库存变化。记录同期价格、断货及其他促销影响，不将销售增长直接等同活动增量。给出继续、调整或停止建议及证据。</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>按需指派，不设固定频次。完整分析30元；有数据证据但关键判断未核实，经负责人确认按初步成果结案计15元；仅转发报表或AI原文、无证据或无具体建议，退回补充，暂不结算。初步15元后补成完整分析只补15元，同一任务累计基础金额30元。不以篇幅长短判定；关键数据不可得须说明原因，不自动减半。独立分析与后续独立执行分别验收，相同分析若已包含在其他任务中不重复计酬。同一范围及期间的销量、利润和活动分析使用同一交付时只选一项，不按报告名称重复计费。本人责任纠错不另计酬。负责人安排倍率1；自主发起按未明确项目暂为1，不自行套用高倍率。</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>同一站点、一个独立Coupon／Promotion／Deal活动、一次完整复盘：30元；初步15元。活动包含多个ASIN仍按一份复盘计费；若同一方案的多个活动共用一份报告，合并计费。</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>活动ID、站点和ASIN范围、对比期间与数据来源、成本收益口径、同期影响因素、分析结论及后续建议。</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>核实数据，提交原因判断、证据和可执行建议，经负责人按完整或初步档位验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="320" customHeight="1" s="1">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>费用与异常处理</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>费用异常核查与Case申诉</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>核对实际收费与对应商品尺寸、重量、适用计费依据或交易记录，整理费用差异及证据，提交Case并跟进回复、补充资料及核验处理结果。适用于商品尺寸重量引起的费用疑问或其他收费异常；不包含普通FBA货件问题。</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>包含异常核查、差额计算、证据整理、Case提交及补充跟进，不另叠加利润分析或Listing异常处理的相同交付。平台是否退款／更正与任务完成分别记录；处理完成并核验，或证据及回复完整且负责人确认阶段结案后计酬。仍处理中暂不结算，同一问题阶段结案后恢复或到账不重复计费。不以退款金额或催办次数加价。本人责任纠错不另计酬。负责人安排倍率1；主动发现并完成处理，按异常处理主动倍率1.5，即30元。</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>20元/独立费用问题（含核查、证据整理、开Case及跟进）。同站点、同类收费原因且共用证据与处理过程的对象合并；不按ASIN、SKU、收费记录或Case数量累加。</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>费用类型、涉及商品或交易、实际收费及依据、证据、Case编号、最终回复、费用更正／退款核验或负责人阶段结案记录。</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>处理结果核验完成，或凭证齐全且负责人确认阶段结案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="360" customHeight="1" s="1">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>品牌保护</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>跟卖监控</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>按要求检查指定ASIN的其他报价及卖家变化，记录时间、ASIN、卖家标识、价格及可获得证据，发现疑似异常及时报告。</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>固定监控倍率1；程序自动监控且无需人工核验不计人工任务金额。未发现异常但完成约定核验仍可验收。监控记录与后续独立取证投诉可分别计费，同一发现不额外领取发现费。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>5元/站点/约定监控清单/自然周。按完成的约定检查次数÷应检查次数折算；当周无任务为0。不得拆清单提高金额。</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>清单、应查及实查记录、异常及通知记录。</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>按周验收，无异常也可完成；本周全部检查完成5元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="360" customHeight="1" s="1">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>品牌保护</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>跟卖取证与举报／Case处理</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>核实疑似违规；确需Test Buy时经负责人确认采购及预算，跟进收货、保留订单与实物照片并核对差异。依据证据选择亚马逊举报、Case或Brand Registry适用渠道，跟进处理及报价状态。</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>站点＋被举报卖家＋同一违规事实及共用证据为案件范围；多ASIN共用证据处理时合并，多渠道或多Case不累加。存在其他报价不等于违规；不以未获品牌授权直接认定假货，不提交无依据投诉。下架后核验，或调查及跟进完整、负责人确认阶段结案后计酬；未下架不自动判定未完成。Test Buy未发现违规时提交证据与不投诉结论，可按实际取证范围由负责人结案，确已完成完整Test Buy调查可计50元。样品购买不叠加样品备货协调分；同一交付不叠加Buy Box或Listing申诉。主动发现并完成案件处理倍率1.5；仅例行监控后按既定职责处理，按正常履职确认来源。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>已有有效证据，完成核查、举报／Case及跟进：30元/独立案件；另需完成Test Buy取证全过程：整案50元。两档只取最高，先结30元后补足最多20元。</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>案件编号、卖家及ASIN、订单/收货证据、差异判断、投诉依据、Case与回复、状态核验及结案确认。</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>多渠道反复投诉仍30元；独立完成Test Buy取证及案件处理50元。实际货款运费另行处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="360" customHeight="1" s="1">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>品牌项目</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>Vine报名与跟进</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>核对参与资格、商品、库存、报名数量及费用，按确认方案报名，核验提交结果并记录约定跟进节点的领取和评论状态。</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>首次资格核查、报名、常规修正和约定节点跟进合并15元；派单时约定验收节点，不逐周重复收费。不以好评、星级或评论必然产生作为验收条件，不要求员工干预评论。平台报名费及赠送商品成本不含任务金额。早期评论人计划已停止，不设该项目任务。自主发起仍按未明确项目倍率1，后续另定不自动套高倍率。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>15元/独立Vine报名项目。以后台报名记录去重，不按子SKU、领取件数或评论数量累加。</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>报名ID、商品范围、费用确认、报名结果、约定节点状态及负责人验收。</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>一个报名项目覆盖多个子SKU：15元；同一报名重复查看或修改不新增报酬。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="360" customHeight="1" s="1">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>品牌内容</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story品牌故事制作与维护</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>构思品牌故事、文案及图片要求，协调制作，设置卡片和链接、提交并核验；或按确认范围修改现有内容、维护ASIN绑定。</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>新建75元含策划、制作跟进、发布及首次绑定；同一内容多ASIN共用只计一次。局部修改不按卡片数量累加。新建或重做不叠加局部修改；同一份内容不再领取A+制作/修改或相同素材图片策划金额。不同的产品A+与品牌故事确有独立交付时可分别验收。自主实质重做有证据方案且完成复盘适用内容重写倍率2；自主局部维护或绑定倍率1.5；首次制作按发布核验，后续优化按复盘规则。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>全新策划或完全重做：75元/独立内容；局部修改：10元/同份同轮；仅为已有内容新增绑定：5元/ASIN。</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>内容ID、方案/修改前后记录、素材、链接及绑定范围、发布核验；优化另附原因和复盘。</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>同份品牌故事应用20个ASIN，新建合计75元；后续独立绑定3个ASIN计15元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="360" customHeight="1" s="1">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>订阅销售</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>Subscribe &amp; Save设置与管理</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>核对后台可参与商品及资格，按负责人确认方案加入或退出商品、设置或调整订阅优惠，并核验参与状态、折扣及生效情况。</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>不按SKU、订阅订单或设置次数累加；不把平台自动加入、自动折扣或无需人工的变化当作任务。默认按确认方案执行；员工主动发现独立机会并完成，经认定可按促销执行倍率1.5。设置已含的参数修正不另计，不与同一价格或促销交付重复计费。不以产生订阅订单作为执行验收条件。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>同次安排、同站点、同一订阅方案的一批设置或更新：10元。包含多个ASIN或多个调整动作仍计一次。</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>方案与费用/折扣确认、商品清单、修改记录和状态核验。</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>同批10个ASIN加入并设折扣：10元；主动任务符合1.5倍时15元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="360" customHeight="1" s="1">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>组合销售</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle创建与维护</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>核对后台资格及组成商品，按确认组合填写文案、图片、价格等可编辑资料，创建并核验；维护时按后台实际允许的字段更新及核验。</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>新建包含初始配置、提交、常规报错修正及核验，不再叠加普通Listing创建、初始文案填入或图片上传。需要独立原创内容或素材策划且不属创建中已有资料改写时，按对应独立交付验收，相同工作只计一次。FBA虚拟组合不计重新包装或实物发货任务。不得通过重复建立相同组合、删后重建或拆分任务增加金额；后台不允许编辑的组成变更须先确认方案。主动专项倍率暂按未明确项目1。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>新建：25元/独立虚拟捆绑商品；已有捆绑同轮内容或可编辑设置维护：10元/个。</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>捆绑ID、组成ASIN、价格及方案确认、内容记录、创建或更新结果核验。</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>新建1个虚拟组合25元；同组合本轮改标题和价格合计10元；新建时这些初始配置不另加10元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1" s="1">
+      <c r="A61" s="116" t="inlineStr">
+        <is>
+          <t>项目状态与规则来源（核对日期2026-09-08；参与资格以目标站点后台为准，任务金额为内部建议，并非亚马逊收费标准）。早期评论人计划已停止，仅保留Vine。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="65" customHeight="1" s="1">
+      <c r="A62" s="116" t="inlineStr">
+        <is>
+          <t>早期评论人计划停止公告</t>
+        </is>
+      </c>
+      <c r="B62" s="116" t="inlineStr">
+        <is>
+          <t>https://sellercentral.amazon.com/seller-forums/discussions/t/2bb2eaeec50cbc448f676c1a6f000ff9</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="65" customHeight="1" s="1">
+      <c r="A63" s="116" t="inlineStr">
+        <is>
+          <t>Vine</t>
+        </is>
+      </c>
+      <c r="B63" s="116" t="inlineStr">
+        <is>
+          <t>https://sell.amazon.com/programs/vine</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="65" customHeight="1" s="1">
+      <c r="A64" s="116" t="inlineStr">
+        <is>
+          <t>Subscribe &amp; Save</t>
+        </is>
+      </c>
+      <c r="B64" s="116" t="inlineStr">
+        <is>
+          <t>https://sell.amazon.com/programs/subscribe-and-save/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="65" customHeight="1" s="1">
+      <c r="A65" s="116" t="inlineStr">
+        <is>
+          <t>Virtual Bundles</t>
+        </is>
+      </c>
+      <c r="B65" s="116" t="inlineStr">
+        <is>
+          <t>https://sell.amazon.com/blog/product-bundling</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="65" customHeight="1" s="1">
+      <c r="A66" s="116" t="inlineStr">
+        <is>
+          <t>品牌故事</t>
+        </is>
+      </c>
+      <c r="B66" s="116" t="inlineStr">
+        <is>
+          <t>https://sell.amazon.com/tools/a-content</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="65" customHeight="1" s="1">
+      <c r="A67" s="116" t="inlineStr">
+        <is>
+          <t>品牌保护与Test Buy</t>
+        </is>
+      </c>
+      <c r="B67" s="116" t="inlineStr">
+        <is>
+          <t>https://sell.amazon.com/brand-registry/project-zero/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="65" customHeight="1" s="1">
+      <c r="A68" s="116" t="inlineStr">
+        <is>
+          <t>正品转售说明</t>
+        </is>
+      </c>
+      <c r="B68" s="116" t="inlineStr">
+        <is>
+          <t>https://sell.amazon.com/blog/sell-branded-products-on-amazon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A61:G61"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3633,7 +4115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.35000038146973"/>
   <cols>
     <col width="18" customWidth="1" style="42" min="1" max="1"/>
@@ -3704,7 +4186,7 @@
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
-          <t>任务金额＝累计基础金额×难度系数×适用主动倍率，保留2位小数；每项任务只结算一次。月度任务绩效＝OA已验收任务金额＋Streamlit已验收主动任务金额＋当月核定成果奖励。同一任务跨两处记录须去重。成果奖按“改善成果奖励”页结算，不乘难度或主动倍率。</t>
+          <t>任务金额＝累计基础金额×难度系数×适用主动倍率，保留2位小数；每项任务只结算一次。月度任务绩效＝OA已验收任务金额＋Streamlit已验收主动任务金额＋当月核定成果奖励。同一任务跨两处记录须去重。成果奖按“改善成果奖励”页结算，不乘难度或主动倍率。 本人责任纠错不另计任务报酬、主动加成或成果奖励；以操作时确认资料和执行记录判定，详见“优化登记与复盘规则”责任纠错部分。</t>
         </is>
       </c>
       <c r="B5" s="43" t="n"/>
@@ -3787,7 +4269,7 @@
           <t>Listing创建</t>
         </is>
       </c>
-      <c r="C8" s="81" t="n">
+      <c r="C8" s="113" t="n">
         <v>25</v>
       </c>
       <c r="D8" s="82" t="n">
@@ -3809,7 +4291,7 @@
 混合独立SKU和变体SKU时，只统计本次需处理关系的父体数</t>
         </is>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="115">
         <f>ROUND(C8*D8,2)</f>
         <v/>
       </c>
@@ -3832,7 +4314,7 @@
           <t>图片上传维护</t>
         </is>
       </c>
-      <c r="C9" s="81" t="n">
+      <c r="C9" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D9" s="82" t="n">
@@ -3851,7 +4333,7 @@
 等待时间长短不增加系数。</t>
         </is>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="115">
         <f>ROUND(C9*D9,2)</f>
         <v/>
       </c>
@@ -3878,7 +4360,7 @@
           <t>样品备货与拍摄协调</t>
         </is>
       </c>
-      <c r="C10" s="81" t="n">
+      <c r="C10" s="113" t="n">
         <v>25</v>
       </c>
       <c r="D10" s="82" t="n">
@@ -3895,7 +4377,7 @@
           <t>固定1.0；每个完整任务25元，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G10" s="83">
+      <c r="G10" s="115">
         <f>ROUND(C10*D10,2)</f>
         <v/>
       </c>
@@ -3922,7 +4404,7 @@
           <t>A+制作发布</t>
         </is>
       </c>
-      <c r="C11" s="81" t="n">
+      <c r="C11" s="113" t="n">
         <v>75</v>
       </c>
       <c r="D11" s="82" t="n">
@@ -3940,7 +4422,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="115">
         <f>ROUND(C11*D11,2)</f>
         <v/>
       </c>
@@ -3966,7 +4448,7 @@
           <t>视频上传与信息维护</t>
         </is>
       </c>
-      <c r="C12" s="81" t="n">
+      <c r="C12" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D12" s="82" t="n">
@@ -3984,7 +4466,7 @@
           <t>固定1.0；按视频及操作类型计费。</t>
         </is>
       </c>
-      <c r="G12" s="83">
+      <c r="G12" s="115">
         <f>ROUND(C12*D12,2)</f>
         <v/>
       </c>
@@ -4013,7 +4495,7 @@
           <t>Listing纠错</t>
         </is>
       </c>
-      <c r="C13" s="81" t="n">
+      <c r="C13" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D13" s="82" t="n">
@@ -4030,7 +4512,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="115">
         <f>ROUND(C13*D13,2)</f>
         <v/>
       </c>
@@ -4057,7 +4539,7 @@
           <t>标题编写与优化</t>
         </is>
       </c>
-      <c r="C14" s="81" t="n">
+      <c r="C14" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="82" t="n">
@@ -4073,7 +4555,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="115">
         <f>ROUND(C14*D14,2)</f>
         <v/>
       </c>
@@ -4100,7 +4582,7 @@
           <t>五点编写与优化</t>
         </is>
       </c>
-      <c r="C15" s="81" t="n">
+      <c r="C15" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D15" s="82" t="n">
@@ -4116,7 +4598,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="115">
         <f>ROUND(C15*D15,2)</f>
         <v/>
       </c>
@@ -4143,7 +4625,7 @@
           <t>描述编写与优化</t>
         </is>
       </c>
-      <c r="C16" s="81" t="n">
+      <c r="C16" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D16" s="82" t="n">
@@ -4159,7 +4641,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="115">
         <f>ROUND(C16*D16,2)</f>
         <v/>
       </c>
@@ -4186,7 +4668,7 @@
           <t>Generic Keywords编写与优化</t>
         </is>
       </c>
-      <c r="C17" s="81" t="n">
+      <c r="C17" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D17" s="82" t="n">
@@ -4202,7 +4684,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="115">
         <f>ROUND(C17*D17,2)</f>
         <v/>
       </c>
@@ -4229,7 +4711,7 @@
           <t>全新制作或完全重做A+</t>
         </is>
       </c>
-      <c r="C18" s="81" t="n">
+      <c r="C18" s="113" t="n">
         <v>75</v>
       </c>
       <c r="D18" s="82" t="n">
@@ -4245,7 +4727,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="115">
         <f>ROUND(C18*D18,2)</f>
         <v/>
       </c>
@@ -4271,7 +4753,7 @@
           <t>A+内容增删修改</t>
         </is>
       </c>
-      <c r="C19" s="81" t="n">
+      <c r="C19" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D19" s="82" t="n">
@@ -4288,7 +4770,7 @@
           <t>固定1.0；按计费单位累计，不另加难度系数。</t>
         </is>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="115">
         <f>ROUND(C19*D19,2)</f>
         <v/>
       </c>
@@ -4316,7 +4798,7 @@
           <t>变体关系维护</t>
         </is>
       </c>
-      <c r="C20" s="81" t="n">
+      <c r="C20" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D20" s="82" t="n">
@@ -4337,7 +4819,7 @@
 基础金额与系数分别选择；系数只取适用最高档。</t>
         </is>
       </c>
-      <c r="G20" s="83">
+      <c r="G20" s="115">
         <f>ROUND(C20*D20,2)</f>
         <v/>
       </c>
@@ -4368,7 +4850,7 @@
           <t>图片维护</t>
         </is>
       </c>
-      <c r="C21" s="81" t="n">
+      <c r="C21" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D21" s="82" t="n">
@@ -4387,7 +4869,7 @@
 等待时间长短不增加系数。</t>
         </is>
       </c>
-      <c r="G21" s="83">
+      <c r="G21" s="115">
         <f>ROUND(C21*D21,2)</f>
         <v/>
       </c>
@@ -4413,7 +4895,7 @@
           <t>价格调整</t>
         </is>
       </c>
-      <c r="C22" s="81" t="n">
+      <c r="C22" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D22" s="82" t="n">
@@ -4430,7 +4912,7 @@
           <t>固定1.0；负责人明确目标价格，员工执行并核验。</t>
         </is>
       </c>
-      <c r="G22" s="83">
+      <c r="G22" s="115">
         <f>ROUND(C22*D22,2)</f>
         <v/>
       </c>
@@ -4456,7 +4938,7 @@
           <t>Buy Box异常处理</t>
         </is>
       </c>
-      <c r="C23" s="81" t="n">
+      <c r="C23" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D23" s="82" t="n">
@@ -4464,30 +4946,31 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>每个独立Buy Box异常处理任务：15元。
-同站点、同ASIN、同原因的连续异常算一个任务；多个ASIN共用同一套证据与处理过程时合并计费。</t>
+          <t>15元/ASIN（基础金额）。同一站点、同一ASIN、同一原因的连续异常只计一次；同一ASIN对应多个SKU不重复计费。不同ASIN分别计费，即使共用证据或同一个Case，也按实际处理并逐个验收的ASIN数量计算。</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>固定1.0；按独立异常任务计费，不按Case数量提高系数。</t>
-        </is>
-      </c>
-      <c r="G23" s="83">
+          <t>固定1.0；按实际处理并验收的ASIN计费，不按SKU或Case数量提高系数。</t>
+        </is>
+      </c>
+      <c r="G23" s="115">
         <f>ROUND(C23*D23,2)</f>
         <v/>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>包含售价及运费核查、截图取证、整理材料、开Case及后续跟进。同一任务不按Case数量、重试次数或处理时长增加金额；已包含的改价不另计费。恢复后核验验收；未恢复时提交取证截图、Case编号及最终回复，经负责人确认阶段结案后也计15元。处理中暂不结算，阶段结案后恢复不再重复计费。</t>
+          <t>包含售价及运费核查、截图取证、材料整理、开Case及后续跟进。按站点＋ASIN＋同一异常识别任务，不按SKU、Case、重试次数或处理时长增加金额；已含改价不另计费。每个ASIN须记录处理及核验结果。恢复后核验验收；未恢复时凭证齐全并经负责人确认阶段结案可结算。处理中暂不结算，阶段结案后同一异常恢复不重复计费。本人责任纠错不另计酬，主动任务按适用倍率结算。</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>1个Case后恢复并核验：15元。
-多个Case后恢复：仍为15元。
-未恢复，凭证齐全且负责人确认阶段结案：15元。
-未结案仍在处理中：暂不结算。</t>
+          <t>以下均为负责人安排、倍率1的示例：
+同站点1个ASIN对应3个SKU：15元。
+同站点3个ASIN共用1个Case且均验收：45元。
+30个ASIN均验收：450元。
+同一ASIN同一异常多次开Case：仍为15元。
+未恢复但确认阶段结案可计费，仍处理中暂不结算。</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4985,7 @@
           <t>主动价格优化（说明项，不独立计费）</t>
         </is>
       </c>
-      <c r="C24" s="81" t="n">
+      <c r="C24" s="113" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="82" t="n">
@@ -4520,7 +5003,7 @@
 难度按关联主任务的等级选择</t>
         </is>
       </c>
-      <c r="G24" s="83">
+      <c r="G24" s="115">
         <f>ROUND(C24*D24,2)</f>
         <v/>
       </c>
@@ -4542,7 +5025,7 @@
           <t>Coupon与Promotion创建</t>
         </is>
       </c>
-      <c r="C25" s="81" t="n">
+      <c r="C25" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D25" s="82" t="n">
@@ -4559,7 +5042,7 @@
           <t>固定1.0；负责人明确优惠方案，员工执行并核验。</t>
         </is>
       </c>
-      <c r="G25" s="83">
+      <c r="G25" s="115">
         <f>ROUND(C25*D25,2)</f>
         <v/>
       </c>
@@ -4587,7 +5070,7 @@
           <t>Deal活动提报</t>
         </is>
       </c>
-      <c r="C26" s="81" t="n">
+      <c r="C26" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D26" s="82" t="n">
@@ -4604,7 +5087,7 @@
           <t>固定1.0；按独立Deal数量计费。</t>
         </is>
       </c>
-      <c r="G26" s="83">
+      <c r="G26" s="115">
         <f>ROUND(C26*D26,2)</f>
         <v/>
       </c>
@@ -4632,7 +5115,7 @@
           <t>SP广告创建</t>
         </is>
       </c>
-      <c r="C27" s="81" t="n">
+      <c r="C27" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D27" s="82" t="n">
@@ -4649,7 +5132,7 @@
           <t>固定1.0；按实际独立Campaign数量计费。</t>
         </is>
       </c>
-      <c r="G27" s="83">
+      <c r="G27" s="115">
         <f>ROUND(C27*D27,2)</f>
         <v/>
       </c>
@@ -4677,7 +5160,7 @@
           <t>SB广告创建</t>
         </is>
       </c>
-      <c r="C28" s="81" t="n">
+      <c r="C28" s="113" t="n">
         <v>20</v>
       </c>
       <c r="D28" s="82" t="n">
@@ -4694,7 +5177,7 @@
           <t>固定1.0；按实际独立Campaign数量计费。</t>
         </is>
       </c>
-      <c r="G28" s="83">
+      <c r="G28" s="115">
         <f>ROUND(C28*D28,2)</f>
         <v/>
       </c>
@@ -4722,7 +5205,7 @@
           <t>SBV广告创建</t>
         </is>
       </c>
-      <c r="C29" s="81" t="n">
+      <c r="C29" s="113" t="n">
         <v>20</v>
       </c>
       <c r="D29" s="82" t="n">
@@ -4739,7 +5222,7 @@
           <t>固定1.0；按实际独立Campaign数量计费。</t>
         </is>
       </c>
-      <c r="G29" s="83">
+      <c r="G29" s="115">
         <f>ROUND(C29*D29,2)</f>
         <v/>
       </c>
@@ -4767,7 +5250,7 @@
           <t>SD广告创建</t>
         </is>
       </c>
-      <c r="C30" s="81" t="n">
+      <c r="C30" s="113" t="n">
         <v>20</v>
       </c>
       <c r="D30" s="82" t="n">
@@ -4784,7 +5267,7 @@
           <t>固定1.0；按实际独立Campaign数量计费。</t>
         </is>
       </c>
-      <c r="G30" s="83">
+      <c r="G30" s="115">
         <f>ROUND(C30*D30,2)</f>
         <v/>
       </c>
@@ -4859,7 +5342,7 @@
           <t>Listing异常申诉与Case处理</t>
         </is>
       </c>
-      <c r="C32" s="81" t="n">
+      <c r="C32" s="113" t="n">
         <v>20</v>
       </c>
       <c r="D32" s="82" t="n">
@@ -4877,7 +5360,7 @@
           <t>固定1.0；按ASIN及独立异常计费，不按Case数量或处理次数增加系数。</t>
         </is>
       </c>
-      <c r="G32" s="83">
+      <c r="G32" s="115">
         <f>ROUND(C32*D32,2)</f>
         <v/>
       </c>
@@ -4905,7 +5388,7 @@
           <t>二级类目商品维护</t>
         </is>
       </c>
-      <c r="C33" s="81" t="n">
+      <c r="C33" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D33" s="82" t="n">
@@ -4922,7 +5405,7 @@
           <t>固定1.0；按实际更新的二级类目数量计费。</t>
         </is>
       </c>
-      <c r="G33" s="83">
+      <c r="G33" s="115">
         <f>ROUND(C33*D33,2)</f>
         <v/>
       </c>
@@ -4949,7 +5432,7 @@
           <t>二级类目模块新增或重建</t>
         </is>
       </c>
-      <c r="C34" s="81" t="n">
+      <c r="C34" s="113" t="n">
         <v>25</v>
       </c>
       <c r="D34" s="82" t="n">
@@ -4966,7 +5449,7 @@
           <t>固定1.0；按实际调整的二级类目数量计费。</t>
         </is>
       </c>
-      <c r="G34" s="83">
+      <c r="G34" s="115">
         <f>ROUND(C34*D34,2)</f>
         <v/>
       </c>
@@ -4993,7 +5476,7 @@
           <t>提交阻断问题处理</t>
         </is>
       </c>
-      <c r="C35" s="81" t="n">
+      <c r="C35" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D35" s="82" t="n">
@@ -5010,7 +5493,7 @@
           <t>固定1.0；同次提交多个报错合并计费。</t>
         </is>
       </c>
-      <c r="G35" s="83">
+      <c r="G35" s="115">
         <f>ROUND(C35*D35,2)</f>
         <v/>
       </c>
@@ -5037,7 +5520,7 @@
           <t>VOC数据更新与AI分析</t>
         </is>
       </c>
-      <c r="C36" s="81" t="n">
+      <c r="C36" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D36" s="82" t="n">
@@ -5053,7 +5536,7 @@
           <t>固定1.0；按每周完整任务计费。</t>
         </is>
       </c>
-      <c r="G36" s="83">
+      <c r="G36" s="115">
         <f>ROUND(C36*D36,2)</f>
         <v/>
       </c>
@@ -5080,7 +5563,7 @@
           <t>Listing问题处理</t>
         </is>
       </c>
-      <c r="C37" s="81" t="n">
+      <c r="C37" s="113" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="82" t="n">
@@ -5099,7 +5582,7 @@
 难度按关联主任务的等级选择</t>
         </is>
       </c>
-      <c r="G37" s="83">
+      <c r="G37" s="115">
         <f>ROUND(C37*D37,2)</f>
         <v/>
       </c>
@@ -5121,7 +5604,7 @@
           <t>产品质量问题反馈</t>
         </is>
       </c>
-      <c r="C38" s="81" t="n">
+      <c r="C38" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D38" s="82" t="n">
@@ -5143,7 +5626,7 @@
 1.6：跨产品证据相互矛盾，需系统梳理及协调验证结论。</t>
         </is>
       </c>
-      <c r="G38" s="83">
+      <c r="G38" s="115">
         <f>ROUND(C38*D38,2)</f>
         <v/>
       </c>
@@ -5165,7 +5648,7 @@
           <t>FBA货件问题处理</t>
         </is>
       </c>
-      <c r="C39" s="81" t="n">
+      <c r="C39" s="113" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="82" t="n">
@@ -5181,7 +5664,7 @@
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G39" s="83">
+      <c r="G39" s="115">
         <f>ROUND(C39*D39,2)</f>
         <v/>
       </c>
@@ -5207,7 +5690,7 @@
           <t>库存冗余折扣上传</t>
         </is>
       </c>
-      <c r="C40" s="81" t="n">
+      <c r="C40" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D40" s="82" t="n">
@@ -5223,7 +5706,7 @@
           <t>固定1.0；程序提供SKU及折扣方案，员工上传并核验。</t>
         </is>
       </c>
-      <c r="G40" s="83">
+      <c r="G40" s="115">
         <f>ROUND(C40*D40,2)</f>
         <v/>
       </c>
@@ -5249,7 +5732,7 @@
           <t>滞留库存—移除库存</t>
         </is>
       </c>
-      <c r="C41" s="81" t="n">
+      <c r="C41" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D41" s="82" t="n">
@@ -5265,7 +5748,7 @@
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G41" s="83">
+      <c r="G41" s="115">
         <f>ROUND(C41*D41,2)</f>
         <v/>
       </c>
@@ -5292,7 +5775,7 @@
           <t>滞留库存—Relist重新发布</t>
         </is>
       </c>
-      <c r="C42" s="81" t="n">
+      <c r="C42" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D42" s="82" t="n">
@@ -5308,7 +5791,7 @@
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G42" s="83">
+      <c r="G42" s="115">
         <f>ROUND(C42*D42,2)</f>
         <v/>
       </c>
@@ -5335,7 +5818,7 @@
           <t>滞留库存—申诉或Case处理</t>
         </is>
       </c>
-      <c r="C43" s="81" t="n">
+      <c r="C43" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D43" s="82" t="n">
@@ -5351,7 +5834,7 @@
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G43" s="83">
+      <c r="G43" s="115">
         <f>ROUND(C43*D43,2)</f>
         <v/>
       </c>
@@ -5378,7 +5861,7 @@
           <t>滞留库存—已有电池／化学品资料提交</t>
         </is>
       </c>
-      <c r="C44" s="81" t="n">
+      <c r="C44" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D44" s="82" t="n">
@@ -5394,7 +5877,7 @@
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G44" s="83">
+      <c r="G44" s="115">
         <f>ROUND(C44*D44,2)</f>
         <v/>
       </c>
@@ -5421,7 +5904,7 @@
           <t>滞留库存—电池／化学品资料协调与提交</t>
         </is>
       </c>
-      <c r="C45" s="81" t="n">
+      <c r="C45" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D45" s="82" t="n">
@@ -5437,7 +5920,7 @@
           <t>固定1.0。</t>
         </is>
       </c>
-      <c r="G45" s="83">
+      <c r="G45" s="115">
         <f>ROUND(C45*D45,2)</f>
         <v/>
       </c>
@@ -5464,7 +5947,7 @@
           <t>Category Report下载</t>
         </is>
       </c>
-      <c r="C46" s="81" t="n">
+      <c r="C46" s="113" t="n">
         <v>5</v>
       </c>
       <c r="D46" s="82" t="n">
@@ -5482,7 +5965,7 @@
           <t>固定1.0；按每天完成，每周结算。</t>
         </is>
       </c>
-      <c r="G46" s="83">
+      <c r="G46" s="115">
         <f>ROUND(C46*D46,2)</f>
         <v/>
       </c>
@@ -5508,7 +5991,7 @@
           <t>关键词市场占有率统计及竞品检查</t>
         </is>
       </c>
-      <c r="C47" s="81" t="n">
+      <c r="C47" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D47" s="82" t="n">
@@ -5524,7 +6007,7 @@
           <t>固定1.0；按关键词数量及月度任务计费。</t>
         </is>
       </c>
-      <c r="G47" s="83">
+      <c r="G47" s="115">
         <f>ROUND(C47*D47,2)</f>
         <v/>
       </c>
@@ -5546,7 +6029,7 @@
           <t>跨站点Listing创建</t>
         </is>
       </c>
-      <c r="C48" s="81" t="n">
+      <c r="C48" s="113" t="n">
         <v>25</v>
       </c>
       <c r="D48" s="82" t="n">
@@ -5566,7 +6049,7 @@
 1.6：本组需处理父子关系，涉及2个及以上不同父体</t>
         </is>
       </c>
-      <c r="G48" s="83">
+      <c r="G48" s="115">
         <f>ROUND(C48*D48,2)</f>
         <v/>
       </c>
@@ -5589,7 +6072,7 @@
           <t>A+翻译后发布（非新策划）</t>
         </is>
       </c>
-      <c r="C49" s="81" t="n">
+      <c r="C49" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D49" s="82" t="n">
@@ -5606,7 +6089,7 @@
           <t>固定1.0；已有内容的翻译与发布。</t>
         </is>
       </c>
-      <c r="G49" s="83">
+      <c r="G49" s="115">
         <f>ROUND(C49*D49,2)</f>
         <v/>
       </c>
@@ -5628,7 +6111,7 @@
           <t>翻译后批量更新Listing文案</t>
         </is>
       </c>
-      <c r="C50" s="81" t="n">
+      <c r="C50" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D50" s="82" t="n">
@@ -5645,7 +6128,7 @@
           <t>固定1.0；按批次计费。</t>
         </is>
       </c>
-      <c r="G50" s="83">
+      <c r="G50" s="115">
         <f>ROUND(C50*D50,2)</f>
         <v/>
       </c>
@@ -5667,7 +6150,7 @@
           <t>市场调研与产品建议</t>
         </is>
       </c>
-      <c r="C51" s="81" t="n">
+      <c r="C51" s="113" t="n">
         <v>75</v>
       </c>
       <c r="D51" s="82" t="n">
@@ -5683,7 +6166,7 @@
           <t>固定1.0；按独立阶段交付计费。</t>
         </is>
       </c>
-      <c r="G51" s="83">
+      <c r="G51" s="115">
         <f>ROUND(C51*D51,2)</f>
         <v/>
       </c>
@@ -5711,7 +6194,7 @@
           <t>厂家筛选、报价与合作条件确认</t>
         </is>
       </c>
-      <c r="C52" s="81" t="n">
+      <c r="C52" s="113" t="n">
         <v>75</v>
       </c>
       <c r="D52" s="82" t="n">
@@ -5727,7 +6210,7 @@
           <t>固定1.0；按独立阶段交付计费。</t>
         </is>
       </c>
-      <c r="G52" s="83">
+      <c r="G52" s="115">
         <f>ROUND(C52*D52,2)</f>
         <v/>
       </c>
@@ -5755,7 +6238,7 @@
           <t>样品评估及问题跟进</t>
         </is>
       </c>
-      <c r="C53" s="81" t="n">
+      <c r="C53" s="113" t="n">
         <v>75</v>
       </c>
       <c r="D53" s="82" t="n">
@@ -5771,7 +6254,7 @@
           <t>固定1.0；按独立阶段交付计费。</t>
         </is>
       </c>
-      <c r="G53" s="83">
+      <c r="G53" s="115">
         <f>ROUND(C53*D53,2)</f>
         <v/>
       </c>
@@ -5799,7 +6282,7 @@
           <t>产品资料整理与确认</t>
         </is>
       </c>
-      <c r="C54" s="81" t="n">
+      <c r="C54" s="113" t="n">
         <v>40</v>
       </c>
       <c r="D54" s="82" t="n">
@@ -5815,7 +6298,7 @@
           <t>固定1.0；按实际独立交付计费。</t>
         </is>
       </c>
-      <c r="G54" s="83">
+      <c r="G54" s="115">
         <f>ROUND(C54*D54,2)</f>
         <v/>
       </c>
@@ -5841,7 +6324,7 @@
           <t>产品图片策划</t>
         </is>
       </c>
-      <c r="C55" s="81" t="n">
+      <c r="C55" s="113" t="n">
         <v>50</v>
       </c>
       <c r="D55" s="82" t="n">
@@ -5857,7 +6340,7 @@
           <t>固定1.0；按实际独立交付计费。</t>
         </is>
       </c>
-      <c r="G55" s="83">
+      <c r="G55" s="115">
         <f>ROUND(C55*D55,2)</f>
         <v/>
       </c>
@@ -5883,7 +6366,7 @@
           <t>视频字幕文案编写</t>
         </is>
       </c>
-      <c r="C56" s="81" t="n">
+      <c r="C56" s="113" t="n">
         <v>25</v>
       </c>
       <c r="D56" s="82" t="n">
@@ -5899,7 +6382,7 @@
           <t>固定1.0；按实际独立交付计费。</t>
         </is>
       </c>
-      <c r="G56" s="83">
+      <c r="G56" s="115">
         <f>ROUND(C56*D56,2)</f>
         <v/>
       </c>
@@ -5914,425 +6397,1017 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="14.60000038146973" customHeight="1" s="1">
-      <c r="A57" s="9" t="n"/>
-      <c r="B57" s="9" t="n"/>
-      <c r="C57" s="82" t="n"/>
-      <c r="D57" s="82" t="n"/>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="87" t="n"/>
-      <c r="H57" s="9" t="n"/>
-      <c r="I57" s="3" t="n"/>
-    </row>
-    <row r="58" ht="14.60000038146973" customHeight="1" s="1">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="9" t="n"/>
-      <c r="C58" s="82" t="n"/>
-      <c r="D58" s="82" t="n"/>
-      <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="87" t="n"/>
-      <c r="H58" s="9" t="n"/>
-      <c r="I58" s="3" t="n"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1" s="1"/>
-    <row r="60" ht="13.5" customHeight="1" s="1"/>
-    <row r="61" ht="15" customHeight="1" s="1">
+    <row r="57" ht="370" customHeight="1" s="1">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>数据与经营分析</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>利润或亏损原因分析与优化建议</t>
+        </is>
+      </c>
+      <c r="C57" s="113" t="n">
+        <v>30</v>
+      </c>
+      <c r="D57" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>同一站点、一个ASIN、同一次独立利润问题分析：完整30元，初步15元。多个SKU对应同一ASIN不重复计费；多个ASIN共用同一份分析合并，分别独立分析并验收才分别计费。</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际验收档位及计费单位确定基础金额。</t>
+        </is>
+      </c>
+      <c r="G57" s="115">
+        <f>ROUND(C57*D57,2)</f>
+        <v/>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>核查收入、售价与折扣、采购成本、运输及平台费用、广告、退货损失等相关因素，明确利润口径及对比期间，找出主要变化原因。必须给出有依据的优化建议，说明建议动作、预期作用、优先级及必要验证；不要求建议已执行或利润已改善。
+按需指派，不设固定频次。完整分析30元；有数据证据但关键判断未核实，经负责人确认按初步成果结案计15元；仅转发报表或AI原文、无证据或无具体建议，退回补充，暂不结算。初步15元后补成完整分析只补15元，同一任务累计基础金额30元。不以篇幅长短判定；关键数据不可得须说明原因，不自动减半。独立分析与后续独立执行分别验收，相同分析若已包含在其他任务中不重复计酬。同一范围及期间的销量、利润和活动分析使用同一交付时只选一项，不按报告名称重复计费。本人责任纠错不另计酬。负责人安排倍率1；自主发起按未明确项目暂为1，不自行套用高倍率。</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>完整报告30元；初步结案15元，之后补齐只补15元。分析完成后另行执行改价，按价格调整项目验收计酬。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="370" customHeight="1" s="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>数据与经营分析</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>活动效果复盘</t>
+        </is>
+      </c>
+      <c r="C58" s="113" t="n">
+        <v>30</v>
+      </c>
+      <c r="D58" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>同一站点、一个独立Coupon／Promotion／Deal活动、一次完整复盘：30元；初步15元。活动包含多个ASIN仍按一份复盘计费；若同一方案的多个活动共用一份报告，合并计费。</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际验收档位及计费单位确定基础金额。</t>
+        </is>
+      </c>
+      <c r="G58" s="115">
+        <f>ROUND(C58*D58,2)</f>
+        <v/>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>对比活动前、活动期间及适当的后续期间，核查销量、流量、转化、优惠成本、活动费用、广告投入、利润及库存变化。记录同期价格、断货及其他促销影响，不将销售增长直接等同活动增量。给出继续、调整或停止建议及证据。
+按需指派，不设固定频次。完整分析30元；有数据证据但关键判断未核实，经负责人确认按初步成果结案计15元；仅转发报表或AI原文、无证据或无具体建议，退回补充，暂不结算。初步15元后补成完整分析只补15元，同一任务累计基础金额30元。不以篇幅长短判定；关键数据不可得须说明原因，不自动减半。独立分析与后续独立执行分别验收，相同分析若已包含在其他任务中不重复计酬。同一范围及期间的销量、利润和活动分析使用同一交付时只选一项，不按报告名称重复计费。本人责任纠错不另计酬。负责人安排倍率1；自主发起按未明确项目暂为1，不自行套用高倍率。</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>一场活动覆盖10个ASIN，完整复盘30元。创建活动的报酬按原规则，独立复盘另计；日常查看活动数据不逐次计费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="370" customHeight="1" s="1">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>费用与异常处理</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>费用异常核查与Case申诉</t>
+        </is>
+      </c>
+      <c r="C59" s="117" t="n">
+        <v>20</v>
+      </c>
+      <c r="D59" s="118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>20元/独立费用问题（含核查、证据整理、开Case及跟进）。同站点、同类收费原因且共用证据与处理过程的对象合并；不按ASIN、SKU、收费记录或Case数量累加。</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际验收档位及计费单位确定基础金额。</t>
+        </is>
+      </c>
+      <c r="G59" s="114">
+        <f>ROUND(C59*D59,2)</f>
+        <v/>
+      </c>
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>核对实际收费与对应商品尺寸、重量、适用计费依据或交易记录，整理费用差异及证据，提交Case并跟进回复、补充资料及核验处理结果。适用于商品尺寸重量引起的费用疑问或其他收费异常；不包含普通FBA货件问题。
+包含异常核查、差额计算、证据整理、Case提交及补充跟进，不另叠加利润分析或Listing异常处理的相同交付。平台是否退款／更正与任务完成分别记录；处理完成并核验，或证据及回复完整且负责人确认阶段结案后计酬。仍处理中暂不结算，同一问题阶段结案后恢复或到账不重复计费。不以退款金额或催办次数加价。本人责任纠错不另计酬。负责人安排倍率1；主动发现并完成处理，按异常处理主动倍率1.5，即30元。</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>同一费用问题多次开Case：仍20元。平台未支持申请，材料完整且负责人确认结案：20元；仍处理中暂不结算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="410" customHeight="1" s="1">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>品牌保护</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>跟卖监控</t>
+        </is>
+      </c>
+      <c r="C60" s="118" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>5元/站点/约定监控清单/自然周。按完成的约定检查次数÷应检查次数折算；当周无任务为0。不得拆清单提高金额。</t>
+        </is>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际任务档位及单位计费。</t>
+        </is>
+      </c>
+      <c r="G60" s="0">
+        <f>ROUND(C60*D60,2)</f>
+        <v/>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>按要求检查指定ASIN的其他报价及卖家变化，记录时间、ASIN、卖家标识、价格及可获得证据，发现疑似异常及时报告。
+固定监控倍率1；程序自动监控且无需人工核验不计人工任务金额。未发现异常但完成约定核验仍可验收。监控记录与后续独立取证投诉可分别计费，同一发现不额外领取发现费。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t>按周验收，无异常也可完成；本周全部检查完成5元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="410" customHeight="1" s="1">
       <c r="A61" s="49" t="inlineStr">
         <is>
-          <t>主动执行倍率规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="63.75" customHeight="1" s="1">
+          <t>品牌保护</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>跟卖取证与举报／Case处理</t>
+        </is>
+      </c>
+      <c r="C61" s="118" t="n">
+        <v>30</v>
+      </c>
+      <c r="D61" s="118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>已有有效证据，完成核查、举报／Case及跟进：30元/独立案件；另需完成Test Buy取证全过程：整案50元。两档只取最高，先结30元后补足最多20元。</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际任务档位及单位计费。</t>
+        </is>
+      </c>
+      <c r="G61" s="0">
+        <f>ROUND(C61*D61,2)</f>
+        <v/>
+      </c>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>核实疑似违规；确需Test Buy时经负责人确认采购及预算，跟进收货、保留订单与实物照片并核对差异。依据证据选择亚马逊举报、Case或Brand Registry适用渠道，跟进处理及报价状态。
+站点＋被举报卖家＋同一违规事实及共用证据为案件范围；多ASIN共用证据处理时合并，多渠道或多Case不累加。存在其他报价不等于违规；不以未获品牌授权直接认定假货，不提交无依据投诉。下架后核验，或调查及跟进完整、负责人确认阶段结案后计酬；未下架不自动判定未完成。Test Buy未发现违规时提交证据与不投诉结论，可按实际取证范围由负责人结案，确已完成完整Test Buy调查可计50元。样品购买不叠加样品备货协调分；同一交付不叠加Buy Box或Listing申诉。主动发现并完成案件处理倍率1.5；仅例行监控后按既定职责处理，按正常履职确认来源。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>多渠道反复投诉仍30元；独立完成Test Buy取证及案件处理50元。实际货款运费另行处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="410" customHeight="1" s="1">
       <c r="A62" s="50" t="inlineStr">
         <is>
-          <t>主动任务金额 ＝ 正常任务金额 × 主动倍率。主动执行指员工自主发现问题或机会并发起处理，非负责人安排。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="13.10000038146973" customHeight="1" s="1">
+          <t>品牌项目</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>Vine报名与跟进</t>
+        </is>
+      </c>
+      <c r="C62" s="118" t="n">
+        <v>15</v>
+      </c>
+      <c r="D62" s="118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>15元/独立Vine报名项目。以后台报名记录去重，不按子SKU、领取件数或评论数量累加。</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际任务档位及单位计费。</t>
+        </is>
+      </c>
+      <c r="G62" s="0">
+        <f>ROUND(C62*D62,2)</f>
+        <v/>
+      </c>
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>核对参与资格、商品、库存、报名数量及费用，按确认方案报名，核验提交结果并记录约定跟进节点的领取和评论状态。
+首次资格核查、报名、常规修正和约定节点跟进合并15元；派单时约定验收节点，不逐周重复收费。不以好评、星级或评论必然产生作为验收条件，不要求员工干预评论。平台报名费及赠送商品成本不含任务金额。早期评论人计划已停止，不设该项目任务。自主发起仍按未明确项目倍率1，后续另定不自动套高倍率。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>一个报名项目覆盖多个子SKU：15元；同一报名重复查看或修改不新增报酬。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="410" customHeight="1" s="1">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>品牌内容</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story品牌故事制作与维护</t>
+        </is>
+      </c>
+      <c r="C63" s="118" t="n">
+        <v>75</v>
+      </c>
+      <c r="D63" s="118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>全新策划或完全重做：75元/独立内容；局部修改：10元/同份同轮；仅为已有内容新增绑定：5元/ASIN。</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际任务档位及单位计费。</t>
+        </is>
+      </c>
+      <c r="G63" s="0">
+        <f>ROUND(C63*D63,2)</f>
+        <v/>
+      </c>
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t>构思品牌故事、文案及图片要求，协调制作，设置卡片和链接、提交并核验；或按确认范围修改现有内容、维护ASIN绑定。
+新建75元含策划、制作跟进、发布及首次绑定；同一内容多ASIN共用只计一次。局部修改不按卡片数量累加。新建或重做不叠加局部修改；同一份内容不再领取A+制作/修改或相同素材图片策划金额。不同的产品A+与品牌故事确有独立交付时可分别验收。自主实质重做有证据方案且完成复盘适用内容重写倍率2；自主局部维护或绑定倍率1.5；首次制作按发布核验，后续优化按复盘规则。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>同份品牌故事应用20个ASIN，新建合计75元；后续独立绑定3个ASIN计15元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="410" customHeight="1" s="1">
       <c r="A64" s="51" t="inlineStr">
         <is>
-          <t>工作分类</t>
+          <t>订阅销售</t>
         </is>
       </c>
       <c r="B64" s="51" t="inlineStr">
         <is>
-          <t>对应项目</t>
-        </is>
-      </c>
-      <c r="C64" s="52" t="n"/>
-      <c r="D64" s="51" t="inlineStr">
-        <is>
-          <t>主动倍率</t>
-        </is>
+          <t>Subscribe &amp; Save设置与管理</t>
+        </is>
+      </c>
+      <c r="C64" s="119" t="n">
+        <v>10</v>
+      </c>
+      <c r="D64" s="120" t="n">
+        <v>1</v>
       </c>
       <c r="E64" s="51" t="inlineStr">
         <is>
-          <t>认定条件</t>
-        </is>
-      </c>
-      <c r="F64" s="53" t="n"/>
-      <c r="G64" s="53" t="n"/>
-      <c r="H64" s="52" t="n"/>
-    </row>
-    <row r="65" ht="17.64999961853027" customHeight="1" s="1">
+          <t>同次安排、同站点、同一订阅方案的一批设置或更新：10元。包含多个ASIN或多个调整动作仍计一次。</t>
+        </is>
+      </c>
+      <c r="F64" s="53" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际任务档位及单位计费。</t>
+        </is>
+      </c>
+      <c r="G64" s="53">
+        <f>ROUND(C64*D64,2)</f>
+        <v/>
+      </c>
+      <c r="H64" s="52" t="inlineStr">
+        <is>
+          <t>核对后台可参与商品及资格，按负责人确认方案加入或退出商品、设置或调整订阅优惠，并核验参与状态、折扣及生效情况。
+不按SKU、订阅订单或设置次数累加；不把平台自动加入、自动折扣或无需人工的变化当作任务。默认按确认方案执行；员工主动发现独立机会并完成，经认定可按促销执行倍率1.5。设置已含的参数修正不另计，不与同一价格或促销交付重复计费。不以产生订阅订单作为执行验收条件。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>同批10个ASIN加入并设折扣：10元；主动任务符合1.5倍时15元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="410" customHeight="1" s="1">
       <c r="A65" s="54" t="inlineStr">
         <is>
-          <t>Listing内容实质重写</t>
+          <t>组合销售</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>标题编写与优化、五点编写与优化、描述编写与优化、Generic Keywords编写与优化、全新制作或完全重做A+</t>
-        </is>
-      </c>
-      <c r="C65" s="52" t="n"/>
-      <c r="D65" s="55" t="inlineStr">
-        <is>
-          <t>×2</t>
-        </is>
+          <t>Virtual Bundle创建与维护</t>
+        </is>
+      </c>
+      <c r="C65" s="119" t="n">
+        <v>25</v>
+      </c>
+      <c r="D65" s="121" t="n">
+        <v>1</v>
       </c>
       <c r="E65" s="28" t="inlineStr">
         <is>
-          <t>主动分析问题、提出方案，实际重写或重做并完成复盘。单纯纠错、翻译、上传已有内容不属于此档。</t>
-        </is>
-      </c>
-      <c r="F65" s="53" t="n"/>
-      <c r="G65" s="53" t="n"/>
-      <c r="H65" s="52" t="n"/>
+          <t>新建：25元/独立虚拟捆绑商品；已有捆绑同轮内容或可编辑设置维护：10元/个。</t>
+        </is>
+      </c>
+      <c r="F65" s="53" t="inlineStr">
+        <is>
+          <t>固定1.0；按实际任务档位及单位计费。</t>
+        </is>
+      </c>
+      <c r="G65" s="53">
+        <f>ROUND(C65*D65,2)</f>
+        <v/>
+      </c>
+      <c r="H65" s="52" t="inlineStr">
+        <is>
+          <t>核对后台资格及组成商品，按确认组合填写文案、图片、价格等可编辑资料，创建并核验；维护时按后台实际允许的字段更新及核验。
+新建包含初始配置、提交、常规报错修正及核验，不再叠加普通Listing创建、初始文案填入或图片上传。需要独立原创内容或素材策划且不属创建中已有资料改写时，按对应独立交付验收，相同工作只计一次。FBA虚拟组合不计重新包装或实物发货任务。不得通过重复建立相同组合、删后重建或拆分任务增加金额；后台不允许编辑的组成变更须先确认方案。主动专项倍率暂按未明确项目1。
+以下金额为内部试行任务报酬，不含平台费用、样品货款、运费及其他实际支出，实际支出按公司流程另行审批报销。本人责任纠错、失败重试及同一交付不重复计费。仅按目标站点及账户实际开放且符合资格的项目执行；未完成核验暂不结算。</t>
+        </is>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>新建1个虚拟组合25元；同组合本轮改标题和价格合计10元；新建时这些初始配置不另加10元。</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A66" s="54" t="inlineStr">
-        <is>
-          <t>广告新建</t>
-        </is>
-      </c>
-      <c r="B66" s="28" t="inlineStr">
-        <is>
-          <t>SP广告创建、SB广告创建、SBV广告创建、SD广告创建</t>
-        </is>
-      </c>
+      <c r="A66" s="54" t="n"/>
+      <c r="B66" s="28" t="n"/>
       <c r="C66" s="52" t="n"/>
-      <c r="D66" s="55" t="inlineStr">
-        <is>
-          <t>×2</t>
-        </is>
-      </c>
-      <c r="E66" s="28" t="inlineStr">
-        <is>
-          <t>主动提出投放机会，说明产品、投放方向及测试目标，完成创建和复盘。复制已有Campaign不能仅凭新建数量拿双倍。</t>
-        </is>
-      </c>
+      <c r="D66" s="55" t="n"/>
+      <c r="E66" s="28" t="n"/>
       <c r="F66" s="53" t="n"/>
       <c r="G66" s="53" t="n"/>
       <c r="H66" s="52" t="n"/>
     </row>
     <row r="67" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A67" s="54" t="inlineStr">
-        <is>
-          <t>广告调整</t>
-        </is>
-      </c>
-      <c r="B67" s="28" t="inlineStr">
-        <is>
-          <t>广告执行调整（涵盖关键词、否定词、产品归组、ASIN投放、Bid调整）</t>
-        </is>
-      </c>
+      <c r="A67" s="54" t="n"/>
+      <c r="B67" s="28" t="n"/>
       <c r="C67" s="52" t="n"/>
-      <c r="D67" s="55" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="E67" s="28" t="inlineStr">
-        <is>
-          <t>有依据并完成核验。每Campaign每自然周最多计2次，跨人员、跨发起来源合并统计。可关联多条Ads Change。</t>
-        </is>
-      </c>
+      <c r="D67" s="55" t="n"/>
+      <c r="E67" s="28" t="n"/>
       <c r="F67" s="53" t="n"/>
       <c r="G67" s="53" t="n"/>
       <c r="H67" s="52" t="n"/>
     </row>
     <row r="68" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A68" s="54" t="inlineStr">
-        <is>
-          <t>异常处理／申诉</t>
-        </is>
-      </c>
-      <c r="B68" s="28" t="inlineStr">
-        <is>
-          <t>Listing异常申诉与Case处理、Buy Box异常处理、Brand Store提交阻断问题处理</t>
-        </is>
-      </c>
+      <c r="A68" s="54" t="n"/>
+      <c r="B68" s="28" t="n"/>
       <c r="C68" s="52" t="n"/>
-      <c r="D68" s="55" t="inlineStr">
-        <is>
-          <t>×1.5</t>
-        </is>
-      </c>
-      <c r="E68" s="28" t="inlineStr">
-        <is>
-          <t>主动发现、及时记录并推动处理；同一问题反复提交只计一次。</t>
-        </is>
-      </c>
+      <c r="D68" s="55" t="n"/>
+      <c r="E68" s="28" t="n"/>
       <c r="F68" s="53" t="n"/>
       <c r="G68" s="53" t="n"/>
       <c r="H68" s="52" t="n"/>
     </row>
     <row r="69" ht="25.89999961853027" customHeight="1" s="1">
-      <c r="A69" s="54" t="inlineStr">
-        <is>
-          <t>Listing事实纠错及局部维护</t>
-        </is>
-      </c>
-      <c r="B69" s="28" t="inlineStr">
-        <is>
-          <t>Listing纠错、A+内容增删修改、图片维护、视频上传与信息维护、变体关系维护</t>
-        </is>
-      </c>
+      <c r="A69" s="54" t="n"/>
+      <c r="B69" s="28" t="n"/>
       <c r="C69" s="52" t="n"/>
-      <c r="D69" s="55" t="inlineStr">
-        <is>
-          <t>×1.5</t>
-        </is>
-      </c>
-      <c r="E69" s="28" t="inlineStr">
-        <is>
-          <t>主动发现并完成纠正或维护。事实纠错≠内容实质重写，不适用×2。</t>
-        </is>
-      </c>
+      <c r="D69" s="55" t="n"/>
+      <c r="E69" s="28" t="n"/>
       <c r="F69" s="53" t="n"/>
       <c r="G69" s="53" t="n"/>
       <c r="H69" s="52" t="n"/>
     </row>
     <row r="70" ht="25.5" customHeight="1" s="1">
-      <c r="A70" s="54" t="inlineStr">
-        <is>
-          <t>价格／促销／库存等执行类</t>
-        </is>
-      </c>
-      <c r="B70" s="28" t="inlineStr">
-        <is>
-          <t>价格调整、Coupon与Promotion创建、Deal活动提报、库存移除／Relist／申诉／资料提交</t>
-        </is>
-      </c>
+      <c r="A70" s="54" t="n"/>
+      <c r="B70" s="28" t="n"/>
       <c r="C70" s="52" t="n"/>
-      <c r="D70" s="55" t="inlineStr">
-        <is>
-          <t>×1.5</t>
-        </is>
-      </c>
-      <c r="E70" s="28" t="inlineStr">
-        <is>
-          <t>主动发现具体问题或机会，提出合理措施并完成处理。</t>
-        </is>
-      </c>
+      <c r="D70" s="55" t="n"/>
+      <c r="E70" s="28" t="n"/>
       <c r="F70" s="53" t="n"/>
       <c r="G70" s="53" t="n"/>
       <c r="H70" s="52" t="n"/>
     </row>
-    <row r="71" ht="17.64999961853027" customHeight="1" s="1">
+    <row r="71" ht="15" customHeight="1" s="1">
       <c r="A71" s="54" t="inlineStr">
         <is>
-          <t>Brand Store维护</t>
-        </is>
-      </c>
-      <c r="B71" s="28" t="inlineStr">
-        <is>
-          <t>二级类目商品维护、二级类目模块新增或重建</t>
-        </is>
-      </c>
+          <t>主动执行倍率规则</t>
+        </is>
+      </c>
+      <c r="B71" s="28" t="n"/>
       <c r="C71" s="52" t="n"/>
-      <c r="D71" s="55" t="inlineStr">
-        <is>
-          <t>×1.5</t>
-        </is>
-      </c>
-      <c r="E71" s="28" t="inlineStr">
-        <is>
-          <t>主动发现维护需求并完成更新。</t>
-        </is>
-      </c>
+      <c r="D71" s="55" t="n"/>
+      <c r="E71" s="28" t="n"/>
       <c r="F71" s="53" t="n"/>
       <c r="G71" s="53" t="n"/>
       <c r="H71" s="52" t="n"/>
-    </row>
-    <row r="72" ht="17.64999961853027" customHeight="1" s="1">
+      <c r="I71" s="0" t="n"/>
+    </row>
+    <row r="72" ht="63.75" customHeight="1" s="1">
       <c r="A72" s="54" t="inlineStr">
         <is>
-          <t>新品开发</t>
-        </is>
-      </c>
-      <c r="B72" s="28" t="inlineStr">
-        <is>
-          <t>市场调研与产品建议、厂家筛选报价与合作条件确认、样品评估及问题跟进</t>
-        </is>
-      </c>
+          <t>主动任务金额 ＝ 正常任务金额 × 主动倍率。主动执行指员工自主发现问题或机会并发起处理，非负责人安排。</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="n"/>
       <c r="C72" s="52" t="n"/>
-      <c r="D72" s="55" t="inlineStr">
-        <is>
-          <t>×1.5</t>
-        </is>
-      </c>
-      <c r="E72" s="28" t="inlineStr">
-        <is>
-          <t>主动发起开发选题，完成调研、找厂或样品验证的完整阶段交付并通过验收。仅执行已安排任务不属于此档。</t>
-        </is>
-      </c>
+      <c r="D72" s="55" t="n"/>
+      <c r="E72" s="28" t="n"/>
       <c r="F72" s="53" t="n"/>
       <c r="G72" s="53" t="n"/>
       <c r="H72" s="52" t="n"/>
+      <c r="I72" s="0" t="n"/>
     </row>
     <row r="73" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A73" s="54" t="inlineStr">
-        <is>
-          <t>产品内容策划</t>
-        </is>
-      </c>
-      <c r="B73" s="28" t="inlineStr">
-        <is>
-          <t>产品资料整理与确认、产品图片策划、视频字幕文案编写</t>
-        </is>
-      </c>
+      <c r="A73" s="54" t="n"/>
+      <c r="B73" s="28" t="n"/>
       <c r="C73" s="52" t="n"/>
-      <c r="D73" s="55" t="inlineStr">
-        <is>
-          <t>×1.5</t>
-        </is>
-      </c>
-      <c r="E73" s="28" t="inlineStr">
-        <is>
-          <t>主动发起内容准备工作并完成交付。仅复制整理现成资料、使用已有字幕不属于此档。</t>
-        </is>
-      </c>
+      <c r="D73" s="55" t="n"/>
+      <c r="E73" s="28" t="n"/>
       <c r="F73" s="53" t="n"/>
       <c r="G73" s="53" t="n"/>
       <c r="H73" s="52" t="n"/>
-    </row>
-    <row r="74">
+      <c r="I73" s="0" t="n"/>
+    </row>
+    <row r="74" ht="13.10000038146973" customHeight="1" s="1">
       <c r="A74" s="54" t="inlineStr">
         <is>
-          <t>固定例行工作</t>
+          <t>工作分类</t>
         </is>
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>VOC数据更新与AI分析、Category Report下载、关键词市场占有率统计及竞品检查、A+翻译后发布、翻译后批量更新Listing文案</t>
+          <t>对应项目</t>
         </is>
       </c>
       <c r="C74" s="52" t="n"/>
       <c r="D74" s="55" t="inlineStr">
         <is>
-          <t>×1</t>
+          <t>主动倍率</t>
         </is>
       </c>
       <c r="E74" s="28" t="inlineStr">
         <is>
-          <t>固定周期或已有内容的翻译发布任务，不享受主动倍率。</t>
+          <t>认定条件</t>
         </is>
       </c>
       <c r="F74" s="53" t="n"/>
       <c r="G74" s="53" t="n"/>
       <c r="H74" s="52" t="n"/>
-    </row>
-    <row r="75" ht="13.10000038146973" customHeight="1" s="1">
+      <c r="I74" s="0" t="n"/>
+    </row>
+    <row r="75" ht="17.64999961853027" customHeight="1" s="1">
       <c r="A75" s="54" t="inlineStr">
         <is>
+          <t>Listing内容实质重写</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="inlineStr">
+        <is>
+          <t>标题编写与优化、五点编写与优化、描述编写与优化、Generic Keywords编写与优化、全新制作或完全重做A+</t>
+        </is>
+      </c>
+      <c r="C75" s="52" t="n"/>
+      <c r="D75" s="55" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
+        <is>
+          <t>主动分析问题、提出方案，实际重写或重做并完成复盘。单纯纠错、翻译、上传已有内容不属于此档。</t>
+        </is>
+      </c>
+      <c r="F75" s="53" t="n"/>
+      <c r="G75" s="53" t="n"/>
+      <c r="H75" s="52" t="n"/>
+      <c r="I75" s="0" t="n"/>
+    </row>
+    <row r="76" ht="17.64999961853027" customHeight="1" s="1">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>广告新建</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>SP广告创建、SB广告创建、SBV广告创建、SD广告创建</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>主动提出投放机会，说明产品、投放方向及测试目标，完成创建和复盘。复制已有Campaign不能仅凭新建数量拿双倍。</t>
+        </is>
+      </c>
+      <c r="I76" s="0" t="n"/>
+    </row>
+    <row r="77" ht="17.64999961853027" customHeight="1" s="1">
+      <c r="A77" s="56" t="inlineStr">
+        <is>
+          <t>广告调整</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>广告执行调整（涵盖关键词、否定词、产品归组、ASIN投放、Bid调整）</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>有依据并完成核验。每Campaign每自然周最多计2次，跨人员、跨发起来源合并统计。可关联多条Ads Change。</t>
+        </is>
+      </c>
+      <c r="I77" s="0" t="n"/>
+    </row>
+    <row r="78" ht="17.64999961853027" customHeight="1" s="1">
+      <c r="A78" s="50" t="inlineStr">
+        <is>
+          <t>异常处理／申诉</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>Listing异常申诉与Case处理、Buy Box异常处理、Brand Store提交阻断问题处理、费用异常核查与Case申诉</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>主动发现、及时记录并推动处理；同一问题反复提交只计一次。</t>
+        </is>
+      </c>
+      <c r="I78" s="0" t="n"/>
+    </row>
+    <row r="79" ht="25.89999961853027" customHeight="1" s="1">
+      <c r="A79" s="50" t="inlineStr">
+        <is>
+          <t>Listing事实纠错及局部维护</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>Listing纠错、A+内容增删修改、图片维护、视频上传与信息维护、变体关系维护</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>主动发现并完成纠正或维护。事实纠错≠内容实质重写，不适用×2。</t>
+        </is>
+      </c>
+      <c r="I79" s="0" t="n"/>
+    </row>
+    <row r="80" ht="25.5" customHeight="1" s="1">
+      <c r="A80" s="50" t="inlineStr">
+        <is>
+          <t>价格／促销／库存等执行类</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>价格调整、Coupon与Promotion创建、Deal活动提报、库存移除／Relist／申诉／资料提交</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>主动发现具体问题或机会，提出合理措施并完成处理。</t>
+        </is>
+      </c>
+      <c r="I80" s="0" t="n"/>
+    </row>
+    <row r="81" ht="17.64999961853027" customHeight="1" s="1">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>Brand Store维护</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>二级类目商品维护、二级类目模块新增或重建</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>主动发现维护需求并完成更新。</t>
+        </is>
+      </c>
+      <c r="I81" s="0" t="n"/>
+    </row>
+    <row r="82" ht="17.64999961853027" customHeight="1" s="1">
+      <c r="A82" s="56" t="inlineStr">
+        <is>
+          <t>新品开发</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>市场调研与产品建议、厂家筛选报价与合作条件确认、样品评估及问题跟进</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>主动发起开发选题，完成调研、找厂或样品验证的完整阶段交付并通过验收。仅执行已安排任务不属于此档。</t>
+        </is>
+      </c>
+      <c r="I82" s="0" t="n"/>
+    </row>
+    <row r="83" ht="17.64999961853027" customHeight="1" s="1">
+      <c r="A83" s="50" t="inlineStr">
+        <is>
+          <t>产品内容策划</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>产品资料整理与确认、产品图片策划、视频字幕文案编写</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>主动发起内容准备工作并完成交付。仅复制整理现成资料、使用已有字幕不属于此档。</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="50" t="inlineStr">
+        <is>
+          <t>数据与经营分析</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t>利润或亏损原因分析与优化建议、活动效果复盘</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>主动发现经营问题或活动复盘需求，完成分析并提出有依据的建议。仅执行已安排的分析不属于此档。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="13.10000038146973" customHeight="1" s="1">
+      <c r="A85" s="50" t="inlineStr">
+        <is>
+          <t>品牌保护—监控</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>跟卖监控</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>固定巡检任务，不享受主动倍率。程序自动监控且无需人工核验不计人工任务金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="12.75" customHeight="1" s="1">
+      <c r="A86" s="50" t="inlineStr">
+        <is>
+          <t>品牌保护—取证与投诉</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>跟卖取证与举报／Case处理</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>主动发现跟卖并发起取证投诉流程；正常履职的定期排查结果按×1。报酬与Test Buy货款运费分开。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="12.75" customHeight="1" s="1">
+      <c r="A87" s="50" t="inlineStr">
+        <is>
+          <t>品牌内容策划</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Brand Story品牌故事制作与维护</t>
+        </is>
+      </c>
+      <c r="D87" s="122" t="inlineStr">
+        <is>
+          <t>实质重做×2
+局部维护／绑定×1.5</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>全新策划或完全重做按×2（同Listing内容实质重写标准）；局部修改或新增ASIN绑定按×1.5。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="12.75" customHeight="1" s="1">
+      <c r="A88" s="50" t="inlineStr">
+        <is>
+          <t>订阅销售</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Subscribe &amp; Save设置与管理</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>主动发现可参与商品或优化订阅方案并完成设置。按已安排方案执行不属于此档。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="50" t="inlineStr">
+        <is>
+          <t>组合销售与品牌项目</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle创建与维护、Vine报名与跟进</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>按确认方案执行并验收。Virtual Bundle和Vine均为执行类任务，暂不设主动倍率加成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="13.10000038146973" customHeight="1" s="1">
+      <c r="A90" s="123" t="inlineStr">
+        <is>
+          <t>固定例行工作</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>VOC数据更新与AI分析、Category Report下载、关键词市场占有率统计及竞品检查、A+翻译后发布、翻译后批量更新Listing文案</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t>固定周期或已有内容的翻译发布任务，不享受主动倍率。</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="n"/>
+    </row>
+    <row r="91" ht="140" customHeight="1" s="1">
+      <c r="A91" s="123" t="inlineStr">
+        <is>
           <t>未明确列入的项目</t>
         </is>
       </c>
-      <c r="B75" s="28" t="inlineStr">
+      <c r="B91" s="0" t="inlineStr">
         <is>
           <t>（暂按×1，不自行套用高倍率）</t>
         </is>
       </c>
-      <c r="D75" s="55" t="inlineStr">
+      <c r="D91" s="0" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="E75" s="28" t="inlineStr">
+      <c r="E91" s="0" t="inlineStr">
         <is>
           <t>如有争议，由负责人认定适用分类。</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="12.75" customHeight="1" s="1"/>
-    <row r="77" ht="12.75" customHeight="1" s="1">
-      <c r="A77" s="56" t="inlineStr">
+      <c r="I91" s="0" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="n"/>
+      <c r="I92" s="0" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
         <is>
           <t>边界规则</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="12.75" customHeight="1" s="1">
-      <c r="A78" s="50" t="inlineStr">
+      <c r="I93" s="0" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
         <is>
           <t>① 主动发现后及时登记即可，不要求处理完才申报。提出方案后经负责人批准执行，仍算主动；隐瞒或拖延已知问题不享受倍率。</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="50" t="inlineStr">
+      <c r="I94" s="0" t="n"/>
+    </row>
+    <row r="95" ht="60" customHeight="1" s="1">
+      <c r="A95" s="0" t="inlineStr">
         <is>
           <t>② 固定巡检、例行维护、已被安排的任务，以及修复本人错误，不享受主动倍率。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="13.10000038146973" customHeight="1" s="1">
-      <c r="A80" s="50" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
         <is>
           <t>③ 同一工作只计算一次乘倍率后的金额，不再另加正常金额。未完成处理及必要核验的，先保留记录，不提前领取完整金额。</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="140" customHeight="1" s="1"/>
-    <row r="82">
-      <c r="A82" s="56" t="inlineStr">
+      <c r="I96" s="0" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="n"/>
+      <c r="I97" s="0" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
         <is>
           <t>广告调整频次限制</t>
         </is>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="50" t="inlineStr">
+      <c r="B98" s="0" t="n"/>
+      <c r="C98" s="0" t="n"/>
+      <c r="D98" s="0" t="n"/>
+      <c r="E98" s="0" t="n"/>
+      <c r="F98" s="0" t="n"/>
+      <c r="G98" s="0" t="n"/>
+      <c r="H98" s="0" t="n"/>
+      <c r="I98" s="0" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
         <is>
           <t>同一广告账户、同一站点、同一Campaign，每自然周最多结算2次，每次10元、每周最高20元；负责人安排和员工主动执行合并统计，多人参与不增加次数。同一次调整可关联多条Ads Change。超出次数的必要调整仍须执行，但不另结算。
 示例：同周A有效调整2次、B调整1次、C调整3次，分别20元、10元、20元，合计50元。</t>
         </is>
       </c>
+      <c r="B99" s="0" t="n"/>
+      <c r="C99" s="0" t="n"/>
+      <c r="D99" s="0" t="n"/>
+      <c r="E99" s="0" t="n"/>
+      <c r="F99" s="0" t="n"/>
+      <c r="G99" s="0" t="n"/>
+      <c r="H99" s="0" t="n"/>
+      <c r="I99" s="0" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="116" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="B71:C71"/>
+  <mergeCells count="36">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E81:H81"/>
     <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E89:H89"/>
     <mergeCell ref="B75:C75"/>
   </mergeCells>
   <dataValidations count="4">
@@ -6697,15 +7772,15 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="78" customHeight="1" s="1">
+    <row r="18" ht="140" customHeight="1" s="1">
       <c r="A18" s="37" t="inlineStr">
         <is>
-          <t>修复本人操作错误</t>
+          <t>本人责任纠错</t>
         </is>
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>员工纠正自己操作造成的价格、内容、广告或其他错误。</t>
+          <t>不论产品归属，修复本人操作、编写或应核验事项疏漏造成的错误，均不另计任务报酬、主动加成或成果奖励。按操作当时确认的资料与执行记录判责，负责人后续更新或更正资料须区分处理；详见“优化登记与复盘规则”。</t>
         </is>
       </c>
       <c r="C18" s="39" t="inlineStr">
@@ -7053,7 +8128,7 @@
       </c>
       <c r="E33" s="37" t="inlineStr">
         <is>
-          <t>多个ASIN受到同一问题影响可合并；同一ASIN的独立问题有不同依据、措施和交付时可分别认定。</t>
+          <t>按各项目规定的计费单位去重。Buy Box按站点及ASIN分别计费，不因共用证据或Case合并不同ASIN的金额；同一站点同一ASIN同一异常不重复计费。其他项目按对应规则处理。</t>
         </is>
       </c>
     </row>
@@ -7196,7 +8271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H230"/>
+  <dimension ref="A2:H251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -7282,13 +8357,13 @@
           <t>1个独立SKU上架</t>
         </is>
       </c>
-      <c r="C8" s="81" t="n">
+      <c r="C8" s="113" t="n">
         <v>25</v>
       </c>
       <c r="D8" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="83">
+      <c r="E8" s="115">
         <f>ROUND(C8*D8,2)</f>
         <v/>
       </c>
@@ -7319,13 +8394,13 @@
           <t>5个独立SKU上架</t>
         </is>
       </c>
-      <c r="C9" s="81" t="n">
+      <c r="C9" s="113" t="n">
         <v>40</v>
       </c>
       <c r="D9" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="83">
+      <c r="E9" s="115">
         <f>ROUND(C9*D9,2)</f>
         <v/>
       </c>
@@ -7356,13 +8431,13 @@
           <t>5个SKU组成一个变体</t>
         </is>
       </c>
-      <c r="C10" s="81" t="n">
+      <c r="C10" s="113" t="n">
         <v>40</v>
       </c>
       <c r="D10" s="82" t="n">
         <v>1.3</v>
       </c>
-      <c r="E10" s="83">
+      <c r="E10" s="115">
         <f>ROUND(C10*D10,2)</f>
         <v/>
       </c>
@@ -7393,13 +8468,13 @@
           <t>5个SKU加入不同变体</t>
         </is>
       </c>
-      <c r="C11" s="81" t="n">
+      <c r="C11" s="113" t="n">
         <v>40</v>
       </c>
       <c r="D11" s="82" t="n">
         <v>1.6</v>
       </c>
-      <c r="E11" s="83">
+      <c r="E11" s="115">
         <f>ROUND(C11*D11,2)</f>
         <v/>
       </c>
@@ -7430,13 +8505,13 @@
           <t>1个SKU各用独立图片</t>
         </is>
       </c>
-      <c r="C12" s="81" t="n">
+      <c r="C12" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D12" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="83">
+      <c r="E12" s="115">
         <f>ROUND(C12*D12,2)</f>
         <v/>
       </c>
@@ -7467,13 +8542,13 @@
           <t>5个SKU各用独立图片</t>
         </is>
       </c>
-      <c r="C13" s="81" t="n">
+      <c r="C13" s="113" t="n">
         <v>50</v>
       </c>
       <c r="D13" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="83">
+      <c r="E13" s="115">
         <f>ROUND(C13*D13,2)</f>
         <v/>
       </c>
@@ -7504,13 +8579,13 @@
           <t>10个SKU各用独立图片</t>
         </is>
       </c>
-      <c r="C14" s="81" t="n">
+      <c r="C14" s="113" t="n">
         <v>100</v>
       </c>
       <c r="D14" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="83">
+      <c r="E14" s="115">
         <f>ROUND(C14*D14,2)</f>
         <v/>
       </c>
@@ -7541,13 +8616,13 @@
           <t>加入原有A+</t>
         </is>
       </c>
-      <c r="C15" s="81" t="n">
+      <c r="C15" s="113" t="n">
         <v>25</v>
       </c>
       <c r="D15" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="83">
+      <c r="E15" s="115">
         <f>ROUND(C15*D15,2)</f>
         <v/>
       </c>
@@ -7578,13 +8653,13 @@
           <t>多个新产品共用新A+</t>
         </is>
       </c>
-      <c r="C16" s="81" t="n">
+      <c r="C16" s="113" t="n">
         <v>75</v>
       </c>
       <c r="D16" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="83">
+      <c r="E16" s="115">
         <f>ROUND(C16*D16,2)</f>
         <v/>
       </c>
@@ -7615,13 +8690,13 @@
           <t>每个ASIN分别制作不同A+</t>
         </is>
       </c>
-      <c r="C17" s="81" t="n">
+      <c r="C17" s="113" t="n">
         <v>375</v>
       </c>
       <c r="D17" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="83">
+      <c r="E17" s="115">
         <f>ROUND(C17*D17,2)</f>
         <v/>
       </c>
@@ -7652,13 +8727,13 @@
           <t>ASIN加入原有视频</t>
         </is>
       </c>
-      <c r="C18" s="81" t="n">
+      <c r="C18" s="113" t="n">
         <v>10</v>
       </c>
       <c r="D18" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="83">
+      <c r="E18" s="115">
         <f>ROUND(C18*D18,2)</f>
         <v/>
       </c>
@@ -7689,13 +8764,13 @@
           <t>多个产品共用新视频</t>
         </is>
       </c>
-      <c r="C19" s="81" t="n">
+      <c r="C19" s="113" t="n">
         <v>15</v>
       </c>
       <c r="D19" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="83">
+      <c r="E19" s="115">
         <f>ROUND(C19*D19,2)</f>
         <v/>
       </c>
@@ -7726,13 +8801,13 @@
           <t>每个ASIN上传不同视频</t>
         </is>
       </c>
-      <c r="C20" s="81" t="n">
+      <c r="C20" s="113" t="n">
         <v>75</v>
       </c>
       <c r="D20" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="83">
+      <c r="E20" s="115">
         <f>ROUND(C20*D20,2)</f>
         <v/>
       </c>
@@ -9359,7 +10434,7 @@
       <c r="D89" s="22" t="n">
         <v>1.3</v>
       </c>
-      <c r="E89" s="94">
+      <c r="E89" s="114">
         <f>ROUND(C89*D89,2)</f>
         <v/>
       </c>
@@ -9396,7 +10471,7 @@
       <c r="D90" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E90" s="94">
+      <c r="E90" s="114">
         <f>ROUND(C90*D90,2)</f>
         <v/>
       </c>
@@ -9433,7 +10508,7 @@
       <c r="D91" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="94">
+      <c r="E91" s="114">
         <f>ROUND(C91*D91,2)</f>
         <v/>
       </c>
@@ -9470,7 +10545,7 @@
       <c r="D92" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="94">
+      <c r="E92" s="114">
         <f>ROUND(C92*D92,2)</f>
         <v/>
       </c>
@@ -9507,7 +10582,7 @@
       <c r="D93" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="94">
+      <c r="E93" s="114">
         <f>ROUND(C93*D93,2)</f>
         <v/>
       </c>
@@ -9544,7 +10619,7 @@
       <c r="D94" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="94">
+      <c r="E94" s="114">
         <f>ROUND(C94*D94,2)</f>
         <v/>
       </c>
@@ -9581,7 +10656,7 @@
       <c r="D95" s="22" t="n">
         <v>1.6</v>
       </c>
-      <c r="E95" s="94">
+      <c r="E95" s="114">
         <f>ROUND(C95*D95,2)</f>
         <v/>
       </c>
@@ -9661,13 +10736,13 @@
           <t>同一模块增加两项参数</t>
         </is>
       </c>
-      <c r="C100" s="94" t="n">
+      <c r="C100" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D100" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E100" s="94">
+      <c r="E100" s="114">
         <f>ROUND(C100*D100,2)</f>
         <v/>
       </c>
@@ -9694,13 +10769,13 @@
           <t>一个模块增加信息，另一个模块删除信息</t>
         </is>
       </c>
-      <c r="C101" s="94" t="n">
+      <c r="C101" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D101" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="94">
+      <c r="E101" s="114">
         <f>ROUND(C101*D101,2)</f>
         <v/>
       </c>
@@ -9727,13 +10802,13 @@
           <t>修改1个已有视频的标题等信息</t>
         </is>
       </c>
-      <c r="C102" s="94" t="n">
+      <c r="C102" s="114" t="n">
         <v>5</v>
       </c>
       <c r="D102" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="94">
+      <c r="E102" s="114">
         <f>ROUND(C102*D102,2)</f>
         <v/>
       </c>
@@ -9760,13 +10835,13 @@
           <t>替换上传1个视频，并填写标题及首次绑定ASIN</t>
         </is>
       </c>
-      <c r="C103" s="94" t="n">
+      <c r="C103" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D103" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="94">
+      <c r="E103" s="114">
         <f>ROUND(C103*D103,2)</f>
         <v/>
       </c>
@@ -9793,13 +10868,13 @@
           <t>已有视频改标题，并新增1个SKU对应ASIN</t>
         </is>
       </c>
-      <c r="C104" s="94" t="n">
+      <c r="C104" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D104" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="94">
+      <c r="E104" s="114">
         <f>ROUND(C104*D104,2)</f>
         <v/>
       </c>
@@ -9826,13 +10901,13 @@
           <t>已有视频改标题，并新增5个SKU对应ASIN</t>
         </is>
       </c>
-      <c r="C105" s="94" t="n">
+      <c r="C105" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D105" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E105" s="94">
+      <c r="E105" s="114">
         <f>ROUND(C105*D105,2)</f>
         <v/>
       </c>
@@ -9859,13 +10934,13 @@
           <t>上传失败后的重试或重复上传同一文件</t>
         </is>
       </c>
-      <c r="C106" s="94" t="n">
+      <c r="C106" s="114" t="n">
         <v>0</v>
       </c>
       <c r="D106" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E106" s="94">
+      <c r="E106" s="114">
         <f>ROUND(C106*D106,2)</f>
         <v/>
       </c>
@@ -9941,13 +11016,13 @@
           <t>一次安排10个SKU按各自指定价格调整</t>
         </is>
       </c>
-      <c r="C111" s="94" t="n">
+      <c r="C111" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D111" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E111" s="94" t="n">
+      <c r="E111" s="114" t="n">
         <v>15</v>
       </c>
       <c r="F111" s="0" t="inlineStr">
@@ -9973,13 +11048,13 @@
           <t>创建1个Coupon，含20个SKU</t>
         </is>
       </c>
-      <c r="C112" s="94" t="n">
+      <c r="C112" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D112" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E112" s="94" t="n">
+      <c r="E112" s="114" t="n">
         <v>15</v>
       </c>
       <c r="F112" s="0" t="inlineStr">
@@ -10005,13 +11080,13 @@
           <t>创建3个Coupon和2个Promotion</t>
         </is>
       </c>
-      <c r="C113" s="94" t="n">
+      <c r="C113" s="114" t="n">
         <v>75</v>
       </c>
       <c r="D113" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E113" s="94" t="n">
+      <c r="E113" s="114" t="n">
         <v>75</v>
       </c>
       <c r="F113" s="0" t="inlineStr">
@@ -10034,16 +11109,16 @@
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>主动发现并完成3个独立Buy Box任务，均符合1.5倍条件</t>
-        </is>
-      </c>
-      <c r="C114" s="94" t="n">
+          <t>主动发现并完成3个不同ASIN的Buy Box处理，均验收且符合1.5倍条件</t>
+        </is>
+      </c>
+      <c r="C114" s="114" t="n">
         <v>45</v>
       </c>
       <c r="D114" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="94">
+      <c r="E114" s="114">
         <f>ROUND(C114*D114*1.5,2)</f>
         <v/>
       </c>
@@ -10066,7 +11141,7 @@
     <row r="117" ht="30" customHeight="1" s="1">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>Buy Box异常处理：固定15元，处理验收与恢复结果分开记录</t>
+          <t>Buy Box异常处理：基础15元/ASIN，处理验收与恢复结果分开记录</t>
         </is>
       </c>
     </row>
@@ -10120,16 +11195,16 @@
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>首次开Case后恢复</t>
-        </is>
-      </c>
-      <c r="C119" s="94" t="n">
+          <t>同站点1个ASIN：首次开Case后恢复</t>
+        </is>
+      </c>
+      <c r="C119" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D119" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E119" s="94" t="n">
+      <c r="E119" s="114" t="n">
         <v>15</v>
       </c>
       <c r="F119" s="0" t="inlineStr">
@@ -10152,21 +11227,21 @@
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>多次开Case后恢复</t>
-        </is>
-      </c>
-      <c r="C120" s="94" t="n">
+          <t>同站点1个ASIN：多次开Case后恢复</t>
+        </is>
+      </c>
+      <c r="C120" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D120" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E120" s="94" t="n">
+      <c r="E120" s="114" t="n">
         <v>15</v>
       </c>
       <c r="F120" s="0" t="inlineStr">
         <is>
-          <t>同一任务合并计费</t>
+          <t>同一站点同一ASIN同一异常合并计费</t>
         </is>
       </c>
       <c r="G120" s="0" t="inlineStr">
@@ -10184,16 +11259,16 @@
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>未恢复，经负责人确认阶段结案</t>
-        </is>
-      </c>
-      <c r="C121" s="94" t="n">
+          <t>同站点1个ASIN：未恢复，经负责人确认阶段结案</t>
+        </is>
+      </c>
+      <c r="C121" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D121" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E121" s="94" t="n">
+      <c r="E121" s="114" t="n">
         <v>15</v>
       </c>
       <c r="F121" s="0" t="inlineStr">
@@ -10216,7 +11291,7 @@
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>未恢复，仍在处理中</t>
+          <t>同站点1个ASIN：未恢复，仍在处理中</t>
         </is>
       </c>
       <c r="D122" s="0" t="n">
@@ -10246,16 +11321,16 @@
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>已阶段结案计15元，后续同一异常恢复</t>
-        </is>
-      </c>
-      <c r="C123" s="94" t="n">
+          <t>同站点1个ASIN：已阶段结案计15元，后续同一异常恢复</t>
+        </is>
+      </c>
+      <c r="C123" s="114" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E123" s="94" t="n">
+      <c r="E123" s="114" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="0" t="inlineStr">
@@ -10265,7 +11340,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>同一任务累计不超过15元</t>
+          <t>同一站点同一ASIN同一异常基础金额累计15元</t>
         </is>
       </c>
       <c r="H123" s="0" t="n"/>
@@ -10330,13 +11405,13 @@
           <t>提报1个独立Deal，包含多个SKU</t>
         </is>
       </c>
-      <c r="C128" s="94" t="n">
+      <c r="C128" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D128" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="94" t="n">
+      <c r="E128" s="114" t="n">
         <v>10</v>
       </c>
       <c r="F128" s="0" t="inlineStr">
@@ -10362,13 +11437,13 @@
           <t>提报5个独立Deal</t>
         </is>
       </c>
-      <c r="C129" s="94" t="n">
+      <c r="C129" s="114" t="n">
         <v>50</v>
       </c>
       <c r="D129" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E129" s="94" t="n">
+      <c r="E129" s="114" t="n">
         <v>50</v>
       </c>
       <c r="F129" s="0" t="inlineStr">
@@ -10394,13 +11469,13 @@
           <t>1个活动创建中报错，修正后重新提交并核验</t>
         </is>
       </c>
-      <c r="C130" s="94" t="n">
+      <c r="C130" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D130" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E130" s="94" t="n">
+      <c r="E130" s="114" t="n">
         <v>15</v>
       </c>
       <c r="F130" s="0" t="inlineStr">
@@ -10426,13 +11501,13 @@
           <t>同一Deal提交失败，修正参数后重新提报并核验</t>
         </is>
       </c>
-      <c r="C131" s="94" t="n">
+      <c r="C131" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D131" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E131" s="94" t="n">
+      <c r="E131" s="114" t="n">
         <v>10</v>
       </c>
       <c r="F131" s="0" t="inlineStr">
@@ -10507,13 +11582,13 @@
           <t>创建3个独立SP Campaign</t>
         </is>
       </c>
-      <c r="C136" s="94" t="n">
+      <c r="C136" s="114" t="n">
         <v>45</v>
       </c>
       <c r="D136" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="94" t="n">
+      <c r="E136" s="114" t="n">
         <v>45</v>
       </c>
       <c r="F136" s="0" t="inlineStr">
@@ -10543,13 +11618,13 @@
           <t>创建3个独立SB Campaign</t>
         </is>
       </c>
-      <c r="C137" s="94" t="n">
+      <c r="C137" s="114" t="n">
         <v>60</v>
       </c>
       <c r="D137" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E137" s="94" t="n">
+      <c r="E137" s="114" t="n">
         <v>60</v>
       </c>
       <c r="F137" s="0" t="inlineStr">
@@ -10579,13 +11654,13 @@
           <t>创建1个SBV Campaign</t>
         </is>
       </c>
-      <c r="C138" s="94" t="n">
+      <c r="C138" s="114" t="n">
         <v>20</v>
       </c>
       <c r="D138" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E138" s="94" t="n">
+      <c r="E138" s="114" t="n">
         <v>20</v>
       </c>
       <c r="F138" s="0" t="inlineStr">
@@ -10615,13 +11690,13 @@
           <t>创建1个SD Campaign</t>
         </is>
       </c>
-      <c r="C139" s="94" t="n">
+      <c r="C139" s="114" t="n">
         <v>20</v>
       </c>
       <c r="D139" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E139" s="94" t="n">
+      <c r="E139" s="114" t="n">
         <v>20</v>
       </c>
       <c r="F139" s="0" t="inlineStr">
@@ -10651,13 +11726,13 @@
           <t>1个SP Campaign产生多条Ads Change记录</t>
         </is>
       </c>
-      <c r="C140" s="94" t="n">
+      <c r="C140" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D140" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E140" s="94" t="n">
+      <c r="E140" s="114" t="n">
         <v>15</v>
       </c>
       <c r="F140" s="0" t="inlineStr">
@@ -11032,7 +12107,7 @@
       </c>
       <c r="B155" s="28" t="inlineStr">
         <is>
-          <t>主动发现Buy Box丢失，及时截图取证并开Case处理</t>
+          <t>同站点1个ASIN：主动发现Buy Box丢失，及时截图取证并开Case处理</t>
         </is>
       </c>
       <c r="C155" s="95" t="n">
@@ -11453,13 +12528,13 @@
           <t>同次安排同批移除10个SKU</t>
         </is>
       </c>
-      <c r="C170" s="94" t="n">
+      <c r="C170" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D170" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E170" s="94">
+      <c r="E170" s="114">
         <f>ROUND(C170*D170,2)</f>
         <v/>
       </c>
@@ -11490,13 +12565,13 @@
           <t>同批完成多个SKU的Relist</t>
         </is>
       </c>
-      <c r="C171" s="94" t="n">
+      <c r="C171" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D171" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E171" s="94">
+      <c r="E171" s="114">
         <f>ROUND(C171*D171,2)</f>
         <v/>
       </c>
@@ -11527,13 +12602,13 @@
           <t>同一问题先Relist，再申诉并完成处理</t>
         </is>
       </c>
-      <c r="C172" s="94" t="n">
+      <c r="C172" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D172" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E172" s="94">
+      <c r="E172" s="114">
         <f>ROUND(C172*D172,2)</f>
         <v/>
       </c>
@@ -11564,13 +12639,13 @@
           <t>已有完整电池豁免或化学品资料，核对后提交</t>
         </is>
       </c>
-      <c r="C173" s="94" t="n">
+      <c r="C173" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D173" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E173" s="94">
+      <c r="E173" s="114">
         <f>ROUND(C173*D173,2)</f>
         <v/>
       </c>
@@ -11601,13 +12676,13 @@
           <t>需向负责人获取并核对资料，再提交跟进</t>
         </is>
       </c>
-      <c r="C174" s="94" t="n">
+      <c r="C174" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D174" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E174" s="94">
+      <c r="E174" s="114">
         <f>ROUND(C174*D174,2)</f>
         <v/>
       </c>
@@ -11638,13 +12713,13 @@
           <t>申诉未解决，凭证完整且负责人确认阶段结案</t>
         </is>
       </c>
-      <c r="C175" s="94" t="n">
+      <c r="C175" s="114" t="n">
         <v>15</v>
       </c>
       <c r="D175" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E175" s="94">
+      <c r="E175" s="114">
         <f>ROUND(C175*D175,2)</f>
         <v/>
       </c>
@@ -11724,13 +12799,13 @@
           <t>1个ASIN同一异常，多次Appeal或Case后完成处理</t>
         </is>
       </c>
-      <c r="C180" s="94" t="n">
+      <c r="C180" s="114" t="n">
         <v>20</v>
       </c>
       <c r="D180" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E180" s="94" t="n">
+      <c r="E180" s="114" t="n">
         <v>20</v>
       </c>
       <c r="F180" s="0" t="inlineStr">
@@ -11760,13 +12835,13 @@
           <t>5个ASIN共用一个Case，逐个完成处理及核验</t>
         </is>
       </c>
-      <c r="C181" s="94" t="n">
+      <c r="C181" s="114" t="n">
         <v>100</v>
       </c>
       <c r="D181" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E181" s="94" t="n">
+      <c r="E181" s="114" t="n">
         <v>100</v>
       </c>
       <c r="F181" s="0" t="inlineStr">
@@ -11796,13 +12871,13 @@
           <t>1个ASIN未恢复，记录完整且负责人确认阶段结案</t>
         </is>
       </c>
-      <c r="C182" s="94" t="n">
+      <c r="C182" s="114" t="n">
         <v>20</v>
       </c>
       <c r="D182" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E182" s="94" t="n">
+      <c r="E182" s="114" t="n">
         <v>20</v>
       </c>
       <c r="F182" s="0" t="inlineStr">
@@ -11832,13 +12907,13 @@
           <t>同一异常已按滞留库存、Buy Box或变体关系维护计费</t>
         </is>
       </c>
-      <c r="C183" s="94" t="n">
+      <c r="C183" s="114" t="n">
         <v>0</v>
       </c>
       <c r="D183" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="94" t="n">
+      <c r="E183" s="114" t="n">
         <v>0</v>
       </c>
       <c r="F183" s="0" t="inlineStr">
@@ -11917,13 +12992,13 @@
           <t>1/2英寸尺寸类目原有模块中加入10个新品</t>
         </is>
       </c>
-      <c r="C188" s="94" t="n">
+      <c r="C188" s="114" t="n">
         <v>10</v>
       </c>
       <c r="D188" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E188" s="94">
+      <c r="E188" s="114">
         <f>ROUND(C188*D188,2)</f>
         <v/>
       </c>
@@ -11954,13 +13029,13 @@
           <t>1/2英寸与3/4英寸两个类目分别增删商品</t>
         </is>
       </c>
-      <c r="C189" s="94" t="n">
+      <c r="C189" s="114" t="n">
         <v>20</v>
       </c>
       <c r="D189" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E189" s="94">
+      <c r="E189" s="114">
         <f>ROUND(C189*D189,2)</f>
         <v/>
       </c>
@@ -11991,13 +13066,13 @@
           <t>1/2英寸类目重建模块并配置商品</t>
         </is>
       </c>
-      <c r="C190" s="94" t="n">
+      <c r="C190" s="114" t="n">
         <v>25</v>
       </c>
       <c r="D190" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E190" s="94">
+      <c r="E190" s="114">
         <f>ROUND(C190*D190,2)</f>
         <v/>
       </c>
@@ -12028,13 +13103,13 @@
           <t>两个尺寸类目分别重建模块并配置商品</t>
         </is>
       </c>
-      <c r="C191" s="94" t="n">
+      <c r="C191" s="114" t="n">
         <v>50</v>
       </c>
       <c r="D191" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E191" s="94">
+      <c r="E191" s="114">
         <f>ROUND(C191*D191,2)</f>
         <v/>
       </c>
@@ -12065,13 +13140,13 @@
           <t>两个尺寸类目更新，另修复其他板块历史报错后提交</t>
         </is>
       </c>
-      <c r="C192" s="94" t="n">
+      <c r="C192" s="114" t="n">
         <v>35</v>
       </c>
       <c r="D192" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E192" s="94">
+      <c r="E192" s="114">
         <f>ROUND(C192*D192,2)</f>
         <v/>
       </c>
@@ -12102,13 +13177,13 @@
           <t>两个尺寸类目更新，修复本人本次造成的报错</t>
         </is>
       </c>
-      <c r="C193" s="94" t="n">
+      <c r="C193" s="114" t="n">
         <v>20</v>
       </c>
       <c r="D193" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E193" s="94">
+      <c r="E193" s="114">
         <f>ROUND(C193*D193,2)</f>
         <v/>
       </c>
@@ -12572,494 +13647,1034 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="24" t="inlineStr">
+        <is>
+          <t>新增项目计费示例</t>
+        </is>
+      </c>
+    </row>
     <row r="214">
-      <c r="A214" s="24" t="inlineStr">
+      <c r="A214" s="56" t="inlineStr">
+        <is>
+          <t>工作项目</t>
+        </is>
+      </c>
+      <c r="B214" s="56" t="inlineStr">
+        <is>
+          <t>实际场景</t>
+        </is>
+      </c>
+      <c r="C214" s="56" t="inlineStr">
+        <is>
+          <t>累计基础金额</t>
+        </is>
+      </c>
+      <c r="D214" s="56" t="inlineStr">
+        <is>
+          <t>难度系数</t>
+        </is>
+      </c>
+      <c r="E214" s="56" t="inlineStr">
+        <is>
+          <t>任务金额</t>
+        </is>
+      </c>
+      <c r="F214" s="56" t="inlineStr">
+        <is>
+          <t>计算依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t>利润或亏损原因分析与优化建议</t>
+        </is>
+      </c>
+      <c r="B215" s="0" t="inlineStr">
+        <is>
+          <t>完整分析1个ASIN利润问题并提出建议</t>
+        </is>
+      </c>
+      <c r="C215" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D215" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" s="0">
+        <f>ROUND(C215*D215,2)</f>
+        <v/>
+      </c>
+      <c r="F215" s="0" t="inlineStr">
+        <is>
+          <t>30元/完整报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t>利润分析（初步）</t>
+        </is>
+      </c>
+      <c r="B216" s="0" t="inlineStr">
+        <is>
+          <t>初步排查并结案</t>
+        </is>
+      </c>
+      <c r="C216" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="D216" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" s="0">
+        <f>ROUND(C216*D216,2)</f>
+        <v/>
+      </c>
+      <c r="F216" s="0" t="inlineStr">
+        <is>
+          <t>初步15元；之后补齐再补15元</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t>活动效果复盘</t>
+        </is>
+      </c>
+      <c r="B217" s="0" t="inlineStr">
+        <is>
+          <t>1场Coupon活动覆盖10个ASIN的完整复盘</t>
+        </is>
+      </c>
+      <c r="C217" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D217" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" s="0">
+        <f>ROUND(C217*D217,2)</f>
+        <v/>
+      </c>
+      <c r="F217" s="0" t="inlineStr">
+        <is>
+          <t>30元/独立活动，不按ASIN累加</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t>费用异常核查与Case申诉</t>
+        </is>
+      </c>
+      <c r="B218" s="0" t="inlineStr">
+        <is>
+          <t>1个ASIN尺寸分级费用异常，开Case并跟进</t>
+        </is>
+      </c>
+      <c r="C218" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D218" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" s="0">
+        <f>ROUND(C218*D218,2)</f>
+        <v/>
+      </c>
+      <c r="F218" s="0" t="inlineStr">
+        <is>
+          <t>20元/独立费用问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t>跟卖监控</t>
+        </is>
+      </c>
+      <c r="B219" s="0" t="inlineStr">
+        <is>
+          <t>本周完成全部约定检查</t>
+        </is>
+      </c>
+      <c r="C219" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D219" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" s="0">
+        <f>ROUND(C219*D219,2)</f>
+        <v/>
+      </c>
+      <c r="F219" s="0" t="inlineStr">
+        <is>
+          <t>5元/站点/清单/周</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t>跟卖取证与举报</t>
+        </is>
+      </c>
+      <c r="B220" s="0" t="inlineStr">
+        <is>
+          <t>已有证据完成举报并跟进</t>
+        </is>
+      </c>
+      <c r="C220" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="D220" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" s="0">
+        <f>ROUND(C220*D220,2)</f>
+        <v/>
+      </c>
+      <c r="F220" s="0" t="inlineStr">
+        <is>
+          <t>30元/独立案件</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t>跟卖取证（含Test Buy）</t>
+        </is>
+      </c>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t>完成Test Buy取证全过程及案件处理</t>
+        </is>
+      </c>
+      <c r="C221" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D221" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" s="0">
+        <f>ROUND(C221*D221,2)</f>
+        <v/>
+      </c>
+      <c r="F221" s="0" t="inlineStr">
+        <is>
+          <t>整案50元（含取证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t>Vine报名与跟进</t>
+        </is>
+      </c>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t>1个报名项目含多个子SKU</t>
+        </is>
+      </c>
+      <c r="C222" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="D222" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" s="0">
+        <f>ROUND(C222*D222,2)</f>
+        <v/>
+      </c>
+      <c r="F222" s="0" t="inlineStr">
+        <is>
+          <t>15元/报名项目，不按子SKU累加</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story全新策划</t>
+        </is>
+      </c>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t>全新策划1份品牌故事并绑定20个ASIN</t>
+        </is>
+      </c>
+      <c r="C223" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="D223" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" s="0">
+        <f>ROUND(C223*D223,2)</f>
+        <v/>
+      </c>
+      <c r="F223" s="0" t="inlineStr">
+        <is>
+          <t>75元/独立内容，不按ASIN累加</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story局部修改</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>修改已有品牌故事的2张卡片</t>
+        </is>
+      </c>
+      <c r="C224" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D224" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="0">
+        <f>ROUND(C224*D224,2)</f>
+        <v/>
+      </c>
+      <c r="F224" s="0" t="inlineStr">
+        <is>
+          <t>10元/同份同轮</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="inlineStr">
+        <is>
+          <t>Subscribe &amp; Save设置</t>
+        </is>
+      </c>
+      <c r="B225" s="0" t="inlineStr">
+        <is>
+          <t>同批10个ASIN加入并设折扣</t>
+        </is>
+      </c>
+      <c r="C225" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D225" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="0">
+        <f>ROUND(C225*D225,2)</f>
+        <v/>
+      </c>
+      <c r="F225" s="0" t="inlineStr">
+        <is>
+          <t>10元/批，不按ASIN累加</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle新建</t>
+        </is>
+      </c>
+      <c r="B226" s="0" t="inlineStr">
+        <is>
+          <t>新建1个虚拟捆绑商品</t>
+        </is>
+      </c>
+      <c r="C226" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D226" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" s="0">
+        <f>ROUND(C226*D226,2)</f>
+        <v/>
+      </c>
+      <c r="F226" s="0" t="inlineStr">
+        <is>
+          <t>25元/独立捆绑</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle维护</t>
+        </is>
+      </c>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t>已有捆绑修改标题和价格</t>
+        </is>
+      </c>
+      <c r="C227" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D227" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="0">
+        <f>ROUND(C227*D227,2)</f>
+        <v/>
+      </c>
+      <c r="F227" s="0" t="inlineStr">
+        <is>
+          <t>10元/同捆绑同轮维护</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="24" t="inlineStr">
         <is>
           <t>防重复计费速查：常见场景判定</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="31" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="31" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B215" s="31" t="inlineStr">
+      <c r="B231" s="31" t="inlineStr">
         <is>
           <t>场景描述</t>
         </is>
       </c>
-      <c r="C215" s="31" t="inlineStr">
+      <c r="C231" s="31" t="inlineStr">
         <is>
           <t>正确计费</t>
         </is>
       </c>
-      <c r="D215" s="31" t="inlineStr">
+      <c r="D231" s="31" t="inlineStr">
         <is>
           <t>错误计费</t>
         </is>
       </c>
-      <c r="E215" s="31" t="inlineStr">
+      <c r="E231" s="31" t="inlineStr">
         <is>
           <t>判定依据</t>
         </is>
       </c>
-      <c r="F215" s="31" t="inlineStr">
+      <c r="F231" s="31" t="inlineStr">
         <is>
           <t>所在规则</t>
         </is>
       </c>
-      <c r="G215" s="31" t="n"/>
-      <c r="H215" s="31" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B216" s="32" t="inlineStr">
+      <c r="G231" s="31" t="n"/>
+      <c r="H231" s="31" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B232" s="32" t="inlineStr">
         <is>
           <t>A+完全重做后，是否可同时计A+制作发布75元和全新重做75元？</t>
         </is>
       </c>
-      <c r="C216" s="32" t="inlineStr">
+      <c r="C232" s="32" t="inlineStr">
         <is>
           <t>只计一次75元</t>
         </is>
       </c>
-      <c r="D216" s="32" t="inlineStr">
+      <c r="D232" s="32" t="inlineStr">
         <is>
           <t>叠加计150元</t>
         </is>
       </c>
-      <c r="E216" s="32" t="inlineStr">
+      <c r="E232" s="32" t="inlineStr">
         <is>
           <t>同一成果只计一次</t>
         </is>
       </c>
-      <c r="F216" s="32" t="inlineStr">
+      <c r="F232" s="32" t="inlineStr">
         <is>
           <t>任务评分·A+制作发布</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="32" t="n">
+    <row r="233">
+      <c r="A233" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B217" s="32" t="inlineStr">
+      <c r="B233" s="32" t="inlineStr">
         <is>
           <t>同一电压错误出现在标题、五点和A+三个位置</t>
         </is>
       </c>
-      <c r="C217" s="32" t="inlineStr">
+      <c r="C233" s="32" t="inlineStr">
         <is>
           <t>修正全部位置，共10元</t>
         </is>
       </c>
-      <c r="D217" s="32" t="inlineStr">
+      <c r="D233" s="32" t="inlineStr">
         <is>
           <t>按位置分别计30元</t>
         </is>
       </c>
-      <c r="E217" s="32" t="inlineStr">
+      <c r="E233" s="32" t="inlineStr">
         <is>
           <t>同源错误合并为1个错误点</t>
         </is>
       </c>
-      <c r="F217" s="32" t="inlineStr">
+      <c r="F233" s="32" t="inlineStr">
         <is>
           <t>任务评分·Listing纠错</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="32" t="n">
+    <row r="234">
+      <c r="A234" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B218" s="32" t="inlineStr">
+      <c r="B234" s="32" t="inlineStr">
         <is>
           <t>员工自主发现价格异常并修正，是否同时计任务金额和主动金额？</t>
         </is>
       </c>
-      <c r="C218" s="32" t="inlineStr">
+      <c r="C234" s="32" t="inlineStr">
         <is>
           <t>按正常金额×主动倍率</t>
         </is>
       </c>
-      <c r="D218" s="32" t="inlineStr">
+      <c r="D234" s="32" t="inlineStr">
         <is>
           <t>正常金额＋另加主动金额</t>
         </is>
       </c>
-      <c r="E218" s="32" t="inlineStr">
+      <c r="E234" s="32" t="inlineStr">
         <is>
           <t>发起来源互斥：自主发起按倍率，不另加正常金额</t>
         </is>
       </c>
-      <c r="F218" s="32" t="inlineStr">
+      <c r="F234" s="32" t="inlineStr">
         <is>
           <t>主动改善评价·二</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="32" t="n">
+    <row r="235">
+      <c r="A235" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B219" s="32" t="inlineStr">
+      <c r="B235" s="32" t="inlineStr">
         <is>
           <t>员工先提出建议，经负责人批准后建立任务执行</t>
         </is>
       </c>
-      <c r="C219" s="32" t="inlineStr">
+      <c r="C235" s="32" t="inlineStr">
         <is>
           <t>按正常金额×主动倍率</t>
         </is>
       </c>
-      <c r="D219" s="32" t="inlineStr">
+      <c r="D235" s="32" t="inlineStr">
         <is>
           <t>只按普通金额结算，遗漏适用主动倍率</t>
         </is>
       </c>
-      <c r="E219" s="32" t="inlineStr">
+      <c r="E235" s="32" t="inlineStr">
         <is>
           <t>先提出即属主动发起，补建任务不改变来源</t>
         </is>
       </c>
-      <c r="F219" s="32" t="inlineStr">
+      <c r="F235" s="32" t="inlineStr">
         <is>
           <t>主动改善评价·A17</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="32" t="n">
+    <row r="236">
+      <c r="A236" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B220" s="32" t="inlineStr">
+      <c r="B236" s="32" t="inlineStr">
         <is>
           <t>同一滞留库存问题先Relist再申诉</t>
         </is>
       </c>
-      <c r="C220" s="32" t="inlineStr">
+      <c r="C236" s="32" t="inlineStr">
         <is>
           <t>合计15元（取最高档）</t>
         </is>
       </c>
-      <c r="D220" s="32" t="inlineStr">
+      <c r="D236" s="32" t="inlineStr">
         <is>
           <t>移除10元＋申诉15元＝25元</t>
         </is>
       </c>
-      <c r="E220" s="32" t="inlineStr">
+      <c r="E236" s="32" t="inlineStr">
         <is>
           <t>同一问题连续处理只取最高适用金额</t>
         </is>
       </c>
-      <c r="F220" s="32" t="inlineStr">
+      <c r="F236" s="32" t="inlineStr">
         <is>
           <t>任务评分·滞留库存</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="32" t="n">
+    <row r="237">
+      <c r="A237" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B221" s="32" t="inlineStr">
+      <c r="B237" s="32" t="inlineStr">
         <is>
           <t>上架组包含5个SKU，OA记录5条</t>
         </is>
       </c>
-      <c r="C221" s="32" t="inlineStr">
+      <c r="C237" s="32" t="inlineStr">
         <is>
           <t>按组总金额计（如52元）</t>
         </is>
       </c>
-      <c r="D221" s="32" t="inlineStr">
+      <c r="D237" s="32" t="inlineStr">
         <is>
           <t>5条OA各计25元＝125元</t>
         </is>
       </c>
-      <c r="E221" s="32" t="inlineStr">
+      <c r="E237" s="32" t="inlineStr">
         <is>
           <t>以执行组为单位，OA分摊组总金额</t>
         </is>
       </c>
-      <c r="F221" s="32" t="inlineStr">
+      <c r="F237" s="32" t="inlineStr">
         <is>
           <t>场景示例·上架组</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="32" t="n">
+    <row r="238">
+      <c r="A238" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B222" s="32" t="inlineStr">
+      <c r="B238" s="32" t="inlineStr">
         <is>
           <t>5个SKU共用同一份新A+</t>
         </is>
       </c>
-      <c r="C222" s="32" t="inlineStr">
+      <c r="C238" s="32" t="inlineStr">
         <is>
           <t>1份×75元＝75元</t>
         </is>
       </c>
-      <c r="D222" s="32" t="inlineStr">
+      <c r="D238" s="32" t="inlineStr">
         <is>
           <t>5×75元＝375元</t>
         </is>
       </c>
-      <c r="E222" s="32" t="inlineStr">
+      <c r="E238" s="32" t="inlineStr">
         <is>
           <t>共用同一份内容只计一份</t>
         </is>
       </c>
-      <c r="F222" s="32" t="inlineStr">
+      <c r="F238" s="32" t="inlineStr">
         <is>
           <t>任务评分·A+制作发布</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="32" t="n">
+    <row r="239">
+      <c r="A239" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B223" s="32" t="inlineStr">
+      <c r="B239" s="32" t="inlineStr">
         <is>
           <t>同一份A+同一轮修改了6个模块</t>
         </is>
       </c>
-      <c r="C223" s="32" t="inlineStr">
+      <c r="C239" s="32" t="inlineStr">
         <is>
           <t>合计10元</t>
         </is>
       </c>
-      <c r="D223" s="32" t="inlineStr">
+      <c r="D239" s="32" t="inlineStr">
         <is>
           <t>6×10元＝60元</t>
         </is>
       </c>
-      <c r="E223" s="32" t="inlineStr">
+      <c r="E239" s="32" t="inlineStr">
         <is>
           <t>同份同轮合计10元，不按模块数量累加</t>
         </is>
       </c>
-      <c r="F223" s="32" t="inlineStr">
+      <c r="F239" s="32" t="inlineStr">
         <is>
           <t>任务评分·A+增删修改</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="32" t="n">
+    <row r="240">
+      <c r="A240" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B224" s="32" t="inlineStr">
-        <is>
-          <t>Buy Box异常多次开Case后恢复</t>
-        </is>
-      </c>
-      <c r="C224" s="32" t="inlineStr">
+      <c r="B240" s="32" t="inlineStr">
+        <is>
+          <t>同站点1个ASIN的Buy Box异常多次开Case后恢复</t>
+        </is>
+      </c>
+      <c r="C240" s="32" t="inlineStr">
         <is>
           <t>合计15元</t>
         </is>
       </c>
-      <c r="D224" s="32" t="inlineStr">
+      <c r="D240" s="32" t="inlineStr">
         <is>
           <t>按Case数量计费</t>
         </is>
       </c>
-      <c r="E224" s="32" t="inlineStr">
-        <is>
-          <t>同一任务合并计费，不按Case数量加</t>
-        </is>
-      </c>
-      <c r="F224" s="32" t="inlineStr">
+      <c r="E240" s="32" t="inlineStr">
+        <is>
+          <t>按ASIN计费，同一ASIN多个SKU或多个Case不增加金额</t>
+        </is>
+      </c>
+      <c r="F240" s="32" t="inlineStr">
         <is>
           <t>任务评分·Buy Box</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="32" t="n">
+    <row r="241">
+      <c r="A241" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B225" s="32" t="inlineStr">
+      <c r="B241" s="32" t="inlineStr">
         <is>
           <t>同一Listing标题在复盘前又做了一次优化修改</t>
         </is>
       </c>
-      <c r="C225" s="32" t="inlineStr">
+      <c r="C241" s="32" t="inlineStr">
         <is>
           <t>并入原任务，不新增金额</t>
         </is>
       </c>
-      <c r="D225" s="32" t="inlineStr">
+      <c r="D241" s="32" t="inlineStr">
         <is>
           <t>新建优化任务再计10元</t>
         </is>
       </c>
-      <c r="E225" s="32" t="inlineStr">
+      <c r="E241" s="32" t="inlineStr">
         <is>
           <t>同模块复盘前追加并入，不重复</t>
         </is>
       </c>
-      <c r="F225" s="32" t="inlineStr">
+      <c r="F241" s="32" t="inlineStr">
         <is>
           <t>优化登记与复盘规则</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="32" t="n">
+    <row r="242">
+      <c r="A242" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="B226" s="32" t="inlineStr">
+      <c r="B242" s="32" t="inlineStr">
         <is>
           <t>创建1个SP Campaign产生多条Ads Change记录</t>
         </is>
       </c>
-      <c r="C226" s="32" t="inlineStr">
+      <c r="C242" s="32" t="inlineStr">
         <is>
           <t>只计一次15元</t>
         </is>
       </c>
-      <c r="D226" s="32" t="inlineStr">
+      <c r="D242" s="32" t="inlineStr">
         <is>
           <t>按Ads Change条数计费</t>
         </is>
       </c>
-      <c r="E226" s="32" t="inlineStr">
+      <c r="E242" s="32" t="inlineStr">
         <is>
           <t>以Campaign ID去重</t>
         </is>
       </c>
-      <c r="F226" s="32" t="inlineStr">
+      <c r="F242" s="32" t="inlineStr">
         <is>
           <t>任务评分·SP广告创建</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="32" t="n">
+    <row r="243">
+      <c r="A243" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B227" s="32" t="inlineStr">
+      <c r="B243" s="32" t="inlineStr">
         <is>
           <t>纠错修复的是自己上次操作造成的错误</t>
         </is>
       </c>
-      <c r="C227" s="32" t="inlineStr">
+      <c r="C243" s="32" t="inlineStr">
         <is>
           <t>不新增任务金额或主动金额</t>
         </is>
       </c>
-      <c r="D227" s="32" t="inlineStr">
+      <c r="D243" s="32" t="inlineStr">
         <is>
           <t>计纠错10元/错误点</t>
         </is>
       </c>
-      <c r="E227" s="32" t="inlineStr">
+      <c r="E243" s="32" t="inlineStr">
         <is>
           <t>修复本人错误属于返工</t>
         </is>
       </c>
-      <c r="F227" s="32" t="inlineStr">
+      <c r="F243" s="32" t="inlineStr">
         <is>
           <t>运营工作明细·Listing纠错</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="100" t="n">
+    <row r="244">
+      <c r="A244" s="100" t="n">
         <v>13</v>
       </c>
-      <c r="B228" s="100" t="inlineStr">
+      <c r="B244" s="100" t="inlineStr">
         <is>
           <t>3个尺寸共用同一套调研方案，是否分别领取75元？</t>
         </is>
       </c>
-      <c r="C228" s="100" t="inlineStr">
+      <c r="C244" s="100" t="inlineStr">
         <is>
           <t>共用方案只计一次75元</t>
         </is>
       </c>
-      <c r="D228" s="100" t="inlineStr">
+      <c r="D244" s="100" t="inlineStr">
         <is>
           <t>每个尺寸各领75元＝225元</t>
         </is>
       </c>
-      <c r="E228" s="100" t="inlineStr">
+      <c r="E244" s="100" t="inlineStr">
         <is>
           <t>共用调研/厂家/验证方案不重复领取</t>
         </is>
       </c>
-      <c r="F228" s="100" t="inlineStr">
+      <c r="F244" s="100" t="inlineStr">
         <is>
           <t>任务评分·新品开发</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="100" t="n">
+    <row r="245">
+      <c r="A245" s="100" t="n">
         <v>14</v>
       </c>
-      <c r="B229" s="100" t="inlineStr">
+      <c r="B245" s="100" t="inlineStr">
         <is>
           <t>已完成A+制作（75元），是否可同时计图片策划50元？</t>
         </is>
       </c>
-      <c r="C229" s="100" t="inlineStr">
+      <c r="C245" s="100" t="inlineStr">
         <is>
           <t>A+已含素材策划，不另计</t>
         </is>
       </c>
-      <c r="D229" s="100" t="inlineStr">
+      <c r="D245" s="100" t="inlineStr">
         <is>
           <t>叠加计75＋50＝125元</t>
         </is>
       </c>
-      <c r="E229" s="100" t="inlineStr">
+      <c r="E245" s="100" t="inlineStr">
         <is>
           <t>A+制作已包含素材策划</t>
         </is>
       </c>
-      <c r="F229" s="100" t="inlineStr">
+      <c r="F245" s="100" t="inlineStr">
         <is>
           <t>任务评分·产品图片策划</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="100" t="n">
+    <row r="246">
+      <c r="A246" s="100" t="n">
         <v>15</v>
       </c>
-      <c r="B230" s="100" t="inlineStr">
+      <c r="B246" s="100" t="inlineStr">
         <is>
           <t>调研/找厂已交付产品资料，是否可再计资料整理40元？</t>
         </is>
       </c>
-      <c r="C230" s="100" t="inlineStr">
+      <c r="C246" s="100" t="inlineStr">
         <is>
           <t>已交付的相同资料不重复计</t>
         </is>
       </c>
-      <c r="D230" s="100" t="inlineStr">
+      <c r="D246" s="100" t="inlineStr">
         <is>
           <t>调研75＋资料40＝叠加115元</t>
         </is>
       </c>
-      <c r="E230" s="100" t="inlineStr">
+      <c r="E246" s="100" t="inlineStr">
         <is>
           <t>同一交付不按两个项目分别领取</t>
         </is>
       </c>
-      <c r="F230" s="100" t="inlineStr">
+      <c r="F246" s="100" t="inlineStr">
         <is>
           <t>任务评分·产品资料整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story全新策划75元与A+制作发布75元是否叠加？</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>品牌故事和A+是不同内容区域，各自独立计费</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>两者叠加计150元</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story与A+为两种独立内容模块</t>
+        </is>
+      </c>
+      <c r="F247" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·Brand Story / A+制作发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>跟卖监控5元与跟卖取证30元是否叠加？</t>
+        </is>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>监控和取证是独立任务，分别计费</t>
+        </is>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>取证包含监控，只计30元</t>
+        </is>
+      </c>
+      <c r="E248" s="0" t="inlineStr">
+        <is>
+          <t>监控为固定巡检，取证为独立案件处理，可同时存在</t>
+        </is>
+      </c>
+      <c r="F248" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·品牌保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle创建25元与Listing创建25元是否叠加？</t>
+        </is>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle已含初始配置，不叠加Listing创建</t>
+        </is>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t>分别计50元</t>
+        </is>
+      </c>
+      <c r="E249" s="0" t="inlineStr">
+        <is>
+          <t>VB创建已包含文案填入和图片配置</t>
+        </is>
+      </c>
+      <c r="F249" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·Virtual Bundle</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B250" s="0" t="inlineStr">
+        <is>
+          <t>利润分析完成后另行改价，是否叠加？</t>
+        </is>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>分析30元＋价格调整15元，分别计费</t>
+        </is>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t>分析已包含改价</t>
+        </is>
+      </c>
+      <c r="E250" s="0" t="inlineStr">
+        <is>
+          <t>分析是交付报告和建议，改价是独立执行任务</t>
+        </is>
+      </c>
+      <c r="F250" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·利润分析 / 价格调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B251" s="0" t="inlineStr">
+        <is>
+          <t>同一案件先30元举报后补Test Buy，是否计30＋50＝80元？</t>
+        </is>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t>先结30元，补足至50元，不超过50元</t>
+        </is>
+      </c>
+      <c r="D251" s="0" t="inlineStr">
+        <is>
+          <t>分别计80元</t>
+        </is>
+      </c>
+      <c r="E251" s="0" t="inlineStr">
+        <is>
+          <t>两档只取最高，先结30元后补足最多20元</t>
+        </is>
+      </c>
+      <c r="F251" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·跟卖取证</t>
         </is>
       </c>
     </row>
@@ -13109,7 +14724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -13256,7 +14871,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>发现事实、合规或展示错误应及时纠正，不因等待复盘而延误。由本人上次操作造成的错误属于返工，不新增任务金额或主动改善金额。</t>
+          <t>事实错误或合规展示问题应及时处理，不因等待复盘拖延。是否另计酬须按本页“责任纠错与资料变更”规则核定：本人责任纠错不另计酬；按原确认资料正确执行后的新增变更，按对应任务验收计酬。</t>
         </is>
       </c>
     </row>
@@ -13305,6 +14920,114 @@
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>待确认 → 执行中 → 待生效核验 → 待复盘 → 已完成/已结算。数据不足记录延期；复盘未完成不建立同模块的新计费任务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1" s="1">
+      <c r="A17" s="111" t="inlineStr">
+        <is>
+          <t>责任纠错与资料变更</t>
+        </is>
+      </c>
+      <c r="B17" s="112" t="inlineStr">
+        <is>
+          <t>以下规则适用于所有工作项目，包括新品开发、运营执行和主动改善。判断依据是操作当时已确认的资料及执行记录，不以产品归属或当前参数倒推责任。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="115" customHeight="1" s="1">
+      <c r="A18" s="108" t="inlineStr">
+        <is>
+          <t>本人责任纠错不另计酬</t>
+        </is>
+      </c>
+      <c r="B18" s="107" t="inlineStr">
+        <is>
+          <t>因本人操作、编写或应核验事项的疏漏造成的错误，后续纠错、补交及返工属于原任务责任范围，不另计任务报酬、主动加成或成果奖励。跨月、补建OA任务不改变规则。本人开发产品也按此规则，不将该产品后续所有新增工作一律视为返工。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="115" customHeight="1" s="1">
+      <c r="A19" s="106" t="inlineStr">
+        <is>
+          <t>执行错误如何判定</t>
+        </is>
+      </c>
+      <c r="B19" s="105" t="inlineStr">
+        <is>
+          <t>当时确认资料正确，员工填写或上传结果与之不一致，属于执行错误。例：确认12V，上传24V，本人更正为12V不另计酬。资料缺失或冲突时未经确认自行填写导致错误，也属于责任纠错。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="115" customHeight="1" s="1">
+      <c r="A20" s="108" t="inlineStr">
+        <is>
+          <t>负责人更新或更正资料</t>
+        </is>
+      </c>
+      <c r="B20" s="107" t="inlineStr">
+        <is>
+          <t>员工按当时确认资料正确执行，之后负责人更新或更正参数，对执行员工而言按新增修改任务计酬。例：确认12V且上传12V，后续通知改24V，可按对应任务计酬。员工提出疑问并取得确认后正确执行的，适用同一原则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="115" customHeight="1" s="1">
+      <c r="A21" s="106" t="inlineStr">
+        <is>
+          <t>开发责任与新增需求</t>
+        </is>
+      </c>
+      <c r="B21" s="105" t="inlineStr">
+        <is>
+          <t>本人开发时应确认的参数、资料、图片信息或字幕有误或遗漏，或约定样品评估漏检，后续补救不另计酬。产品后续真实规格变更、新客户反馈带来的有效优化、平台规则变化或系统异常，可按对应新增任务计酬。同一人兼任产品负责人及执行人，不得通过更新资料将本人原有错误变为新增任务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="115" customHeight="1" s="1">
+      <c r="A22" s="108" t="inlineStr">
+        <is>
+          <t>保留原资料和执行证据</t>
+        </is>
+      </c>
+      <c r="B22" s="107" t="inlineStr">
+        <is>
+          <t>OA保留操作当时的附件或确认内容、版本及确认时间，后续新文件不得覆盖旧版本。员工自行编写的资料也保留提交确认版本；关联上传文件、修改记录或结果截图，以便比对当时依据和实际执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="115" customHeight="1" s="1">
+      <c r="A23" s="106" t="inlineStr">
+        <is>
+          <t>更正登记与责任确认</t>
+        </is>
+      </c>
+      <c r="B23" s="105" t="inlineStr">
+        <is>
+          <t>更正记录填写原任务编号、原资料版本、原值→新值、变更原因、执行证据及确认人。原因选择“本人责任纠错”或“负责人更新／更正资料等新增变更”；无法判断先标“待核实”。负责人核实确认，不能仅凭员工自行选择类别结算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="115" customHeight="1" s="1">
+      <c r="A24" s="108" t="inlineStr">
+        <is>
+          <t>证据不足与结算</t>
+        </is>
+      </c>
+      <c r="B24" s="107" t="inlineStr">
+        <is>
+          <t>找不到原资料或证据相互冲突时，不直接认定员工操作错误，由负责人核实并记录结论，待核实期间暂不结算该更正任务。确认属于本人责任纠错后，结算金额为0，保留处理记录且不计主动加成和成果奖励；确认属于新增变更后按对应任务标准验收结算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="130" customHeight="1" s="1">
+      <c r="A25" s="104" t="inlineStr">
+        <is>
+          <t>参数更新与已有项目</t>
+        </is>
+      </c>
+      <c r="B25" s="104" t="inlineStr">
+        <is>
+          <t>商品属性或参数更新不新增独立收费行。按实际修改对象使用现有Listing纠错、内容优化或变体关系维护项目；涉及Case时使用对应异常项目，同一交付只计一次。原错误修正与负责人后续更新参数按本页责任判定规则区分，不将准确的新参数更新直接认定为本人纠错。现有项目未覆盖的后台属性批量更新，应先明确适用任务及金额，不自行按多个文案模块叠加。</t>
         </is>
       </c>
     </row>
@@ -13534,12 +15257,12 @@
       </c>
     </row>
     <row r="2" ht="85" customHeight="1" s="1">
-      <c r="A2" s="74" t="inlineStr">
+      <c r="A2" s="104" t="inlineStr">
         <is>
           <t>适用范围</t>
         </is>
       </c>
-      <c r="B2" s="74" t="inlineStr">
+      <c r="B2" s="104" t="inlineStr">
         <is>
           <t>负责人安排或员工主动发起的改善均可申报。任务金额奖励已完成的工作，成果奖励认可经验证的业务改善；同一工作可同时获得任务金额和成果奖励。</t>
         </is>
@@ -13573,7 +15296,7 @@
       </c>
     </row>
     <row r="4" ht="145" customHeight="1" s="1">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="104" t="inlineStr">
         <is>
           <t>明确改善</t>
         </is>
@@ -13581,24 +15304,24 @@
       <c r="B4" s="101" t="n">
         <v>100</v>
       </c>
-      <c r="C4" s="74" t="inlineStr">
+      <c r="C4" s="104" t="inlineStr">
         <is>
           <t>达到事先确认的改善目标；修改前后有可比数据、样本足够，且未明显损害其他关键指标。</t>
         </is>
       </c>
-      <c r="D4" s="74" t="inlineStr">
+      <c r="D4" s="104" t="inlineStr">
         <is>
           <t>改善目标、基线及观察区间、修改记录、前后数据和负责人验收。</t>
         </is>
       </c>
-      <c r="E4" s="74" t="inlineStr">
+      <c r="E4" s="104" t="inlineStr">
         <is>
           <t>同一成果首次达到本档，核定100元；未验收不提前发放。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="145" customHeight="1" s="1">
-      <c r="A5" s="74" t="inlineStr">
+      <c r="A5" s="104" t="inlineStr">
         <is>
           <t>持续改善</t>
         </is>
@@ -13606,64 +15329,64 @@
       <c r="B5" s="101" t="n">
         <v>300</v>
       </c>
-      <c r="C5" s="74" t="inlineStr">
+      <c r="C5" s="104" t="inlineStr">
         <is>
           <t>已确认的改善在后续复查中保持，带来可说明的经济收益，例如减少退货损失或提高广告后利润。</t>
         </is>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>首次验收及后续复查、经济收益的测算口径、数据来源和结论。</t>
         </is>
       </c>
-      <c r="E5" s="74" t="inlineStr">
+      <c r="E5" s="104" t="inlineStr">
         <is>
           <t>300元为该案例本档总奖励；已发100元则本次只补200元，不另发300元。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="145" customHeight="1" s="1">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>重大贡献</t>
         </is>
       </c>
       <c r="B6" s="101" t="n"/>
-      <c r="C6" s="74" t="inlineStr">
+      <c r="C6" s="104" t="inlineStr">
         <is>
           <t>影响范围大、收益明显，普通档位不足以体现贡献。</t>
         </is>
       </c>
-      <c r="D6" s="74" t="inlineStr">
+      <c r="D6" s="104" t="inlineStr">
         <is>
           <t>成果范围、可说明的收益、参与者贡献及负责人批准记录。</t>
         </is>
       </c>
-      <c r="E6" s="74" t="inlineStr">
+      <c r="E6" s="104" t="inlineStr">
         <is>
           <t>由负责人另行确定案例总奖励。金额未确定不结算；如有此前奖励，按批准总额扣除累计已奖励金额。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="85" customHeight="1" s="1">
-      <c r="A7" s="74" t="inlineStr">
+      <c r="A7" s="104" t="inlineStr">
         <is>
           <t>统一原则</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="104" t="inlineStr">
         <is>
           <t>同一成果只取最高核定档，不按月度复盘重复领奖；奖励金额不乘任务难度系数、主动倍率，也不再乘任何积分单价。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="85" customHeight="1" s="1">
-      <c r="A8" s="74" t="inlineStr">
+      <c r="A8" s="104" t="inlineStr">
         <is>
           <t>登记与验证</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="104" t="inlineStr">
         <is>
           <t>改善前登记问题、目标、衡量指标、基线范围、验证日期和关联任务，由负责人确认；先记录目标不代表提前保证奖励。</t>
         </is>
@@ -13697,153 +15420,153 @@
       </c>
     </row>
     <row r="10" ht="145" customHeight="1" s="1">
-      <c r="A10" s="74" t="inlineStr">
+      <c r="A10" s="104" t="inlineStr">
         <is>
           <t>描述／图片／A+改善退货</t>
         </is>
       </c>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="104" t="inlineStr">
         <is>
           <t>相关退货原因及退货损失是否减少。</t>
         </is>
       </c>
-      <c r="C10" s="74" t="inlineStr">
+      <c r="C10" s="104" t="inlineStr">
         <is>
           <t>对比修改前后可比订单批次；记录退货率分母及退货观察时长，确保修改后订单已获得足够退货观察期。</t>
         </is>
       </c>
-      <c r="D10" s="74" t="inlineStr">
+      <c r="D10" s="104" t="inlineStr">
         <is>
           <t>最近几天退货率下降；仅看退货数量、没有订单基数；尚未发生退货被误认为改善。</t>
         </is>
       </c>
-      <c r="E10" s="74" t="inlineStr">
+      <c r="E10" s="104" t="inlineStr">
         <is>
           <t>达到确认目标并满足样本及观察条件后验收；未成熟或样本不足，继续观察。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="145" customHeight="1" s="1">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>内容优化提升销量</t>
         </is>
       </c>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="104" t="inlineStr">
         <is>
           <t>转化率、销量及利润是否改善。</t>
         </is>
       </c>
-      <c r="C11" s="74" t="inlineStr">
+      <c r="C11" s="104" t="inlineStr">
         <is>
           <t>记录价格、促销、广告投入、库存、季节变化等同期因素；使用能支持判断的可比区间。</t>
         </is>
       </c>
-      <c r="D11" s="74" t="inlineStr">
+      <c r="D11" s="104" t="inlineStr">
         <is>
           <t>只看销售额增长，忽略降价、广告投入增加或利润下降。</t>
         </is>
       </c>
-      <c r="E11" s="74" t="inlineStr">
+      <c r="E11" s="104" t="inlineStr">
         <is>
           <t>依据证据判断此次内容调整的贡献；多因素变化且无法支持判断时继续观察。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="145" customHeight="1" s="1">
-      <c r="A12" s="74" t="inlineStr">
+      <c r="A12" s="104" t="inlineStr">
         <is>
           <t>广告优化提升表现</t>
         </is>
       </c>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="104" t="inlineStr">
         <is>
           <t>广告订单、花费、ACOS及产品整体利润的变化。</t>
         </is>
       </c>
-      <c r="C12" s="74" t="inlineStr">
+      <c r="C12" s="104" t="inlineStr">
         <is>
           <t>按事先确认目标选择指标，记录对比区间、订单归因等待和同期价格、库存、促销变化。</t>
         </is>
       </c>
-      <c r="D12" s="74" t="inlineStr">
+      <c r="D12" s="104" t="inlineStr">
         <is>
           <t>只看ACOS降低；缩减投放后销量、利润也下降，不能直接认定为改善。</t>
         </is>
       </c>
-      <c r="E12" s="74" t="inlineStr">
+      <c r="E12" s="104" t="inlineStr">
         <is>
           <t>结合整体收益核验，不要求所有指标同时上涨；未明显损害关键指标且达到目标后认定。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="85" customHeight="1" s="1">
-      <c r="A13" s="74" t="inlineStr">
+      <c r="A13" s="104" t="inlineStr">
         <is>
           <t>重复与协作</t>
         </is>
       </c>
-      <c r="B13" s="74" t="inlineStr">
+      <c r="B13" s="104" t="inlineStr">
         <is>
           <t>同一问题、同一改善目标及同一成果登记唯一成果编号；关联OA或Streamlit任务。多人合作在同一份奖励内分配，个人份额之和不得超过本次可发奖励。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="85" customHeight="1" s="1">
-      <c r="A14" s="74" t="inlineStr">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>跨月与升级</t>
         </is>
       </c>
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="104" t="inlineStr">
         <is>
           <t>已奖励金额跨月累计，不能换月份或任务编号重新领取。按本次核定总奖励减去累计已奖励金额的正差额结算；无新增核定差额则不发放。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="85" customHeight="1" s="1">
-      <c r="A15" s="74" t="inlineStr">
+    <row r="15" ht="115" customHeight="1" s="1">
+      <c r="A15" s="104" t="inlineStr">
         <is>
           <t>任务与成果边界</t>
         </is>
       </c>
-      <c r="B15" s="74" t="inlineStr">
-        <is>
-          <t>任务通过验收可先按任务金额结算；效果仍待观察不阻止已完成任务的结算。成果未达到目标不自动追扣合格任务金额；修复本人错误或无依据操作不作为新成果奖励。</t>
+      <c r="B15" s="104" t="inlineStr">
+        <is>
+          <t>任务通过验收可先按任务金额结算；效果仍待观察不阻止已完成任务的结算。成果未达到目标不自动追扣合格任务金额；修复本人错误或无依据操作不作为新成果奖励。 责任以操作当时已确认资料及执行证据为准；本人开发缺陷、本人执行错误的补救均不另计报酬或成果奖，不能通过更新资料或新建任务转为新成果。资料后续更新及证据不足的处理，详见“优化登记与复盘规则”。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="85" customHeight="1" s="1">
-      <c r="A16" s="74" t="inlineStr">
+      <c r="A16" s="104" t="inlineStr">
         <is>
           <t>月度汇总</t>
         </is>
       </c>
-      <c r="B16" s="74" t="inlineStr">
+      <c r="B16" s="104" t="inlineStr">
         <is>
           <t>当月任务绩效＝OA已验收任务金额＋Streamlit已验收主动任务金额＋当月已确认且未重复结算的成果奖励（含升级补差）。同一任务同时出现在两处时只保留一份任务金额。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="85" customHeight="1" s="1">
-      <c r="A17" s="74" t="inlineStr">
+      <c r="A17" s="104" t="inlineStr">
         <is>
           <t>Streamlit字段</t>
         </is>
       </c>
-      <c r="B17" s="74" t="inlineStr">
+      <c r="B17" s="104" t="inlineStr">
         <is>
           <t>成果编号、负责人及协作者、关联任务、改善对象及站点、问题与措施、改善目标、基线和观察期、前后数据、同期影响因素、复查结论、核定总奖励、累计已奖励金额、本次奖励、核定日期、结算状态和结算月份。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="85" customHeight="1" s="1">
-      <c r="A18" s="74" t="inlineStr">
+      <c r="A18" s="104" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="B18" s="74" t="inlineStr">
+      <c r="B18" s="104" t="inlineStr">
         <is>
           <t>待确认目标 → 执行／观察中 → 待成果验收 → 已核定 → 已结算；未满足条件则继续观察或注明不予奖励原因。</t>
         </is>
@@ -13877,7 +15600,7 @@
       </c>
     </row>
     <row r="20" ht="85" customHeight="1" s="1">
-      <c r="A20" s="74" t="inlineStr">
+      <c r="A20" s="104" t="inlineStr">
         <is>
           <t>首次达到明确改善</t>
         </is>
@@ -13892,14 +15615,14 @@
         <f>MAX(0,B20-C20)</f>
         <v/>
       </c>
-      <c r="E20" s="74" t="inlineStr">
+      <c r="E20" s="104" t="inlineStr">
         <is>
           <t>本次发100元。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="85" customHeight="1" s="1">
-      <c r="A21" s="74" t="inlineStr">
+      <c r="A21" s="104" t="inlineStr">
         <is>
           <t>后续达到持续改善</t>
         </is>
@@ -13914,14 +15637,14 @@
         <f>MAX(0,B21-C21)</f>
         <v/>
       </c>
-      <c r="E21" s="74" t="inlineStr">
+      <c r="E21" s="104" t="inlineStr">
         <is>
           <t>本次补200元，累计300元。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="85" customHeight="1" s="1">
-      <c r="A22" s="74" t="inlineStr">
+      <c r="A22" s="104" t="inlineStr">
         <is>
           <t>同一成果再次复盘，无升级</t>
         </is>
@@ -13936,7 +15659,7 @@
         <f>MAX(0,B22-C22)</f>
         <v/>
       </c>
-      <c r="E22" s="74" t="inlineStr">
+      <c r="E22" s="104" t="inlineStr">
         <is>
           <t>本次0元，不因复盘次数重复领奖。</t>
         </is>
@@ -13970,7 +15693,7 @@
       </c>
     </row>
     <row r="24" ht="85" customHeight="1" s="1">
-      <c r="A24" s="74" t="inlineStr">
+      <c r="A24" s="104" t="inlineStr">
         <is>
           <t>某员工</t>
         </is>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00&quot;元&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -267,6 +267,10 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="45">
     <fill>
@@ -491,7 +495,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="23">
     <border/>
     <border>
       <left style="thin">
@@ -651,6 +655,37 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1">
@@ -802,7 +837,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1109,6 +1144,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0"/>
@@ -6174,7 +6218,8 @@
         <is>
           <t>分析竞品、需求、价格区间、关键规格、客户反馈及初步利润空间，提出产品建议和风险判断。数据注明来源、期间及估算口径。
 调研完整且结论有依据，经负责人确认。无需凑固定竞品数量；结论为不建议开发时，已完成且通过验收的调研照常计费。
-统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列产品开发：共用调研方案的多个规格/尺寸只计一次75元。详见"系列产品开发计费规则"。</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -6218,7 +6263,8 @@
         <is>
           <t>寻找并核实匹配的厂家，比较有效报价、MOQ、交期、包装及定制条件，确认关键费用、供货能力和合作限制，提出选择建议。
 关键合作条件清楚且有记录，经负责人确认。按完整找厂与条件确认交付计费，不按联系次数或报价份数计；无合适厂家时须提供完整调查结论并经负责人确认结案。
-统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列产品开发：共用厂家的多个规格/尺寸只计一次75元。详见"系列产品开发计费规则"。</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -6262,7 +6308,8 @@
         <is>
           <t>按事先确认的验证要求完成样品检查或协调测试，记录问题、跟进整改及复测，形成通过、修改或停止结论。
 形成可供决策的验证结论并经负责人验收；继续修改中不自动结案。同一轮原问题补测、整改、催办合并计费；新增独立验证范围须事先确认，不按每次样品到货计75元。
-统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列产品开发：首个产品建立评估标准计75元；同系列后续产品，需独立验证的75元/个，仅核对基本参数的15元/个，无需验证的不另计。由负责人确认。</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -6304,7 +6351,8 @@
       </c>
       <c r="H54" s="46" t="inlineStr">
         <is>
-          <t>主动核实产品规格、功能、使用方式、限制、卖点依据及包装内容，向厂家解决缺失或矛盾信息，形成经确认的可用事实资料。已有完整资料仅汇总、复制或直接使用不计本项。调研、找厂、样品任务已交付的相同资料不再计40元；只有额外核实、补全且独立验收的资料工作才计。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+          <t>主动核实产品规格、功能、使用方式、限制、卖点依据及包装内容，向厂家解决缺失或矛盾信息，形成经确认的可用事实资料。已有完整资料仅汇总、复制或直接使用不计本项。调研、找厂、样品任务已交付的相同资料不再计40元；只有额外核实、补全且独立验收的资料工作才计。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列产品开发：首个产品完整整理40元；后续产品仅更新差异参数的10元/个。</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -6346,7 +6394,8 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>明确主图和辅图各自展示内容、卖点、参数、文案及参考，提出美工制作要求，跟进修改并核验成图。同一方案多SKU共用只计一次50元；同轮沟通、修改及核验均包含。实际拍摄和修图不属于本人任务。图片上传另按10元/SKU；A+素材策划已含A+75元，相同交付不再计本项。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+          <t>明确主图和辅图各自展示内容、卖点、参数、文案及参考，提出美工制作要求，跟进修改并核验成图。同一方案多SKU共用只计一次50元；同轮沟通、修改及核验均包含。实际拍摄和修图不属于本人任务。图片上传另按10元/SKU；A+素材策划已含A+75元，相同交付不再计本项。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列产品开发：共用拍摄方案的，首个产品50元；后续仅更换实物不重新策划的10元/个。</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -6388,7 +6437,8 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>理解产品和视频内容，编写准确且与画面对应的字幕，核对参数及表述，提供段落或时间对应并交付经确认的可用定稿。不包含完整视频脚本策划、拍摄、剪辑。直接使用已有字幕不计编写金额；同稿反复修改不另计，视频上传另按原规则。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+          <t>理解产品和视频内容，编写准确且与画面对应的字幕，核对参数及表述，提供段落或时间对应并交付经确认的可用定稿。不包含完整视频脚本策划、拍摄、剪辑。直接使用已有字幕不计编写金额；同稿反复修改不另计，视频上传另按原规则。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列产品开发：共用脚本框架的，首个25元；后续仅替换参数的5元/个。</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -6801,7 +6851,11 @@
       <c r="H66" s="52" t="n"/>
     </row>
     <row r="67" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A67" s="54" t="n"/>
+      <c r="A67" s="124" t="inlineStr">
+        <is>
+          <t>系列产品开发计费规则</t>
+        </is>
+      </c>
       <c r="B67" s="28" t="n"/>
       <c r="C67" s="52" t="n"/>
       <c r="D67" s="55" t="n"/>
@@ -6811,24 +6865,36 @@
       <c r="H67" s="52" t="n"/>
     </row>
     <row r="68" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A68" s="54" t="n"/>
-      <c r="B68" s="28" t="n"/>
-      <c r="C68" s="52" t="n"/>
-      <c r="D68" s="55" t="n"/>
-      <c r="E68" s="28" t="n"/>
-      <c r="F68" s="53" t="n"/>
-      <c r="G68" s="53" t="n"/>
-      <c r="H68" s="52" t="n"/>
+      <c r="A68" s="54" t="inlineStr">
+        <is>
+          <t>同一系列产品（仅规格、尺寸、颜色等参数不同）的开发任务，按以下原则计费：
+① 市场调研、厂家筛选：共用同一份方案的，只计一次75元，不按产品数量重复领取。
+② 样品评估：首个产品建立评估标准计75元；同系列后续产品，由负责人逐个确认是否需要独立验证——需独立验证的按75元/个计费，仅需核对尺寸等基本参数的按15元/个计费，无需单独验证的不另计。
+③ 产品资料整理：首个产品完整整理计40元；同系列后续产品仅更新差异参数的计10元/个。
+④ 产品图片策划：共用拍摄方案和视觉风格的，首个产品计50元；后续产品仅更换实物但不重新策划的计10元/个。
+⑤ 视频字幕：共用脚本框架的，首个计25元；后续产品仅替换参数的计5元/个。
+⑥ 系列产品的认定和后续产品的独立验证范围，须在派单时由负责人确认，不由员工自行判定。</t>
+        </is>
+      </c>
+      <c r="B68" s="125" t="n"/>
+      <c r="C68" s="125" t="n"/>
+      <c r="D68" s="125" t="n"/>
+      <c r="E68" s="125" t="n"/>
+      <c r="F68" s="125" t="n"/>
+      <c r="G68" s="125" t="n"/>
+      <c r="H68" s="125" t="n"/>
+      <c r="I68" s="126" t="n"/>
     </row>
     <row r="69" ht="25.89999961853027" customHeight="1" s="1">
-      <c r="A69" s="54" t="n"/>
-      <c r="B69" s="28" t="n"/>
-      <c r="C69" s="52" t="n"/>
-      <c r="D69" s="55" t="n"/>
-      <c r="E69" s="28" t="n"/>
-      <c r="F69" s="53" t="n"/>
-      <c r="G69" s="53" t="n"/>
-      <c r="H69" s="52" t="n"/>
+      <c r="A69" s="127" t="n"/>
+      <c r="B69" s="128" t="n"/>
+      <c r="C69" s="128" t="n"/>
+      <c r="D69" s="128" t="n"/>
+      <c r="E69" s="128" t="n"/>
+      <c r="F69" s="128" t="n"/>
+      <c r="G69" s="128" t="n"/>
+      <c r="H69" s="128" t="n"/>
+      <c r="I69" s="129" t="n"/>
     </row>
     <row r="70" ht="25.5" customHeight="1" s="1">
       <c r="A70" s="54" t="n"/>
@@ -7169,7 +7235,7 @@
           <t>品牌保护—取证与投诉</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>跟卖取证与举报／Case处理</t>
         </is>
@@ -7191,7 +7257,7 @@
           <t>品牌内容策划</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>Brand Story品牌故事制作与维护</t>
         </is>
@@ -7214,7 +7280,7 @@
           <t>订阅销售</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>Subscribe &amp; Save设置与管理</t>
         </is>
@@ -7372,8 +7438,9 @@
       <c r="A101" s="116" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="B91:C91"/>
+    <mergeCell ref="A68:I69"/>
     <mergeCell ref="B90:C90"/>
     <mergeCell ref="B81:C81"/>
     <mergeCell ref="E91:H91"/>
@@ -8271,7 +8338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H251"/>
+  <dimension ref="A2:H263"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -14037,644 +14104,881 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" s="130" t="inlineStr">
+        <is>
+          <t>系列产品开发计费示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>正确计费</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>错误计费</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>计算依据</t>
+        </is>
+      </c>
+    </row>
     <row r="230">
-      <c r="A230" s="24" t="inlineStr">
+      <c r="A230" s="32" t="inlineStr">
+        <is>
+          <t>10个尺寸的同款阀门
+共用调研和厂家</t>
+        </is>
+      </c>
+      <c r="B230" s="32" t="inlineStr">
+        <is>
+          <t>调研、找厂方案完全相同，样品需逐个验证</t>
+        </is>
+      </c>
+      <c r="C230" s="32" t="inlineStr">
+        <is>
+          <t>调研75＋找厂75＋样品(首个75＋9个×15)＝360元</t>
+        </is>
+      </c>
+      <c r="D230" s="32" t="inlineStr">
+        <is>
+          <t>调研750＋找厂750＋样品750＝2,250元</t>
+        </is>
+      </c>
+      <c r="E230" s="32" t="inlineStr">
+        <is>
+          <t>共用方案只计一次；后续产品仅核对尺寸参数按15元</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="32" t="inlineStr">
+        <is>
+          <t>10个尺寸的同款阀门
+含资料和图片</t>
+        </is>
+      </c>
+      <c r="B231" s="32" t="inlineStr">
+        <is>
+          <t>续上例，加上资料整理和图片策划</t>
+        </is>
+      </c>
+      <c r="C231" s="32" t="inlineStr">
+        <is>
+          <t>资料(40＋9×10)＋图片(50＋9×10)＝270元
+开发360＋内容270＝630元</t>
+        </is>
+      </c>
+      <c r="D231" s="32" t="inlineStr">
+        <is>
+          <t>资料400＋图片500＝900元
+开发2,250＋内容900＝3,150元</t>
+        </is>
+      </c>
+      <c r="E231" s="32" t="inlineStr">
+        <is>
+          <t>首个产品完整计费，后续仅更新差异参数和更换实物</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="32" t="inlineStr">
+        <is>
+          <t>3个完全不同的产品线</t>
+        </is>
+      </c>
+      <c r="B232" s="32" t="inlineStr">
+        <is>
+          <t>产品类型、市场、厂家均不同</t>
+        </is>
+      </c>
+      <c r="C232" s="32" t="inlineStr">
+        <is>
+          <t>各自独立：3×(75＋75＋75)＝675元</t>
+        </is>
+      </c>
+      <c r="D232" s="32" t="inlineStr">
+        <is>
+          <t>按系列产品规则减免</t>
+        </is>
+      </c>
+      <c r="E232" s="32" t="inlineStr">
+        <is>
+          <t>不同产品线的调研和厂家不共用，各自独立计费</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="32" t="inlineStr">
+        <is>
+          <t>同系列5个尺寸
+其中2个需独立样品验证</t>
+        </is>
+      </c>
+      <c r="B233" s="32" t="inlineStr">
+        <is>
+          <t>负责人确认2个特殊尺寸需独立验证</t>
+        </is>
+      </c>
+      <c r="C233" s="32" t="inlineStr">
+        <is>
+          <t>样品：首个75＋2个独立验证×75＋2个基本核对×15＝300元</t>
+        </is>
+      </c>
+      <c r="D233" s="32" t="inlineStr">
+        <is>
+          <t>5×75＝375元</t>
+        </is>
+      </c>
+      <c r="E233" s="32" t="inlineStr">
+        <is>
+          <t>由负责人逐个确认验证范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="32" t="inlineStr">
+        <is>
+          <t>同系列产品的字幕
+共用脚本框架</t>
+        </is>
+      </c>
+      <c r="B234" s="32" t="inlineStr">
+        <is>
+          <t>10个产品的视频字幕，框架相同仅替换参数</t>
+        </is>
+      </c>
+      <c r="C234" s="32" t="inlineStr">
+        <is>
+          <t>首个25＋9×5＝70元</t>
+        </is>
+      </c>
+      <c r="D234" s="32" t="inlineStr">
+        <is>
+          <t>10×25＝250元</t>
+        </is>
+      </c>
+      <c r="E234" s="32" t="inlineStr">
+        <is>
+          <t>共用脚本框架的后续产品按5元/个</t>
+        </is>
+      </c>
+    </row>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240">
+      <c r="A240" s="24" t="inlineStr">
         <is>
           <t>防重复计费速查：常见场景判定</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="31" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="31" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B231" s="31" t="inlineStr">
+      <c r="B241" s="31" t="inlineStr">
         <is>
           <t>场景描述</t>
         </is>
       </c>
-      <c r="C231" s="31" t="inlineStr">
+      <c r="C241" s="31" t="inlineStr">
         <is>
           <t>正确计费</t>
         </is>
       </c>
-      <c r="D231" s="31" t="inlineStr">
+      <c r="D241" s="31" t="inlineStr">
         <is>
           <t>错误计费</t>
         </is>
       </c>
-      <c r="E231" s="31" t="inlineStr">
+      <c r="E241" s="31" t="inlineStr">
         <is>
           <t>判定依据</t>
         </is>
       </c>
-      <c r="F231" s="31" t="inlineStr">
+      <c r="F241" s="31" t="inlineStr">
         <is>
           <t>所在规则</t>
         </is>
       </c>
-      <c r="G231" s="31" t="n"/>
-      <c r="H231" s="31" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B232" s="32" t="inlineStr">
-        <is>
-          <t>A+完全重做后，是否可同时计A+制作发布75元和全新重做75元？</t>
-        </is>
-      </c>
-      <c r="C232" s="32" t="inlineStr">
-        <is>
-          <t>只计一次75元</t>
-        </is>
-      </c>
-      <c r="D232" s="32" t="inlineStr">
-        <is>
-          <t>叠加计150元</t>
-        </is>
-      </c>
-      <c r="E232" s="32" t="inlineStr">
-        <is>
-          <t>同一成果只计一次</t>
-        </is>
-      </c>
-      <c r="F232" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·A+制作发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="B233" s="32" t="inlineStr">
-        <is>
-          <t>同一电压错误出现在标题、五点和A+三个位置</t>
-        </is>
-      </c>
-      <c r="C233" s="32" t="inlineStr">
-        <is>
-          <t>修正全部位置，共10元</t>
-        </is>
-      </c>
-      <c r="D233" s="32" t="inlineStr">
-        <is>
-          <t>按位置分别计30元</t>
-        </is>
-      </c>
-      <c r="E233" s="32" t="inlineStr">
-        <is>
-          <t>同源错误合并为1个错误点</t>
-        </is>
-      </c>
-      <c r="F233" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·Listing纠错</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="B234" s="32" t="inlineStr">
-        <is>
-          <t>员工自主发现价格异常并修正，是否同时计任务金额和主动金额？</t>
-        </is>
-      </c>
-      <c r="C234" s="32" t="inlineStr">
-        <is>
-          <t>按正常金额×主动倍率</t>
-        </is>
-      </c>
-      <c r="D234" s="32" t="inlineStr">
-        <is>
-          <t>正常金额＋另加主动金额</t>
-        </is>
-      </c>
-      <c r="E234" s="32" t="inlineStr">
-        <is>
-          <t>发起来源互斥：自主发起按倍率，不另加正常金额</t>
-        </is>
-      </c>
-      <c r="F234" s="32" t="inlineStr">
-        <is>
-          <t>主动改善评价·二</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="B235" s="32" t="inlineStr">
-        <is>
-          <t>员工先提出建议，经负责人批准后建立任务执行</t>
-        </is>
-      </c>
-      <c r="C235" s="32" t="inlineStr">
-        <is>
-          <t>按正常金额×主动倍率</t>
-        </is>
-      </c>
-      <c r="D235" s="32" t="inlineStr">
-        <is>
-          <t>只按普通金额结算，遗漏适用主动倍率</t>
-        </is>
-      </c>
-      <c r="E235" s="32" t="inlineStr">
-        <is>
-          <t>先提出即属主动发起，补建任务不改变来源</t>
-        </is>
-      </c>
-      <c r="F235" s="32" t="inlineStr">
-        <is>
-          <t>主动改善评价·A17</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="B236" s="32" t="inlineStr">
-        <is>
-          <t>同一滞留库存问题先Relist再申诉</t>
-        </is>
-      </c>
-      <c r="C236" s="32" t="inlineStr">
-        <is>
-          <t>合计15元（取最高档）</t>
-        </is>
-      </c>
-      <c r="D236" s="32" t="inlineStr">
-        <is>
-          <t>移除10元＋申诉15元＝25元</t>
-        </is>
-      </c>
-      <c r="E236" s="32" t="inlineStr">
-        <is>
-          <t>同一问题连续处理只取最高适用金额</t>
-        </is>
-      </c>
-      <c r="F236" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·滞留库存</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="B237" s="32" t="inlineStr">
-        <is>
-          <t>上架组包含5个SKU，OA记录5条</t>
-        </is>
-      </c>
-      <c r="C237" s="32" t="inlineStr">
-        <is>
-          <t>按组总金额计（如52元）</t>
-        </is>
-      </c>
-      <c r="D237" s="32" t="inlineStr">
-        <is>
-          <t>5条OA各计25元＝125元</t>
-        </is>
-      </c>
-      <c r="E237" s="32" t="inlineStr">
-        <is>
-          <t>以执行组为单位，OA分摊组总金额</t>
-        </is>
-      </c>
-      <c r="F237" s="32" t="inlineStr">
-        <is>
-          <t>场景示例·上架组</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="B238" s="32" t="inlineStr">
-        <is>
-          <t>5个SKU共用同一份新A+</t>
-        </is>
-      </c>
-      <c r="C238" s="32" t="inlineStr">
-        <is>
-          <t>1份×75元＝75元</t>
-        </is>
-      </c>
-      <c r="D238" s="32" t="inlineStr">
-        <is>
-          <t>5×75元＝375元</t>
-        </is>
-      </c>
-      <c r="E238" s="32" t="inlineStr">
-        <is>
-          <t>共用同一份内容只计一份</t>
-        </is>
-      </c>
-      <c r="F238" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·A+制作发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="B239" s="32" t="inlineStr">
-        <is>
-          <t>同一份A+同一轮修改了6个模块</t>
-        </is>
-      </c>
-      <c r="C239" s="32" t="inlineStr">
-        <is>
-          <t>合计10元</t>
-        </is>
-      </c>
-      <c r="D239" s="32" t="inlineStr">
-        <is>
-          <t>6×10元＝60元</t>
-        </is>
-      </c>
-      <c r="E239" s="32" t="inlineStr">
-        <is>
-          <t>同份同轮合计10元，不按模块数量累加</t>
-        </is>
-      </c>
-      <c r="F239" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·A+增删修改</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="B240" s="32" t="inlineStr">
-        <is>
-          <t>同站点1个ASIN的Buy Box异常多次开Case后恢复</t>
-        </is>
-      </c>
-      <c r="C240" s="32" t="inlineStr">
-        <is>
-          <t>合计15元</t>
-        </is>
-      </c>
-      <c r="D240" s="32" t="inlineStr">
-        <is>
-          <t>按Case数量计费</t>
-        </is>
-      </c>
-      <c r="E240" s="32" t="inlineStr">
-        <is>
-          <t>按ASIN计费，同一ASIN多个SKU或多个Case不增加金额</t>
-        </is>
-      </c>
-      <c r="F240" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·Buy Box</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="B241" s="32" t="inlineStr">
-        <is>
-          <t>同一Listing标题在复盘前又做了一次优化修改</t>
-        </is>
-      </c>
-      <c r="C241" s="32" t="inlineStr">
-        <is>
-          <t>并入原任务，不新增金额</t>
-        </is>
-      </c>
-      <c r="D241" s="32" t="inlineStr">
-        <is>
-          <t>新建优化任务再计10元</t>
-        </is>
-      </c>
-      <c r="E241" s="32" t="inlineStr">
-        <is>
-          <t>同模块复盘前追加并入，不重复</t>
-        </is>
-      </c>
-      <c r="F241" s="32" t="inlineStr">
-        <is>
-          <t>优化登记与复盘规则</t>
-        </is>
-      </c>
+      <c r="G241" s="31" t="n"/>
+      <c r="H241" s="31" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="32" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B242" s="32" t="inlineStr">
         <is>
-          <t>创建1个SP Campaign产生多条Ads Change记录</t>
+          <t>A+完全重做后，是否可同时计A+制作发布75元和全新重做75元？</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
         <is>
-          <t>只计一次15元</t>
+          <t>只计一次75元</t>
         </is>
       </c>
       <c r="D242" s="32" t="inlineStr">
         <is>
-          <t>按Ads Change条数计费</t>
+          <t>叠加计150元</t>
         </is>
       </c>
       <c r="E242" s="32" t="inlineStr">
         <is>
-          <t>以Campaign ID去重</t>
+          <t>同一成果只计一次</t>
         </is>
       </c>
       <c r="F242" s="32" t="inlineStr">
         <is>
-          <t>任务评分·SP广告创建</t>
+          <t>任务评分·A+制作发布</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B243" s="32" t="inlineStr">
+        <is>
+          <t>同一电压错误出现在标题、五点和A+三个位置</t>
+        </is>
+      </c>
+      <c r="C243" s="32" t="inlineStr">
+        <is>
+          <t>修正全部位置，共10元</t>
+        </is>
+      </c>
+      <c r="D243" s="32" t="inlineStr">
+        <is>
+          <t>按位置分别计30元</t>
+        </is>
+      </c>
+      <c r="E243" s="32" t="inlineStr">
+        <is>
+          <t>同源错误合并为1个错误点</t>
+        </is>
+      </c>
+      <c r="F243" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·Listing纠错</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B244" s="32" t="inlineStr">
+        <is>
+          <t>员工自主发现价格异常并修正，是否同时计任务金额和主动金额？</t>
+        </is>
+      </c>
+      <c r="C244" s="32" t="inlineStr">
+        <is>
+          <t>按正常金额×主动倍率</t>
+        </is>
+      </c>
+      <c r="D244" s="32" t="inlineStr">
+        <is>
+          <t>正常金额＋另加主动金额</t>
+        </is>
+      </c>
+      <c r="E244" s="32" t="inlineStr">
+        <is>
+          <t>发起来源互斥：自主发起按倍率，不另加正常金额</t>
+        </is>
+      </c>
+      <c r="F244" s="32" t="inlineStr">
+        <is>
+          <t>主动改善评价·二</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B245" s="32" t="inlineStr">
+        <is>
+          <t>员工先提出建议，经负责人批准后建立任务执行</t>
+        </is>
+      </c>
+      <c r="C245" s="32" t="inlineStr">
+        <is>
+          <t>按正常金额×主动倍率</t>
+        </is>
+      </c>
+      <c r="D245" s="32" t="inlineStr">
+        <is>
+          <t>只按普通金额结算，遗漏适用主动倍率</t>
+        </is>
+      </c>
+      <c r="E245" s="32" t="inlineStr">
+        <is>
+          <t>先提出即属主动发起，补建任务不改变来源</t>
+        </is>
+      </c>
+      <c r="F245" s="32" t="inlineStr">
+        <is>
+          <t>主动改善评价·A17</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B246" s="32" t="inlineStr">
+        <is>
+          <t>同一滞留库存问题先Relist再申诉</t>
+        </is>
+      </c>
+      <c r="C246" s="32" t="inlineStr">
+        <is>
+          <t>合计15元（取最高档）</t>
+        </is>
+      </c>
+      <c r="D246" s="32" t="inlineStr">
+        <is>
+          <t>移除10元＋申诉15元＝25元</t>
+        </is>
+      </c>
+      <c r="E246" s="32" t="inlineStr">
+        <is>
+          <t>同一问题连续处理只取最高适用金额</t>
+        </is>
+      </c>
+      <c r="F246" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·滞留库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B247" s="32" t="inlineStr">
+        <is>
+          <t>上架组包含5个SKU，OA记录5条</t>
+        </is>
+      </c>
+      <c r="C247" s="32" t="inlineStr">
+        <is>
+          <t>按组总金额计（如52元）</t>
+        </is>
+      </c>
+      <c r="D247" s="32" t="inlineStr">
+        <is>
+          <t>5条OA各计25元＝125元</t>
+        </is>
+      </c>
+      <c r="E247" s="32" t="inlineStr">
+        <is>
+          <t>以执行组为单位，OA分摊组总金额</t>
+        </is>
+      </c>
+      <c r="F247" s="32" t="inlineStr">
+        <is>
+          <t>场景示例·上架组</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B248" s="32" t="inlineStr">
+        <is>
+          <t>5个SKU共用同一份新A+</t>
+        </is>
+      </c>
+      <c r="C248" s="32" t="inlineStr">
+        <is>
+          <t>1份×75元＝75元</t>
+        </is>
+      </c>
+      <c r="D248" s="32" t="inlineStr">
+        <is>
+          <t>5×75元＝375元</t>
+        </is>
+      </c>
+      <c r="E248" s="32" t="inlineStr">
+        <is>
+          <t>共用同一份内容只计一份</t>
+        </is>
+      </c>
+      <c r="F248" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·A+制作发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B249" s="32" t="inlineStr">
+        <is>
+          <t>同一份A+同一轮修改了6个模块</t>
+        </is>
+      </c>
+      <c r="C249" s="32" t="inlineStr">
+        <is>
+          <t>合计10元</t>
+        </is>
+      </c>
+      <c r="D249" s="32" t="inlineStr">
+        <is>
+          <t>6×10元＝60元</t>
+        </is>
+      </c>
+      <c r="E249" s="32" t="inlineStr">
+        <is>
+          <t>同份同轮合计10元，不按模块数量累加</t>
+        </is>
+      </c>
+      <c r="F249" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·A+增删修改</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B250" s="32" t="inlineStr">
+        <is>
+          <t>同站点1个ASIN的Buy Box异常多次开Case后恢复</t>
+        </is>
+      </c>
+      <c r="C250" s="32" t="inlineStr">
+        <is>
+          <t>合计15元</t>
+        </is>
+      </c>
+      <c r="D250" s="32" t="inlineStr">
+        <is>
+          <t>按Case数量计费</t>
+        </is>
+      </c>
+      <c r="E250" s="32" t="inlineStr">
+        <is>
+          <t>按ASIN计费，同一ASIN多个SKU或多个Case不增加金额</t>
+        </is>
+      </c>
+      <c r="F250" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·Buy Box</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B251" s="32" t="inlineStr">
+        <is>
+          <t>同一Listing标题在复盘前又做了一次优化修改</t>
+        </is>
+      </c>
+      <c r="C251" s="32" t="inlineStr">
+        <is>
+          <t>并入原任务，不新增金额</t>
+        </is>
+      </c>
+      <c r="D251" s="32" t="inlineStr">
+        <is>
+          <t>新建优化任务再计10元</t>
+        </is>
+      </c>
+      <c r="E251" s="32" t="inlineStr">
+        <is>
+          <t>同模块复盘前追加并入，不重复</t>
+        </is>
+      </c>
+      <c r="F251" s="32" t="inlineStr">
+        <is>
+          <t>优化登记与复盘规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B252" s="32" t="inlineStr">
+        <is>
+          <t>创建1个SP Campaign产生多条Ads Change记录</t>
+        </is>
+      </c>
+      <c r="C252" s="32" t="inlineStr">
+        <is>
+          <t>只计一次15元</t>
+        </is>
+      </c>
+      <c r="D252" s="32" t="inlineStr">
+        <is>
+          <t>按Ads Change条数计费</t>
+        </is>
+      </c>
+      <c r="E252" s="32" t="inlineStr">
+        <is>
+          <t>以Campaign ID去重</t>
+        </is>
+      </c>
+      <c r="F252" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·SP广告创建</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B243" s="32" t="inlineStr">
+      <c r="B253" s="32" t="inlineStr">
         <is>
           <t>纠错修复的是自己上次操作造成的错误</t>
         </is>
       </c>
-      <c r="C243" s="32" t="inlineStr">
+      <c r="C253" s="32" t="inlineStr">
         <is>
           <t>不新增任务金额或主动金额</t>
         </is>
       </c>
-      <c r="D243" s="32" t="inlineStr">
+      <c r="D253" s="32" t="inlineStr">
         <is>
           <t>计纠错10元/错误点</t>
         </is>
       </c>
-      <c r="E243" s="32" t="inlineStr">
+      <c r="E253" s="32" t="inlineStr">
         <is>
           <t>修复本人错误属于返工</t>
         </is>
       </c>
-      <c r="F243" s="32" t="inlineStr">
+      <c r="F253" s="32" t="inlineStr">
         <is>
           <t>运营工作明细·Listing纠错</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="100" t="n">
+    <row r="254">
+      <c r="A254" s="100" t="n">
         <v>13</v>
       </c>
-      <c r="B244" s="100" t="inlineStr">
+      <c r="B254" s="100" t="inlineStr">
         <is>
           <t>3个尺寸共用同一套调研方案，是否分别领取75元？</t>
         </is>
       </c>
-      <c r="C244" s="100" t="inlineStr">
+      <c r="C254" s="100" t="inlineStr">
         <is>
           <t>共用方案只计一次75元</t>
         </is>
       </c>
-      <c r="D244" s="100" t="inlineStr">
+      <c r="D254" s="100" t="inlineStr">
         <is>
           <t>每个尺寸各领75元＝225元</t>
         </is>
       </c>
-      <c r="E244" s="100" t="inlineStr">
+      <c r="E254" s="100" t="inlineStr">
         <is>
           <t>共用调研/厂家/验证方案不重复领取</t>
         </is>
       </c>
-      <c r="F244" s="100" t="inlineStr">
+      <c r="F254" s="100" t="inlineStr">
         <is>
           <t>任务评分·新品开发</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="100" t="n">
+    <row r="255">
+      <c r="A255" s="100" t="n">
         <v>14</v>
       </c>
-      <c r="B245" s="100" t="inlineStr">
+      <c r="B255" s="100" t="inlineStr">
         <is>
           <t>已完成A+制作（75元），是否可同时计图片策划50元？</t>
         </is>
       </c>
-      <c r="C245" s="100" t="inlineStr">
+      <c r="C255" s="100" t="inlineStr">
         <is>
           <t>A+已含素材策划，不另计</t>
         </is>
       </c>
-      <c r="D245" s="100" t="inlineStr">
+      <c r="D255" s="100" t="inlineStr">
         <is>
           <t>叠加计75＋50＝125元</t>
         </is>
       </c>
-      <c r="E245" s="100" t="inlineStr">
+      <c r="E255" s="100" t="inlineStr">
         <is>
           <t>A+制作已包含素材策划</t>
         </is>
       </c>
-      <c r="F245" s="100" t="inlineStr">
+      <c r="F255" s="100" t="inlineStr">
         <is>
           <t>任务评分·产品图片策划</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="100" t="n">
+    <row r="256">
+      <c r="A256" s="100" t="n">
         <v>15</v>
       </c>
-      <c r="B246" s="100" t="inlineStr">
+      <c r="B256" s="100" t="inlineStr">
         <is>
           <t>调研/找厂已交付产品资料，是否可再计资料整理40元？</t>
         </is>
       </c>
-      <c r="C246" s="100" t="inlineStr">
+      <c r="C256" s="100" t="inlineStr">
         <is>
           <t>已交付的相同资料不重复计</t>
         </is>
       </c>
-      <c r="D246" s="100" t="inlineStr">
+      <c r="D256" s="100" t="inlineStr">
         <is>
           <t>调研75＋资料40＝叠加115元</t>
         </is>
       </c>
-      <c r="E246" s="100" t="inlineStr">
+      <c r="E256" s="100" t="inlineStr">
         <is>
           <t>同一交付不按两个项目分别领取</t>
         </is>
       </c>
-      <c r="F246" s="100" t="inlineStr">
+      <c r="F256" s="100" t="inlineStr">
         <is>
           <t>任务评分·产品资料整理</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="0" t="n">
+    <row r="257">
+      <c r="A257" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="B247" s="0" t="inlineStr">
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t>Brand Story全新策划75元与A+制作发布75元是否叠加？</t>
         </is>
       </c>
-      <c r="C247" s="0" t="inlineStr">
+      <c r="C257" s="0" t="inlineStr">
         <is>
           <t>品牌故事和A+是不同内容区域，各自独立计费</t>
         </is>
       </c>
-      <c r="D247" s="0" t="inlineStr">
+      <c r="D257" s="0" t="inlineStr">
         <is>
           <t>两者叠加计150元</t>
         </is>
       </c>
-      <c r="E247" s="0" t="inlineStr">
+      <c r="E257" s="0" t="inlineStr">
         <is>
           <t>Brand Story与A+为两种独立内容模块</t>
         </is>
       </c>
-      <c r="F247" s="0" t="inlineStr">
+      <c r="F257" s="0" t="inlineStr">
         <is>
           <t>任务评分·Brand Story / A+制作发布</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="0" t="n">
+    <row r="258">
+      <c r="A258" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="B248" s="0" t="inlineStr">
+      <c r="B258" s="0" t="inlineStr">
         <is>
           <t>跟卖监控5元与跟卖取证30元是否叠加？</t>
         </is>
       </c>
-      <c r="C248" s="0" t="inlineStr">
+      <c r="C258" s="0" t="inlineStr">
         <is>
           <t>监控和取证是独立任务，分别计费</t>
         </is>
       </c>
-      <c r="D248" s="0" t="inlineStr">
+      <c r="D258" s="0" t="inlineStr">
         <is>
           <t>取证包含监控，只计30元</t>
         </is>
       </c>
-      <c r="E248" s="0" t="inlineStr">
+      <c r="E258" s="0" t="inlineStr">
         <is>
           <t>监控为固定巡检，取证为独立案件处理，可同时存在</t>
         </is>
       </c>
-      <c r="F248" s="0" t="inlineStr">
+      <c r="F258" s="0" t="inlineStr">
         <is>
           <t>任务评分·品牌保护</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="0" t="n">
+    <row r="259">
+      <c r="A259" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="B249" s="0" t="inlineStr">
+      <c r="B259" s="0" t="inlineStr">
         <is>
           <t>Virtual Bundle创建25元与Listing创建25元是否叠加？</t>
         </is>
       </c>
-      <c r="C249" s="0" t="inlineStr">
+      <c r="C259" s="0" t="inlineStr">
         <is>
           <t>Virtual Bundle已含初始配置，不叠加Listing创建</t>
         </is>
       </c>
-      <c r="D249" s="0" t="inlineStr">
+      <c r="D259" s="0" t="inlineStr">
         <is>
           <t>分别计50元</t>
         </is>
       </c>
-      <c r="E249" s="0" t="inlineStr">
+      <c r="E259" s="0" t="inlineStr">
         <is>
           <t>VB创建已包含文案填入和图片配置</t>
         </is>
       </c>
-      <c r="F249" s="0" t="inlineStr">
+      <c r="F259" s="0" t="inlineStr">
         <is>
           <t>任务评分·Virtual Bundle</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="0" t="n">
+    <row r="260">
+      <c r="A260" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="B250" s="0" t="inlineStr">
+      <c r="B260" s="0" t="inlineStr">
         <is>
           <t>利润分析完成后另行改价，是否叠加？</t>
         </is>
       </c>
-      <c r="C250" s="0" t="inlineStr">
+      <c r="C260" s="0" t="inlineStr">
         <is>
           <t>分析30元＋价格调整15元，分别计费</t>
         </is>
       </c>
-      <c r="D250" s="0" t="inlineStr">
+      <c r="D260" s="0" t="inlineStr">
         <is>
           <t>分析已包含改价</t>
         </is>
       </c>
-      <c r="E250" s="0" t="inlineStr">
+      <c r="E260" s="0" t="inlineStr">
         <is>
           <t>分析是交付报告和建议，改价是独立执行任务</t>
         </is>
       </c>
-      <c r="F250" s="0" t="inlineStr">
+      <c r="F260" s="0" t="inlineStr">
         <is>
           <t>任务评分·利润分析 / 价格调整</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="0" t="n">
+    <row r="261">
+      <c r="A261" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="B251" s="0" t="inlineStr">
+      <c r="B261" s="0" t="inlineStr">
         <is>
           <t>同一案件先30元举报后补Test Buy，是否计30＋50＝80元？</t>
         </is>
       </c>
-      <c r="C251" s="0" t="inlineStr">
+      <c r="C261" s="0" t="inlineStr">
         <is>
           <t>先结30元，补足至50元，不超过50元</t>
         </is>
       </c>
-      <c r="D251" s="0" t="inlineStr">
+      <c r="D261" s="0" t="inlineStr">
         <is>
           <t>分别计80元</t>
         </is>
       </c>
-      <c r="E251" s="0" t="inlineStr">
+      <c r="E261" s="0" t="inlineStr">
         <is>
           <t>两档只取最高，先结30元后补足最多20元</t>
         </is>
       </c>
-      <c r="F251" s="0" t="inlineStr">
+      <c r="F261" s="0" t="inlineStr">
         <is>
           <t>任务评分·跟卖取证</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>21</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>同系列10个尺寸共用调研方案，是否各领75元？</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>共用方案只计一次75元</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>10×75＝750元</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>系列产品开发计费规则①</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>任务评分·系列产品开发计费规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>22</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>同系列后续产品的样品评估，是否都按75元？</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>由负责人确认：独立验证75元，基本核对15元，无需验证0元</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>统一按75元/个</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>系列产品开发计费规则②</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>任务评分·系列产品开发计费规则</t>
         </is>
       </c>
     </row>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -10,6 +10,7 @@
     <sheet name="优化登记与复盘规则" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="广告优化认定规则（已归档）" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="改善成果奖励" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="系列开发计酬" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00&quot;元&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="46">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -267,12 +268,8 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="45">
+  <fills count="48">
     <fill>
       <patternFill/>
     </fill>
@@ -494,8 +491,24 @@
         <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="18">
     <border/>
     <border>
       <left style="thin">
@@ -655,37 +668,6 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1">
@@ -837,7 +819,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1144,15 +1126,35 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0"/>
@@ -2092,7 +2094,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="300" customHeight="1" s="1">
+    <row r="8" ht="380" customHeight="1" s="1">
       <c r="A8" s="60" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -2111,7 +2113,8 @@
       <c r="D8" s="61" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="E8" s="61" t="inlineStr">
@@ -2130,7 +2133,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="300" customHeight="1" s="1">
+    <row r="9" ht="380" customHeight="1" s="1">
       <c r="A9" s="60" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -2149,7 +2152,8 @@
       <c r="D9" s="61" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="E9" s="61" t="inlineStr">
@@ -2168,7 +2172,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="300" customHeight="1" s="1">
+    <row r="10" ht="380" customHeight="1" s="1">
       <c r="A10" s="60" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -2187,7 +2191,8 @@
       <c r="D10" s="61" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="E10" s="61" t="inlineStr">
@@ -2206,7 +2211,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="300" customHeight="1" s="1">
+    <row r="11" ht="380" customHeight="1" s="1">
       <c r="A11" s="60" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -2225,7 +2230,8 @@
       <c r="D11" s="61" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="E11" s="61" t="inlineStr">
@@ -3486,7 +3492,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="300" customHeight="1" s="1">
+    <row r="45" ht="420" customHeight="1" s="1">
       <c r="A45" s="60" t="inlineStr">
         <is>
           <t>新品开发</t>
@@ -3505,12 +3511,13 @@
       <c r="D45" s="61" t="inlineStr">
         <is>
           <t>调研完整且结论有依据，经负责人确认。无需凑固定竞品数量；结论为不建议开发时，已完成且通过验收的调研照常计费。
-统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="E45" s="61" t="inlineStr">
         <is>
-          <t>每个独立开发项目75元。</t>
+          <t>75元/独立开发项目的本阶段交付；同系列共用调研或厂家方案只计一次，不按SKU数累加。</t>
         </is>
       </c>
       <c r="F45" s="61" t="inlineStr">
@@ -3524,7 +3531,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="300" customHeight="1" s="1">
+    <row r="46" ht="420" customHeight="1" s="1">
       <c r="A46" s="60" t="inlineStr">
         <is>
           <t>新品开发</t>
@@ -3543,12 +3550,13 @@
       <c r="D46" s="61" t="inlineStr">
         <is>
           <t>关键合作条件清楚且有记录，经负责人确认。按完整找厂与条件确认交付计费，不按联系次数或报价份数计；无合适厂家时须提供完整调查结论并经负责人确认结案。
-统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="E46" s="61" t="inlineStr">
         <is>
-          <t>每个独立开发项目75元。</t>
+          <t>75元/独立开发项目的本阶段交付；同系列共用调研或厂家方案只计一次，不按SKU数累加。</t>
         </is>
       </c>
       <c r="F46" s="61" t="inlineStr">
@@ -3562,7 +3570,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="300" customHeight="1" s="1">
+    <row r="47" ht="420" customHeight="1" s="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>新品开发</t>
@@ -3581,12 +3589,13 @@
       <c r="D47" s="3" t="inlineStr">
         <is>
           <t>形成可供决策的验证结论并经负责人验收；继续修改中不自动结案。同一轮原问题补测、整改、催办合并计费；新增独立验证范围须事先确认，不按每次样品到货计75元。
-统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>每个约定的独立样品验证任务75元。</t>
+          <t>75元/事先约定的独立样品验证任务；同一验证方案内的不同参数检查、原问题整改及复测合并。不因样品或SKU数量增加而自动增加任务数。</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -3600,7 +3609,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="300" customHeight="1" s="1">
+    <row r="48" ht="420" customHeight="1" s="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>新品开发与内容准备</t>
@@ -3618,7 +3627,8 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>主动核实产品规格、功能、使用方式、限制、卖点依据及包装内容，向厂家解决缺失或矛盾信息，形成经确认的可用事实资料。已有完整资料仅汇总、复制或直接使用不计本项。调研、找厂、样品任务已交付的相同资料不再计40元；只有额外核实、补全且独立验收的资料工作才计。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+          <t>主动核实产品规格、功能、使用方式、限制、卖点依据及包装内容，向厂家解决缺失或矛盾信息，形成经确认的可用事实资料。已有完整资料仅汇总、复制或直接使用不计本项。调研、找厂、样品任务已交付的相同资料不再计40元；只有额外核实、补全且独立验收的资料工作才计。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -3637,7 +3647,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="300" customHeight="1" s="1">
+    <row r="49" ht="420" customHeight="1" s="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>新品开发与内容准备</t>
@@ -3655,7 +3665,8 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>明确主图和辅图各自展示内容、卖点、参数、文案及参考，提出美工制作要求，跟进修改并核验成图。同一方案多SKU共用只计一次50元；同轮沟通、修改及核验均包含。实际拍摄和修图不属于本人任务。图片上传另按10元/SKU；A+素材策划已含A+75元，相同交付不再计本项。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+          <t>明确主图和辅图各自展示内容、卖点、参数、文案及参考，提出美工制作要求，跟进修改并核验成图。同一方案多SKU共用只计一次50元；同轮沟通、修改及核验均包含。实际拍摄和修图不属于本人任务。图片上传另按10元/SKU；A+素材策划已含A+75元，相同交付不再计本项。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3674,7 +3685,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="300" customHeight="1" s="1">
+    <row r="50" ht="420" customHeight="1" s="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>新品开发与内容准备</t>
@@ -3692,7 +3703,8 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>理解产品和视频内容，编写准确且与画面对应的字幕，核对参数及表述，提供段落或时间对应并交付经确认的可用定稿。不包含完整视频脚本策划、拍摄、剪辑。直接使用已有字幕不计编写金额；同稿反复修改不另计，视频上传另按原规则。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。</t>
+          <t>理解产品和视频内容，编写准确且与画面对应的字幕，核对参数及表述，提供段落或时间对应并交付经确认的可用定稿。不包含完整视频脚本策划、拍摄、剪辑。直接使用已有字幕不计编写金额；同稿反复修改不另计，视频上传另按原规则。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4051,91 +4063,91 @@
       </c>
     </row>
     <row r="61" ht="60" customHeight="1" s="1">
-      <c r="A61" s="116" t="inlineStr">
+      <c r="A61" s="133" t="inlineStr">
         <is>
           <t>项目状态与规则来源（核对日期2026-09-08；参与资格以目标站点后台为准，任务金额为内部建议，并非亚马逊收费标准）。早期评论人计划已停止，仅保留Vine。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="65" customHeight="1" s="1">
-      <c r="A62" s="116" t="inlineStr">
+      <c r="A62" s="133" t="inlineStr">
         <is>
           <t>早期评论人计划停止公告</t>
         </is>
       </c>
-      <c r="B62" s="116" t="inlineStr">
+      <c r="B62" s="133" t="inlineStr">
         <is>
           <t>https://sellercentral.amazon.com/seller-forums/discussions/t/2bb2eaeec50cbc448f676c1a6f000ff9</t>
         </is>
       </c>
     </row>
     <row r="63" ht="65" customHeight="1" s="1">
-      <c r="A63" s="116" t="inlineStr">
+      <c r="A63" s="133" t="inlineStr">
         <is>
           <t>Vine</t>
         </is>
       </c>
-      <c r="B63" s="116" t="inlineStr">
+      <c r="B63" s="133" t="inlineStr">
         <is>
           <t>https://sell.amazon.com/programs/vine</t>
         </is>
       </c>
     </row>
     <row r="64" ht="65" customHeight="1" s="1">
-      <c r="A64" s="116" t="inlineStr">
+      <c r="A64" s="133" t="inlineStr">
         <is>
           <t>Subscribe &amp; Save</t>
         </is>
       </c>
-      <c r="B64" s="116" t="inlineStr">
+      <c r="B64" s="133" t="inlineStr">
         <is>
           <t>https://sell.amazon.com/programs/subscribe-and-save/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="65" customHeight="1" s="1">
-      <c r="A65" s="116" t="inlineStr">
+      <c r="A65" s="133" t="inlineStr">
         <is>
           <t>Virtual Bundles</t>
         </is>
       </c>
-      <c r="B65" s="116" t="inlineStr">
+      <c r="B65" s="133" t="inlineStr">
         <is>
           <t>https://sell.amazon.com/blog/product-bundling</t>
         </is>
       </c>
     </row>
     <row r="66" ht="65" customHeight="1" s="1">
-      <c r="A66" s="116" t="inlineStr">
+      <c r="A66" s="133" t="inlineStr">
         <is>
           <t>品牌故事</t>
         </is>
       </c>
-      <c r="B66" s="116" t="inlineStr">
+      <c r="B66" s="133" t="inlineStr">
         <is>
           <t>https://sell.amazon.com/tools/a-content</t>
         </is>
       </c>
     </row>
     <row r="67" ht="65" customHeight="1" s="1">
-      <c r="A67" s="116" t="inlineStr">
+      <c r="A67" s="133" t="inlineStr">
         <is>
           <t>品牌保护与Test Buy</t>
         </is>
       </c>
-      <c r="B67" s="116" t="inlineStr">
+      <c r="B67" s="133" t="inlineStr">
         <is>
           <t>https://sell.amazon.com/brand-registry/project-zero/</t>
         </is>
       </c>
     </row>
     <row r="68" ht="65" customHeight="1" s="1">
-      <c r="A68" s="116" t="inlineStr">
+      <c r="A68" s="133" t="inlineStr">
         <is>
           <t>正品转售说明</t>
         </is>
       </c>
-      <c r="B68" s="116" t="inlineStr">
+      <c r="B68" s="133" t="inlineStr">
         <is>
           <t>https://sell.amazon.com/blog/sell-branded-products-on-amazon</t>
         </is>
@@ -4572,7 +4584,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="330" customHeight="1" s="1">
+    <row r="14" ht="420" customHeight="1" s="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -4606,7 +4618,8 @@
       <c r="H14" s="9" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -4615,7 +4628,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="330" customHeight="1" s="1">
+    <row r="15" ht="420" customHeight="1" s="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -4649,7 +4662,8 @@
       <c r="H15" s="9" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4658,7 +4672,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="330" customHeight="1" s="1">
+    <row r="16" ht="420" customHeight="1" s="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -4692,7 +4706,8 @@
       <c r="H16" s="9" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -4701,7 +4716,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="330" customHeight="1" s="1">
+    <row r="17" ht="420" customHeight="1" s="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Listing内容维护</t>
@@ -4735,7 +4750,8 @@
       <c r="H17" s="9" t="inlineStr">
         <is>
           <t>独立计费前提：需要员工自行研究产品、构思内容并交付原创文案。将别人提供的文案用Codex改写后填表上传，属于上架任务，不另计本项。
-首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。</t>
+首次编写：依据已确认产品资料完成原创文案，核对参数、卖点及表述，交付可供上架的定稿并经确认后计费，不强制等待上线效果复盘。同次定稿前修改合并，不另计费。后续实质优化：登记问题依据、修改范围、目标及复盘日期，更新核验并完成复盘后结算；同模块复盘前追加修改并入原任务。单纯翻译已有文案归翻译更新项目。
+同系列首次文案共用时，按实际独立原创内容套数计费：统一文案仅替换确认后的尺寸、电压、颜色等参数，标题/五点/描述/关键词各计一套，共50元；参数替换、填表及核对包含在上架执行中。不按复制出的Listing数量重复领取原创费。不同功能或卖点确需独立研究并原创的内容，按实际独立交付计费；参数不同不能作为唯一依据。</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -6183,7 +6199,7 @@
       </c>
       <c r="I50" s="3" t="n"/>
     </row>
-    <row r="51" ht="330" customHeight="1" s="1">
+    <row r="51" ht="440" customHeight="1" s="1">
       <c r="A51" s="46" t="inlineStr">
         <is>
           <t>新品开发</t>
@@ -6202,7 +6218,7 @@
       </c>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>每个独立开发项目75元。</t>
+          <t>75元/独立开发项目的本阶段交付；同系列共用调研或厂家方案只计一次，不按SKU数累加。</t>
         </is>
       </c>
       <c r="F51" s="46" t="inlineStr">
@@ -6219,7 +6235,7 @@
           <t>分析竞品、需求、价格区间、关键规格、客户反馈及初步利润空间，提出产品建议和风险判断。数据注明来源、期间及估算口径。
 调研完整且结论有依据，经负责人确认。无需凑固定竞品数量；结论为不建议开发时，已完成且通过验收的调研照常计费。
 统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
-系列产品开发：共用调研方案的多个规格/尺寸只计一次75元。详见"系列产品开发计费规则"。</t>
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -6228,7 +6244,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="330" customHeight="1" s="1">
+    <row r="52" ht="440" customHeight="1" s="1">
       <c r="A52" s="46" t="inlineStr">
         <is>
           <t>新品开发</t>
@@ -6247,7 +6263,7 @@
       </c>
       <c r="E52" s="46" t="inlineStr">
         <is>
-          <t>每个独立开发项目75元。</t>
+          <t>75元/独立开发项目的本阶段交付；同系列共用调研或厂家方案只计一次，不按SKU数累加。</t>
         </is>
       </c>
       <c r="F52" s="46" t="inlineStr">
@@ -6264,7 +6280,7 @@
           <t>寻找并核实匹配的厂家，比较有效报价、MOQ、交期、包装及定制条件，确认关键费用、供货能力和合作限制，提出选择建议。
 关键合作条件清楚且有记录，经负责人确认。按完整找厂与条件确认交付计费，不按联系次数或报价份数计；无合适厂家时须提供完整调查结论并经负责人确认结案。
 统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
-系列产品开发：共用厂家的多个规格/尺寸只计一次75元。详见"系列产品开发计费规则"。</t>
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -6273,7 +6289,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="330" customHeight="1" s="1">
+    <row r="53" ht="440" customHeight="1" s="1">
       <c r="A53" s="46" t="inlineStr">
         <is>
           <t>新品开发</t>
@@ -6292,7 +6308,7 @@
       </c>
       <c r="E53" s="46" t="inlineStr">
         <is>
-          <t>每个约定的独立样品验证任务75元。</t>
+          <t>75元/事先约定的独立样品验证任务；同一验证方案内的不同参数检查、原问题整改及复测合并。不因样品或SKU数量增加而自动增加任务数。</t>
         </is>
       </c>
       <c r="F53" s="46" t="inlineStr">
@@ -6309,7 +6325,7 @@
           <t>按事先确认的验证要求完成样品检查或协调测试，记录问题、跟进整改及复测，形成通过、修改或停止结论。
 形成可供决策的验证结论并经负责人验收；继续修改中不自动结案。同一轮原问题补测、整改、催办合并计费；新增独立验证范围须事先确认，不按每次样品到货计75元。
 统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
-系列产品开发：首个产品建立评估标准计75元；同系列后续产品，需独立验证的75元/个，仅核对基本参数的15元/个，无需验证的不另计。由负责人确认。</t>
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -6318,7 +6334,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="330" customHeight="1" s="1">
+    <row r="54" ht="440" customHeight="1" s="1">
       <c r="A54" s="46" t="inlineStr">
         <is>
           <t>新品开发与内容准备</t>
@@ -6352,7 +6368,7 @@
       <c r="H54" s="46" t="inlineStr">
         <is>
           <t>主动核实产品规格、功能、使用方式、限制、卖点依据及包装内容，向厂家解决缺失或矛盾信息，形成经确认的可用事实资料。已有完整资料仅汇总、复制或直接使用不计本项。调研、找厂、样品任务已交付的相同资料不再计40元；只有额外核实、补全且独立验收的资料工作才计。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
-系列产品开发：首个产品完整整理40元；后续产品仅更新差异参数的10元/个。</t>
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -6361,7 +6377,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="330" customHeight="1" s="1">
+    <row r="55" ht="440" customHeight="1" s="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
           <t>新品开发与内容准备</t>
@@ -6395,7 +6411,7 @@
       <c r="H55" s="9" t="inlineStr">
         <is>
           <t>明确主图和辅图各自展示内容、卖点、参数、文案及参考，提出美工制作要求，跟进修改并核验成图。同一方案多SKU共用只计一次50元；同轮沟通、修改及核验均包含。实际拍摄和修图不属于本人任务。图片上传另按10元/SKU；A+素材策划已含A+75元，相同交付不再计本项。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
-系列产品开发：共用拍摄方案的，首个产品50元；后续仅更换实物不重新策划的10元/个。</t>
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -6404,7 +6420,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="330" customHeight="1" s="1">
+    <row r="56" ht="440" customHeight="1" s="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
           <t>新品开发与内容准备</t>
@@ -6438,7 +6454,7 @@
       <c r="H56" s="9" t="inlineStr">
         <is>
           <t>理解产品和视频内容，编写准确且与画面对应的字幕，核对参数及表述，提供段落或时间对应并交付经确认的可用定稿。不包含完整视频脚本策划、拍摄、剪辑。直接使用已有字幕不计编写金额；同稿反复修改不另计，视频上传另按原规则。统一关联新品开发项目编号。共用调研、厂家或验证方案的多个尺寸/SKU不重复领取完整金额；确需独立完成的交付按确认范围计。等待厂家、催办、失败重试或修复本人错误不增加金额。负责人指定产品后的执行按倍率1；主动开发规则未另定，不自动给全部后续任务加倍。同一交付在调研、找厂、样品、资料整理及样品协调之间只计一次。
-系列产品开发：共用脚本框架的，首个25元；后续仅替换参数的5元/个。</t>
+系列开发计酬：同一产品用途、核心设计和供应方案，仅尺寸、电压、颜色等参数不同且可共用交付的SKU，按一个系列开发项目登记，共用阶段只计一次，不按SKU数量乘开发总金额。参数变化本身不等于工作相同，涉及不同安全要求、功能、结构或性能验证时，应记录实际差异并事先确认独立工作范围。新SKU、新OA编号或跨月不自动构成新项目。详见“系列开发计酬”。</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -6851,11 +6867,7 @@
       <c r="H66" s="52" t="n"/>
     </row>
     <row r="67" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A67" s="124" t="inlineStr">
-        <is>
-          <t>系列产品开发计费规则</t>
-        </is>
-      </c>
+      <c r="A67" s="54" t="n"/>
       <c r="B67" s="28" t="n"/>
       <c r="C67" s="52" t="n"/>
       <c r="D67" s="55" t="n"/>
@@ -6865,36 +6877,24 @@
       <c r="H67" s="52" t="n"/>
     </row>
     <row r="68" ht="17.64999961853027" customHeight="1" s="1">
-      <c r="A68" s="54" t="inlineStr">
-        <is>
-          <t>同一系列产品（仅规格、尺寸、颜色等参数不同）的开发任务，按以下原则计费：
-① 市场调研、厂家筛选：共用同一份方案的，只计一次75元，不按产品数量重复领取。
-② 样品评估：首个产品建立评估标准计75元；同系列后续产品，由负责人逐个确认是否需要独立验证——需独立验证的按75元/个计费，仅需核对尺寸等基本参数的按15元/个计费，无需单独验证的不另计。
-③ 产品资料整理：首个产品完整整理计40元；同系列后续产品仅更新差异参数的计10元/个。
-④ 产品图片策划：共用拍摄方案和视觉风格的，首个产品计50元；后续产品仅更换实物但不重新策划的计10元/个。
-⑤ 视频字幕：共用脚本框架的，首个计25元；后续产品仅替换参数的计5元/个。
-⑥ 系列产品的认定和后续产品的独立验证范围，须在派单时由负责人确认，不由员工自行判定。</t>
-        </is>
-      </c>
-      <c r="B68" s="125" t="n"/>
-      <c r="C68" s="125" t="n"/>
-      <c r="D68" s="125" t="n"/>
-      <c r="E68" s="125" t="n"/>
-      <c r="F68" s="125" t="n"/>
-      <c r="G68" s="125" t="n"/>
-      <c r="H68" s="125" t="n"/>
-      <c r="I68" s="126" t="n"/>
+      <c r="A68" s="54" t="n"/>
+      <c r="B68" s="28" t="n"/>
+      <c r="C68" s="52" t="n"/>
+      <c r="D68" s="55" t="n"/>
+      <c r="E68" s="28" t="n"/>
+      <c r="F68" s="53" t="n"/>
+      <c r="G68" s="53" t="n"/>
+      <c r="H68" s="52" t="n"/>
     </row>
     <row r="69" ht="25.89999961853027" customHeight="1" s="1">
-      <c r="A69" s="127" t="n"/>
-      <c r="B69" s="128" t="n"/>
-      <c r="C69" s="128" t="n"/>
-      <c r="D69" s="128" t="n"/>
-      <c r="E69" s="128" t="n"/>
-      <c r="F69" s="128" t="n"/>
-      <c r="G69" s="128" t="n"/>
-      <c r="H69" s="128" t="n"/>
-      <c r="I69" s="129" t="n"/>
+      <c r="A69" s="54" t="n"/>
+      <c r="B69" s="28" t="n"/>
+      <c r="C69" s="52" t="n"/>
+      <c r="D69" s="55" t="n"/>
+      <c r="E69" s="28" t="n"/>
+      <c r="F69" s="53" t="n"/>
+      <c r="G69" s="53" t="n"/>
+      <c r="H69" s="52" t="n"/>
     </row>
     <row r="70" ht="25.5" customHeight="1" s="1">
       <c r="A70" s="54" t="n"/>
@@ -7435,12 +7435,11 @@
       <c r="I99" s="0" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="116" t="n"/>
+      <c r="A101" s="133" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="36">
     <mergeCell ref="B91:C91"/>
-    <mergeCell ref="A68:I69"/>
     <mergeCell ref="B90:C90"/>
     <mergeCell ref="B81:C81"/>
     <mergeCell ref="E91:H91"/>
@@ -8338,7 +8337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H263"/>
+  <dimension ref="A2:H251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -13764,10 +13763,10 @@
           <t>完整分析1个ASIN利润问题并提出建议</t>
         </is>
       </c>
-      <c r="C215" s="0" t="n">
+      <c r="C215" s="134" t="n">
         <v>30</v>
       </c>
-      <c r="D215" s="0" t="n">
+      <c r="D215" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E215" s="0">
@@ -13791,10 +13790,10 @@
           <t>初步排查并结案</t>
         </is>
       </c>
-      <c r="C216" s="0" t="n">
+      <c r="C216" s="134" t="n">
         <v>15</v>
       </c>
-      <c r="D216" s="0" t="n">
+      <c r="D216" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E216" s="0">
@@ -13818,10 +13817,10 @@
           <t>1场Coupon活动覆盖10个ASIN的完整复盘</t>
         </is>
       </c>
-      <c r="C217" s="0" t="n">
+      <c r="C217" s="134" t="n">
         <v>30</v>
       </c>
-      <c r="D217" s="0" t="n">
+      <c r="D217" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E217" s="0">
@@ -13845,10 +13844,10 @@
           <t>1个ASIN尺寸分级费用异常，开Case并跟进</t>
         </is>
       </c>
-      <c r="C218" s="0" t="n">
+      <c r="C218" s="134" t="n">
         <v>20</v>
       </c>
-      <c r="D218" s="0" t="n">
+      <c r="D218" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E218" s="0">
@@ -13872,10 +13871,10 @@
           <t>本周完成全部约定检查</t>
         </is>
       </c>
-      <c r="C219" s="0" t="n">
+      <c r="C219" s="134" t="n">
         <v>5</v>
       </c>
-      <c r="D219" s="0" t="n">
+      <c r="D219" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E219" s="0">
@@ -13899,10 +13898,10 @@
           <t>已有证据完成举报并跟进</t>
         </is>
       </c>
-      <c r="C220" s="0" t="n">
+      <c r="C220" s="134" t="n">
         <v>30</v>
       </c>
-      <c r="D220" s="0" t="n">
+      <c r="D220" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E220" s="0">
@@ -13926,10 +13925,10 @@
           <t>完成Test Buy取证全过程及案件处理</t>
         </is>
       </c>
-      <c r="C221" s="0" t="n">
+      <c r="C221" s="134" t="n">
         <v>50</v>
       </c>
-      <c r="D221" s="0" t="n">
+      <c r="D221" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E221" s="0">
@@ -13953,10 +13952,10 @@
           <t>1个报名项目含多个子SKU</t>
         </is>
       </c>
-      <c r="C222" s="0" t="n">
+      <c r="C222" s="134" t="n">
         <v>15</v>
       </c>
-      <c r="D222" s="0" t="n">
+      <c r="D222" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E222" s="0">
@@ -13980,10 +13979,10 @@
           <t>全新策划1份品牌故事并绑定20个ASIN</t>
         </is>
       </c>
-      <c r="C223" s="0" t="n">
+      <c r="C223" s="134" t="n">
         <v>75</v>
       </c>
-      <c r="D223" s="0" t="n">
+      <c r="D223" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E223" s="0">
@@ -14007,10 +14006,10 @@
           <t>修改已有品牌故事的2张卡片</t>
         </is>
       </c>
-      <c r="C224" s="0" t="n">
+      <c r="C224" s="134" t="n">
         <v>10</v>
       </c>
-      <c r="D224" s="0" t="n">
+      <c r="D224" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E224" s="0">
@@ -14034,10 +14033,10 @@
           <t>同批10个ASIN加入并设折扣</t>
         </is>
       </c>
-      <c r="C225" s="0" t="n">
+      <c r="C225" s="134" t="n">
         <v>10</v>
       </c>
-      <c r="D225" s="0" t="n">
+      <c r="D225" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E225" s="0">
@@ -14061,10 +14060,10 @@
           <t>新建1个虚拟捆绑商品</t>
         </is>
       </c>
-      <c r="C226" s="0" t="n">
+      <c r="C226" s="134" t="n">
         <v>25</v>
       </c>
-      <c r="D226" s="0" t="n">
+      <c r="D226" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E226" s="0">
@@ -14088,10 +14087,10 @@
           <t>已有捆绑修改标题和价格</t>
         </is>
       </c>
-      <c r="C227" s="0" t="n">
+      <c r="C227" s="134" t="n">
         <v>10</v>
       </c>
-      <c r="D227" s="0" t="n">
+      <c r="D227" s="134" t="n">
         <v>1</v>
       </c>
       <c r="E227" s="0">
@@ -14104,881 +14103,644 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="130" t="inlineStr">
-        <is>
-          <t>系列产品开发计费示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>场景</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="24" t="inlineStr">
+        <is>
+          <t>防重复计费速查：常见场景判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="31" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B231" s="31" t="inlineStr">
+        <is>
+          <t>场景描述</t>
+        </is>
+      </c>
+      <c r="C231" s="31" t="inlineStr">
         <is>
           <t>正确计费</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D231" s="31" t="inlineStr">
         <is>
           <t>错误计费</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>计算依据</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="32" t="inlineStr">
-        <is>
-          <t>10个尺寸的同款阀门
-共用调研和厂家</t>
-        </is>
-      </c>
-      <c r="B230" s="32" t="inlineStr">
-        <is>
-          <t>调研、找厂方案完全相同，样品需逐个验证</t>
-        </is>
-      </c>
-      <c r="C230" s="32" t="inlineStr">
-        <is>
-          <t>调研75＋找厂75＋样品(首个75＋9个×15)＝360元</t>
-        </is>
-      </c>
-      <c r="D230" s="32" t="inlineStr">
-        <is>
-          <t>调研750＋找厂750＋样品750＝2,250元</t>
-        </is>
-      </c>
-      <c r="E230" s="32" t="inlineStr">
-        <is>
-          <t>共用方案只计一次；后续产品仅核对尺寸参数按15元</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="32" t="inlineStr">
-        <is>
-          <t>10个尺寸的同款阀门
-含资料和图片</t>
-        </is>
-      </c>
-      <c r="B231" s="32" t="inlineStr">
-        <is>
-          <t>续上例，加上资料整理和图片策划</t>
-        </is>
-      </c>
-      <c r="C231" s="32" t="inlineStr">
-        <is>
-          <t>资料(40＋9×10)＋图片(50＋9×10)＝270元
-开发360＋内容270＝630元</t>
-        </is>
-      </c>
-      <c r="D231" s="32" t="inlineStr">
-        <is>
-          <t>资料400＋图片500＝900元
-开发2,250＋内容900＝3,150元</t>
-        </is>
-      </c>
-      <c r="E231" s="32" t="inlineStr">
-        <is>
-          <t>首个产品完整计费，后续仅更新差异参数和更换实物</t>
-        </is>
-      </c>
+      <c r="E231" s="31" t="inlineStr">
+        <is>
+          <t>判定依据</t>
+        </is>
+      </c>
+      <c r="F231" s="31" t="inlineStr">
+        <is>
+          <t>所在规则</t>
+        </is>
+      </c>
+      <c r="G231" s="31" t="n"/>
+      <c r="H231" s="31" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="32" t="inlineStr">
-        <is>
-          <t>3个完全不同的产品线</t>
-        </is>
+      <c r="A232" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B232" s="32" t="inlineStr">
         <is>
-          <t>产品类型、市场、厂家均不同</t>
+          <t>A+完全重做后，是否可同时计A+制作发布75元和全新重做75元？</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
         <is>
-          <t>各自独立：3×(75＋75＋75)＝675元</t>
+          <t>只计一次75元</t>
         </is>
       </c>
       <c r="D232" s="32" t="inlineStr">
         <is>
-          <t>按系列产品规则减免</t>
+          <t>叠加计150元</t>
         </is>
       </c>
       <c r="E232" s="32" t="inlineStr">
         <is>
-          <t>不同产品线的调研和厂家不共用，各自独立计费</t>
+          <t>同一成果只计一次</t>
+        </is>
+      </c>
+      <c r="F232" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·A+制作发布</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="32" t="inlineStr">
-        <is>
-          <t>同系列5个尺寸
-其中2个需独立样品验证</t>
-        </is>
+      <c r="A233" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B233" s="32" t="inlineStr">
         <is>
-          <t>负责人确认2个特殊尺寸需独立验证</t>
+          <t>同一电压错误出现在标题、五点和A+三个位置</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
         <is>
-          <t>样品：首个75＋2个独立验证×75＋2个基本核对×15＝300元</t>
+          <t>修正全部位置，共10元</t>
         </is>
       </c>
       <c r="D233" s="32" t="inlineStr">
         <is>
-          <t>5×75＝375元</t>
+          <t>按位置分别计30元</t>
         </is>
       </c>
       <c r="E233" s="32" t="inlineStr">
         <is>
-          <t>由负责人逐个确认验证范围</t>
+          <t>同源错误合并为1个错误点</t>
+        </is>
+      </c>
+      <c r="F233" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·Listing纠错</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="32" t="inlineStr">
-        <is>
-          <t>同系列产品的字幕
-共用脚本框架</t>
-        </is>
+      <c r="A234" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B234" s="32" t="inlineStr">
         <is>
-          <t>10个产品的视频字幕，框架相同仅替换参数</t>
+          <t>员工自主发现价格异常并修正，是否同时计任务金额和主动金额？</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
         <is>
-          <t>首个25＋9×5＝70元</t>
+          <t>按正常金额×主动倍率</t>
         </is>
       </c>
       <c r="D234" s="32" t="inlineStr">
         <is>
-          <t>10×25＝250元</t>
+          <t>正常金额＋另加主动金额</t>
         </is>
       </c>
       <c r="E234" s="32" t="inlineStr">
         <is>
-          <t>共用脚本框架的后续产品按5元/个</t>
-        </is>
-      </c>
-    </row>
-    <row r="238"/>
-    <row r="239"/>
+          <t>发起来源互斥：自主发起按倍率，不另加正常金额</t>
+        </is>
+      </c>
+      <c r="F234" s="32" t="inlineStr">
+        <is>
+          <t>主动改善评价·二</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B235" s="32" t="inlineStr">
+        <is>
+          <t>员工先提出建议，经负责人批准后建立任务执行</t>
+        </is>
+      </c>
+      <c r="C235" s="32" t="inlineStr">
+        <is>
+          <t>按正常金额×主动倍率</t>
+        </is>
+      </c>
+      <c r="D235" s="32" t="inlineStr">
+        <is>
+          <t>只按普通金额结算，遗漏适用主动倍率</t>
+        </is>
+      </c>
+      <c r="E235" s="32" t="inlineStr">
+        <is>
+          <t>先提出即属主动发起，补建任务不改变来源</t>
+        </is>
+      </c>
+      <c r="F235" s="32" t="inlineStr">
+        <is>
+          <t>主动改善评价·A17</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B236" s="32" t="inlineStr">
+        <is>
+          <t>同一滞留库存问题先Relist再申诉</t>
+        </is>
+      </c>
+      <c r="C236" s="32" t="inlineStr">
+        <is>
+          <t>合计15元（取最高档）</t>
+        </is>
+      </c>
+      <c r="D236" s="32" t="inlineStr">
+        <is>
+          <t>移除10元＋申诉15元＝25元</t>
+        </is>
+      </c>
+      <c r="E236" s="32" t="inlineStr">
+        <is>
+          <t>同一问题连续处理只取最高适用金额</t>
+        </is>
+      </c>
+      <c r="F236" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·滞留库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B237" s="32" t="inlineStr">
+        <is>
+          <t>上架组包含5个SKU，OA记录5条</t>
+        </is>
+      </c>
+      <c r="C237" s="32" t="inlineStr">
+        <is>
+          <t>按组总金额计（如52元）</t>
+        </is>
+      </c>
+      <c r="D237" s="32" t="inlineStr">
+        <is>
+          <t>5条OA各计25元＝125元</t>
+        </is>
+      </c>
+      <c r="E237" s="32" t="inlineStr">
+        <is>
+          <t>以执行组为单位，OA分摊组总金额</t>
+        </is>
+      </c>
+      <c r="F237" s="32" t="inlineStr">
+        <is>
+          <t>场景示例·上架组</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B238" s="32" t="inlineStr">
+        <is>
+          <t>5个SKU共用同一份新A+</t>
+        </is>
+      </c>
+      <c r="C238" s="32" t="inlineStr">
+        <is>
+          <t>1份×75元＝75元</t>
+        </is>
+      </c>
+      <c r="D238" s="32" t="inlineStr">
+        <is>
+          <t>5×75元＝375元</t>
+        </is>
+      </c>
+      <c r="E238" s="32" t="inlineStr">
+        <is>
+          <t>共用同一份内容只计一份</t>
+        </is>
+      </c>
+      <c r="F238" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·A+制作发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B239" s="32" t="inlineStr">
+        <is>
+          <t>同一份A+同一轮修改了6个模块</t>
+        </is>
+      </c>
+      <c r="C239" s="32" t="inlineStr">
+        <is>
+          <t>合计10元</t>
+        </is>
+      </c>
+      <c r="D239" s="32" t="inlineStr">
+        <is>
+          <t>6×10元＝60元</t>
+        </is>
+      </c>
+      <c r="E239" s="32" t="inlineStr">
+        <is>
+          <t>同份同轮合计10元，不按模块数量累加</t>
+        </is>
+      </c>
+      <c r="F239" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·A+增删修改</t>
+        </is>
+      </c>
+    </row>
     <row r="240">
-      <c r="A240" s="24" t="inlineStr">
-        <is>
-          <t>防重复计费速查：常见场景判定</t>
+      <c r="A240" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B240" s="32" t="inlineStr">
+        <is>
+          <t>同站点1个ASIN的Buy Box异常多次开Case后恢复</t>
+        </is>
+      </c>
+      <c r="C240" s="32" t="inlineStr">
+        <is>
+          <t>合计15元</t>
+        </is>
+      </c>
+      <c r="D240" s="32" t="inlineStr">
+        <is>
+          <t>按Case数量计费</t>
+        </is>
+      </c>
+      <c r="E240" s="32" t="inlineStr">
+        <is>
+          <t>按ASIN计费，同一ASIN多个SKU或多个Case不增加金额</t>
+        </is>
+      </c>
+      <c r="F240" s="32" t="inlineStr">
+        <is>
+          <t>任务评分·Buy Box</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="31" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B241" s="31" t="inlineStr">
-        <is>
-          <t>场景描述</t>
-        </is>
-      </c>
-      <c r="C241" s="31" t="inlineStr">
-        <is>
-          <t>正确计费</t>
-        </is>
-      </c>
-      <c r="D241" s="31" t="inlineStr">
-        <is>
-          <t>错误计费</t>
-        </is>
-      </c>
-      <c r="E241" s="31" t="inlineStr">
-        <is>
-          <t>判定依据</t>
-        </is>
-      </c>
-      <c r="F241" s="31" t="inlineStr">
-        <is>
-          <t>所在规则</t>
-        </is>
-      </c>
-      <c r="G241" s="31" t="n"/>
-      <c r="H241" s="31" t="n"/>
+      <c r="A241" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B241" s="32" t="inlineStr">
+        <is>
+          <t>同一Listing标题在复盘前又做了一次优化修改</t>
+        </is>
+      </c>
+      <c r="C241" s="32" t="inlineStr">
+        <is>
+          <t>并入原任务，不新增金额</t>
+        </is>
+      </c>
+      <c r="D241" s="32" t="inlineStr">
+        <is>
+          <t>新建优化任务再计10元</t>
+        </is>
+      </c>
+      <c r="E241" s="32" t="inlineStr">
+        <is>
+          <t>同模块复盘前追加并入，不重复</t>
+        </is>
+      </c>
+      <c r="F241" s="32" t="inlineStr">
+        <is>
+          <t>优化登记与复盘规则</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="32" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B242" s="32" t="inlineStr">
         <is>
-          <t>A+完全重做后，是否可同时计A+制作发布75元和全新重做75元？</t>
+          <t>创建1个SP Campaign产生多条Ads Change记录</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
         <is>
-          <t>只计一次75元</t>
+          <t>只计一次15元</t>
         </is>
       </c>
       <c r="D242" s="32" t="inlineStr">
         <is>
-          <t>叠加计150元</t>
+          <t>按Ads Change条数计费</t>
         </is>
       </c>
       <c r="E242" s="32" t="inlineStr">
         <is>
-          <t>同一成果只计一次</t>
+          <t>以Campaign ID去重</t>
         </is>
       </c>
       <c r="F242" s="32" t="inlineStr">
         <is>
-          <t>任务评分·A+制作发布</t>
+          <t>任务评分·SP广告创建</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="32" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B243" s="32" t="inlineStr">
         <is>
-          <t>同一电压错误出现在标题、五点和A+三个位置</t>
+          <t>纠错修复的是自己上次操作造成的错误</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
         <is>
-          <t>修正全部位置，共10元</t>
+          <t>不新增任务金额或主动金额</t>
         </is>
       </c>
       <c r="D243" s="32" t="inlineStr">
         <is>
-          <t>按位置分别计30元</t>
+          <t>计纠错10元/错误点</t>
         </is>
       </c>
       <c r="E243" s="32" t="inlineStr">
         <is>
-          <t>同源错误合并为1个错误点</t>
+          <t>修复本人错误属于返工</t>
         </is>
       </c>
       <c r="F243" s="32" t="inlineStr">
         <is>
-          <t>任务评分·Listing纠错</t>
+          <t>运营工作明细·Listing纠错</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="B244" s="32" t="inlineStr">
-        <is>
-          <t>员工自主发现价格异常并修正，是否同时计任务金额和主动金额？</t>
-        </is>
-      </c>
-      <c r="C244" s="32" t="inlineStr">
-        <is>
-          <t>按正常金额×主动倍率</t>
-        </is>
-      </c>
-      <c r="D244" s="32" t="inlineStr">
-        <is>
-          <t>正常金额＋另加主动金额</t>
-        </is>
-      </c>
-      <c r="E244" s="32" t="inlineStr">
-        <is>
-          <t>发起来源互斥：自主发起按倍率，不另加正常金额</t>
-        </is>
-      </c>
-      <c r="F244" s="32" t="inlineStr">
-        <is>
-          <t>主动改善评价·二</t>
+      <c r="A244" s="100" t="n">
+        <v>13</v>
+      </c>
+      <c r="B244" s="100" t="inlineStr">
+        <is>
+          <t>3个尺寸共用同一套调研方案，是否分别领取75元？</t>
+        </is>
+      </c>
+      <c r="C244" s="100" t="inlineStr">
+        <is>
+          <t>共用方案只计一次75元</t>
+        </is>
+      </c>
+      <c r="D244" s="100" t="inlineStr">
+        <is>
+          <t>每个尺寸各领75元＝225元</t>
+        </is>
+      </c>
+      <c r="E244" s="100" t="inlineStr">
+        <is>
+          <t>共用调研/厂家/验证方案不重复领取</t>
+        </is>
+      </c>
+      <c r="F244" s="100" t="inlineStr">
+        <is>
+          <t>任务评分·新品开发</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="B245" s="32" t="inlineStr">
-        <is>
-          <t>员工先提出建议，经负责人批准后建立任务执行</t>
-        </is>
-      </c>
-      <c r="C245" s="32" t="inlineStr">
-        <is>
-          <t>按正常金额×主动倍率</t>
-        </is>
-      </c>
-      <c r="D245" s="32" t="inlineStr">
-        <is>
-          <t>只按普通金额结算，遗漏适用主动倍率</t>
-        </is>
-      </c>
-      <c r="E245" s="32" t="inlineStr">
-        <is>
-          <t>先提出即属主动发起，补建任务不改变来源</t>
-        </is>
-      </c>
-      <c r="F245" s="32" t="inlineStr">
-        <is>
-          <t>主动改善评价·A17</t>
+      <c r="A245" s="100" t="n">
+        <v>14</v>
+      </c>
+      <c r="B245" s="100" t="inlineStr">
+        <is>
+          <t>已完成A+制作（75元），是否可同时计图片策划50元？</t>
+        </is>
+      </c>
+      <c r="C245" s="100" t="inlineStr">
+        <is>
+          <t>A+已含素材策划，不另计</t>
+        </is>
+      </c>
+      <c r="D245" s="100" t="inlineStr">
+        <is>
+          <t>叠加计75＋50＝125元</t>
+        </is>
+      </c>
+      <c r="E245" s="100" t="inlineStr">
+        <is>
+          <t>A+制作已包含素材策划</t>
+        </is>
+      </c>
+      <c r="F245" s="100" t="inlineStr">
+        <is>
+          <t>任务评分·产品图片策划</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="B246" s="32" t="inlineStr">
-        <is>
-          <t>同一滞留库存问题先Relist再申诉</t>
-        </is>
-      </c>
-      <c r="C246" s="32" t="inlineStr">
-        <is>
-          <t>合计15元（取最高档）</t>
-        </is>
-      </c>
-      <c r="D246" s="32" t="inlineStr">
-        <is>
-          <t>移除10元＋申诉15元＝25元</t>
-        </is>
-      </c>
-      <c r="E246" s="32" t="inlineStr">
-        <is>
-          <t>同一问题连续处理只取最高适用金额</t>
-        </is>
-      </c>
-      <c r="F246" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·滞留库存</t>
+      <c r="A246" s="100" t="n">
+        <v>15</v>
+      </c>
+      <c r="B246" s="100" t="inlineStr">
+        <is>
+          <t>调研/找厂已交付产品资料，是否可再计资料整理40元？</t>
+        </is>
+      </c>
+      <c r="C246" s="100" t="inlineStr">
+        <is>
+          <t>已交付的相同资料不重复计</t>
+        </is>
+      </c>
+      <c r="D246" s="100" t="inlineStr">
+        <is>
+          <t>调研75＋资料40＝叠加115元</t>
+        </is>
+      </c>
+      <c r="E246" s="100" t="inlineStr">
+        <is>
+          <t>同一交付不按两个项目分别领取</t>
+        </is>
+      </c>
+      <c r="F246" s="100" t="inlineStr">
+        <is>
+          <t>任务评分·产品资料整理</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="B247" s="32" t="inlineStr">
-        <is>
-          <t>上架组包含5个SKU，OA记录5条</t>
-        </is>
-      </c>
-      <c r="C247" s="32" t="inlineStr">
-        <is>
-          <t>按组总金额计（如52元）</t>
-        </is>
-      </c>
-      <c r="D247" s="32" t="inlineStr">
-        <is>
-          <t>5条OA各计25元＝125元</t>
-        </is>
-      </c>
-      <c r="E247" s="32" t="inlineStr">
-        <is>
-          <t>以执行组为单位，OA分摊组总金额</t>
-        </is>
-      </c>
-      <c r="F247" s="32" t="inlineStr">
-        <is>
-          <t>场景示例·上架组</t>
+      <c r="A247" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story全新策划75元与A+制作发布75元是否叠加？</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>确有独立交付时可分别计费，合计150元</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>共用相同素材或策划，仅做一套内容却按两个项目各报75元</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t>Brand Story与A+为独立内容模块；同一份素材或策划不按名称重复领取</t>
+        </is>
+      </c>
+      <c r="F247" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·Brand Story / A+制作发布</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="B248" s="32" t="inlineStr">
-        <is>
-          <t>5个SKU共用同一份新A+</t>
-        </is>
-      </c>
-      <c r="C248" s="32" t="inlineStr">
-        <is>
-          <t>1份×75元＝75元</t>
-        </is>
-      </c>
-      <c r="D248" s="32" t="inlineStr">
-        <is>
-          <t>5×75元＝375元</t>
-        </is>
-      </c>
-      <c r="E248" s="32" t="inlineStr">
-        <is>
-          <t>共用同一份内容只计一份</t>
-        </is>
-      </c>
-      <c r="F248" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·A+制作发布</t>
+      <c r="A248" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>跟卖监控5元与跟卖取证30元是否叠加？</t>
+        </is>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>监控和取证是独立任务，分别计费</t>
+        </is>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>取证包含监控，只计30元</t>
+        </is>
+      </c>
+      <c r="E248" s="0" t="inlineStr">
+        <is>
+          <t>监控为固定巡检，取证为独立案件处理，可同时存在</t>
+        </is>
+      </c>
+      <c r="F248" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·品牌保护</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="B249" s="32" t="inlineStr">
-        <is>
-          <t>同一份A+同一轮修改了6个模块</t>
-        </is>
-      </c>
-      <c r="C249" s="32" t="inlineStr">
-        <is>
-          <t>合计10元</t>
-        </is>
-      </c>
-      <c r="D249" s="32" t="inlineStr">
-        <is>
-          <t>6×10元＝60元</t>
-        </is>
-      </c>
-      <c r="E249" s="32" t="inlineStr">
-        <is>
-          <t>同份同轮合计10元，不按模块数量累加</t>
-        </is>
-      </c>
-      <c r="F249" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·A+增删修改</t>
+      <c r="A249" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle创建25元与Listing创建25元是否叠加？</t>
+        </is>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>Virtual Bundle已含初始配置，不叠加Listing创建</t>
+        </is>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t>分别计50元</t>
+        </is>
+      </c>
+      <c r="E249" s="0" t="inlineStr">
+        <is>
+          <t>VB创建已包含文案填入和图片配置</t>
+        </is>
+      </c>
+      <c r="F249" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·Virtual Bundle</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="B250" s="32" t="inlineStr">
-        <is>
-          <t>同站点1个ASIN的Buy Box异常多次开Case后恢复</t>
-        </is>
-      </c>
-      <c r="C250" s="32" t="inlineStr">
-        <is>
-          <t>合计15元</t>
-        </is>
-      </c>
-      <c r="D250" s="32" t="inlineStr">
-        <is>
-          <t>按Case数量计费</t>
-        </is>
-      </c>
-      <c r="E250" s="32" t="inlineStr">
-        <is>
-          <t>按ASIN计费，同一ASIN多个SKU或多个Case不增加金额</t>
-        </is>
-      </c>
-      <c r="F250" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·Buy Box</t>
+      <c r="A250" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B250" s="0" t="inlineStr">
+        <is>
+          <t>利润分析完成后另行改价，是否叠加？</t>
+        </is>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>分析30元＋价格调整15元，分别计费</t>
+        </is>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t>分析已包含改价</t>
+        </is>
+      </c>
+      <c r="E250" s="0" t="inlineStr">
+        <is>
+          <t>分析是交付报告和建议，改价是独立执行任务</t>
+        </is>
+      </c>
+      <c r="F250" s="0" t="inlineStr">
+        <is>
+          <t>任务评分·利润分析 / 价格调整</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="B251" s="32" t="inlineStr">
-        <is>
-          <t>同一Listing标题在复盘前又做了一次优化修改</t>
-        </is>
-      </c>
-      <c r="C251" s="32" t="inlineStr">
-        <is>
-          <t>并入原任务，不新增金额</t>
-        </is>
-      </c>
-      <c r="D251" s="32" t="inlineStr">
-        <is>
-          <t>新建优化任务再计10元</t>
-        </is>
-      </c>
-      <c r="E251" s="32" t="inlineStr">
-        <is>
-          <t>同模块复盘前追加并入，不重复</t>
-        </is>
-      </c>
-      <c r="F251" s="32" t="inlineStr">
-        <is>
-          <t>优化登记与复盘规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="B252" s="32" t="inlineStr">
-        <is>
-          <t>创建1个SP Campaign产生多条Ads Change记录</t>
-        </is>
-      </c>
-      <c r="C252" s="32" t="inlineStr">
-        <is>
-          <t>只计一次15元</t>
-        </is>
-      </c>
-      <c r="D252" s="32" t="inlineStr">
-        <is>
-          <t>按Ads Change条数计费</t>
-        </is>
-      </c>
-      <c r="E252" s="32" t="inlineStr">
-        <is>
-          <t>以Campaign ID去重</t>
-        </is>
-      </c>
-      <c r="F252" s="32" t="inlineStr">
-        <is>
-          <t>任务评分·SP广告创建</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="B253" s="32" t="inlineStr">
-        <is>
-          <t>纠错修复的是自己上次操作造成的错误</t>
-        </is>
-      </c>
-      <c r="C253" s="32" t="inlineStr">
-        <is>
-          <t>不新增任务金额或主动金额</t>
-        </is>
-      </c>
-      <c r="D253" s="32" t="inlineStr">
-        <is>
-          <t>计纠错10元/错误点</t>
-        </is>
-      </c>
-      <c r="E253" s="32" t="inlineStr">
-        <is>
-          <t>修复本人错误属于返工</t>
-        </is>
-      </c>
-      <c r="F253" s="32" t="inlineStr">
-        <is>
-          <t>运营工作明细·Listing纠错</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="100" t="n">
-        <v>13</v>
-      </c>
-      <c r="B254" s="100" t="inlineStr">
-        <is>
-          <t>3个尺寸共用同一套调研方案，是否分别领取75元？</t>
-        </is>
-      </c>
-      <c r="C254" s="100" t="inlineStr">
-        <is>
-          <t>共用方案只计一次75元</t>
-        </is>
-      </c>
-      <c r="D254" s="100" t="inlineStr">
-        <is>
-          <t>每个尺寸各领75元＝225元</t>
-        </is>
-      </c>
-      <c r="E254" s="100" t="inlineStr">
-        <is>
-          <t>共用调研/厂家/验证方案不重复领取</t>
-        </is>
-      </c>
-      <c r="F254" s="100" t="inlineStr">
-        <is>
-          <t>任务评分·新品开发</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="100" t="n">
-        <v>14</v>
-      </c>
-      <c r="B255" s="100" t="inlineStr">
-        <is>
-          <t>已完成A+制作（75元），是否可同时计图片策划50元？</t>
-        </is>
-      </c>
-      <c r="C255" s="100" t="inlineStr">
-        <is>
-          <t>A+已含素材策划，不另计</t>
-        </is>
-      </c>
-      <c r="D255" s="100" t="inlineStr">
-        <is>
-          <t>叠加计75＋50＝125元</t>
-        </is>
-      </c>
-      <c r="E255" s="100" t="inlineStr">
-        <is>
-          <t>A+制作已包含素材策划</t>
-        </is>
-      </c>
-      <c r="F255" s="100" t="inlineStr">
-        <is>
-          <t>任务评分·产品图片策划</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="100" t="n">
-        <v>15</v>
-      </c>
-      <c r="B256" s="100" t="inlineStr">
-        <is>
-          <t>调研/找厂已交付产品资料，是否可再计资料整理40元？</t>
-        </is>
-      </c>
-      <c r="C256" s="100" t="inlineStr">
-        <is>
-          <t>已交付的相同资料不重复计</t>
-        </is>
-      </c>
-      <c r="D256" s="100" t="inlineStr">
-        <is>
-          <t>调研75＋资料40＝叠加115元</t>
-        </is>
-      </c>
-      <c r="E256" s="100" t="inlineStr">
-        <is>
-          <t>同一交付不按两个项目分别领取</t>
-        </is>
-      </c>
-      <c r="F256" s="100" t="inlineStr">
-        <is>
-          <t>任务评分·产品资料整理</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="B257" s="0" t="inlineStr">
-        <is>
-          <t>Brand Story全新策划75元与A+制作发布75元是否叠加？</t>
-        </is>
-      </c>
-      <c r="C257" s="0" t="inlineStr">
-        <is>
-          <t>品牌故事和A+是不同内容区域，各自独立计费</t>
-        </is>
-      </c>
-      <c r="D257" s="0" t="inlineStr">
-        <is>
-          <t>两者叠加计150元</t>
-        </is>
-      </c>
-      <c r="E257" s="0" t="inlineStr">
-        <is>
-          <t>Brand Story与A+为两种独立内容模块</t>
-        </is>
-      </c>
-      <c r="F257" s="0" t="inlineStr">
-        <is>
-          <t>任务评分·Brand Story / A+制作发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="B258" s="0" t="inlineStr">
-        <is>
-          <t>跟卖监控5元与跟卖取证30元是否叠加？</t>
-        </is>
-      </c>
-      <c r="C258" s="0" t="inlineStr">
-        <is>
-          <t>监控和取证是独立任务，分别计费</t>
-        </is>
-      </c>
-      <c r="D258" s="0" t="inlineStr">
-        <is>
-          <t>取证包含监控，只计30元</t>
-        </is>
-      </c>
-      <c r="E258" s="0" t="inlineStr">
-        <is>
-          <t>监控为固定巡检，取证为独立案件处理，可同时存在</t>
-        </is>
-      </c>
-      <c r="F258" s="0" t="inlineStr">
-        <is>
-          <t>任务评分·品牌保护</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="B259" s="0" t="inlineStr">
-        <is>
-          <t>Virtual Bundle创建25元与Listing创建25元是否叠加？</t>
-        </is>
-      </c>
-      <c r="C259" s="0" t="inlineStr">
-        <is>
-          <t>Virtual Bundle已含初始配置，不叠加Listing创建</t>
-        </is>
-      </c>
-      <c r="D259" s="0" t="inlineStr">
-        <is>
-          <t>分别计50元</t>
-        </is>
-      </c>
-      <c r="E259" s="0" t="inlineStr">
-        <is>
-          <t>VB创建已包含文案填入和图片配置</t>
-        </is>
-      </c>
-      <c r="F259" s="0" t="inlineStr">
-        <is>
-          <t>任务评分·Virtual Bundle</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="B260" s="0" t="inlineStr">
-        <is>
-          <t>利润分析完成后另行改价，是否叠加？</t>
-        </is>
-      </c>
-      <c r="C260" s="0" t="inlineStr">
-        <is>
-          <t>分析30元＋价格调整15元，分别计费</t>
-        </is>
-      </c>
-      <c r="D260" s="0" t="inlineStr">
-        <is>
-          <t>分析已包含改价</t>
-        </is>
-      </c>
-      <c r="E260" s="0" t="inlineStr">
-        <is>
-          <t>分析是交付报告和建议，改价是独立执行任务</t>
-        </is>
-      </c>
-      <c r="F260" s="0" t="inlineStr">
-        <is>
-          <t>任务评分·利润分析 / 价格调整</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="0" t="n">
+      <c r="A251" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="B261" s="0" t="inlineStr">
+      <c r="B251" s="0" t="inlineStr">
         <is>
           <t>同一案件先30元举报后补Test Buy，是否计30＋50＝80元？</t>
         </is>
       </c>
-      <c r="C261" s="0" t="inlineStr">
+      <c r="C251" s="0" t="inlineStr">
         <is>
           <t>先结30元，补足至50元，不超过50元</t>
         </is>
       </c>
-      <c r="D261" s="0" t="inlineStr">
+      <c r="D251" s="0" t="inlineStr">
         <is>
           <t>分别计80元</t>
         </is>
       </c>
-      <c r="E261" s="0" t="inlineStr">
+      <c r="E251" s="0" t="inlineStr">
         <is>
           <t>两档只取最高，先结30元后补足最多20元</t>
         </is>
       </c>
-      <c r="F261" s="0" t="inlineStr">
+      <c r="F251" s="0" t="inlineStr">
         <is>
           <t>任务评分·跟卖取证</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>21</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>同系列10个尺寸共用调研方案，是否各领75元？</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>共用方案只计一次75元</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>10×75＝750元</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>系列产品开发计费规则①</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>任务评分·系列产品开发计费规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>22</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>同系列后续产品的样品评估，是否都按75元？</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>由负责人确认：独立验证75元，基本核对15元，无需验证0元</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>统一按75元/个</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>系列产品开发计费规则②</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>任务评分·系列产品开发计费规则</t>
         </is>
       </c>
     </row>
@@ -15028,7 +14790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -15324,14 +15086,26 @@
       </c>
     </row>
     <row r="25" ht="130" customHeight="1" s="1">
-      <c r="A25" s="104" t="inlineStr">
+      <c r="A25" s="125" t="inlineStr">
         <is>
           <t>参数更新与已有项目</t>
         </is>
       </c>
-      <c r="B25" s="104" t="inlineStr">
+      <c r="B25" s="125" t="inlineStr">
         <is>
           <t>商品属性或参数更新不新增独立收费行。按实际修改对象使用现有Listing纠错、内容优化或变体关系维护项目；涉及Case时使用对应异常项目，同一交付只计一次。原错误修正与负责人后续更新参数按本页责任判定规则区分，不将准确的新参数更新直接认定为本人纠错。现有项目未覆盖的后台属性批量更新，应先明确适用任务及金额，不自行按多个文案模块叠加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="100" customHeight="1" s="1">
+      <c r="A26" s="133" t="inlineStr">
+        <is>
+          <t>系列新品共用内容</t>
+        </is>
+      </c>
+      <c r="B26" s="133" t="inlineStr">
+        <is>
+          <t>同一系列仅参数不同的首次内容，按独立原创套数计酬；参数替换、复制填表不按每个Listing领取原创费。详见“系列开发计酬”，共用与独立内容须关联同一系列项目编号并确认。</t>
         </is>
       </c>
     </row>
@@ -15561,12 +15335,12 @@
       </c>
     </row>
     <row r="2" ht="85" customHeight="1" s="1">
-      <c r="A2" s="104" t="inlineStr">
+      <c r="A2" s="125" t="inlineStr">
         <is>
           <t>适用范围</t>
         </is>
       </c>
-      <c r="B2" s="104" t="inlineStr">
+      <c r="B2" s="125" t="inlineStr">
         <is>
           <t>负责人安排或员工主动发起的改善均可申报。任务金额奖励已完成的工作，成果奖励认可经验证的业务改善；同一工作可同时获得任务金额和成果奖励。</t>
         </is>
@@ -15600,7 +15374,7 @@
       </c>
     </row>
     <row r="4" ht="145" customHeight="1" s="1">
-      <c r="A4" s="104" t="inlineStr">
+      <c r="A4" s="125" t="inlineStr">
         <is>
           <t>明确改善</t>
         </is>
@@ -15608,24 +15382,24 @@
       <c r="B4" s="101" t="n">
         <v>100</v>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="125" t="inlineStr">
         <is>
           <t>达到事先确认的改善目标；修改前后有可比数据、样本足够，且未明显损害其他关键指标。</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="D4" s="125" t="inlineStr">
         <is>
           <t>改善目标、基线及观察区间、修改记录、前后数据和负责人验收。</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="125" t="inlineStr">
         <is>
           <t>同一成果首次达到本档，核定100元；未验收不提前发放。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="145" customHeight="1" s="1">
-      <c r="A5" s="104" t="inlineStr">
+      <c r="A5" s="125" t="inlineStr">
         <is>
           <t>持续改善</t>
         </is>
@@ -15633,64 +15407,64 @@
       <c r="B5" s="101" t="n">
         <v>300</v>
       </c>
-      <c r="C5" s="104" t="inlineStr">
+      <c r="C5" s="125" t="inlineStr">
         <is>
           <t>已确认的改善在后续复查中保持，带来可说明的经济收益，例如减少退货损失或提高广告后利润。</t>
         </is>
       </c>
-      <c r="D5" s="104" t="inlineStr">
+      <c r="D5" s="125" t="inlineStr">
         <is>
           <t>首次验收及后续复查、经济收益的测算口径、数据来源和结论。</t>
         </is>
       </c>
-      <c r="E5" s="104" t="inlineStr">
+      <c r="E5" s="125" t="inlineStr">
         <is>
           <t>300元为该案例本档总奖励；已发100元则本次只补200元，不另发300元。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="145" customHeight="1" s="1">
-      <c r="A6" s="104" t="inlineStr">
+      <c r="A6" s="125" t="inlineStr">
         <is>
           <t>重大贡献</t>
         </is>
       </c>
       <c r="B6" s="101" t="n"/>
-      <c r="C6" s="104" t="inlineStr">
+      <c r="C6" s="125" t="inlineStr">
         <is>
           <t>影响范围大、收益明显，普通档位不足以体现贡献。</t>
         </is>
       </c>
-      <c r="D6" s="104" t="inlineStr">
+      <c r="D6" s="125" t="inlineStr">
         <is>
           <t>成果范围、可说明的收益、参与者贡献及负责人批准记录。</t>
         </is>
       </c>
-      <c r="E6" s="104" t="inlineStr">
+      <c r="E6" s="125" t="inlineStr">
         <is>
           <t>由负责人另行确定案例总奖励。金额未确定不结算；如有此前奖励，按批准总额扣除累计已奖励金额。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="85" customHeight="1" s="1">
-      <c r="A7" s="104" t="inlineStr">
+      <c r="A7" s="125" t="inlineStr">
         <is>
           <t>统一原则</t>
         </is>
       </c>
-      <c r="B7" s="104" t="inlineStr">
+      <c r="B7" s="125" t="inlineStr">
         <is>
           <t>同一成果只取最高核定档，不按月度复盘重复领奖；奖励金额不乘任务难度系数、主动倍率，也不再乘任何积分单价。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="85" customHeight="1" s="1">
-      <c r="A8" s="104" t="inlineStr">
+      <c r="A8" s="125" t="inlineStr">
         <is>
           <t>登记与验证</t>
         </is>
       </c>
-      <c r="B8" s="104" t="inlineStr">
+      <c r="B8" s="125" t="inlineStr">
         <is>
           <t>改善前登记问题、目标、衡量指标、基线范围、验证日期和关联任务，由负责人确认；先记录目标不代表提前保证奖励。</t>
         </is>
@@ -15724,153 +15498,153 @@
       </c>
     </row>
     <row r="10" ht="145" customHeight="1" s="1">
-      <c r="A10" s="104" t="inlineStr">
+      <c r="A10" s="125" t="inlineStr">
         <is>
           <t>描述／图片／A+改善退货</t>
         </is>
       </c>
-      <c r="B10" s="104" t="inlineStr">
+      <c r="B10" s="125" t="inlineStr">
         <is>
           <t>相关退货原因及退货损失是否减少。</t>
         </is>
       </c>
-      <c r="C10" s="104" t="inlineStr">
+      <c r="C10" s="125" t="inlineStr">
         <is>
           <t>对比修改前后可比订单批次；记录退货率分母及退货观察时长，确保修改后订单已获得足够退货观察期。</t>
         </is>
       </c>
-      <c r="D10" s="104" t="inlineStr">
+      <c r="D10" s="125" t="inlineStr">
         <is>
           <t>最近几天退货率下降；仅看退货数量、没有订单基数；尚未发生退货被误认为改善。</t>
         </is>
       </c>
-      <c r="E10" s="104" t="inlineStr">
+      <c r="E10" s="125" t="inlineStr">
         <is>
           <t>达到确认目标并满足样本及观察条件后验收；未成熟或样本不足，继续观察。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="145" customHeight="1" s="1">
-      <c r="A11" s="104" t="inlineStr">
+      <c r="A11" s="125" t="inlineStr">
         <is>
           <t>内容优化提升销量</t>
         </is>
       </c>
-      <c r="B11" s="104" t="inlineStr">
+      <c r="B11" s="125" t="inlineStr">
         <is>
           <t>转化率、销量及利润是否改善。</t>
         </is>
       </c>
-      <c r="C11" s="104" t="inlineStr">
+      <c r="C11" s="125" t="inlineStr">
         <is>
           <t>记录价格、促销、广告投入、库存、季节变化等同期因素；使用能支持判断的可比区间。</t>
         </is>
       </c>
-      <c r="D11" s="104" t="inlineStr">
+      <c r="D11" s="125" t="inlineStr">
         <is>
           <t>只看销售额增长，忽略降价、广告投入增加或利润下降。</t>
         </is>
       </c>
-      <c r="E11" s="104" t="inlineStr">
+      <c r="E11" s="125" t="inlineStr">
         <is>
           <t>依据证据判断此次内容调整的贡献；多因素变化且无法支持判断时继续观察。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="145" customHeight="1" s="1">
-      <c r="A12" s="104" t="inlineStr">
+      <c r="A12" s="125" t="inlineStr">
         <is>
           <t>广告优化提升表现</t>
         </is>
       </c>
-      <c r="B12" s="104" t="inlineStr">
+      <c r="B12" s="125" t="inlineStr">
         <is>
           <t>广告订单、花费、ACOS及产品整体利润的变化。</t>
         </is>
       </c>
-      <c r="C12" s="104" t="inlineStr">
+      <c r="C12" s="125" t="inlineStr">
         <is>
           <t>按事先确认目标选择指标，记录对比区间、订单归因等待和同期价格、库存、促销变化。</t>
         </is>
       </c>
-      <c r="D12" s="104" t="inlineStr">
+      <c r="D12" s="125" t="inlineStr">
         <is>
           <t>只看ACOS降低；缩减投放后销量、利润也下降，不能直接认定为改善。</t>
         </is>
       </c>
-      <c r="E12" s="104" t="inlineStr">
+      <c r="E12" s="125" t="inlineStr">
         <is>
           <t>结合整体收益核验，不要求所有指标同时上涨；未明显损害关键指标且达到目标后认定。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="85" customHeight="1" s="1">
-      <c r="A13" s="104" t="inlineStr">
+      <c r="A13" s="125" t="inlineStr">
         <is>
           <t>重复与协作</t>
         </is>
       </c>
-      <c r="B13" s="104" t="inlineStr">
+      <c r="B13" s="125" t="inlineStr">
         <is>
           <t>同一问题、同一改善目标及同一成果登记唯一成果编号；关联OA或Streamlit任务。多人合作在同一份奖励内分配，个人份额之和不得超过本次可发奖励。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="85" customHeight="1" s="1">
-      <c r="A14" s="104" t="inlineStr">
+      <c r="A14" s="125" t="inlineStr">
         <is>
           <t>跨月与升级</t>
         </is>
       </c>
-      <c r="B14" s="104" t="inlineStr">
+      <c r="B14" s="125" t="inlineStr">
         <is>
           <t>已奖励金额跨月累计，不能换月份或任务编号重新领取。按本次核定总奖励减去累计已奖励金额的正差额结算；无新增核定差额则不发放。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="115" customHeight="1" s="1">
-      <c r="A15" s="104" t="inlineStr">
+      <c r="A15" s="125" t="inlineStr">
         <is>
           <t>任务与成果边界</t>
         </is>
       </c>
-      <c r="B15" s="104" t="inlineStr">
+      <c r="B15" s="125" t="inlineStr">
         <is>
           <t>任务通过验收可先按任务金额结算；效果仍待观察不阻止已完成任务的结算。成果未达到目标不自动追扣合格任务金额；修复本人错误或无依据操作不作为新成果奖励。 责任以操作当时已确认资料及执行证据为准；本人开发缺陷、本人执行错误的补救均不另计报酬或成果奖，不能通过更新资料或新建任务转为新成果。资料后续更新及证据不足的处理，详见“优化登记与复盘规则”。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="85" customHeight="1" s="1">
-      <c r="A16" s="104" t="inlineStr">
+      <c r="A16" s="125" t="inlineStr">
         <is>
           <t>月度汇总</t>
         </is>
       </c>
-      <c r="B16" s="104" t="inlineStr">
+      <c r="B16" s="125" t="inlineStr">
         <is>
           <t>当月任务绩效＝OA已验收任务金额＋Streamlit已验收主动任务金额＋当月已确认且未重复结算的成果奖励（含升级补差）。同一任务同时出现在两处时只保留一份任务金额。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="85" customHeight="1" s="1">
-      <c r="A17" s="104" t="inlineStr">
+      <c r="A17" s="125" t="inlineStr">
         <is>
           <t>Streamlit字段</t>
         </is>
       </c>
-      <c r="B17" s="104" t="inlineStr">
+      <c r="B17" s="125" t="inlineStr">
         <is>
           <t>成果编号、负责人及协作者、关联任务、改善对象及站点、问题与措施、改善目标、基线和观察期、前后数据、同期影响因素、复查结论、核定总奖励、累计已奖励金额、本次奖励、核定日期、结算状态和结算月份。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="85" customHeight="1" s="1">
-      <c r="A18" s="104" t="inlineStr">
+      <c r="A18" s="125" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="B18" s="104" t="inlineStr">
+      <c r="B18" s="125" t="inlineStr">
         <is>
           <t>待确认目标 → 执行／观察中 → 待成果验收 → 已核定 → 已结算；未满足条件则继续观察或注明不予奖励原因。</t>
         </is>
@@ -15904,66 +15678,66 @@
       </c>
     </row>
     <row r="20" ht="85" customHeight="1" s="1">
-      <c r="A20" s="104" t="inlineStr">
+      <c r="A20" s="125" t="inlineStr">
         <is>
           <t>首次达到明确改善</t>
         </is>
       </c>
-      <c r="B20" s="102" t="n">
+      <c r="B20" s="129" t="n">
         <v>100</v>
       </c>
-      <c r="C20" s="102" t="n">
+      <c r="C20" s="129" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="102">
+      <c r="D20" s="129">
         <f>MAX(0,B20-C20)</f>
         <v/>
       </c>
-      <c r="E20" s="104" t="inlineStr">
+      <c r="E20" s="125" t="inlineStr">
         <is>
           <t>本次发100元。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="85" customHeight="1" s="1">
-      <c r="A21" s="104" t="inlineStr">
+      <c r="A21" s="125" t="inlineStr">
         <is>
           <t>后续达到持续改善</t>
         </is>
       </c>
-      <c r="B21" s="102" t="n">
+      <c r="B21" s="129" t="n">
         <v>300</v>
       </c>
-      <c r="C21" s="102" t="n">
+      <c r="C21" s="129" t="n">
         <v>100</v>
       </c>
-      <c r="D21" s="102">
+      <c r="D21" s="129">
         <f>MAX(0,B21-C21)</f>
         <v/>
       </c>
-      <c r="E21" s="104" t="inlineStr">
+      <c r="E21" s="125" t="inlineStr">
         <is>
           <t>本次补200元，累计300元。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="85" customHeight="1" s="1">
-      <c r="A22" s="104" t="inlineStr">
+      <c r="A22" s="125" t="inlineStr">
         <is>
           <t>同一成果再次复盘，无升级</t>
         </is>
       </c>
-      <c r="B22" s="102" t="n">
+      <c r="B22" s="129" t="n">
         <v>300</v>
       </c>
-      <c r="C22" s="102" t="n">
+      <c r="C22" s="129" t="n">
         <v>300</v>
       </c>
-      <c r="D22" s="102">
+      <c r="D22" s="129">
         <f>MAX(0,B22-C22)</f>
         <v/>
       </c>
-      <c r="E22" s="104" t="inlineStr">
+      <c r="E22" s="125" t="inlineStr">
         <is>
           <t>本次0元，不因复盘次数重复领奖。</t>
         </is>
@@ -15997,21 +15771,21 @@
       </c>
     </row>
     <row r="24" ht="85" customHeight="1" s="1">
-      <c r="A24" s="104" t="inlineStr">
+      <c r="A24" s="125" t="inlineStr">
         <is>
           <t>某员工</t>
         </is>
       </c>
-      <c r="B24" s="102" t="n">
+      <c r="B24" s="129" t="n">
         <v>2000</v>
       </c>
-      <c r="C24" s="102" t="n">
+      <c r="C24" s="129" t="n">
         <v>600</v>
       </c>
-      <c r="D24" s="102" t="n">
+      <c r="D24" s="129" t="n">
         <v>200</v>
       </c>
-      <c r="E24" s="102">
+      <c r="E24" s="129">
         <f>SUM(B24:D24)</f>
         <v/>
       </c>
@@ -16031,4 +15805,556 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" style="1" min="1" max="1"/>
+    <col width="24" customWidth="1" style="1" min="2" max="2"/>
+    <col width="27" customWidth="1" style="1" min="3" max="3"/>
+    <col width="78" customWidth="1" style="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="65" customHeight="1" s="1">
+      <c r="A1" s="128" t="inlineStr">
+        <is>
+          <t>系列产品开发计酬规则与结算示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1" s="1">
+      <c r="A2" s="125" t="inlineStr">
+        <is>
+          <t>总原则</t>
+        </is>
+      </c>
+      <c r="B2" s="125" t="inlineStr">
+        <is>
+          <t>按实际独立交付计酬，不按开发SKU数量乘单品总额。开发阶段费用、上架执行费用分别累计；没有独立交付的环节不计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="105" customHeight="1" s="1">
+      <c r="A3" s="125" t="inlineStr">
+        <is>
+          <t>同一系列如何认定</t>
+        </is>
+      </c>
+      <c r="B3" s="125" t="inlineStr">
+        <is>
+          <t>负责人在开发前确认系列项目编号、SKU及参数差异表、共用调研/供应方案、验证范围及内容交付；不能仅凭SKU字母或名称认定。仅一个参数不同通常可共用，但须核实是否影响结构、性能、使用限制或验证要求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="105" customHeight="1" s="1">
+      <c r="A4" s="125" t="inlineStr">
+        <is>
+          <t>示例边界</t>
+        </is>
+      </c>
+      <c r="B4" s="125" t="inlineStr">
+        <is>
+          <t>以下是同一人完成、负责人安排、美国站、全部通过验收、无额外资料核实任务的比较。10款只差一个参数，共用一份调研、同一厂家、一个完整验证方案、原创文案、主辅图策划、A+、字幕及视频；10个SKU各自图片上传，共用一张上架表，先按不处理变体计算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1" s="1">
+      <c r="A5" s="125" t="inlineStr">
+        <is>
+          <t>系列上架基础金额（元）</t>
+        </is>
+      </c>
+      <c r="B5" s="132" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" s="125" t="inlineStr">
+        <is>
+          <t>按现有上架规则：2个及以上SKU可共用上架表，基础40元；独立上架仍引用任务评分25元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1" s="1">
+      <c r="A6" s="128" t="inlineStr">
+        <is>
+          <t>工作环节</t>
+        </is>
+      </c>
+      <c r="B6" s="128" t="inlineStr">
+        <is>
+          <t>1个SKU金额（元）</t>
+        </is>
+      </c>
+      <c r="C6" s="128" t="inlineStr">
+        <is>
+          <t>10个同系列SKU金额（元）</t>
+        </is>
+      </c>
+      <c r="D6" s="128" t="inlineStr">
+        <is>
+          <t>计费说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1" s="1">
+      <c r="A7" s="125" t="inlineStr">
+        <is>
+          <t>市场调研与产品建议</t>
+        </is>
+      </c>
+      <c r="B7" s="129">
+        <f>'任务评分'!C51</f>
+        <v/>
+      </c>
+      <c r="C7" s="129">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D7" s="125" t="inlineStr">
+        <is>
+          <t>共用同一份系列调研，只计一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1" s="1">
+      <c r="A8" s="125" t="inlineStr">
+        <is>
+          <t>厂家筛选与条件确认</t>
+        </is>
+      </c>
+      <c r="B8" s="129">
+        <f>'任务评分'!C52</f>
+        <v/>
+      </c>
+      <c r="C8" s="129">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="D8" s="125" t="inlineStr">
+        <is>
+          <t>同一厂家及合作方案涵盖参数差异，只计一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1" s="1">
+      <c r="A9" s="125" t="inlineStr">
+        <is>
+          <t>样品评估及问题跟进</t>
+        </is>
+      </c>
+      <c r="B9" s="129">
+        <f>'任务评分'!C53</f>
+        <v/>
+      </c>
+      <c r="C9" s="129">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="D9" s="125" t="inlineStr">
+        <is>
+          <t>约定验证范围完整执行并验收，合并计一次；不代表每个规格都可免检。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1" s="1">
+      <c r="A10" s="125" t="inlineStr">
+        <is>
+          <t>主图、辅图策划</t>
+        </is>
+      </c>
+      <c r="B10" s="129">
+        <f>'任务评分'!C55</f>
+        <v/>
+      </c>
+      <c r="C10" s="129">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="D10" s="125" t="inlineStr">
+        <is>
+          <t>独立于A+的一套主辅图方案；参数替换不视为重新策划。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1" s="1">
+      <c r="A11" s="125" t="inlineStr">
+        <is>
+          <t>视频字幕</t>
+        </is>
+      </c>
+      <c r="B11" s="129">
+        <f>'任务评分'!C56</f>
+        <v/>
+      </c>
+      <c r="C11" s="129">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="D11" s="125" t="inlineStr">
+        <is>
+          <t>共用一份准确适用的字幕稿，只计一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1" s="1">
+      <c r="A12" s="125" t="inlineStr">
+        <is>
+          <t>原创标题</t>
+        </is>
+      </c>
+      <c r="B12" s="129">
+        <f>'任务评分'!C14</f>
+        <v/>
+      </c>
+      <c r="C12" s="129">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="D12" s="125" t="inlineStr">
+        <is>
+          <t>共用原创文案，分别替换参数不重复领取原创费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1" s="1">
+      <c r="A13" s="125" t="inlineStr">
+        <is>
+          <t>原创五点</t>
+        </is>
+      </c>
+      <c r="B13" s="129">
+        <f>'任务评分'!C15</f>
+        <v/>
+      </c>
+      <c r="C13" s="129">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="D13" s="125" t="inlineStr">
+        <is>
+          <t>共用一套五点，不按SKU复制份数累计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1" s="1">
+      <c r="A14" s="125" t="inlineStr">
+        <is>
+          <t>原创描述</t>
+        </is>
+      </c>
+      <c r="B14" s="129">
+        <f>'任务评分'!C16</f>
+        <v/>
+      </c>
+      <c r="C14" s="129">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="D14" s="125" t="inlineStr">
+        <is>
+          <t>共用一份描述，不按SKU复制份数累计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1" s="1">
+      <c r="A15" s="125" t="inlineStr">
+        <is>
+          <t>Generic Keywords</t>
+        </is>
+      </c>
+      <c r="B15" s="129">
+        <f>'任务评分'!C17</f>
+        <v/>
+      </c>
+      <c r="C15" s="129">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="D15" s="125" t="inlineStr">
+        <is>
+          <t>共用一套关键词，只计一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1" s="1">
+      <c r="A16" s="125" t="inlineStr">
+        <is>
+          <t>新建A+</t>
+        </is>
+      </c>
+      <c r="B16" s="129">
+        <f>'任务评分'!C11</f>
+        <v/>
+      </c>
+      <c r="C16" s="129">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="D16" s="125" t="inlineStr">
+        <is>
+          <t>同一份适用于整个系列的独立内容，含首次绑定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1" s="1">
+      <c r="A17" s="125" t="inlineStr">
+        <is>
+          <t>视频上传</t>
+        </is>
+      </c>
+      <c r="B17" s="129">
+        <f>'任务评分'!C12</f>
+        <v/>
+      </c>
+      <c r="C17" s="129">
+        <f>B17</f>
+        <v/>
+      </c>
+      <c r="D17" s="125" t="inlineStr">
+        <is>
+          <t>共用一个视频，含首次关联。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1" s="1">
+      <c r="A18" s="125" t="inlineStr">
+        <is>
+          <t>Listing创建</t>
+        </is>
+      </c>
+      <c r="B18" s="129">
+        <f>'任务评分'!C8</f>
+        <v/>
+      </c>
+      <c r="C18" s="129">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D18" s="125" t="inlineStr">
+        <is>
+          <t>1个SKU25元；10个SKU共用一张表40元，不按SKU累乘。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1" s="1">
+      <c r="A19" s="125" t="inlineStr">
+        <is>
+          <t>图片上传</t>
+        </is>
+      </c>
+      <c r="B19" s="129">
+        <f>'任务评分'!C9</f>
+        <v/>
+      </c>
+      <c r="C19" s="129">
+        <f>'任务评分'!C9*10</f>
+        <v/>
+      </c>
+      <c r="D19" s="125" t="inlineStr">
+        <is>
+          <t>各SKU有自己的可用图片，按每个SKU10元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1" s="1">
+      <c r="A20" s="128" t="inlineStr">
+        <is>
+          <t>上述工作合计</t>
+        </is>
+      </c>
+      <c r="B20" s="130">
+        <f>SUM(B7:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="130">
+        <f>SUM(C7:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="128" t="inlineStr">
+        <is>
+          <t>不含额外资料核实、广告、跨站点上架、成果奖励及平台/采购费用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1" s="1">
+      <c r="A21" s="125" t="inlineStr">
+        <is>
+          <t>如确有额外独立资料核实</t>
+        </is>
+      </c>
+      <c r="B21" s="129">
+        <f>'任务评分'!C54</f>
+        <v/>
+      </c>
+      <c r="C21" s="129">
+        <f>'任务评分'!C54</f>
+        <v/>
+      </c>
+      <c r="D21" s="125" t="inlineStr">
+        <is>
+          <t>仅在前述阶段未交付且确需额外核实、补全并验收时另加；同系列共用一套只加一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1" s="1">
+      <c r="A22" s="125" t="inlineStr">
+        <is>
+          <t>如上架时组成同一个变体，增加金额</t>
+        </is>
+      </c>
+      <c r="B22" s="129">
+        <f>ROUND(B18*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="C22" s="129">
+        <f>ROUND(C18*0.3,2)</f>
+        <v/>
+      </c>
+      <c r="D22" s="125" t="inlineStr">
+        <is>
+          <t>系数由1变1.3，仅对上架执行组基础金额增加30%；不再叠加变体维护。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="65" customHeight="1" s="1">
+      <c r="A23" s="125" t="inlineStr">
+        <is>
+          <t>组成同一个变体后的合计</t>
+        </is>
+      </c>
+      <c r="B23" s="129">
+        <f>B20+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="129">
+        <f>C20+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="125" t="inlineStr">
+        <is>
+          <t>基于第20行，仅增加上架变体差额，不含可选的资料核实。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="65" customHeight="1" s="1">
+      <c r="A24" s="125" t="n"/>
+      <c r="B24" s="125" t="n"/>
+      <c r="C24" s="125" t="n"/>
+      <c r="D24" s="125" t="n"/>
+    </row>
+    <row r="25" ht="65" customHeight="1" s="1">
+      <c r="A25" s="128" t="inlineStr">
+        <is>
+          <t>实际结算与防重复规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="105" customHeight="1" s="1">
+      <c r="A26" s="125" t="inlineStr">
+        <is>
+          <t>系列共用工作如何验收</t>
+        </is>
+      </c>
+      <c r="B26" s="125" t="inlineStr">
+        <is>
+          <t>调研须覆盖本批参数需求；找厂须覆盖各规格报价、MOQ及供货条件；验证按事先确认方案执行；资料及内容须覆盖各规格差异。共用不代表漏做各规格必需检查。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="105" customHeight="1" s="1">
+      <c r="A27" s="125" t="inlineStr">
+        <is>
+          <t>仅增加参数款</t>
+        </is>
+      </c>
+      <c r="B27" s="125" t="inlineStr">
+        <is>
+          <t>首次约定范围内增加参数映射、报价补充、原测试及内容修订包含在原阶段中，不重收整套开发费。原项目结案后新增参数款，先判断本次独立交付；无需重新调研、找厂、策划的阶段不再付费，只支付本次确实新增且验收的上架、图片上传或独立验证等任务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="105" customHeight="1" s="1">
+      <c r="A28" s="125" t="inlineStr">
+        <is>
+          <t>确有独立开发工作</t>
+        </is>
+      </c>
+      <c r="B28" s="125" t="inlineStr">
+        <is>
+          <t>例如新电压需不同电控方案、不同功能需新卖点、尺寸变化需独立性能测试，可为受影响阶段建立独立任务并按原标准计酬。须事先记录区别、范围及验收要求；不能因此把未重做的调研、找厂、文案等全部再算一遍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="105" customHeight="1" s="1">
+      <c r="A29" s="125" t="inlineStr">
+        <is>
+          <t>内容与素材按实际独立份数</t>
+        </is>
+      </c>
+      <c r="B29" s="125" t="inlineStr">
+        <is>
+          <t>10份图片文件并不等于10套图片策划；只改参数文字、替换同布局实物图不自动增加策划费。A+、主辅图方案、字幕及文案按独立原创交付计数；确需不同结构或卖点方案，提供独立方案及确认记录。图片上传仍按实际SKU，实际修图/拍摄不在本例员工任务范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="105" customHeight="1" s="1">
+      <c r="A30" s="125" t="inlineStr">
+        <is>
+          <t>不能共享时如何计算</t>
+        </is>
+      </c>
+      <c r="B30" s="125" t="inlineStr">
+        <is>
+          <t>按实际交付数量替换本例数量，不直接用475乘SKU。不同上架模板分组计费，不同站点分别计上架；共用开发资料不因站点增加再领开发费。独立A+、视频及图片方案分别按各项目标准验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="105" customHeight="1" s="1">
+      <c r="A31" s="125" t="inlineStr">
+        <is>
+          <t>台账与分配</t>
+        </is>
+      </c>
+      <c r="B31" s="125" t="inlineStr">
+        <is>
+          <t>记录系列项目编号、SKU参数清单、阶段任务编号、共用/独立范围、交付ID、参与人和验收日期。OA按SKU拆单时关联同一阶段交付ID；多人协作共享该交付的总报酬，不每人领取一份。跨月结算及后续新增款沿用系列ID，避免重新认领旧交付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="105" customHeight="1" s="1">
+      <c r="A32" s="125" t="inlineStr">
+        <is>
+          <t>主动倍率与责任纠错</t>
+        </is>
+      </c>
+      <c r="B32" s="125" t="inlineStr">
+        <is>
+          <t>本页比较均按指派任务倍率1，不表示新增统一的系列主动倍率。员工主动提出系列也不能把每个SKU都乘出一份开发金额；先按本页确定真实独立交付金额，再按已确认适用倍率计。原任务错误补交、返工不另计酬。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -11,6 +11,7 @@
     <sheet name="广告优化认定规则（已归档）" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="改善成果奖励" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="系列开发计酬" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="研发考核规则" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00&quot;元&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -268,8 +269,14 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="48">
+  <fills count="49">
     <fill>
       <patternFill/>
     </fill>
@@ -507,8 +514,14 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="21">
     <border/>
     <border>
       <left style="thin">
@@ -668,6 +681,18 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1">
@@ -819,7 +844,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1155,6 +1180,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="46" fillId="48" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="47" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0"/>
@@ -16357,4 +16395,483 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="1" min="1" max="1"/>
+    <col width="90" customWidth="1" style="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="135" t="inlineStr">
+        <is>
+          <t>技术研发考核规则（试行）</t>
+        </is>
+      </c>
+      <c r="B1" s="136" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="137" t="inlineStr">
+        <is>
+          <t>适用范围</t>
+        </is>
+      </c>
+      <c r="B2" s="137" t="inlineStr">
+        <is>
+          <t>适用于需要独立研究、技术攻关或产品创新的研发项目。技术研发单独使用本规则，不套用运营考核中普通新品开发（调研75元、找厂75元、样品75元）的标准。
+普通新品开发仍按"运营考核"任务评分执行；同一交付物不在两套体系中重复计费。研发阶段与运营阶段以"投产验收"为分界：投产验收前按本规则计酬，投产验收后的上架、图片、A+、广告等按运营考核规则计酬。
+研发期间产出的产品资料、图片策划、字幕等，如果直接用于后续上架且无需独立重做，运营阶段不再另计该部分金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="137" t="inlineStr">
+        <is>
+          <t>计价说明</t>
+        </is>
+      </c>
+      <c r="B3" s="137" t="inlineStr">
+        <is>
+          <t>本页直接以人民币元计价，与运营考核保持统一口径。以下数值为试行建议，立项时可根据项目难度调整具体金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="135" t="inlineStr">
+        <is>
+          <t>奖励层级</t>
+        </is>
+      </c>
+      <c r="B5" s="136" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="135" t="inlineStr">
+        <is>
+          <t>奖励层级</t>
+        </is>
+      </c>
+      <c r="B6" s="135" t="inlineStr">
+        <is>
+          <t>考核内容、建议金额与验收条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="138" t="inlineStr">
+        <is>
+          <t>研究任务金额</t>
+        </is>
+      </c>
+      <c r="B7" s="137" t="inlineStr">
+        <is>
+          <t>考核内容：完成约定的调查、分析、设计和试验。
+建议金额：50元/独立研究任务（立项时可根据任务范围和难度调整）。
+验收条件：有研究记录、新增证据、阶段结论和下一步方案；认真研究但尚未突破也可验收。仅有"还在研究"、没有实际记录和结论的，不能验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="138" t="inlineStr">
+        <is>
+          <t>阶段突破额外金额</t>
+        </is>
+      </c>
+      <c r="B8" s="137" t="inlineStr">
+        <is>
+          <t>考核内容：解决关键技术问题，达到约定的技术指标或目标。
+建议金额：关键突破100元/独立突破目标（立项时可调整）；重大突破由负责人另行确定金额。
+验收条件：有可复现的验证结果，证明问题得到解决或方案达到指标。
+关键突破与重大突破的区别：关键突破解决单个项目的核心技术难题；重大突破具有显著创新性，影响多个产品线或形成可保护的技术方案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="138" t="inlineStr">
+        <is>
+          <t>投产金额</t>
+        </is>
+      </c>
+      <c r="B9" s="137" t="inlineStr">
+        <is>
+          <t>考核内容：研发成果完成生产转化。
+建议金额：100元/独立研发项目。
+验收条件：设计文件、BOM、检验标准及工艺文件完成交接；首批产品通过约定的检验项目且良率达到立项时确认的目标（未约定时以≥95%为默认）。
+质量责任：生产交接后3个月内因设计缺陷导致的批量质量问题，研发人员有配合排查义务，不另计研究或突破金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="138" t="inlineStr">
+        <is>
+          <t>销售提成</t>
+        </is>
+      </c>
+      <c r="B10" s="137" t="inlineStr">
+        <is>
+          <t>考核内容：产品持续产生经营收益。
+建议比例：项目可提成贡献利润的3%。
+起算时间：从首批产品可售之日起算24个月；中间断货不暂停计时，但断货期间无销售则无提成。
+结算周期：月度统计、季度结算。
+最低门槛：单月贡献利润低于500元时不计提成，避免微利产品产生过高管理成本。
+提成基数：扣除退货成本和质量索赔后的净贡献利润。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="139" t="inlineStr">
+        <is>
+          <t>可调整参数</t>
+        </is>
+      </c>
+      <c r="B11" s="139" t="inlineStr">
+        <is>
+          <t>上述金额（50元、100元、100元、3%、500元门槛、24个月期限、95%良率）均为试行建议，立项时由负责人根据项目情况确认。确认后记入立项文件，项目周期内不随意变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="135" t="inlineStr">
+        <is>
+          <t>立项要求</t>
+        </is>
+      </c>
+      <c r="B13" s="136" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="137" t="inlineStr">
+        <is>
+          <t>研究任务立项</t>
+        </is>
+      </c>
+      <c r="B14" s="137" t="inlineStr">
+        <is>
+          <t>每项研究任务开始前，写清以下内容：
+① 研究问题：明确本次任务要回答的具体技术问题。
+② 交付成果：约定需提交的记录、数据、结论或方案。
+③ 约定金额：根据任务范围和难度确认本次金额。
+④ 检查时间：约定阶段检查或最终提交日期。
+每个研究任务对应一个独立研究问题。同一研究问题拆成多个阶段提交，合并为一个研究任务；不同研究问题即使在同一周完成也分别计费。以立项时约定的研究问题为去重依据，不以OA条数、周报次数或文档份数累加。研究任务不等同于一个自然周，不能每周自动领取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="137" t="inlineStr">
+        <is>
+          <t>突破目标立项</t>
+        </is>
+      </c>
+      <c r="B15" s="137" t="inlineStr">
+        <is>
+          <t>突破目标另外写清以下内容：
+① 技术指标：约定需达到的可量化目标或可判断的技术条件。
+② 验证方法：约定如何复现和验证突破结果。
+③ 额外金额：根据难度和影响确认突破金额。
+④ 关键突破或重大突破的预判：立项时初步判断，验收时可根据实际成果调整。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="137" t="inlineStr">
+        <is>
+          <t>提成口径立项</t>
+        </is>
+      </c>
+      <c r="B16" s="137" t="inlineStr">
+        <is>
+          <t>项目立项时提前固定以下内容：
+① 关联产品：明确哪些SKU或产品线纳入提成计算。
+② 成本扣除项：约定哪些成本从收入中扣除（采购、运费、平台费、广告、退货等）。
+③ 退货调整：退货成本和质量索赔从提成基数中扣除。
+④ 起止日期：首批产品可售之日起24个月。
+⑤ 人员调岗或离开项目：按在项目中的参与月份÷项目总月份 × 应得提成比例分配。离职后仍发放剩余期限的提成（已约定的合同义务），但不再参与新立项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="135" t="inlineStr">
+        <is>
+          <t>执行规则</t>
+        </is>
+      </c>
+      <c r="B18" s="136" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="137" t="inlineStr">
+        <is>
+          <t>① 过程和突破分别验收</t>
+        </is>
+      </c>
+      <c r="B19" s="137" t="inlineStr">
+        <is>
+          <t>认真研究但尚未突破，可以拿研究任务金额；只有"还在研究"、没有实际记录和结论，不能验收。突破需有可复现的验证结果，独立于研究过程验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="137" t="inlineStr">
+        <is>
+          <t>② 可靠的失败结论有价值</t>
+        </is>
+      </c>
+      <c r="B20" s="137" t="inlineStr">
+        <is>
+          <t>证明某路线不可行，有充分证据和分析的，可以取得研究任务金额。若事先将"判明可行性"明确为技术目标，也可按约定认定突破成果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="137" t="inlineStr">
+        <is>
+          <t>③ 同一成果不重复包装</t>
+        </is>
+      </c>
+      <c r="B21" s="137" t="inlineStr">
+        <is>
+          <t>多个独立突破可分别奖励，必须在立项时明确区别。普通新品开发任务与研发任务的相同交付只计一次，不在两套体系中重复计费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="137" t="inlineStr">
+        <is>
+          <t>④ 正常调试和本人缺陷返工不新增奖励</t>
+        </is>
+      </c>
+      <c r="B22" s="137" t="inlineStr">
+        <is>
+          <t>正常开发调试过程不单独领取研究或突破金额。本人设计缺陷的修复属于原任务返工，不另计酬。新增需求或新技术问题，确认新增范围后另立任务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="137" t="inlineStr">
+        <is>
+          <t>⑤ 共用系列、多人合作按项目分配</t>
+        </is>
+      </c>
+      <c r="B23" s="137" t="inlineStr">
+        <is>
+          <t>同一方案衍生多个SKU，不重复领取整套研究、突破和投产金额。多人合作在同一份项目金额及提成池内分配，提前明确分配比例，个人份额之和不得超过项目总金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="137" t="inlineStr">
+        <is>
+          <t>⑥ 提成口径提前固定</t>
+        </is>
+      </c>
+      <c r="B24" s="137" t="inlineStr">
+        <is>
+          <t>明确关联产品、成本扣除项、退货调整、起止日期及人员变动规则。提成期限内不因人员调动改变已约定的口径，但可因产品线调整经双方确认更新关联SKU。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="137" t="inlineStr">
+        <is>
+          <t>⑦ 超期管理</t>
+        </is>
+      </c>
+      <c r="B25" s="137" t="inlineStr">
+        <is>
+          <t>研究任务超过立项时约定的检查时间仍未提交任何成果或进展说明的，暂停该任务金额确认，直到补交记录。超过约定时间60天仍无实质进展，由负责人决定是否终止任务或调整方案。终止不追扣已验收的研究金额，但不发放未验收部分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="135" t="inlineStr">
+        <is>
+          <t>过程管理</t>
+        </is>
+      </c>
+      <c r="B27" s="136" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="137" t="inlineStr">
+        <is>
+          <t>周报更新</t>
+        </is>
+      </c>
+      <c r="B28" s="137" t="inlineStr">
+        <is>
+          <t>每周一次更新"新增成果、当前卡点、下一步"。既不要求每周都突破，也不能长期没有证据地重复领取研究金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="137" t="inlineStr">
+        <is>
+          <t>月度统计</t>
+        </is>
+      </c>
+      <c r="B29" s="137" t="inlineStr">
+        <is>
+          <t>月底统计已验收的研究任务金额和突破金额，计入当月绩效。投产金额在验收完成月计入。销售提成按季度结算，不计入月度任务绩效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="137" t="inlineStr">
+        <is>
+          <t>台账字段</t>
+        </is>
+      </c>
+      <c r="B30" s="137" t="inlineStr">
+        <is>
+          <t>项目编号｜研究任务编号｜人员及分配比例｜研究问题｜交付成果要求｜约定金额｜立项日期｜检查日期｜周报记录｜验收状态｜验收日期｜突破目标编号（如有）｜技术指标｜验证方法｜突破金额｜投产验收日期｜关联产品SKU｜提成口径｜提成起止日期｜提成结算记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="135" t="inlineStr">
+        <is>
+          <t>计费示例</t>
+        </is>
+      </c>
+      <c r="B32" s="136" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="137" t="inlineStr">
+        <is>
+          <t>示例：一个项目约定两项研究任务、一个突破目标</t>
+        </is>
+      </c>
+      <c r="B33" s="137" t="inlineStr">
+        <is>
+          <t>① 完成第一项研究任务（材料选型调查）：验收通过，50元。
+② 完成第二项研究任务（结构方案设计与试验）：验收通过，50元。累计100元。
+③ 取得并验证关键突破（达到约定的性能指标）：额外100元。累计200元。
+④ 首批投产验收通过：再加100元。累计300元。
+⑤ 后续销售：另按项目净贡献利润的3%提成，月度统计、季度结算，持续24个月。不占用上述金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="137" t="inlineStr">
+        <is>
+          <t>示例：研究完成但未突破</t>
+        </is>
+      </c>
+      <c r="B34" s="137" t="inlineStr">
+        <is>
+          <t>完成两项研究任务，认真调查并提交了充分证据和结论，证明当前路线不可行。
+研究任务金额：50＋50＝100元，正常验收。
+突破金额：0元（未达到约定指标）。
+投产金额：0元（未进入生产）。
+提成：无。
+说明：可靠的失败结论有价值，研究金额照常发放。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="137" t="inlineStr">
+        <is>
+          <t>示例：同一方案衍生3个SKU</t>
+        </is>
+      </c>
+      <c r="B35" s="137" t="inlineStr">
+        <is>
+          <t>共用同一套研究方案和技术突破，衍生3个尺寸的产品。
+研究任务金额：按实际独立研究任务计（如共用方案只计一次50元，不按SKU数乘3）。
+突破金额：共用同一突破只计一次100元。
+投产金额：共用同一设计方案和BOM体系，只计一次100元。
+提成：3个SKU的净贡献利润合并计算，按约定比例提成。
+与运营考核的衔接：投产后的上架、图片等按运营考核规则计酬，系列产品按"系列开发计酬"页规则处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="137" t="inlineStr">
+        <is>
+          <t>示例：多人合作</t>
+        </is>
+      </c>
+      <c r="B36" s="137" t="inlineStr">
+        <is>
+          <t>两人合作完成一个研发项目，立项时约定A负责60%、B负责40%。
+研究任务100元（2项×50元）：A得60元，B得40元。
+突破100元：A得60元，B得40元。
+投产100元：A得60元，B得40元。
+提成：A按3%×60%＝1.8%，B按3%×40%＝1.2%，各自按份额结算。
+两人金额之和不超过项目总金额，不因多人参与增加项目总额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="135" t="inlineStr">
+        <is>
+          <t>与运营考核的边界</t>
+        </is>
+      </c>
+      <c r="B38" s="136" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="137" t="inlineStr">
+        <is>
+          <t>分界点</t>
+        </is>
+      </c>
+      <c r="B39" s="137" t="inlineStr">
+        <is>
+          <t>研发阶段与运营阶段以"投产验收"为分界。投产验收前的工作按本规则（研究任务、突破、投产）计酬；投产验收后的上架、图片、A+、广告等按"运营考核"任务评分规则计酬。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="137" t="inlineStr">
+        <is>
+          <t>共用交付物</t>
+        </is>
+      </c>
+      <c r="B40" s="137" t="inlineStr">
+        <is>
+          <t>研发期间产出的产品资料、图片策划、字幕等，如果直接用于后续上架且无需独立重做，运营阶段不再另计该部分金额。与"系列开发计酬"页的共用内容原则一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="137" t="inlineStr">
+        <is>
+          <t>不重复计费</t>
+        </is>
+      </c>
+      <c r="B41" s="137" t="inlineStr">
+        <is>
+          <t>同一交付物不在研发考核和运营考核两套体系中重复计费。例如：研发期间已计入研究任务金额的产品资料核实，不再按运营考核的"产品资料整理与确认"40元另计。但研发期间未涉及的运营工作（如后续独立的广告创建、价格调整等），按运营考核正常计酬。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="137" t="inlineStr">
+        <is>
+          <t>提成与成果奖励</t>
+        </is>
+      </c>
+      <c r="B42" s="137" t="inlineStr">
+        <is>
+          <t>研发项目的销售提成按本页规则结算。运营考核中的"改善成果奖励"适用于运营阶段的改善工作，与研发提成不重复：同一产品的同一经营改善不同时领取提成和成果奖励。运营人员对研发产品的后续优化可按运营考核的成果奖励规则另行申请，但需确认与研发提成无重叠。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="任务评分" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="任务报酬" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="主动改善评价" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="运营工作明细" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="广告优化规则" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Listing异常合批规则" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="临时工作分档" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="临时任务金额档位" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="优化登记与复盘规则" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="研发考核规则" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="月度结算与参数" sheetId="9" state="visible" r:id="rId9"/>
@@ -22,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Carlito"/>
@@ -78,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -103,7 +105,25 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -381,13 +401,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L117"/>
+  <dimension ref="A2:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
@@ -395,48 +415,48 @@
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>任务评分</t>
+          <t>运营任务报酬标准（人民币元）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11统一版：任务以积分计，不再用旧人民币单价或难度系数。110个计分行沿用最近确认的独立档位。</t>
+          <t>直接按人民币金额结算；本版按已确认的原标准等值换算，日常登记不再使用积分。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>P044—P051固定10分；广告优化2/3/5/8/10/15分，受派和主动均×1。Buy Box为3/5分，Listing异常为2/4分并按同因合批。</t>
+          <t>普通开发及经营分析每项50元；广告调整与优化10/15/25/40/50/75元，受派和主动均×1。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>本档主动积分为单位示例；真实批次须按数量、合批、附加及已付差额结算。主动必须满足来源和实质贡献认定。</t>
+          <t>主动报酬＝本档金额×主动倍率。先按实际计酬单位合批，再扣已付金额；共用工作只计一次。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>积分换算金额须使用项目/期间确认的积分单价；本版不擅自把1分改成1元。研发另见研发考核规则；现金成果奖保留元单位。</t>
+          <t>黄色D列是直接金额标准；I列仅记录修改建议，不参与计算。修改金额时同步更新适用条件及示例。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>计分项编号</t>
+          <t>项目编号</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -451,12 +471,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>本档分值</t>
+          <t>本档金额（元）</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>计分单位</t>
+          <t>计酬单位</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -466,17 +486,17 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>合批、互斥及重复计分规则</t>
+          <t>合批、互斥及重复计酬规则</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>定分说明</t>
+          <t>定价说明</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>你的调整</t>
+          <t>你的调整建议</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -491,7 +511,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>本档主动积分（单位示例）</t>
+          <t>本档主动报酬（元）</t>
         </is>
       </c>
     </row>
@@ -511,8 +531,8 @@
           <t>Listing创建</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>5</v>
+      <c r="D8" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
@@ -526,7 +546,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>5分/上架执行组，包含本次必要的父子关系组合及上传核验；不另叠加变体维护分。按同一需求、同站点、可共用上架表分组，不按OA条数拆分。</t>
+          <t>25元/上架执行组，包含本次必要的父子关系组合及上传核验；不另叠加变体维护报酬。按同一需求、同站点、可共用上架表分组，不按OA条数拆分。</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -544,7 +564,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="15">
         <f>D8*K8</f>
         <v/>
       </c>
@@ -565,8 +585,8 @@
           <t>首轮图片上传：已有图片</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>2</v>
+      <c r="D9" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -598,7 +618,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="16">
         <f>D9*K9</f>
         <v/>
       </c>
@@ -619,27 +639,27 @@
           <t>首轮图片上传：需要取图—标准处理</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>3</v>
+      <c r="D10" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>SKU；多SKU共用的沟通工作需注明。</t>
+          <t>同一需求的一批SKU；上传逐SKU，共用取图协调按次。</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>需向一个明确负责人索要并确认图片，再完成一个SKU上传。</t>
+          <t>向一个明确负责人索要并确认可用图片，完成本批图片上传及核验。</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>本批总报酬＝10元×实际上传SKU数＋取图协调5元/独立安排。D列15元仅为1个SKU的完整任务金额；多个SKU共用协调不能直接用D列乘SKU数。普通及复杂协调只选一档。与P002-a不重复领上传费，与P003已付的相同收图工作不重复。</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>比直接上传多出资料确认和沟通，但不等同图片设计。</t>
+          <t>区分逐SKU上传和一次共用协调。等待久不加价，不得自行拆分安排增加报酬。</t>
         </is>
       </c>
       <c r="I10" s="9" t="n"/>
@@ -652,7 +672,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="15">
         <f>D10*K10</f>
         <v/>
       </c>
@@ -670,30 +690,30 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>首轮图片上传：需要取图—4分档</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>4</v>
+          <t>首轮图片上传：需要取图—20元档</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>SKU；多SKU共用的沟通工作需注明。</t>
+          <t>同一需求的一批SKU；上传逐SKU，共用取图协调按次。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>在完成该项目基本交付的基础上：需核对多个冲突版本或协调多方确认可用图片；等待久不升档。多人多SKU共用协调不得逐SKU重复加同一协调部分。</t>
+          <t>核对多个冲突版本或协调多方确认可用图片，完成本批图片上传及核验。</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>本批总报酬＝10元×实际上传SKU数＋取图协调10元/独立安排。D列20元仅为1个SKU的完整任务金额；多个SKU共用协调不能直接用D列乘SKU数。普通及复杂协调只选一档。与P002-a不重复领上传费，与P003已付的相同收图工作不重复。</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原4分标准；不是新增累计任务。</t>
+          <t>区分逐SKU上传和一次共用协调。等待久不加价，不得自行拆分安排增加报酬。</t>
         </is>
       </c>
       <c r="I11" s="9" t="n"/>
@@ -706,7 +726,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="16">
         <f>D11*K11</f>
         <v/>
       </c>
@@ -727,8 +747,8 @@
           <t>样品备货与拍摄协调—标准处理</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>4</v>
+      <c r="D12" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -742,7 +762,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -760,7 +780,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="15">
         <f>D12*K12</f>
         <v/>
       </c>
@@ -778,11 +798,11 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>样品备货与拍摄协调—5分档</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>5</v>
+          <t>样品备货与拍摄协调—25元档</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -796,12 +816,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I13" s="9" t="n"/>
@@ -814,7 +834,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="16">
         <f>D13*K13</f>
         <v/>
       </c>
@@ -835,8 +855,8 @@
           <t>已有A+新增绑定</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>1</v>
+      <c r="D14" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -855,7 +875,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>适用关系已明确，执行简单绑定和核验；不包含内容制作，按1分档。</t>
+          <t>适用关系已明确，执行简单绑定和核验；不包含内容制作，按5元档。</t>
         </is>
       </c>
       <c r="I14" s="9" t="n"/>
@@ -868,7 +888,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="15">
         <f>D14*K14</f>
         <v/>
       </c>
@@ -889,8 +909,8 @@
           <t>已有视频信息修改—标准处理</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>1</v>
+      <c r="D15" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -904,12 +924,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>已有文字的少量信息替换，按1分；独立表达不属于简单修改。</t>
+          <t>已有文字的少量信息替换，按5元；独立表达不属于简单修改。</t>
         </is>
       </c>
       <c r="I15" s="9" t="n"/>
@@ -922,7 +942,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="16">
         <f>D15*K15</f>
         <v/>
       </c>
@@ -940,11 +960,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>已有视频信息修改—3分档</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>3</v>
+          <t>已有视频信息修改—15元档</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
@@ -958,12 +978,12 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I16" s="9" t="n"/>
@@ -976,7 +996,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="15">
         <f>D16*K16</f>
         <v/>
       </c>
@@ -997,8 +1017,8 @@
           <t>视频上传或替换—标准处理</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>3</v>
+      <c r="D17" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -1012,7 +1032,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1030,7 +1050,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="16">
         <f>D17*K17</f>
         <v/>
       </c>
@@ -1048,11 +1068,11 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>视频上传或替换—4分档</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>4</v>
+          <t>视频上传或替换—20元档</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -1066,12 +1086,12 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原4分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原20元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I18" s="9" t="n"/>
@@ -1084,7 +1104,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="15">
         <f>D18*K18</f>
         <v/>
       </c>
@@ -1105,8 +1125,8 @@
           <t>已有视频新增ASIN—标准处理</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>2</v>
+      <c r="D19" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -1120,7 +1140,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1138,7 +1158,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="16">
         <f>D19*K19</f>
         <v/>
       </c>
@@ -1156,11 +1176,11 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>已有视频新增ASIN—3分档</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>3</v>
+          <t>已有视频新增ASIN—15元档</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
@@ -1174,12 +1194,12 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I20" s="9" t="n"/>
@@ -1192,7 +1212,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="15">
         <f>D20*K20</f>
         <v/>
       </c>
@@ -1213,8 +1233,8 @@
           <t>事实字段纠错</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>3</v>
+      <c r="D21" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -1228,7 +1248,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>同因同批合并；另有多来源核查及冲突确认时选择P006-T5，两档互斥。本人责任纠错不另计分，相同成果不重复计其他项目。</t>
+          <t>同因同批合并；另有多来源核查及冲突确认时选择P006-T5，两档互斥。本人责任纠错不另计酬，相同成果不重复计其他项目。</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1246,7 +1266,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="16">
         <f>D21*K21</f>
         <v/>
       </c>
@@ -1267,8 +1287,8 @@
           <t>事实字段纠错—资料冲突核查</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>5</v>
+      <c r="D22" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
@@ -1282,12 +1302,12 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>同因同批合并；另有多来源核查及冲突确认时选择P006-T5，两档互斥。本人责任纠错不另计分，相同成果不重复计其他项目。</t>
+          <t>同因同批合并；另有多来源核查及冲突确认时选择P006-T5，两档互斥。本人责任纠错不另计酬，相同成果不重复计其他项目。</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>将原“最高5分”的模糊说明按已有资料冲突核查范围明确列为5分档；与标准3分互斥。</t>
+          <t>将原“最高25元”的模糊说明按已有资料冲突核查范围明确列为25元档；与标准15元互斥。</t>
         </is>
       </c>
       <c r="I22" s="9" t="n"/>
@@ -1300,7 +1320,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="15">
         <f>D22*K22</f>
         <v/>
       </c>
@@ -1321,8 +1341,8 @@
           <t>逐份内容的简单事实纠错—标准处理</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>2</v>
+      <c r="D23" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -1336,7 +1356,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1354,7 +1374,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="16">
         <f>D23*K23</f>
         <v/>
       </c>
@@ -1372,11 +1392,11 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>逐份内容的简单事实纠错—3分档</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>3</v>
+          <t>逐份内容的简单事实纠错—15元档</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
@@ -1390,12 +1410,12 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I24" s="9" t="n"/>
@@ -1408,7 +1428,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="15">
         <f>D24*K24</f>
         <v/>
       </c>
@@ -1429,8 +1449,8 @@
           <t>标题改写与优化（已有内容）</t>
         </is>
       </c>
-      <c r="D25" s="9" t="n">
-        <v>2</v>
+      <c r="D25" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -1444,12 +1464,12 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>固定2分；同轮修改合并。五点不按改了几点拆分；共用文案仅替换型号参数不按SKU重复计完整改写分。另有独立调研分析须事先确认交付，同一成果不重复计分。</t>
+          <t>固定10元；同轮修改合并。五点不按改了几点拆分；共用文案仅替换型号参数不按SKU重复计完整改写报酬。另有独立调研分析须事先确认交付，同一成果不重复计酬。</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>已有内容和Skill已提供主要写作基础，实际工作是组织输入、核验及修订，不按从零创作5分计。</t>
+          <t>已有内容和Skill已提供主要写作基础，实际工作是组织输入、核验及修订，不按从零创作25元计。</t>
         </is>
       </c>
       <c r="I25" s="9" t="n"/>
@@ -1462,7 +1482,7 @@
         <f>'主动改善评价'!C8</f>
         <v/>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="16">
         <f>D25*K25</f>
         <v/>
       </c>
@@ -1483,8 +1503,8 @@
           <t>五点改写与优化（已有内容）</t>
         </is>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>2</v>
+      <c r="D26" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
@@ -1498,12 +1518,12 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>固定2分；同轮修改合并。五点不按改了几点拆分；共用文案仅替换型号参数不按SKU重复计完整改写分。另有独立调研分析须事先确认交付，同一成果不重复计分。</t>
+          <t>固定10元；同轮修改合并。五点不按改了几点拆分；共用文案仅替换型号参数不按SKU重复计完整改写报酬。另有独立调研分析须事先确认交付，同一成果不重复计酬。</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>已有内容和Skill已提供主要写作基础，实际工作是组织输入、核验及修订，不按从零创作5分计。</t>
+          <t>已有内容和Skill已提供主要写作基础，实际工作是组织输入、核验及修订，不按从零创作25元计。</t>
         </is>
       </c>
       <c r="I26" s="9" t="n"/>
@@ -1516,7 +1536,7 @@
         <f>'主动改善评价'!C8</f>
         <v/>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="15">
         <f>D26*K26</f>
         <v/>
       </c>
@@ -1537,8 +1557,8 @@
           <t>描述改写与优化（已有内容）</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>2</v>
+      <c r="D27" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -1552,12 +1572,12 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>固定2分；同轮修改合并。五点不按改了几点拆分；共用文案仅替换型号参数不按SKU重复计完整改写分。另有独立调研分析须事先确认交付，同一成果不重复计分。</t>
+          <t>固定10元；同轮修改合并。五点不按改了几点拆分；共用文案仅替换型号参数不按SKU重复计完整改写报酬。另有独立调研分析须事先确认交付，同一成果不重复计酬。</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>已有内容和Skill已提供主要写作基础，实际工作是组织输入、核验及修订，不按从零创作5分计。</t>
+          <t>已有内容和Skill已提供主要写作基础，实际工作是组织输入、核验及修订，不按从零创作25元计。</t>
         </is>
       </c>
       <c r="I27" s="9" t="n"/>
@@ -1570,7 +1590,7 @@
         <f>'主动改善评价'!C8</f>
         <v/>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="16">
         <f>D27*K27</f>
         <v/>
       </c>
@@ -1591,8 +1611,8 @@
           <t>Generic Keywords编写或优化—标准处理</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>3</v>
+      <c r="D28" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -1606,12 +1626,12 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>基础工作是筛选、去重和相关性判断；系统研究增加分析投入。</t>
+          <t>基础工作是筛选、去重和相关性判断；系统研究增加价析投入。</t>
         </is>
       </c>
       <c r="I28" s="9" t="n"/>
@@ -1624,7 +1644,7 @@
         <f>'主动改善评价'!C8</f>
         <v/>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="15">
         <f>D28*K28</f>
         <v/>
       </c>
@@ -1642,11 +1662,11 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Generic Keywords编写或优化—5分档</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>5</v>
+          <t>Generic Keywords编写或优化—25元档</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -1660,12 +1680,12 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I29" s="9" t="n"/>
@@ -1678,115 +1698,115 @@
         <f>'主动改善评价'!C8</f>
         <v/>
       </c>
-      <c r="L29" s="4">
+      <c r="L29" s="16">
         <f>D29*K29</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="30" ht="85" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>P011-a</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>A+内容</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>A+复用模板制作与发布</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D30" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>一份实际独立A+内容；共用内容的SKU列在同一份下。</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>沿用已有A+结构和表达方式，适配产品文案及图片并制作发布。新建内容时记录来源模板/原内容ID和新内容ID，说明实际适配部分，核验约定商品应用结果。</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>固定3分；与同份同轮完全重做或局部修改档互斥。仅复制并替换型号、参数或少量图片按P012，不能因新建内容ID认定完全重做。制作含本次约定商品首次绑定。</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>沿用模板减少独立构思工作，低于全新5分、高于局部修改2分。</t>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>固定15元；与同份同轮完全重做或局部修改档互斥。仅复制并替换型号、参数或少量图片按P012，不能因新建内容ID认定完全重做。制作含本次约定商品首次绑定。</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>沿用模板减少独立构思工作，低于全新25元、高于局部修改10元。</t>
         </is>
       </c>
       <c r="I30" s="9" t="n"/>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>未明确列入的项目</t>
         </is>
       </c>
-      <c r="K30" s="4">
+      <c r="K30" s="8">
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L30" s="4">
+      <c r="L30" s="15">
         <f>D30*K30</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="85" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>P011-b</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>A+内容</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>A+全新或完全重做（策划及制作）</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="D31" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>一份新增独立方案；系列共用方案只记录一次。</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>完成独立策划、文案、图片要求、素材协调及制作发布。原A+不好需完全重做时，必须保留旧A+、另建新A+，记录旧/新内容ID、重做原因及结构、卖点、文案、图片要求的实质变化。首次全新制作无旧版的，标记首次创建。新版本审核通过后核验目标ASIN已应用新内容，并完成约定复盘。</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>同份同轮完整策划制作总计5分，不叠加模板制作、局部修改和本次首次绑定分。旧A+留档对照，不要求继续应用在商品上；不得直接覆盖旧A+代替完全重做留档。仅新建内容ID不等于完全重做，复制后仅换参数按局部修改，模板适配按复用档。</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>日常运营内容制作最高5分；原策划与制作的累计15分规则取消。</t>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>同份同轮完整策划制作总计25元，不叠加模板制作、局部修改和本次首次绑定费用。旧A+留档对照，不要求继续应用在商品上；不得直接覆盖旧A+代替完全重做留档。仅新建内容ID不等于完全重做，复制后仅换参数按局部修改，模板适配按复用档。</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>日常运营内容制作最高25元；原策划与制作的累计75元规则取消。</t>
         </is>
       </c>
       <c r="I31" s="9" t="n"/>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>Listing内容实质重写</t>
         </is>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="4">
         <f>'主动改善评价'!C8</f>
         <v/>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="16">
         <f>D31*K31</f>
         <v/>
       </c>
@@ -1807,8 +1827,8 @@
           <t>A+局部增删修改</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>2</v>
+      <c r="D32" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -1822,7 +1842,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>固定2分/份/轮，同轮局部修改合并。与复用制作及完全重做档互斥；若确需完全重做，保留原A+并新建版本，转P011-b且只补同轮已付差额。</t>
+          <t>固定10元/份/轮，同轮局部修改合并。与复用制作及完全重做档互斥；若确需完全重做，保留原A+并新建版本，转P011-b且只补同轮已付差额。</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1840,7 +1860,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L32" s="8">
+      <c r="L32" s="15">
         <f>D32*K32</f>
         <v/>
       </c>
@@ -1861,8 +1881,8 @@
           <t>变体选项名称或属性值调整</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>2</v>
+      <c r="D33" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -1876,7 +1896,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>固定2分/独立调整方案；同次修改与核验合并。涉及关系加入、组合或拆分重组，转对应档且只取一个最高适用档。</t>
+          <t>固定10元/独立调整方案；同次修改与核验合并。涉及关系加入、组合或拆分重组，转对应档且只取一个最高适用档。</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1894,7 +1914,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L33" s="4">
+      <c r="L33" s="16">
         <f>D33*K33</f>
         <v/>
       </c>
@@ -1915,8 +1935,8 @@
           <t>已上架商品加入已有变体</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>4</v>
+      <c r="D34" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -1930,7 +1950,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>固定4分/独立加入方案；需处理旧关系拆分后再组合时转重组5分，不叠加。新品上架已含关系不另计。</t>
+          <t>固定20元/独立加入方案；需处理旧关系拆分后再组合时转重组25元，不叠加。新品上架已含关系不另计。</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -1948,7 +1968,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L34" s="8">
+      <c r="L34" s="15">
         <f>D34*K34</f>
         <v/>
       </c>
@@ -1969,8 +1989,8 @@
           <t>已上架独立商品组合成新变体</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>3</v>
+      <c r="D35" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -1984,7 +2004,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>固定3分/同站点独立组合方案；新品上架任务中的必要变体组合已含上架分，不另计。需拆旧关系后重新组合转P013-d。</t>
+          <t>固定15元/同站点独立组合方案；新品上架任务中的必要变体组合已含上架报酬，不另计。需拆旧关系后重新组合转P013-d。</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2002,7 +2022,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L35" s="4">
+      <c r="L35" s="16">
         <f>D35*K35</f>
         <v/>
       </c>
@@ -2023,8 +2043,8 @@
           <t>原有变体拆分、迁移后重新组合</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>5</v>
+      <c r="D36" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
@@ -2038,7 +2058,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>固定5分/同站点完整重组方案；先拆分、再加入、最后重组只取5分，不叠加。多个SKU共用方案不逐SKU计整份分；反复上传重试不加分。</t>
+          <t>固定25元/同站点完整重组方案；先拆分、再加入、最后重组只取25元，不叠加。多个SKU共用方案不逐SKU计整份报酬；反复上传重试不加价。</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2056,7 +2076,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="15">
         <f>D36*K36</f>
         <v/>
       </c>
@@ -2077,8 +2097,8 @@
           <t>后续图片更新：已有图片</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>2</v>
+      <c r="D37" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -2110,7 +2130,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L37" s="4">
+      <c r="L37" s="16">
         <f>D37*K37</f>
         <v/>
       </c>
@@ -2131,8 +2151,8 @@
           <t>后续图片更新：需要协调取图—标准处理</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>3</v>
+      <c r="D38" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
@@ -2146,7 +2166,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -2164,7 +2184,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L38" s="8">
+      <c r="L38" s="15">
         <f>D38*K38</f>
         <v/>
       </c>
@@ -2182,11 +2202,11 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>后续图片更新：需要协调取图—4分档</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>4</v>
+          <t>后续图片更新：需要协调取图—20元档</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -2200,12 +2220,12 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原4分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原20元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I39" s="9" t="n"/>
@@ -2218,7 +2238,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L39" s="4">
+      <c r="L39" s="16">
         <f>D39*K39</f>
         <v/>
       </c>
@@ -2239,8 +2259,8 @@
           <t>按指定目标调整价格—标准处理</t>
         </is>
       </c>
-      <c r="D40" s="9" t="n">
-        <v>2</v>
+      <c r="D40" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -2254,12 +2274,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>策略已给定，主要是执行；不能按调价金额高低加分。</t>
+          <t>策略已给定，主要是执行；不能按调价金额高低加价。</t>
         </is>
       </c>
       <c r="I40" s="9" t="n"/>
@@ -2272,7 +2292,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L40" s="8">
+      <c r="L40" s="15">
         <f>D40*K40</f>
         <v/>
       </c>
@@ -2290,11 +2310,11 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>按指定目标调整价格—3分档</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>3</v>
+          <t>按指定目标调整价格—15元档</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -2308,12 +2328,12 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I41" s="9" t="n"/>
@@ -2326,7 +2346,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L41" s="4">
+      <c r="L41" s="16">
         <f>D41*K41</f>
         <v/>
       </c>
@@ -2344,11 +2364,11 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>按指定目标调整价格—5分档</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>5</v>
+          <t>按指定目标调整价格—25元档</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -2362,12 +2382,12 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I42" s="9" t="n"/>
@@ -2380,7 +2400,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L42" s="8">
+      <c r="L42" s="15">
         <f>D42*K42</f>
         <v/>
       </c>
@@ -2401,8 +2421,8 @@
           <t>Buy Box处理—已有依据执行</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n">
-        <v>3</v>
+      <c r="D43" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
@@ -2416,7 +2436,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>仅适用3分档；若实际新增独立原因核查及完整取证，转P016-b，总计5分，已计3分只补2分。</t>
+          <t>仅适用15元档；若实际新增独立原因核查及完整取证，转P016-b，总计25元，已计15元只补10元。</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2434,7 +2454,7 @@
         <f>'主动改善评价'!C11</f>
         <v/>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="16">
         <f>D43*K43</f>
         <v/>
       </c>
@@ -2455,8 +2475,8 @@
           <t>Buy Box处理—独立核查与取证</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n">
-        <v>5</v>
+      <c r="D44" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
@@ -2470,12 +2490,12 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>本项固定5分；同异常反复Case、催办、等待或补交不升档。同站点同ASIN同异常与P016-a只取一档。</t>
+          <t>本项固定25元；同异常反复Case、催办、等待或补交不升档。同站点同ASIN同异常与P016-a只取一档。</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>比3分多出独立原因判断、报价口径核对与证据组织；不是按Case次数或销量影响定分。</t>
+          <t>比15元多出独立原因判断、报价口径核对与证据组织；不是按Case次数或销量影响定价。</t>
         </is>
       </c>
       <c r="I44" s="9" t="n"/>
@@ -2488,7 +2508,7 @@
         <f>'主动改善评价'!C11</f>
         <v/>
       </c>
-      <c r="L44" s="8">
+      <c r="L44" s="15">
         <f>D44*K44</f>
         <v/>
       </c>
@@ -2509,8 +2529,8 @@
           <t>Coupon与Promotion创建</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n">
-        <v>2</v>
+      <c r="D45" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
@@ -2524,7 +2544,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>固定2分/独立活动；包含参数核对、创建或提报、常规报错修正和结果核验，多次修改或重提不重复计分。</t>
+          <t>固定10元/独立活动；包含参数核对、创建或提报、常规报错修正和结果核验，多次修改或重提不重复计酬。</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2542,7 +2562,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L45" s="4">
+      <c r="L45" s="16">
         <f>D45*K45</f>
         <v/>
       </c>
@@ -2563,8 +2583,8 @@
           <t>Deal活动提报</t>
         </is>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>2</v>
+      <c r="D46" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
@@ -2578,7 +2598,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>固定2分/独立活动；包含参数核对、创建或提报、常规报错修正和结果核验，多次修改或重提不重复计分。</t>
+          <t>固定10元/独立活动；包含参数核对、创建或提报、常规报错修正和结果核验，多次修改或重提不重复计酬。</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -2596,7 +2616,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L46" s="8">
+      <c r="L46" s="15">
         <f>D46*K46</f>
         <v/>
       </c>
@@ -2617,8 +2637,8 @@
           <t>SP Campaign创建—标准处理</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n">
-        <v>2</v>
+      <c r="D47" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -2632,7 +2652,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2650,7 +2670,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L47" s="4">
+      <c r="L47" s="16">
         <f>D47*K47</f>
         <v/>
       </c>
@@ -2668,11 +2688,11 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>SP Campaign创建—5分档</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>5</v>
+          <t>SP Campaign创建—25元档</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -2686,12 +2706,12 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I48" s="9" t="n"/>
@@ -2704,7 +2724,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L48" s="8">
+      <c r="L48" s="15">
         <f>D48*K48</f>
         <v/>
       </c>
@@ -2725,8 +2745,8 @@
           <t>SB Campaign创建—标准处理</t>
         </is>
       </c>
-      <c r="D49" s="9" t="n">
-        <v>3</v>
+      <c r="D49" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -2740,7 +2760,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2758,7 +2778,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L49" s="4">
+      <c r="L49" s="16">
         <f>D49*K49</f>
         <v/>
       </c>
@@ -2776,11 +2796,11 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>SB Campaign创建—5分档</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="n">
-        <v>5</v>
+          <t>SB Campaign创建—25元档</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
@@ -2794,12 +2814,12 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I50" s="9" t="n"/>
@@ -2812,7 +2832,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L50" s="8">
+      <c r="L50" s="15">
         <f>D50*K50</f>
         <v/>
       </c>
@@ -2833,8 +2853,8 @@
           <t>SBV Campaign创建—标准处理</t>
         </is>
       </c>
-      <c r="D51" s="9" t="n">
-        <v>3</v>
+      <c r="D51" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
@@ -2848,7 +2868,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2866,7 +2886,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L51" s="4">
+      <c r="L51" s="16">
         <f>D51*K51</f>
         <v/>
       </c>
@@ -2884,11 +2904,11 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>SBV Campaign创建—5分档</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="n">
-        <v>5</v>
+          <t>SBV Campaign创建—25元档</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
@@ -2902,12 +2922,12 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I52" s="9" t="n"/>
@@ -2920,7 +2940,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L52" s="8">
+      <c r="L52" s="15">
         <f>D52*K52</f>
         <v/>
       </c>
@@ -2941,8 +2961,8 @@
           <t>SD Campaign创建—标准处理</t>
         </is>
       </c>
-      <c r="D53" s="9" t="n">
-        <v>3</v>
+      <c r="D53" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
@@ -2956,7 +2976,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2974,7 +2994,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L53" s="4">
+      <c r="L53" s="16">
         <f>D53*K53</f>
         <v/>
       </c>
@@ -2992,11 +3012,11 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>SD Campaign创建—5分档</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="n">
-        <v>5</v>
+          <t>SD Campaign创建—25元档</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
@@ -3010,12 +3030,12 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I54" s="9" t="n"/>
@@ -3028,7 +3048,7 @@
         <f>'主动改善评价'!C9</f>
         <v/>
       </c>
-      <c r="L54" s="8">
+      <c r="L54" s="15">
         <f>D54*K54</f>
         <v/>
       </c>
@@ -3049,8 +3069,8 @@
           <t>广告优化—按明确指令调整</t>
         </is>
       </c>
-      <c r="D55" s="9" t="n">
-        <v>2</v>
+      <c r="D55" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -3082,7 +3102,7 @@
         <f>'主动改善评价'!C10</f>
         <v/>
       </c>
-      <c r="L55" s="4">
+      <c r="L55" s="16">
         <f>D55*K55</f>
         <v/>
       </c>
@@ -3103,8 +3123,8 @@
           <t>广告优化—常规减少无效花费</t>
         </is>
       </c>
-      <c r="D56" s="9" t="n">
-        <v>3</v>
+      <c r="D56" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
@@ -3136,7 +3156,7 @@
         <f>'主动改善评价'!C10</f>
         <v/>
       </c>
-      <c r="L56" s="8">
+      <c r="L56" s="15">
         <f>D56*K56</f>
         <v/>
       </c>
@@ -3157,8 +3177,8 @@
           <t>广告优化—独立分析并实施优化</t>
         </is>
       </c>
-      <c r="D57" s="9" t="n">
-        <v>5</v>
+      <c r="D57" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -3190,7 +3210,7 @@
         <f>'主动改善评价'!C10</f>
         <v/>
       </c>
-      <c r="L57" s="4">
+      <c r="L57" s="16">
         <f>D57*K57</f>
         <v/>
       </c>
@@ -3211,8 +3231,8 @@
           <t>广告优化—有效改善广告效率</t>
         </is>
       </c>
-      <c r="D58" s="9" t="n">
-        <v>8</v>
+      <c r="D58" s="14" t="n">
+        <v>40</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -3244,7 +3264,7 @@
         <f>'主动改善评价'!C10</f>
         <v/>
       </c>
-      <c r="L58" s="8">
+      <c r="L58" s="15">
         <f>D58*K58</f>
         <v/>
       </c>
@@ -3265,8 +3285,8 @@
           <t>广告优化—有效扩大销售</t>
         </is>
       </c>
-      <c r="D59" s="9" t="n">
-        <v>10</v>
+      <c r="D59" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -3298,7 +3318,7 @@
         <f>'主动改善评价'!C10</f>
         <v/>
       </c>
-      <c r="L59" s="4">
+      <c r="L59" s="16">
         <f>D59*K59</f>
         <v/>
       </c>
@@ -3319,8 +3339,8 @@
           <t>广告优化—持续、显著的改善</t>
         </is>
       </c>
-      <c r="D60" s="9" t="n">
-        <v>15</v>
+      <c r="D60" s="14" t="n">
+        <v>75</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -3352,7 +3372,7 @@
         <f>'主动改善评价'!C10</f>
         <v/>
       </c>
-      <c r="L60" s="8">
+      <c r="L60" s="15">
         <f>D60*K60</f>
         <v/>
       </c>
@@ -3373,27 +3393,27 @@
           <t>Listing异常处理—已有依据执行</t>
         </is>
       </c>
-      <c r="D61" s="9" t="n">
-        <v>2</v>
+      <c r="D61" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>同站点、同原因、共用证据及方案的一批问题；确需分别处理按去重ASIN附加1分。同ASIN多个SKU只计一个。</t>
+          <t>同站点、同原因、共用证据及方案的一批问题；确需分别处理按去重ASIN附加5元。同ASIN多个SKU只计一个。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>原因、可用证据及处理要求已明确，整理提交申诉或Case、跟进并核验。同站点同原因、共用证据方案且可合并处理的一批ASIN共计2分。</t>
+          <t>原因、可用证据及处理要求已明确，整理提交申诉或Case、跟进并核验。同站点同原因、共用证据方案且可合并处理的一批ASIN共计10元。</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>同因可合并的ASIN按一批计基础档；确需分别处理的额外执行选P025-ADD。同批基础档互斥，升级只补差额；自行拆Case、同ASIN多SKU及反复提交不加分。详见Listing异常合批规则。</t>
+          <t>同因可合并的ASIN按一批计基础档；确需分别处理的额外执行选P025-ADD。同批基础档互斥，升级只补差额；自行拆Case、同ASIN多SKU及反复提交不加价。详见Listing异常合批规则。</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>已有依据的处理执行按2分基础档；共用工作计一次，必要的逐ASIN执行每增加一个加1分。</t>
+          <t>已有依据的处理执行按10元基础档；共用工作计一次，必要的逐ASIN执行每增加一个加5元。</t>
         </is>
       </c>
       <c r="I61" s="9" t="n"/>
@@ -3406,7 +3426,7 @@
         <f>'主动改善评价'!C11</f>
         <v/>
       </c>
-      <c r="L61" s="4">
+      <c r="L61" s="16">
         <f>D61*K61</f>
         <v/>
       </c>
@@ -3427,27 +3447,27 @@
           <t>Listing异常处理—独立排查取证</t>
         </is>
       </c>
-      <c r="D62" s="9" t="n">
-        <v>4</v>
+      <c r="D62" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>同站点、同原因、共用证据及方案的一批问题；确需分别处理按去重ASIN附加1分。同ASIN多个SKU只计一个。</t>
+          <t>同站点、同原因、共用证据及方案的一批问题；确需分别处理按去重ASIN附加5元。同ASIN多个SKU只计一个。</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>自行排查原因、核对资料、收集证据并制定方案，完成申诉、跟进及核验。同站点同原因、共用证据方案且可合并处理的一批ASIN共计4分。</t>
+          <t>自行排查原因、核对资料、收集证据并制定方案，完成申诉、跟进及核验。同站点同原因、共用证据方案且可合并处理的一批ASIN共计20元。</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>同因可合并的ASIN按一批计基础档；确需分别处理的额外执行选P025-ADD。同批基础档互斥，升级只补差额；自行拆Case、同ASIN多SKU及反复提交不加分。详见Listing异常合批规则。</t>
+          <t>同因可合并的ASIN按一批计基础档；确需分别处理的额外执行选P025-ADD。同批基础档互斥，升级只补差额；自行拆Case、同ASIN多SKU及反复提交不加价。详见Listing异常合批规则。</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>独立排查取证基础档4分；同原因的排查成果计一次，真实额外执行按每个ASIN加1分。</t>
+          <t>独立排查取证基础档20元；同原因的排查成果计一次，真实额外执行按每个ASIN加5元。</t>
         </is>
       </c>
       <c r="I62" s="9" t="n"/>
@@ -3460,7 +3480,7 @@
         <f>'主动改善评价'!C11</f>
         <v/>
       </c>
-      <c r="L62" s="8">
+      <c r="L62" s="15">
         <f>D62*K62</f>
         <v/>
       </c>
@@ -3481,12 +3501,12 @@
           <t>Listing异常—必要逐ASIN处理附加</t>
         </is>
       </c>
-      <c r="D63" s="9" t="n">
-        <v>1</v>
+      <c r="D63" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>每个额外必要处理的去重ASIN；首个已含在2/4分基础档中。</t>
+          <t>每个额外必要处理的去重ASIN；首个已含在10/20元基础档中。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3501,7 +3521,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>将已确认每额外ASIN加1分明确列行，原公式及合批范围不变。</t>
+          <t>将已确认每额外ASIN加5元明确列行，原公式及合批范围不变。</t>
         </is>
       </c>
       <c r="I63" s="9" t="n"/>
@@ -3514,7 +3534,7 @@
         <f>'主动改善评价'!C11</f>
         <v/>
       </c>
-      <c r="L63" s="4">
+      <c r="L63" s="16">
         <f>D63*K63</f>
         <v/>
       </c>
@@ -3535,8 +3555,8 @@
           <t>二级类目商品维护—标准处理</t>
         </is>
       </c>
-      <c r="D64" s="9" t="n">
-        <v>2</v>
+      <c r="D64" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -3550,7 +3570,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -3568,7 +3588,7 @@
         <f>'主动改善评价'!C14</f>
         <v/>
       </c>
-      <c r="L64" s="8">
+      <c r="L64" s="15">
         <f>D64*K64</f>
         <v/>
       </c>
@@ -3586,11 +3606,11 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>二级类目商品维护—3分档</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="n">
-        <v>3</v>
+          <t>二级类目商品维护—15元档</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
@@ -3604,12 +3624,12 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I65" s="9" t="n"/>
@@ -3622,7 +3642,7 @@
         <f>'主动改善评价'!C14</f>
         <v/>
       </c>
-      <c r="L65" s="4">
+      <c r="L65" s="16">
         <f>D65*K65</f>
         <v/>
       </c>
@@ -3643,8 +3663,8 @@
           <t>二级类目模块新增或重建</t>
         </is>
       </c>
-      <c r="D66" s="9" t="n">
-        <v>5</v>
+      <c r="D66" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -3658,7 +3678,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>常规运营本项最高5分；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计分。</t>
+          <t>常规运营本项最高25元；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计酬。</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -3676,7 +3696,7 @@
         <f>'主动改善评价'!C14</f>
         <v/>
       </c>
-      <c r="L66" s="8">
+      <c r="L66" s="15">
         <f>D66*K66</f>
         <v/>
       </c>
@@ -3697,8 +3717,8 @@
           <t>其他板块原有报错阻断提交—标准处理</t>
         </is>
       </c>
-      <c r="D67" s="9" t="n">
-        <v>3</v>
+      <c r="D67" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
@@ -3712,7 +3732,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3730,7 +3750,7 @@
         <f>'主动改善评价'!C11</f>
         <v/>
       </c>
-      <c r="L67" s="4">
+      <c r="L67" s="16">
         <f>D67*K67</f>
         <v/>
       </c>
@@ -3748,11 +3768,11 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>其他板块原有报错阻断提交—5分档</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="n">
-        <v>5</v>
+          <t>其他板块原有报错阻断提交—25元档</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -3766,12 +3786,12 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I68" s="9" t="n"/>
@@ -3784,7 +3804,7 @@
         <f>'主动改善评价'!C11</f>
         <v/>
       </c>
-      <c r="L68" s="8">
+      <c r="L68" s="15">
         <f>D68*K68</f>
         <v/>
       </c>
@@ -3805,8 +3825,8 @@
           <t>每周VOC数据更新与AI分析—标准处理</t>
         </is>
       </c>
-      <c r="D69" s="9" t="n">
-        <v>2</v>
+      <c r="D69" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
@@ -3820,7 +3840,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3838,7 +3858,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L69" s="4">
+      <c r="L69" s="16">
         <f>D69*K69</f>
         <v/>
       </c>
@@ -3856,11 +3876,11 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>每周VOC数据更新与AI分析—3分档</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="n">
-        <v>3</v>
+          <t>每周VOC数据更新与AI分析—15元档</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -3874,12 +3894,12 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I70" s="9" t="n"/>
@@ -3892,7 +3912,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L70" s="8">
+      <c r="L70" s="15">
         <f>D70*K70</f>
         <v/>
       </c>
@@ -3913,8 +3933,8 @@
           <t>产品质量共性问题整理与反馈—标准处理</t>
         </is>
       </c>
-      <c r="D71" s="9" t="n">
-        <v>4</v>
+      <c r="D71" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
@@ -3928,7 +3948,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3946,7 +3966,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L71" s="4">
+      <c r="L71" s="16">
         <f>D71*K71</f>
         <v/>
       </c>
@@ -3964,11 +3984,11 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>产品质量共性问题整理与反馈—5分档</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>5</v>
+          <t>产品质量共性问题整理与反馈—25元档</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
@@ -3982,12 +4002,12 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I72" s="9" t="n"/>
@@ -4000,7 +4020,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L72" s="8">
+      <c r="L72" s="15">
         <f>D72*K72</f>
         <v/>
       </c>
@@ -4018,11 +4038,11 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>产品质量共性问题整理与反馈—10分档</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="n">
-        <v>10</v>
+          <t>产品质量共性问题整理与反馈—50元档</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
@@ -4036,12 +4056,12 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原10分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原50元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I73" s="9" t="n"/>
@@ -4054,7 +4074,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L73" s="4">
+      <c r="L73" s="16">
         <f>D73*K73</f>
         <v/>
       </c>
@@ -4075,8 +4095,8 @@
           <t>FBA shipment问题处理</t>
         </is>
       </c>
-      <c r="D74" s="9" t="n">
-        <v>1</v>
+      <c r="D74" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -4095,7 +4115,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>按当前职责仅查看并接受或提交常规Appeal，步骤和判断有限，按1分。</t>
+          <t>按当前职责仅查看并接受或提交常规Appeal，步骤和判断有限，按5元。</t>
         </is>
       </c>
       <c r="I74" s="9" t="n"/>
@@ -4108,7 +4128,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L74" s="8">
+      <c r="L74" s="15">
         <f>D74*K74</f>
         <v/>
       </c>
@@ -4129,8 +4149,8 @@
           <t>程序生成的冗余库存折扣上传—标准处理</t>
         </is>
       </c>
-      <c r="D75" s="9" t="n">
-        <v>2</v>
+      <c r="D75" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
@@ -4144,7 +4164,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -4162,7 +4182,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L75" s="4">
+      <c r="L75" s="16">
         <f>D75*K75</f>
         <v/>
       </c>
@@ -4180,11 +4200,11 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>程序生成的冗余库存折扣上传—3分档</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="n">
-        <v>3</v>
+          <t>程序生成的冗余库存折扣上传—15元档</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
@@ -4198,12 +4218,12 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I76" s="9" t="n"/>
@@ -4216,7 +4236,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L76" s="8">
+      <c r="L76" s="15">
         <f>D76*K76</f>
         <v/>
       </c>
@@ -4237,8 +4257,8 @@
           <t>库存移除—标准处理</t>
         </is>
       </c>
-      <c r="D77" s="9" t="n">
-        <v>2</v>
+      <c r="D77" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
@@ -4252,7 +4272,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4270,7 +4290,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L77" s="4">
+      <c r="L77" s="16">
         <f>D77*K77</f>
         <v/>
       </c>
@@ -4288,11 +4308,11 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>库存移除—3分档</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="n">
-        <v>3</v>
+          <t>库存移除—15元档</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
@@ -4306,12 +4326,12 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I78" s="9" t="n"/>
@@ -4324,7 +4344,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L78" s="8">
+      <c r="L78" s="15">
         <f>D78*K78</f>
         <v/>
       </c>
@@ -4345,8 +4365,8 @@
           <t>Relist重新发布—标准处理</t>
         </is>
       </c>
-      <c r="D79" s="9" t="n">
-        <v>2</v>
+      <c r="D79" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
@@ -4360,7 +4380,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4378,7 +4398,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L79" s="4">
+      <c r="L79" s="16">
         <f>D79*K79</f>
         <v/>
       </c>
@@ -4396,11 +4416,11 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Relist重新发布—3分档</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="n">
-        <v>3</v>
+          <t>Relist重新发布—15元档</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
@@ -4414,12 +4434,12 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I80" s="9" t="n"/>
@@ -4432,7 +4452,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L80" s="8">
+      <c r="L80" s="15">
         <f>D80*K80</f>
         <v/>
       </c>
@@ -4453,8 +4473,8 @@
           <t>库存专属问题申诉或Case—标准处理</t>
         </is>
       </c>
-      <c r="D81" s="9" t="n">
-        <v>3</v>
+      <c r="D81" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
@@ -4468,7 +4488,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4486,7 +4506,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L81" s="4">
+      <c r="L81" s="16">
         <f>D81*K81</f>
         <v/>
       </c>
@@ -4504,11 +4524,11 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>库存专属问题申诉或Case—5分档</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="n">
-        <v>5</v>
+          <t>库存专属问题申诉或Case—25元档</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
@@ -4522,12 +4542,12 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I82" s="9" t="n"/>
@@ -4540,7 +4560,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L82" s="8">
+      <c r="L82" s="15">
         <f>D82*K82</f>
         <v/>
       </c>
@@ -4561,8 +4581,8 @@
           <t>已有电池或化学品资料提交—标准处理</t>
         </is>
       </c>
-      <c r="D83" s="9" t="n">
-        <v>2</v>
+      <c r="D83" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
@@ -4576,7 +4596,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -4594,7 +4614,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L83" s="4">
+      <c r="L83" s="16">
         <f>D83*K83</f>
         <v/>
       </c>
@@ -4612,11 +4632,11 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>已有电池或化学品资料提交—3分档</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="n">
-        <v>3</v>
+          <t>已有电池或化学品资料提交—15元档</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
@@ -4630,12 +4650,12 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I84" s="9" t="n"/>
@@ -4648,7 +4668,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L84" s="8">
+      <c r="L84" s="15">
         <f>D84*K84</f>
         <v/>
       </c>
@@ -4669,8 +4689,8 @@
           <t>电池或化学品资料协调与提交</t>
         </is>
       </c>
-      <c r="D85" s="9" t="n">
-        <v>3</v>
+      <c r="D85" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
@@ -4684,12 +4704,12 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>固定3分/独立资料协调及提交任务；包含获取、核对、提交及跟进，不再叠加P037的2分。同批共用协调不按SKU重复计。</t>
+          <t>固定15元/独立资料协调及提交任务；包含获取、核对、提交及跟进，不再叠加P037的10元。同批共用协调不按SKU重复计。</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>较已有资料直接提交增加获取与沟通，固定多1分；等待不加分。</t>
+          <t>较已有资料直接提交增加获取与沟通，固定多5元；等待不加价。</t>
         </is>
       </c>
       <c r="I85" s="9" t="n"/>
@@ -4702,7 +4722,7 @@
         <f>'主动改善评价'!C13</f>
         <v/>
       </c>
-      <c r="L85" s="4">
+      <c r="L85" s="16">
         <f>D85*K85</f>
         <v/>
       </c>
@@ -4723,8 +4743,8 @@
           <t>Category Report下载</t>
         </is>
       </c>
-      <c r="D86" s="9" t="n">
-        <v>1</v>
+      <c r="D86" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
@@ -4743,7 +4763,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>简单重复下载以周计1分；不按每天或重复操作累计。</t>
+          <t>简单重复下载以周计5元；不按每天或重复操作累计。</t>
         </is>
       </c>
       <c r="I86" s="9" t="n"/>
@@ -4756,7 +4776,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L86" s="8">
+      <c r="L86" s="15">
         <f>D86*K86</f>
         <v/>
       </c>
@@ -4777,8 +4797,8 @@
           <t>关键词市场占有率统计及竞品检查—标准处理</t>
         </is>
       </c>
-      <c r="D87" s="9" t="n">
-        <v>4</v>
+      <c r="D87" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
@@ -4792,7 +4812,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -4810,7 +4830,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L87" s="4">
+      <c r="L87" s="16">
         <f>D87*K87</f>
         <v/>
       </c>
@@ -4828,11 +4848,11 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>关键词市场占有率统计及竞品检查—5分档</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="n">
-        <v>5</v>
+          <t>关键词市场占有率统计及竞品检查—25元档</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
@@ -4846,12 +4866,12 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I88" s="9" t="n"/>
@@ -4864,7 +4884,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L88" s="8">
+      <c r="L88" s="15">
         <f>D88*K88</f>
         <v/>
       </c>
@@ -4885,8 +4905,8 @@
           <t>CA/MX/BR等站点Listing上架</t>
         </is>
       </c>
-      <c r="D89" s="9" t="n">
-        <v>5</v>
+      <c r="D89" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
@@ -4900,7 +4920,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>5分/上架执行组，包含本次必要的父子关系组合及上传核验；不另叠加变体维护分。按同一需求、同站点、可共用上架表分组，不按OA条数拆分。</t>
+          <t>25元/上架执行组，包含本次必要的父子关系组合及上传核验；不另叠加变体维护报酬。按同一需求、同站点、可共用上架表分组，不按OA条数拆分。</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4918,7 +4938,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L89" s="4">
+      <c r="L89" s="16">
         <f>D89*K89</f>
         <v/>
       </c>
@@ -4939,8 +4959,8 @@
           <t>已有A+翻译并发布—标准处理</t>
         </is>
       </c>
-      <c r="D90" s="9" t="n">
-        <v>3</v>
+      <c r="D90" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
@@ -4954,7 +4974,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -4972,7 +4992,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L90" s="8">
+      <c r="L90" s="15">
         <f>D90*K90</f>
         <v/>
       </c>
@@ -4990,11 +5010,11 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>已有A+翻译并发布—5分档</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="n">
-        <v>5</v>
+          <t>已有A+翻译并发布—25元档</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -5008,12 +5028,12 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I91" s="9" t="n"/>
@@ -5026,7 +5046,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L91" s="4">
+      <c r="L91" s="16">
         <f>D91*K91</f>
         <v/>
       </c>
@@ -5047,8 +5067,8 @@
           <t>已有文案翻译后批量更新—标准处理</t>
         </is>
       </c>
-      <c r="D92" s="9" t="n">
-        <v>2</v>
+      <c r="D92" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
@@ -5062,7 +5082,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -5080,7 +5100,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L92" s="8">
+      <c r="L92" s="15">
         <f>D92*K92</f>
         <v/>
       </c>
@@ -5098,11 +5118,11 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>已有文案翻译后批量更新—3分档</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="n">
-        <v>3</v>
+          <t>已有文案翻译后批量更新—15元档</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
@@ -5116,12 +5136,12 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I93" s="9" t="n"/>
@@ -5134,7 +5154,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L93" s="4">
+      <c r="L93" s="16">
         <f>D93*K93</f>
         <v/>
       </c>
@@ -5152,11 +5172,11 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>已有文案翻译后批量更新—5分档</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="n">
-        <v>5</v>
+          <t>已有文案翻译后批量更新—25元档</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
@@ -5170,12 +5190,12 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I94" s="9" t="n"/>
@@ -5188,7 +5208,7 @@
         <f>'主动改善评价'!C15</f>
         <v/>
       </c>
-      <c r="L94" s="8">
+      <c r="L94" s="15">
         <f>D94*K94</f>
         <v/>
       </c>
@@ -5209,8 +5229,8 @@
           <t>市场调研与产品建议</t>
         </is>
       </c>
-      <c r="D95" s="9" t="n">
-        <v>10</v>
+      <c r="D95" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
@@ -5224,12 +5244,12 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I95" s="9" t="n"/>
@@ -5242,7 +5262,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L95" s="4">
+      <c r="L95" s="16">
         <f>D95*K95</f>
         <v/>
       </c>
@@ -5263,8 +5283,8 @@
           <t>厂家筛选、报价及合作条件确认</t>
         </is>
       </c>
-      <c r="D96" s="9" t="n">
-        <v>10</v>
+      <c r="D96" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
@@ -5278,12 +5298,12 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I96" s="9" t="n"/>
@@ -5296,7 +5316,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L96" s="8">
+      <c r="L96" s="15">
         <f>D96*K96</f>
         <v/>
       </c>
@@ -5317,8 +5337,8 @@
           <t>样品评估及问题跟进</t>
         </is>
       </c>
-      <c r="D97" s="9" t="n">
-        <v>10</v>
+      <c r="D97" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
@@ -5332,12 +5352,12 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I97" s="9" t="n"/>
@@ -5350,7 +5370,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L97" s="4">
+      <c r="L97" s="16">
         <f>D97*K97</f>
         <v/>
       </c>
@@ -5371,8 +5391,8 @@
           <t>额外产品资料核实与整理</t>
         </is>
       </c>
-      <c r="D98" s="9" t="n">
-        <v>10</v>
+      <c r="D98" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
@@ -5386,12 +5406,12 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I98" s="9" t="n"/>
@@ -5404,7 +5424,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L98" s="8">
+      <c r="L98" s="15">
         <f>D98*K98</f>
         <v/>
       </c>
@@ -5425,8 +5445,8 @@
           <t>产品主辅图策划</t>
         </is>
       </c>
-      <c r="D99" s="9" t="n">
-        <v>10</v>
+      <c r="D99" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
@@ -5440,12 +5460,12 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I99" s="9" t="n"/>
@@ -5458,7 +5478,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L99" s="4">
+      <c r="L99" s="16">
         <f>D99*K99</f>
         <v/>
       </c>
@@ -5479,8 +5499,8 @@
           <t>视频字幕文案编写</t>
         </is>
       </c>
-      <c r="D100" s="9" t="n">
-        <v>10</v>
+      <c r="D100" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
@@ -5494,12 +5514,12 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I100" s="9" t="n"/>
@@ -5512,7 +5532,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L100" s="8">
+      <c r="L100" s="15">
         <f>D100*K100</f>
         <v/>
       </c>
@@ -5533,8 +5553,8 @@
           <t>利润或亏损原因分析与建议</t>
         </is>
       </c>
-      <c r="D101" s="9" t="n">
-        <v>10</v>
+      <c r="D101" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
@@ -5548,12 +5568,12 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I101" s="9" t="n"/>
@@ -5566,7 +5586,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L101" s="4">
+      <c r="L101" s="16">
         <f>D101*K101</f>
         <v/>
       </c>
@@ -5587,8 +5607,8 @@
           <t>活动效果复盘</t>
         </is>
       </c>
-      <c r="D102" s="9" t="n">
-        <v>10</v>
+      <c r="D102" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
@@ -5602,12 +5622,12 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>固定10分，按本行计量单位及完整交付验收，不分8/10/15等难度档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增分。</t>
+          <t>固定50元，按本行计量单位及完整交付验收，不另设难度金额档。系列或多商品共用成果只计一次；尚未完成不自动按完整阶段结算，补做返工不新增报酬。</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>按用户确认，新品开发与经营分析P044—P051每项统一10分；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
+          <t>按用户确认，新品开发与经营分析P044—P051每项统一50元；各项须有独立实际交付，不能重复包装同一成果。技术研发另见'研发考核规则'页。</t>
         </is>
       </c>
       <c r="I102" s="9" t="n"/>
@@ -5620,7 +5640,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L102" s="8">
+      <c r="L102" s="15">
         <f>D102*K102</f>
         <v/>
       </c>
@@ -5641,8 +5661,8 @@
           <t>费用核查与Case申诉</t>
         </is>
       </c>
-      <c r="D103" s="9" t="n">
-        <v>5</v>
+      <c r="D103" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
@@ -5656,7 +5676,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>常规运营本项最高5分；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计分。</t>
+          <t>常规运营本项最高25元；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计酬。</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -5674,7 +5694,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L103" s="4">
+      <c r="L103" s="16">
         <f>D103*K103</f>
         <v/>
       </c>
@@ -5695,8 +5715,8 @@
           <t>跟卖情况检查（是否保留待确认）</t>
         </is>
       </c>
-      <c r="D104" s="9" t="n">
-        <v>1</v>
+      <c r="D104" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
@@ -5710,12 +5730,12 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>不按发现数量加分；独立案件处理另按实际交付，无人工工作的自动监控不计人工分。</t>
+          <t>不按发现数量加价；独立案件处理另按实际交付，无人工工作的自动监控不计人工报酬。</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>小范围固定清单的简单人工例行检查，按周1分；是否启用仍待确认。</t>
+          <t>小范围固定清单的简单人工例行检查，按周5元；是否启用仍待确认。</t>
         </is>
       </c>
       <c r="I104" s="9" t="n"/>
@@ -5728,7 +5748,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L104" s="8">
+      <c r="L104" s="15">
         <f>D104*K104</f>
         <v/>
       </c>
@@ -5749,8 +5769,8 @@
           <t>跟卖相关Brand Registry或Case处理</t>
         </is>
       </c>
-      <c r="D105" s="9" t="n">
-        <v>5</v>
+      <c r="D105" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
@@ -5764,7 +5784,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>常规运营本项最高5分；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计分。</t>
+          <t>常规运营本项最高25元；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计酬。</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5782,7 +5802,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L105" s="4">
+      <c r="L105" s="16">
         <f>D105*K105</f>
         <v/>
       </c>
@@ -5803,8 +5823,8 @@
           <t>Vine报名及约定跟进—标准处理</t>
         </is>
       </c>
-      <c r="D106" s="9" t="n">
-        <v>3</v>
+      <c r="D106" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
@@ -5818,7 +5838,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -5836,7 +5856,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L106" s="8">
+      <c r="L106" s="15">
         <f>D106*K106</f>
         <v/>
       </c>
@@ -5854,11 +5874,11 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Vine报名及约定跟进—5分档</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="n">
-        <v>5</v>
+          <t>Vine报名及约定跟进—25元档</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
@@ -5872,12 +5892,12 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>原升降档条件独立列行，沿用原25元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I107" s="9" t="n"/>
@@ -5890,7 +5910,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L107" s="4">
+      <c r="L107" s="16">
         <f>D107*K107</f>
         <v/>
       </c>
@@ -5911,8 +5931,8 @@
           <t>Brand Story全新制作或整体重做</t>
         </is>
       </c>
-      <c r="D108" s="9" t="n">
-        <v>5</v>
+      <c r="D108" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
@@ -5926,12 +5946,12 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>本行为全新或整体重做；沿用已有方案适配选择P056-template，同份同轮不叠加，两种场景沿用同一分值。</t>
+          <t>全新或整体重做25元、模板适配15元、局改10元。同份同轮只选一档；制作含本次约定首次绑定。整体重做保留旧版本及新旧内容记录。</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>品牌故事整体策划与发布属于运营内容制作，完整交付最高5分。</t>
+          <t>品牌故事整体策划与发布属于运营内容制作，完整交付最高25元。</t>
         </is>
       </c>
       <c r="I108" s="9" t="n"/>
@@ -5944,7 +5964,7 @@
         <f>'主动改善评价'!C8</f>
         <v/>
       </c>
-      <c r="L108" s="8">
+      <c r="L108" s="15">
         <f>D108*K108</f>
         <v/>
       </c>
@@ -5965,8 +5985,8 @@
           <t>Brand Story复用现成方案适配</t>
         </is>
       </c>
-      <c r="D109" s="9" t="n">
-        <v>3</v>
+      <c r="D109" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
@@ -5980,12 +6000,12 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>同份同轮与全新制作或局部修改互斥；不另叠加原方案策划分。</t>
+          <t>模板适配15元/份，低于独立全新制作25元；同份同轮与全新、局改互斥，制作含本次约定首次绑定。</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>原规则已有的复用适配场景独立列行，本次只改展示结构，沿用5分。</t>
+          <t>原规则已有的复用适配场景独立列行，本次只改展示结构，沿用25元。</t>
         </is>
       </c>
       <c r="I109" s="9" t="n"/>
@@ -5998,7 +6018,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L109" s="4">
+      <c r="L109" s="16">
         <f>D109*K109</f>
         <v/>
       </c>
@@ -6016,11 +6036,11 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Brand Story局部修改—标准处理</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="n">
-        <v>3</v>
+          <t>Brand Story局部修改</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
@@ -6029,17 +6049,17 @@
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>一份已有品牌故事的局部内容修改及核验。</t>
+          <t>在原有品牌故事上增删信息、替换参数、少量图片或链接，保存前后记录并核验。</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>固定10元/份/轮；不按修改次数累加，不设局改高档。确需模板适配或整体重做时转对应档，只补同轮已付差额。</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>局部修改的工作量低于整体策划制作。</t>
+          <t>与A+局部修改采用相同金额。</t>
         </is>
       </c>
       <c r="I110" s="9" t="n"/>
@@ -6052,7 +6072,7 @@
         <f>'主动改善评价'!C12</f>
         <v/>
       </c>
-      <c r="L110" s="8">
+      <c r="L110" s="15">
         <f>D110*K110</f>
         <v/>
       </c>
@@ -6060,7 +6080,7 @@
     <row r="111" ht="85" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>P056-edit-T5</t>
+          <t>P056-bind</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -6070,43 +6090,43 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Brand Story局部修改—5分档</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="n">
+          <t>已有Brand Story新增绑定</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>一份内容的一轮修改</t>
+          <t>一个新增ASIN</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>在完成该项目基本交付的基础上：需独立构思新增信息并协调素材；完整重做转整体制作，事实纠错转纠错。</t>
+          <t>给一个原范围外新增ASIN绑定现有品牌故事并核验。</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>无自动升档；原范围补绑重绑属于原任务。</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原5分标准；不是新增累计任务。</t>
+          <t>适用关系已明确，执行简单绑定和核验；不包含内容制作，按5元档。</t>
         </is>
       </c>
       <c r="I111" s="9" t="n"/>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Listing事实纠错及局部维护</t>
+          <t>未明确列入的项目</t>
         </is>
       </c>
       <c r="K111" s="4">
-        <f>'主动改善评价'!C12</f>
-        <v/>
-      </c>
-      <c r="L111" s="4">
+        <f>'主动改善评价'!C16</f>
+        <v/>
+      </c>
+      <c r="L111" s="16">
         <f>D111*K111</f>
         <v/>
       </c>
@@ -6114,40 +6134,40 @@
     <row r="112" ht="85" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>P056-bind</t>
+          <t>P057</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>品牌内容</t>
+          <t>订阅销售</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>已有Brand Story新增绑定</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="n">
-        <v>1</v>
+          <t>Subscribe &amp; Save设置与维护—标准处理</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>一个新增ASIN</t>
+          <t>同站点、同一订阅方案的一批设置。</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>给一个原范围外新增ASIN绑定现有品牌故事并核验。</t>
+          <t>按确认方案完成同站点一批订阅商品或折扣设置与核验。</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>无自动升档；原范围补绑重绑属于原任务。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>适用关系已明确，执行简单绑定和核验；不包含内容制作，按1分档。</t>
+          <t>主要为既定方案执行。</t>
         </is>
       </c>
       <c r="I112" s="9" t="n"/>
@@ -6160,7 +6180,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L112" s="8">
+      <c r="L112" s="15">
         <f>D112*K112</f>
         <v/>
       </c>
@@ -6168,7 +6188,7 @@
     <row r="113" ht="85" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>P057</t>
+          <t>P057-T3</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -6178,11 +6198,11 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Subscribe &amp; Save设置与维护—标准处理</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="n">
-        <v>2</v>
+          <t>Subscribe &amp; Save设置与维护—15元档</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
@@ -6191,17 +6211,17 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>按确认方案完成同站点一批订阅商品或折扣设置与核验。</t>
+          <t>在完成该项目基本交付的基础上：需逐项核对资格差异或解决设置对应问题；独立订阅策略分析另定范围。</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>主要为既定方案执行。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I113" s="9" t="n"/>
@@ -6214,7 +6234,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L113" s="4">
+      <c r="L113" s="16">
         <f>D113*K113</f>
         <v/>
       </c>
@@ -6222,40 +6242,40 @@
     <row r="114" ht="85" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>P057-T3</t>
+          <t>P058-new</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>订阅销售</t>
+          <t>组合销售</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Subscribe &amp; Save设置与维护—3分档</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="n">
-        <v>3</v>
+          <t>Virtual Bundle创建</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>同站点、同一订阅方案的一批设置。</t>
+          <t>一个独立组合的新建或一轮维护</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>在完成该项目基本交付的基础上：需逐项核对资格差异或解决设置对应问题；独立订阅策略分析另定范围。</t>
+          <t>组合方案与素材已提供，完成一个Virtual Bundle创建和核验。</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>常规运营本项最高25元；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计酬。</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
+          <t>包含组合及多项商品资料核对，工作量接近标准Listing创建。</t>
         </is>
       </c>
       <c r="I114" s="9" t="n"/>
@@ -6268,7 +6288,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L114" s="8">
+      <c r="L114" s="15">
         <f>D114*K114</f>
         <v/>
       </c>
@@ -6276,7 +6296,7 @@
     <row r="115" ht="85" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>P058-new</t>
+          <t>P058-edit</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -6286,11 +6306,11 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Virtual Bundle创建</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="n">
-        <v>5</v>
+          <t>Virtual Bundle维护—标准处理</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
@@ -6299,17 +6319,17 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>组合方案与素材已提供，完成一个Virtual Bundle创建和核验。</t>
+          <t>按明确要求维护一个已有虚拟组合的可编辑内容及核验。</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>常规运营本项最高5分；复杂情况仍须完成约定核查及交付，不因SKU数、操作次数或等待增加档位。需要独立数据分析时先明确新交付，同一分析及执行成果不重复计分。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>包含组合及多项商品资料核对，工作量接近标准Listing创建。</t>
+          <t>标准局部维护，复杂度低于新建。</t>
         </is>
       </c>
       <c r="I115" s="9" t="n"/>
@@ -6322,7 +6342,7 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L115" s="4">
+      <c r="L115" s="16">
         <f>D115*K115</f>
         <v/>
       </c>
@@ -6330,7 +6350,7 @@
     <row r="116" ht="85" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>P058-edit</t>
+          <t>P058-edit-T3</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
@@ -6340,11 +6360,11 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Virtual Bundle维护—标准处理</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="n">
-        <v>2</v>
+          <t>Virtual Bundle维护—15元档</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
@@ -6353,17 +6373,17 @@
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>按明确要求维护一个已有虚拟组合的可编辑内容及核验。</t>
+          <t>在完成该项目基本交付的基础上：需核实并解决多个对应关系或资料差异；重新设计组合需另确认实际新范围。</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
+          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高金额。其他包含及排除范围沿用工作内容。</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>标准局部维护，复杂度低于新建。</t>
+          <t>原升降档条件独立列行，沿用原15元标准；不是新增累计任务。</t>
         </is>
       </c>
       <c r="I116" s="9" t="n"/>
@@ -6376,62 +6396,8 @@
         <f>'主动改善评价'!C16</f>
         <v/>
       </c>
-      <c r="L116" s="8">
+      <c r="L116" s="15">
         <f>D116*K116</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="85" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>P058-edit-T3</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>组合销售</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Virtual Bundle维护—3分档</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>一个独立组合的新建或一轮维护</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>在完成该项目基本交付的基础上：需核实并解决多个对应关系或资料差异；重新设计组合需另确认实际新范围。</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>同一任务同一轮只选择一个适用档；不得把低档和高档相加。实际发生对应条件并完成交付才可选档；等待、反复提交和本人返工不提高分值。其他包含及排除范围沿用工作内容。</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>原升降档条件独立列行，沿用原3分标准；不是新增累计任务。</t>
-        </is>
-      </c>
-      <c r="I117" s="9" t="n"/>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>未明确列入的项目</t>
-        </is>
-      </c>
-      <c r="K117" s="4">
-        <f>'主动改善评价'!C16</f>
-        <v/>
-      </c>
-      <c r="L117" s="4">
-        <f>D117*K117</f>
         <v/>
       </c>
     </row>
@@ -6466,7 +6432,7 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>现金奖励保留原明确改善100元、持续改善累计300元，重大贡献另定，不把元与积分混用。</t>
+          <t>成果现金奖保持明确改善100元、持续改善累计300元，重大贡献另定；这些原有现金金额不乘5。</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6446,7 @@
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>广告同一效果高档积分与现金成果奖互斥；研发产品的独立运营改善可奖励。</t>
+          <t>广告同一效果高档金额与现金成果奖互斥；研发产品的独立运营改善可奖励。</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6565,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>同成果只取最高核定现金总额，跨月累计补差，不乘难度、主动倍率或积分单价。研发提成与独立运营贡献可并存，不按产品一刀切。</t>
+          <t>同成果只取最高核定现金总额，跨月累计补差，不乘主动倍率。研发提成与独立运营贡献可并存。</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -6725,7 +6691,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>先检查是否已按同一效果领取广告8/10/15分；已领取不重复核现金奖。不同独立成果须另行认定，不换编号重复领取。</t>
+          <t>先检查同一效果是否已按广告优化40/50/75元档结算，已结算不重复领现金成果奖。若之前已领现金成果奖，同一效果不再补领广告成果档；实际独立执行报酬可按对应低档验收。新独立成果另认定。</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6748,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>当月任务积分乘已确认适用单价，再加当月已核定未付现金成果奖；研发销售提成按项目约定周期另结。未确认单价时不输出应付金额。</t>
+          <t>本月核定未付任务报酬（包含研发研究报酬）＋本月核定未付突破/投产奖金＋本月核定未付现金成果奖；各项只汇总一次，销售提成按约定周期另结。</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
@@ -6830,7 +6796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B15"/>
+  <dimension ref="A2:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6847,7 +6813,7 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>用积分替换原1SKU/10SKU金额示例，避免旧75元阶段单价重新参与计算。</t>
+          <t>系列共用成果只付一次；每项金额以任务报酬表为准。</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6834,7 @@
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>责任纠错和原范围补做不新增积分。</t>
+          <t>责任纠错和原范围补做不新增金额。</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6846,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>计分方式</t>
+          <t>计酬方式</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6858,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>同系列共用调研、找厂、验证或内容方案只计一次；真实独立交付才分别登记，不能按10个SKU乘全套开发分。</t>
+          <t>同系列共用调研、找厂、验证或内容方案只计一次；真实独立交付才分别登记，不能按10个SKU乘全套开发报酬。</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6870,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>P044—P051每项10分，按实际发生且验收的独立阶段/成果计算。利润分析和活动复盘不是每个新品默认必做的开发收费。</t>
+          <t>P044—P051每项50元，按实际发生且验收的独立阶段/成果计算。利润分析和活动复盘不是每个新品默认必做的开发收费。</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6882,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>同站点同一业务需求、可共用上架表的一组5分，含本次必要关系和既有资料改写；不按OA条数重复计。</t>
+          <t>同站点同一业务需求、可共用上架表的一组25元，含本次必要关系和既有资料改写；不按OA条数重复计。</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6894,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>每SKU按实际已有图/需协调取图等对应档；共用协调不得逐SKU重复计完整协调。</t>
+          <t>已有图片上传10元/SKU；本批需要共用取图协调时，普通协调另加5元、复杂协调另加10元，两档只选一档。多个SKU共用协调只加一次，和样品拍摄协调已付的相同工作不重叠。</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6906,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>同份全新5分、模板3分、局改2分、后续新增绑定1分/SKU；制作含本次首次绑定。完全重做保留旧A+另建新ID。</t>
+          <t>同份全新25元、模板15元、局改10元、后续新增绑定5元/SKU；制作含本次首次绑定。完全重做保留旧A+另建新ID。</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6918,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>按研发立项总分、阶段节点及独立突破验收；共用技术不因型号尺寸衍生重复领取整份研发/投产分。</t>
+          <t>按研发立项总报酬、阶段节点及独立突破验收；共用技术不因型号尺寸衍生重复领取整份研发/投产分。</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6930,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>相同产品资料或图稿若已在研发验收付分，后续直接复用不重领；实际新增运营执行仍可独立计。</t>
+          <t>相同产品资料或图稿若已在研发验收付酬，后续直接复用不重领；实际新增运营执行仍可独立计。</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6942,19 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>项目ID、SKU及参数差异、共用成果ID、独立工作依据、责任人及分配、验收、已结算积分；跨月保持原关联。</t>
+          <t>项目ID、SKU及参数差异、共用成果ID、独立工作依据、责任人及分配、验收、已结算金额；跨月保持原关联。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="85" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>多人合作分配</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>同一交付由多人共同完成，先核定该交付的总金额，再按已确认贡献分配，份额合计100%。不同人员分别完成不同独立交付，例如甲策划、乙上架，则各按对应项目计酬；不要求所有协作一律合成一项。</t>
         </is>
       </c>
     </row>
@@ -6991,15 +6969,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G18"/>
+  <dimension ref="A2:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="85" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -7013,7 +6991,7 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>统一为积分示例，不恢复旧单价；研发50/100仅演示立项确认后的计算。</t>
+          <t>全部示例直接显示人民币元；主动倍率已经包含在总金额中，不另加一份普通任务报酬。</t>
         </is>
       </c>
     </row>
@@ -7027,14 +7005,14 @@
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>销售提成比例、成本口径、期限未确认前，不输出实际应付提成。</t>
+          <t>销售提成仍需确认项目比例、成本口径、期限及个人份额，未确认不作为实发。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>三项研发示例合计300分，不是300元；金额按已确认的积分单价另算。</t>
+          <t>研发示例：两项研究共500元＋突破500元＋投产500元＝1500元，分阶段验收后支付。</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7029,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>单位积分</t>
+          <t>单位金额（元）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>数量/份额</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -7066,7 +7044,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>总积分</t>
+          <t>总金额（元）</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -7087,7 +7065,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>1</v>
@@ -7117,7 +7095,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>5</v>
@@ -7131,7 +7109,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>5×2，共10分。</t>
+          <t>5个SKU×10元＝50元，无额外取图协调。</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7125,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>1</v>
@@ -7161,7 +7139,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>仅模板适配，不能算全新5分。</t>
+          <t>仅模板适配，不能算全新25元。</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7155,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>1</v>
@@ -7207,7 +7185,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>1</v>
@@ -7221,7 +7199,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>可共同处理只计一批4分。</t>
+          <t>可共同处理只计一批20元。</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7215,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1</v>
@@ -7251,7 +7229,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>独立排查4＋额外4个ASIN各1＝8分。</t>
+          <t>独立排查20元＋额外4个ASIN各5元＝40元。</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7245,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>1</v>
@@ -7281,7 +7259,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>同批总分8×1.5＝12分。</t>
+          <t>同批40元×主动倍率1.5＝60元。</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7275,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1</v>
@@ -7311,7 +7289,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>已结算5分则只补5分；此列为同轮总额。</t>
+          <t>已结算25元则只补25元；此列为同轮总额。</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7305,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -7341,7 +7319,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>仅演示两项已批准50分研究任务；阶段节点累计不重复。</t>
+          <t>仅演示两项已批准250元研究任务；阶段节点累计不重复。</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7335,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>1</v>
@@ -7371,7 +7349,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>示例已按立项确认100分，并通过验证。</t>
+          <t>示例已按立项确认500元，并通过验证。</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7365,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>1</v>
@@ -7401,7 +7379,217 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>示例已确认100分，首批验收通过。</t>
+          <t>示例已确认500元，首批验收通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="85" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>5个SKU共用一次普通取图</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>P002-b</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
+        <f>C19*D19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>上传5×10元＋共用取图5元＝55元。不是5×15元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="85" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>5个SKU共用一次复杂取图</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>P002-b-T4</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8">
+        <f>C20*D20*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>上传5×10元＋共用协调10元＝60元。不是5×20元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="85" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>两人合作研究：甲</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>RD01</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
+        <f>C21*D21*E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>示例甲60%得150元，乙40%得100元；同一任务总额仍为250元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="85" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>两人合作研究：乙</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>RD01</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8">
+        <f>C22*D22*E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>示例比例须按实际分工确认，不是固定按人数均分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="85" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Brand Story局改</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>P056-edit</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <f>C23*D23*E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>同份同轮局部修改合并。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Brand Story模板制作</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>P056-template</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8">
+        <f>C24*D24*E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>复用现成方案，主动默认×1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="85" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Brand Story主动全新制作</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>P056-new</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4">
+        <f>C25*D25*E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>满足主动分析、实质制作及复盘条件，总报酬50元。</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7630,7 @@
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>员工先提出建议、经批准后执行仍属主动；负责人已安排的工作不是自主发起。本人责任纠错、漏做补做不新增积分。</t>
+          <t>员工先提出建议、经批准后执行仍属主动；负责人已安排的工作不是自主发起。本人责任纠错、漏做补做不新增金额。</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7644,7 @@
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>同一交付只结算一次乘倍率后的积分；广告方案内创建与调整按专项互斥。</t>
+          <t>同一交付只结算一次乘倍率后的金额；广告方案内创建与调整按专项互斥。</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7678,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>标题编写与优化、五点编写与优化、描述编写与优化、Generic Keywords编写与优化、全新制作或完全重做A+</t>
+          <t>标题编写与优化、五点编写与优化、描述编写与优化、Generic Keywords编写与优化、全新制作或完全重做A+、Brand Story全新制作或整体重做</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -7518,7 +7706,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>仅独立创建任务：主动提出投放机会，说明产品、方向和测试目标，完成创建和复盘。若新建包含于一个优化方案，改按广告优化×1整轮计，不叠加创建分；已付创建分从同案最终积分中扣除，不重复结算。</t>
+          <t>仅独立创建任务：主动提出投放机会，说明产品、方向和测试目标，完成创建和复盘。若新建包含于一个优化方案，改按广告优化×1整轮计，不叠加创建报酬；已付创建报酬从同案最终金额中扣除，不重复结算。</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7718,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>广告执行及分析优化六档：2、3、5、8、10、15分</t>
+          <t>广告执行及分析优化六档：10、15、25、40、50、75元</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -7538,7 +7726,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>受派、主动均固定×1。同Campaign同轮最高15分，升级只补差额；每自然周最多2次有效调整，跨人员、来源合并。同一成果不跨周重领，不重复领取同效果成果奖金。详见广告优化规则。</t>
+          <t>受派、主动均固定×1。同Campaign同轮最高75元，升级只补差额；每自然周最多2次有效调整，跨人员、来源合并。同一成果不跨周重领，不重复领取同效果成果奖金。详见广告优化规则。</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7758,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Listing纠错、A+内容增删修改、图片维护、视频上传与信息维护、变体关系维护</t>
+          <t>Listing纠错、A+内容增删修改、图片维护、视频上传与信息维护、变体关系维护、Brand Story局部修改</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
@@ -7698,7 +7886,7 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>原工作内容作为范围说明保留；计分档位、单位及互斥条件统一以任务评分为准。</t>
+          <t>工作内容用于界定范围；直接金额、单位及互斥规则以任务报酬为准。</t>
         </is>
       </c>
     </row>
@@ -7712,14 +7900,14 @@
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>P011-b现为完整A+策划制作5分，不再把旧内容说明中的策划与制作两阶段累计收费。</t>
+          <t>P011-b现为完整A+策划制作25元，不再把旧内容说明中的策划与制作两阶段累计收费。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>原项目编号供关联使用；实际工作在任务评分中已进一步拆为独立档位。</t>
+          <t>原项目编号供关联使用；实际工作在任务报酬中已进一步拆为独立档位。</t>
         </is>
       </c>
     </row>
@@ -7816,8 +8004,8 @@
           <t>区分无变体、处理一个父体、处理多个父体。已有文案改写属于本项；独立研究卖点和原创内容另看实际交付，不能重复算。</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
     </row>
     <row r="9" ht="85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -7860,8 +8048,8 @@
           <t>每个SKU使用自己的图片；上传失败重试和原范围漏图补传包含在本次任务中。</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
     </row>
     <row r="10" ht="85" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -7904,8 +8092,8 @@
           <t>主要增加资料确认和沟通工作；等待时间单独记录。需要安排样品拍摄时，转相应协调任务。</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
     </row>
     <row r="11" ht="85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -7948,8 +8136,8 @@
           <t>系统审核、专人采购、美工拍摄；本人不承担实际采购、拍照或修图。多SKU共用一次安排需标明。</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
     </row>
     <row r="12" ht="85" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -7992,8 +8180,8 @@
           <t>新制作A+原本应绑定的商品、漏绑补绑、解绑重绑包含在原任务中，不另立新增工作。</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
     </row>
     <row r="13" ht="85" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -8036,8 +8224,8 @@
           <t>不包含重拍或剪辑；上传新视频时首次标题填写已含在上传中。</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
     </row>
     <row r="14" ht="85" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -8080,8 +8268,8 @@
           <t>包含本次范围内的首次绑定；不含拍摄、剪辑、字幕原创。重复上传同一文件不算新交付。</t>
         </is>
       </c>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
     </row>
     <row r="15" ht="85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -8124,8 +8312,8 @@
           <t>同一ASIN对应多个SKU只作关联；原视频任务已要求绑定的商品不属于新增范围。</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
     </row>
     <row r="16" ht="85" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -8168,8 +8356,8 @@
           <t>本人原先操作或应核验疏漏造成的返工不另计。负责人后续变更参数需保留新旧版本。</t>
         </is>
       </c>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
     </row>
     <row r="17" ht="85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -8212,8 +8400,8 @@
           <t>不按模块数或关联SKU数计内容份数。重新设计、重拍或原创改写需另界定，混合字段纠错不能重复算基础工作。</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
     </row>
     <row r="18" ht="85" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -8256,8 +8444,8 @@
           <t>区分首次原创、实质优化、已有文字翻译、简单纠错。上传任务已包含的AI改写不能再算同一工作。</t>
         </is>
       </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
     </row>
     <row r="19" ht="85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -8300,8 +8488,8 @@
           <t>改一点或多点均需说明实际工作；仅粘贴负责人给定内容不等于独立策划。</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
     </row>
     <row r="20" ht="85" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -8344,8 +8532,8 @@
           <t>与直接翻译、指定内容更新、事实纠错分开；相同系列共用的内容需说明。</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
     </row>
     <row r="21" ht="85" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -8388,8 +8576,8 @@
           <t>AI可辅助，但员工要判断相关性。仅执行负责人给定的关键词清单属于执行工作。</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
     </row>
     <row r="22" ht="85" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -8432,8 +8620,8 @@
           <t>复用通用品牌模块不代表重新策划；需要说明哪些产品内容确实重新构思。主辅图策划与A+策划有重合时不能重复算。</t>
         </is>
       </c>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
     </row>
     <row r="23" ht="85" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -8476,8 +8664,8 @@
           <t>只替换少量参数或图片可属于局部修改；原方案直接复用不再算一次整体策划。初始绑定及报错修正包含在本项。</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
     </row>
     <row r="24" ht="85" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -8520,8 +8708,8 @@
           <t>不按模块数量累加；事实纠错走纠错工作。确需整体重做时重新确认范围，不能同时算局部修改和整体制作。</t>
         </is>
       </c>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
     </row>
     <row r="25" ht="85" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -8564,8 +8752,8 @@
           <t>仅改名称和数值；若需要解绑或重建关系，说明实际升级的工作范围。</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
     </row>
     <row r="26" ht="85" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -8608,8 +8796,8 @@
           <t>区分方案已明确与需要排查冲突。新品上架已经包含的加入关系不再重复列项。</t>
         </is>
       </c>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
     </row>
     <row r="27" ht="85" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -8652,8 +8840,8 @@
           <t>重点记录是否需要自己排查、多父体迁移或Case跟进。同一关系问题的连续尝试属于一个方案。</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
     </row>
     <row r="28" ht="85" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -8696,8 +8884,8 @@
           <t>原任务漏传或本人传错属于返工；事实错误的修正归纠错。</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
     </row>
     <row r="29" ht="85" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -8740,8 +8928,8 @@
           <t>等待天数不等于工作量；新安排样品及拍摄的独立工作另列，避免重复计算协调部分。</t>
         </is>
       </c>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
     </row>
     <row r="30" ht="85" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
@@ -8784,8 +8972,8 @@
           <t>不要求员工自行制定价格策略；不同目标价格、拆文件或重试不自然形成新任务。</t>
         </is>
       </c>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
     </row>
     <row r="31" ht="85" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -8828,8 +9016,8 @@
           <t>同ASIN多个SKU不重复；多次Case或反复回复仍属同一问题。只是执行给定价格的调整需与独立异常调查区分。</t>
         </is>
       </c>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
     </row>
     <row r="32" ht="85" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -8872,8 +9060,8 @@
           <t>多个商品共用一个活动不按SKU拆分；要求外另做活动方案分析时说明独立交付。</t>
         </is>
       </c>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
     </row>
     <row r="33" ht="85" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -8916,8 +9104,8 @@
           <t>平台未批准不等于员工没完成提报；本次提报中的反复修正不另算新任务。</t>
         </is>
       </c>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
     </row>
     <row r="34" ht="85" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -8960,8 +9148,8 @@
           <t>标明投放方案已给定还是员工需要分析；初始配置和一般报错属于创建范围，不按广告组或目标数量拆任务。</t>
         </is>
       </c>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
     </row>
     <row r="35" ht="85" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -9004,8 +9192,8 @@
           <t>素材已提供与需独立策划素材应区分；普通素材配置及审核修正包含在创建中。</t>
         </is>
       </c>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
     </row>
     <row r="36" ht="85" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
@@ -9048,8 +9236,8 @@
           <t>不同时归入SB和SBV重复算；视频拍摄、剪辑、原创字幕另看是否有独立交付。</t>
         </is>
       </c>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
     </row>
     <row r="37" ht="85" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -9092,8 +9280,8 @@
           <t>标明是否需额外判断受众和素材；创建中的初始配置只包含一次。</t>
         </is>
       </c>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
     </row>
     <row r="38" ht="85" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
@@ -9136,8 +9324,8 @@
           <t>一次包含多种动作合并；区分照方案执行和自行分析。再次调整需有新依据，保留每Campaign每周最多两次的原规则待整体复核。</t>
         </is>
       </c>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
     </row>
     <row r="39" ht="85" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -9180,8 +9368,8 @@
           <t>区分Listing自身问题与变体、Buy Box、库存专属问题；同一原因反复Case不成为新任务。</t>
         </is>
       </c>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
     </row>
     <row r="40" ht="85" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
@@ -9224,8 +9412,8 @@
           <t>例如某阀门尺寸类目；不按SKU数拆分。必须新增或重建模块时转对应场景。</t>
         </is>
       </c>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
     </row>
     <row r="41" ht="85" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -9268,8 +9456,8 @@
           <t>包含本次模块中的商品增删；不能再重复算同一类目的普通商品维护。</t>
         </is>
       </c>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
     </row>
     <row r="42" ht="85" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
@@ -9312,8 +9500,8 @@
           <t>本人本次改动造成的错误是返工；同一次提交多个报错不逐条拆分。</t>
         </is>
       </c>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
     </row>
     <row r="43" ht="85" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -9356,8 +9544,8 @@
           <t>运行AI不等于独立分析报告；另行核实问题、提出建议时需说明新增交付。</t>
         </is>
       </c>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
     </row>
     <row r="44" ht="85" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
@@ -9400,8 +9588,8 @@
           <t>不是转发单条消息；与VOC分析或开发验证中已包含的同一反馈不重复算。是否由运营承担请确认。</t>
         </is>
       </c>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
     </row>
     <row r="45" ht="85" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -9444,8 +9632,8 @@
           <t>以简单查看及后台操作为主；如需另行调查收费、遗失或复杂证据，描述新增范围再判断。</t>
         </is>
       </c>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
     </row>
     <row r="46" ht="85" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
@@ -9488,8 +9676,8 @@
           <t>不包含自己分析冗余原因和制定折扣；不按SKU、文件数或重试次数增加任务。</t>
         </is>
       </c>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
     </row>
     <row r="47" ht="85" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -9532,8 +9720,8 @@
           <t>订单执行等待单独记录；同一问题已包含在其他库存处置任务中时不重复。</t>
         </is>
       </c>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
     </row>
     <row r="48" ht="85" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
@@ -9576,8 +9764,8 @@
           <t>同一问题Relist无效再转申诉属于连续处理，不把尝试分别算成完整任务。</t>
         </is>
       </c>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="9" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
     </row>
     <row r="49" ht="85" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -9620,8 +9808,8 @@
           <t>Listing本身异常造成滞留且由同一修复解决时归Listing异常；不重复算同一Case成果。</t>
         </is>
       </c>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
     </row>
     <row r="50" ht="85" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
@@ -9664,8 +9852,8 @@
           <t>员工不负责凭空补造产品资料；资料尚在审核时记录进度，不把等待算新工作。</t>
         </is>
       </c>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
     </row>
     <row r="51" ht="85" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -9708,8 +9896,8 @@
           <t>包含提交工作，不再重复列“已有资料提交”；等待时间与实际沟通时间分开记录。</t>
         </is>
       </c>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
     </row>
     <row r="52" ht="85" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
@@ -9752,8 +9940,8 @@
           <t>同一天重复下载不增加任务；全自动且无需人工核验的部分不作为人工工作量。</t>
         </is>
       </c>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
     </row>
     <row r="53" ht="85" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -9796,8 +9984,8 @@
           <t>每个关键词需单独处理；必须写清占有率分母和范围，不能把搜索结果样本直接当作全市场销售份额。</t>
         </is>
       </c>
-      <c r="I53" s="9" t="n"/>
-      <c r="J53" s="9" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
     </row>
     <row r="54" ht="85" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
@@ -9840,8 +10028,8 @@
           <t>与美国站同样区分无变体、一个父体、多个父体；本次上架包含的翻译不能再重复单列。</t>
         </is>
       </c>
-      <c r="I54" s="9" t="n"/>
-      <c r="J54" s="9" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
     </row>
     <row r="55" ht="85" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -9884,8 +10072,8 @@
           <t>区分语言转换与独立新策划；同批首次发布绑定已包含，共用内容不按SKU增加份数。</t>
         </is>
       </c>
-      <c r="I55" s="9" t="n"/>
-      <c r="J55" s="9" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
     </row>
     <row r="56" ht="85" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
@@ -9928,8 +10116,8 @@
           <t>标明程序可完成与需逐条手动处理的数量；不属于独立原创文案，也不重复算上架中已含的翻译。</t>
         </is>
       </c>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
     </row>
     <row r="57" ht="85" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -9972,8 +10160,8 @@
           <t>参数略不同、共用研究的系列不按SKU重复。完整调研后建议不开发也属于有效交付；未完成阶段需写明。</t>
         </is>
       </c>
-      <c r="I57" s="9" t="n"/>
-      <c r="J57" s="9" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
     </row>
     <row r="58" ht="85" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
@@ -10016,8 +10204,8 @@
           <t>不按联系次数或报价张数计工作；现成厂家简单询价与从零寻找需要区分。无合适厂家时交付调查结论。</t>
         </is>
       </c>
-      <c r="I58" s="9" t="n"/>
-      <c r="J58" s="9" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
     </row>
     <row r="59" ht="85" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -10060,8 +10248,8 @@
           <t>同系列共用验证、不同参数的额外检查要写清；原问题整改及补测属于同一阶段，不按收样次数重复算。</t>
         </is>
       </c>
-      <c r="I59" s="9" t="n"/>
-      <c r="J59" s="9" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
     </row>
     <row r="60" ht="85" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
@@ -10104,8 +10292,8 @@
           <t>仅汇总已有完整资料不等于独立核实；调研、找厂、样品阶段已经交付的相同资料不重复算。</t>
         </is>
       </c>
-      <c r="I60" s="9" t="n"/>
-      <c r="J60" s="9" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
     </row>
     <row r="61" ht="85" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -10148,8 +10336,8 @@
           <t>实际拍照、设计修图由美工承担；上传另外列明。A+策划已包含的相同素材构思不能重复算。</t>
         </is>
       </c>
-      <c r="I61" s="9" t="n"/>
-      <c r="J61" s="9" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
     </row>
     <row r="62" ht="85" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
@@ -10192,8 +10380,8 @@
           <t>不含完整视频脚本、拍摄和剪辑；直接使用已有字幕与原创编写区分，翻译情形请补充。</t>
         </is>
       </c>
-      <c r="I62" s="9" t="n"/>
-      <c r="J62" s="9" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
     </row>
     <row r="63" ht="85" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -10236,8 +10424,8 @@
           <t>区分初步核查和完整分析；不是直接转发报表或AI原文。建议落实可另列独立执行，相同分析不重复。</t>
         </is>
       </c>
-      <c r="I63" s="9" t="n"/>
-      <c r="J63" s="9" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
     </row>
     <row r="64" ht="85" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
@@ -10280,8 +10468,8 @@
           <t>活动带来的新增销量与原有销量需区分；资料缺失要说明，不仅凭销售上涨判定有效。</t>
         </is>
       </c>
-      <c r="I64" s="9" t="n"/>
-      <c r="J64" s="9" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
     </row>
     <row r="65" ht="85" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -10324,8 +10512,8 @@
           <t>不按收费记录、SKU、Case或催办次数累加；退款结果与实际处理工作分开记录。</t>
         </is>
       </c>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
     </row>
     <row r="66" ht="85" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
@@ -10368,8 +10556,8 @@
           <t>你们目前较少遇到，先确认是否需要人工固定检查；程序自动完成的部分不当作人工工作。</t>
         </is>
       </c>
-      <c r="I66" s="9" t="n"/>
-      <c r="J66" s="9" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
     </row>
     <row r="67" ht="85" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -10412,8 +10600,8 @@
           <t>按你当前实际范围描述，不包括Test Buy。出现其他卖家不自动等于违规；多个Case不重复算整案。</t>
         </is>
       </c>
-      <c r="I67" s="9" t="n"/>
-      <c r="J67" s="9" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
     </row>
     <row r="68" ht="85" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
@@ -10456,8 +10644,8 @@
           <t>不按领取件数、评论条数或好评数量计工作；平台费用和商品成本与任务报酬分开。</t>
         </is>
       </c>
-      <c r="I68" s="9" t="n"/>
-      <c r="J68" s="9" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
     </row>
     <row r="69" ht="85" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -10500,8 +10688,8 @@
           <t>复用与原创部分需说明；同一内容覆盖多个ASIN共用。与产品A+有独立交付才分别列项。</t>
         </is>
       </c>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="9" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
     </row>
     <row r="70" ht="85" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
@@ -10544,8 +10732,8 @@
           <t>区分局部修改、简单纠错及整体重做；原制作范围漏绑补绑不属于新任务。</t>
         </is>
       </c>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="9" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
     </row>
     <row r="71" ht="85" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -10588,8 +10776,8 @@
           <t>平台自动变化不算人工操作；同一更新中包含的价格或促销动作不能重复列项。</t>
         </is>
       </c>
-      <c r="I71" s="9" t="n"/>
-      <c r="J71" s="9" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
     </row>
     <row r="72" ht="85" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
@@ -10632,8 +10820,8 @@
           <t>新建包含初始配置和现有资料填入，不重复算普通上架、图片上传；不包含实物重新包装。</t>
         </is>
       </c>
-      <c r="I72" s="9" t="n"/>
-      <c r="J72" s="9" t="n"/>
+      <c r="I72" s="8" t="n"/>
+      <c r="J72" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10651,7 +10839,7 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="115" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -10665,7 +10853,7 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>适用于任务评分P024-a至P024-f；同轮选一个最高档，受派/主动都×1，最高15分。</t>
+          <t>适用于任务报酬P024-a至P024-f；同轮选一个最高档，受派/主动都×1，最高75元。</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10891,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>积分</t>
+          <t>金额（元）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -10724,7 +10912,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -10744,7 +10932,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -10764,7 +10952,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -10784,7 +10972,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -10804,7 +10992,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
@@ -10824,7 +11012,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -10846,7 +11034,7 @@
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>负责人安排与员工自主发起都按×1。广告优化总档位上限15分/同Campaign同轮，不再叠加主动倍率。</t>
+          <t>负责人安排与员工自主发起都按×1。广告优化总档位上限75元/同Campaign同轮，不再叠加主动倍率。</t>
         </is>
       </c>
     </row>
@@ -10882,7 +11070,7 @@
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>同Campaign同轮只取最高档。先结算5分，后达10分补5分；再达15分补5分。复盘和升级不占新调整次数，也不使同一成果重新计整档。重复执行、补做本人错误不新增积分。</t>
+          <t>同Campaign同轮只取最高档。先结算25元，后达50元补25元；再达75元补25元。复盘和升级不占新调整次数，也不使同一成果重新计整档。重复执行、补做本人错误不新增金额。</t>
         </is>
       </c>
     </row>
@@ -10900,7 +11088,7 @@
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>记录基准期间、观察期间、订单/销售额、花费、ACOS；写清“明显增长”“未明显萎缩”、ACOS可接受范围以及15分的持续观察标准，由负责人确认后冻结。不同产品可用不同门槛，不事后挑有利窗口。</t>
+          <t>记录基准期间、观察期间、订单/销售额、花费、ACOS；写清“明显增长”“未明显萎缩”、ACOS可接受范围以及75元的持续观察标准，由负责人确认后冻结。不同产品可用不同门槛，不事后挑有利窗口。</t>
         </is>
       </c>
     </row>
@@ -10930,13 +11118,13 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>8/10/15分的判断</t>
+          <t>40/50/75元的判断</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>8分须效率改善且销售未明显萎缩；10分须有效增加订单或销售且ACOS可接受；15分须明显增量并持续满足效率或利润目标。不限Bid/关键词等动作类别，否定投放同样可凭结果升档。不能只以ACOS下降或广告销售额增长单一数字认定贡献。</t>
+          <t>40元须效率改善且销售未明显萎缩；50元须有效增加订单或销售且ACOS可接受；75元须明显增量并持续满足效率或利润目标。不限Bid/关键词等动作类别，否定投放同样可凭结果升档。不能只以ACOS下降或广告销售额增长单一数字认定贡献。</t>
         </is>
       </c>
     </row>
@@ -10954,7 +11142,7 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>独立创建任务仍用广告创建规则。若新Campaign属于同一优化方案，其创建和初始设置包含在整轮优化，不重复领创建分；既往同案已付创建积分含主动部分，从本轮最终积分扣除，只结非负差额，不追扣。核对产品整体销售，排除仅在Campaign间转移订单。</t>
+          <t>独立创建任务仍用广告创建规则。若新Campaign属于同一优化方案，其创建和初始设置包含在整轮优化，不重复领创建报酬；既往同案已付创建金额含主动部分，从本轮最终金额扣除，只结非负差额，不追扣。核对产品整体销售，排除仅在Campaign间转移订单。</t>
         </is>
       </c>
     </row>
@@ -10972,7 +11160,7 @@
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>同一方案涉及多个Campaign，只有各自有独立工作与独立效果证据才分别计高档。仅有产品整体增量、无法区分各Campaign贡献的，按一个合并案例取最高档总分并分配，不让各Campaign重复领取整份成果分。</t>
+          <t>同一方案涉及多个Campaign，只有各自有独立工作与独立效果证据才分别计高档。仅有产品整体增量、无法区分各Campaign贡献的，按一个合并案例取最高档总报酬并分配，不让各Campaign重复领取整份成果报酬。</t>
         </is>
       </c>
     </row>
@@ -10990,7 +11178,7 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>已经凭同一效果领取8/10/15分，不再用同一证据重复领取改善成果奖金。后续达到新的独立成果标准再认定；若存在原已付奖金，先核对奖励范围，不能把金额直接当积分相减。多人协作分配同一案例总分，每人不能都领完整档。</t>
+          <t>同一效果已领取40/50/75元档，不再领取现金成果奖；如先领现金成果奖，同一效果也不再补领广告成果档。独立实际执行可按对应低档验收，不重复奖励同一结果。多人分配同一案例总报酬。</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11196,7 @@
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>账户、站点、Campaign ID、任务/案例ID、轮次ID、发起来源、执行人及分工、执行日期及时区、问题及方案、Ads Change、前后数据及观察门槛、实际结果、核定档位、累计已结算积分、本次补差、验收人和日期、关联成果奖励。</t>
+          <t>账户、站点、Campaign ID、任务/案例ID、轮次ID、发起来源、执行人及分工、执行日期及时区、问题及方案、Ads Change、前后数据及观察门槛、实际结果、核定档位、累计已结算金额、本次补差、验收人和日期、关联成果奖励。</t>
         </is>
       </c>
     </row>
@@ -11041,28 +11229,28 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>适用P025-a/P025-b；本页不改变Buy Box、变体维护及滞留库存的原计分单位。</t>
+          <t>适用P025-a/P025-b；本页不改变Buy Box、变体维护及滞留库存的原计酬单位。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>能共同处理的同原因ASIN只计一批；必须逐ASIN提交、跟进及核验的，在首个基础档上每增加一个加1分。</t>
+          <t>能共同处理的同原因ASIN只计一批；必须逐ASIN提交、跟进及核验的，在首个基础档上每增加一个加5元。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>同一批只选已有依据2分或独立排查4分；系列名称不决定合批，实际原因、证据、方案与处理过程才是依据。</t>
+          <t>同一批只选已有依据10元或独立排查20元；系列名称不决定合批，实际原因、证据、方案与处理过程才是依据。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>任务评分L列为基础档主动积分示例；实际批次合计按本页核算后乘倍率，不能把L列当成每ASIN单价。</t>
+          <t>任务报酬L列为基础档主动金额示例；实际批次合计按本页核算后乘倍率，不能把L列当成每ASIN单价。</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11267,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>计分与认定</t>
+          <t>计酬与认定</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11284,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2分/批；1个ASIN也按一批。</t>
+          <t>10元/批；1个ASIN也按一批。</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11301,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>4分/批；不按共用证据的ASIN数乘4。</t>
+          <t>20元/批；不按共用证据的ASIN数量重复领取20元。</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11318,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>N为实际逐个处理并验收的去重ASIN数，N≥1：基础总分＝所选档位＋(N－1)×1。无交付不计。</t>
+          <t>N为实际逐个处理并验收的去重ASIN数，N≥1：基础报酬＝所选档位金额＋(N－1)×5元。无交付不计。</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11369,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>不增加积分。同ASIN多SKU只计一个；同批多人分配总分，不每人领完整档。</t>
+          <t>不增加金额。同ASIN多SKU只计一个；同批多人分配总报酬，不每人领完整档。</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11386,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>事先记录可共用的实际处理组；每组共同提交及核验算一个处理单元，必须逐ASIN的各算一个。按基础档＋额外必要处理单元数×1，共用排查不重计。</t>
+          <t>记录必须独立提交及核验的处理单元；基础档金额＋额外必要处理单元数×5元，共用排查不重复计费。</t>
         </is>
       </c>
     </row>
@@ -11210,12 +11398,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2分档实际补充独立排查，转4分档；或原批追加必要分别处理的ASIN</t>
+          <t>10元档实际补充独立排查，转20元档；或原批追加必要分别处理的ASIN</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>重新计算同批累计应得总分，扣除同批已结算积分，仅补差额；跨月不重领基础档。</t>
+          <t>重新计算同批累计应得总报酬，扣除同批已结算金额，仅补差额；跨月不重领基础档。</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11420,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>实际积分＝(基础档＋必要逐项执行附加分)×倍率；同批倍率沿用来源，不把附加操作重新认定主动。</t>
+          <t>实际金额＝(基础档＋必要逐项执行附加金额)×倍率；同批倍率沿用来源，不把附加操作重新认定主动。</t>
         </is>
       </c>
     </row>
@@ -11249,7 +11437,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>未解决须完整证据并经负责人确认阶段结案；仍处理中不自动结算。本人纠错不计；同一变体、库存或Buy Box修复成果不重复计分。</t>
+          <t>未解决须完整证据并经负责人确认阶段结案；仍处理中不自动结算。本人纠错不计；同一变体、库存或Buy Box修复成果不重复计酬。</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11454,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>受派4分；主动4×1.5＝6分。</t>
+          <t>受派20元；主动20×1.5＝30元。</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11471,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>受派4＋(5－1)＝8分；主动8×1.5＝12分。</t>
+          <t>受派20＋(5－1)×5＝40元；主动40×1.5＝60元。</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11488,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>受派2＋(5－1)＝6分；主动6×1.5＝9分。</t>
+          <t>受派10＋(5－1)×5＝30元；主动30×1.5＝45元。</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11505,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>仍按一批：已有依据2分，独立排查4分；不能按Case数增加。</t>
+          <t>仍按一批：已有依据10元，独立排查20元；不能按Case数增加。</t>
         </is>
       </c>
     </row>
@@ -11337,7 +11525,7 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
@@ -11346,14 +11534,14 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>临时工作分档</t>
+          <t>临时任务金额档位</t>
         </is>
       </c>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>日常运营1—5分；P044—P051固定10分。8及15分在现有任务中保留给广告专项，不能套到开发分析上。</t>
+          <t>日常运营5—25元；P044—P051固定50元。8及75元在现有任务中保留给广告专项，不能套到开发报酬析上。</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11555,7 @@
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>这些分值是可讨论的相对权重，不代表既有金额；本版未引入月度上限。</t>
+          <t>这些金额是可讨论的相对权重，不代表既有金额；本版未引入月度上限。</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11579,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>建议分</t>
+          <t>金额（元）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -11413,7 +11601,7 @@
     <row r="8" ht="85" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>1分</t>
+          <t>5元</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -11422,7 +11610,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -11436,14 +11624,14 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>按约定单位验收；周度事项不拆成每天计分。</t>
+          <t>按约定单位验收；周度事项不拆成每天计酬。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2分</t>
+          <t>10元</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -11452,7 +11640,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -11473,7 +11661,7 @@
     <row r="10" ht="85" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>3分</t>
+          <t>15元</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -11482,7 +11670,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -11496,14 +11684,14 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>留下核对结果和完成记录；Case次数不是分值依据。</t>
+          <t>留下核对结果和完成记录；Case次数不是金额依据。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>4分</t>
+          <t>20元</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -11512,7 +11700,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -11533,7 +11721,7 @@
     <row r="12" ht="85" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>5分</t>
+          <t>25元</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -11542,7 +11730,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
@@ -11556,14 +11744,14 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>已有内容经Skill改写标题/五点/描述各2分，不套本档。</t>
+          <t>已有内容经Skill改写标题/五点/描述各10元，不套本档。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="85" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>8分</t>
+          <t>40元</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -11572,7 +11760,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -11586,14 +11774,14 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>P044—P051不使用8分档，均固定10分；未列临时事项先明确规则。</t>
+          <t>P044—P051不使用40元档，均固定50元；未列临时事项先明确规则。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="85" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>50元</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -11602,11 +11790,11 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>P044—P051每项固定10分；按各自计量单位和完整交付验收。</t>
+          <t>P044—P051每项固定50元；按各自计量单位和完整交付验收。</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -11616,14 +11804,14 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>不再分难度高低；系列共用成果只计一次。广告10分另按有效扩大销售验收。</t>
+          <t>不再分难度高低；系列共用成果只计一次。广告50元另按有效扩大销售验收。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>15分</t>
+          <t>75元</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -11632,11 +11820,11 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>仅保留广告专项中持续显著改善的15分标准。</t>
+          <t>仅保留广告专项中持续显著改善的75元标准。</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -11646,7 +11834,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>新品开发及经营分析不使用15分；广告×1且同轮只取最高档。</t>
+          <t>新品开发及经营分析不使用75元；广告×1且同轮只取最高档。</t>
         </is>
       </c>
     </row>
@@ -11664,17 +11852,17 @@
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>1、2、3、4、5、8、10、15为完整档位，取一档。</t>
+          <t>5、10、15、20、25、40、50、75元为完整金额档位，只取一档。</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>例如基础5分，符合8分条件，整项计8分。</t>
+          <t>例如基础25元，符合40元条件，整项计40元。</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>不用5+8，也不再乘难度系数；主动倍率另按既定规则。</t>
+          <t>不把25元和40元相加，也不乘难度系数；主动倍率按对应规则。</t>
         </is>
       </c>
     </row>
@@ -11697,12 +11885,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>同系列仅参数不同，共用调研、厂家和策划不得每SKU领取全套开发分。</t>
+          <t>同系列仅参数不同，共用调研、厂家和策划不得每SKU领取全套开发报酬。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>确有不同调研或验证工作时，先明确新增独立范围再定分。</t>
+          <t>确有不同调研或验证工作时，先明确新增独立范围再定价。</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11908,7 @@
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>全新/完全重做5分；复用模板3分；局部修改2分；已有内容新增绑定1分/SKU。</t>
+          <t>全新/完全重做25元；复用模板15元；局部修改10元；已有内容新增绑定5元/SKU。</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -11753,12 +11941,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>本人错误纠正、漏做补做和重复提交不新增分；有证据的外部变更按新任务。</t>
+          <t>本人错误纠正、漏做补做和重复提交不新增报酬；有证据的外部变更按新任务。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>有效调研得出不开发结论也可计分；尚未完成的报告不直接领取完整阶段分。</t>
+          <t>有效调研得出不开发结论也可计酬；尚未完成的报告不直接领取完整阶段报酬。</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11969,12 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>日常运营1—5分；开发及经营分析完整独立交付10分；广告按专项。其他未列事项先补规则。</t>
+          <t>日常运营5—25元；开发及经营分析完整独立交付50元；广告按专项。其他未列事项先补规则。</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>长期事项仅按真正独立可验收阶段登记；不人为拆碎成果，不用难度系数扩大固定10分。</t>
+          <t>长期事项仅按真正独立可验收阶段登记；不人为拆碎成果，不用难度系数扩大固定50元。</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11990,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -11811,12 +11999,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>经营分析完整交付固定10分，不再设置15分或不同难度档。</t>
+          <t>经营分析完整交付固定50元，不再设置75元或不同难度档。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>只分析有证据的相关项；后续优化另有独立交付才计，不能重复分析分。</t>
+          <t>只分析有证据的相关项；后续优化另有独立交付才计，不能重复分析报酬。</t>
         </is>
       </c>
     </row>
@@ -11839,12 +12027,12 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>常规资料核对修正按1—5分；如属P047额外开发资料核实，按该项完整交付固定10分，不能重复领取。</t>
+          <t>常规资料核对修正按5—25元；如属P047额外开发资料核实，按该项完整交付固定50元，不能重复领取。</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>范围未明确，不直接定固定分。</t>
+          <t>范围未明确，不直接定固定价。</t>
         </is>
       </c>
     </row>
@@ -11860,7 +12048,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -11869,7 +12057,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2分：直接套模板；5分：需设计并核验对象匹配或转换规则。</t>
+          <t>10元：直接套模板；25元：需设计并核验对象匹配或转换规则。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11890,7 +12078,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -11899,7 +12087,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>3分：程序不支持须逐项手动处理；5分：需解决资料与对象映射问题。</t>
+          <t>15元：程序不支持须逐项手动处理；25元：需解决资料与对象映射问题。</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -11920,7 +12108,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -11929,12 +12117,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2分：简单转交；5分：需解决实际多方冲突。</t>
+          <t>10元：简单转交；25元：需解决实际多方冲突。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>不按催办次数或等待天数加分。</t>
+          <t>不按催办次数或等待天数加价。</t>
         </is>
       </c>
     </row>
@@ -11957,7 +12145,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>当前不直接套8/10/15分；不属于现有运营或新品开发范围时另行确定规则。</t>
+          <t>当前不直接套40/50/75元；不属于现有运营或新品开发范围时另行确定规则。</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -11985,12 +12173,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>已有图片上传2分；运营内容制作1—5分；新品开发独立主辅图策划可按10分。</t>
+          <t>已有图片上传10元；运营内容制作5—25元；新品开发独立主辅图策划可按50元。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>实际设计拍摄职责需说明，不能仅按任务标题定分。</t>
+          <t>实际设计拍摄职责需说明，不能仅按任务标题定价。</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12206,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>定分理由应说明比相邻低档多了什么实际工作。</t>
+          <t>定价理由应说明比相邻低档多了什么实际工作。</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12238,7 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>保留原表有效的复盘、资料版本和责任纠错规则；更新旧金额及难度系数引用。</t>
+          <t>按直接金额保留复盘、资料版本和责任纠错规则。</t>
         </is>
       </c>
     </row>
@@ -12107,7 +12295,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>登记任务编号、人员、站点、Listing/SKU或A+内容编号、具体问题、证据、拟修改模块、预期目标、预计积分及复盘日期。负责人确认后执行；主动提出的方案同样登记。</t>
+          <t>登记任务编号、人员、站点、Listing/SKU或A+内容编号、具体问题、证据、拟修改模块、预期目标、预计金额及复盘日期。负责人确认后执行；主动提出的方案同样登记。</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12319,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>各项目分值以任务评分为唯一数值规则。Skill辅助改写标题、五点、描述各2分；A+全新5分、复用3分、局改2分、绑定1分/SKU。无难度系数。</t>
+          <t>各项目金额以任务报酬为唯一数值规则。Skill辅助改写标题、五点、描述各10元；A+全新25元、复用15元、局改10元、绑定5元/SKU。无难度系数。</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12331,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>同一站点、同一Listing的同一模块，或同一份共享A+，在上轮复盘完成前不得再领取该模块的新优化积分。追加修改、调试、回滚、返工并入原任务；换OA编号、拆分五点、换人员或跨月不解除限制。</t>
+          <t>同一站点、同一Listing的同一模块，或同一份共享A+，在上轮复盘完成前不得再领取该模块的新优化金额。追加修改、调试、回滚、返工并入原任务；换OA编号、拆分五点、换人员或跨月不解除限制。</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12379,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>负责人安排的优化先登记预计任务积分，内容发布核验且复盘形成结论后结算。自主发起改善按正常任务积分×主动倍率结算（见"任务评分"主动执行倍率规则），不再使用主动改善等级金额。结果未增长不自动判为零金额，按依据、实际交付及复盘验收；同一工作不跨两条路径重复计费。 新品首次文案编写按可用定稿验收，不适用本页优化复盘等待要求；其他制作及发布任务按各项目完成条件验收。</t>
+          <t>负责人安排的优化先登记预计任务金额，内容发布核验且复盘形成结论后结算。自主发起改善按正常任务金额×主动倍率结算（见“主动改善评价”），不再使用主动改善等级金额。结果未增长不自动判为零金额，按依据、实际交付及复盘验收；同一工作不跨两条路径重复计费。 新品首次文案编写按可用定稿验收，不适用本页优化复盘等待要求；其他制作及发布任务按各项目完成条件验收。</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12391,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>上一轮已完成复盘，且出现新证据、新问题或经确认的新目标，才能建立新的计分优化任务。完成复盘本身不是再次领取金额的依据。</t>
+          <t>上一轮已完成复盘，且出现新证据、新问题或经确认的新目标，才能建立新的计酬优化任务。完成复盘本身不是再次领取金额的依据。</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12415,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>同份同轮A+只选一个制作档，制作含本次首次绑定；同一纠错不再领优化或图片修改积分。原有A+完全重做须保留旧版、另建新ID，记录原因及前后差异，核验新版本应用。</t>
+          <t>同份同轮A+只选一个制作档，制作含本次首次绑定；同一纠错不再领优化或图片修改金额。原有A+完全重做须保留旧版、另建新ID，记录原因及前后差异，核验新版本应用。</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12427,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>任务积分按真实来源和主动改善评价计算；本人责任0分。普通任务与主动任务不重复结算。现金成果奖励另按改善成果奖励，广告已按同一效果取得8/10/15分不再重复领现金成果奖。</t>
+          <t>任务金额按真实来源和主动改善评价计算；本人责任0元。普通任务与主动任务不重复结算。现金成果奖励另按改善成果奖励，广告已按同一效果取得40/50/75元不再重复领现金成果奖。</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12439,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>原任务及来源、计分项、计分组、对象、问题及证据、预期目标、前后内容、实际生效日、复盘日期与结论、核定积分、已结算积分、补差、结算月份；已有OA/Ads Change直接关联，不重复抄录。</t>
+          <t>原任务及来源、计酬项、计酬组、对象、问题及证据、预期目标、前后内容、实际生效日、复盘日期与结论、核定金额、已结算金额、补差、结算月份；已有OA/Ads Change直接关联，不重复抄录。</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12559,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>根据实际修改对象选择Listing纠错、内容优化或变体维护。同一交付只选一项；未覆盖的后台更新先明确工作范围和计分。依据原确认资料及变更记录判定责任。</t>
+          <t>根据实际修改对象选择Listing纠错、内容优化或变体维护。同一交付只选一项；未覆盖的后台更新先明确工作范围和计酬。依据原确认资料及变更记录判定责任。</t>
         </is>
       </c>
     </row>
@@ -12403,7 +12591,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="105" customWidth="1" min="6" max="6"/>
@@ -12419,14 +12607,14 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>技术研发专用：研究积分＋突破额外积分＋投产积分＋销售提成。普通新品开发P044—P051固定10分规则保持。</t>
+          <t>技术研发：研究报酬＋突破额外奖金＋投产奖金＋销售提成；普通新品开发各独立交付仍按50元。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>50/100/100的单位恢复为积分，不是人民币元；都是试行参考，技术攻关的具体范围及积分在立项时确认。</t>
+          <t>研究250元/独立任务、突破500元/独立目标、投产500元/独立项目，均为立项参考；不是整个研发项目的固定总价。</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12628,7 @@
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>已经验收的阶段可当月结算；未完成节点不按口头进度比例发分。相同任务和成果不得在两套体系重复计分。</t>
+          <t>按已验收节点在当月付款；突破与投产达到各自标准后额外发放，不从研究报酬中扣除。</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12645,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>参考值</t>
+          <t>参考金额/参数</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -12484,25 +12672,25 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>研究积分</t>
+          <t>研究任务报酬</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>分/独立研究任务</t>
+          <t>元/独立研究任务</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>试行参考；立项确认具体总分</t>
+          <t>试行参考；立项确认具体总报酬</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>约定调查、拆解、分析、设计及实验。有新增证据、阶段结论和下一步方案；无突破也可验收。不是每周自动领取。</t>
+          <t>立项确定一个技术问题、范围、交付和验证方法，参考总报酬250元。资料调查、拆解、分析及试验是该任务的节点，不各自再领完整任务价。一个项目确有多个独立技术问题可分别立项；明显更复杂的任务在开始前另定总金额。无突破但有可靠证据及结论，也可验收研究工作。</t>
         </is>
       </c>
     </row>
@@ -12514,25 +12702,25 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>阶段突破额外积分</t>
+          <t>阶段突破额外奖金</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>分/独立突破目标</t>
+          <t>元/独立突破目标</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>试行参考；立项确认指标及总分</t>
+          <t>试行参考；立项确认指标及总报酬</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>达到事先约定技术目标，有可复现验证。与研究积分可同时领取；同一目标按阶段累计只领一次总额。重大突破另确认，不自动倍增。</t>
+          <t>达到事先约定技术目标，有可复现验证。与研究报酬可同时领取；同一目标按阶段累计只领一次总额。重大突破另确认，不自动倍增。</t>
         </is>
       </c>
     </row>
@@ -12544,15 +12732,15 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>投产积分</t>
+          <t>投产验收奖金</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>分/独立研发项目</t>
+          <t>元/独立研发项目</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -12577,7 +12765,7 @@
           <t>销售提成比例</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="17" t="n">
         <v>0.03</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -12650,7 +12838,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>同一研究任务先定总分，再分配独立可验收节点，节点积分合计等于任务总分。按已验收节点所在月结算，不要求等整个问题研究结束。</t>
+          <t>同一研究任务先定总报酬，再分配独立可验收节点，节点金额合计等于任务总报酬。按已验收节点所在月结算，不要求等整个问题研究结束。</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12856,7 @@
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>分</t>
+          <t>元</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -12678,7 +12866,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>研究总分50分，可约定分析方案10分、关键试验20分、结论及后续建议20分。只完成前两节点计30分；全部完成累计50分，不叠加另一份完整50分。</t>
+          <t>参考研究任务250元：分析方案50元、关键试验100元、结论与下一步100元。验收前两节点当月付150元，最后节点完成补100元；全任务累计250元。达到独立突破目标另奖500元，项目投产通过验收另奖500元。</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12894,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>可靠地排除一条路线可以拿研究积分。只有事先把判明可行性设为突破目标时，才按约定认定突破。正常探索和有效失败不是责任返工；本人疏漏违反已确认要求造成的返工不另计。</t>
+          <t>可靠地排除一条路线可以拿研究报酬。只有事先把判明可行性设为突破目标时，才按约定认定突破。正常探索和有效失败不是责任返工；本人疏漏违反已确认要求造成的返工不另计。</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12922,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>每周一次记录新增成果、当前卡点、下一步，保留已有工作记录。无突破不等于偷懒；无新增证据、反复尝试不总结需复核方法。周报不单独给分。</t>
+          <t>每周一次记录新增成果、当前卡点、下一步，保留已有工作记录。无突破不等于偷懒；无新增证据、反复尝试不总结需复核方法。周报不单独付酬。</t>
         </is>
       </c>
     </row>
@@ -12762,7 +12950,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>按约定检查点说明障碍、已尝试方法和下一步，负责人决定继续、调整或暂停。合理等待不扣已验收分。原表60天终止判断不作为默认，按项目确认检查安排。</t>
+          <t>按约定检查点说明障碍、已尝试方法和下一步，负责人决定继续、调整或暂停。合理等待不扣已验收报酬。原表60天终止判断不作为默认，按项目确认检查安排。</t>
         </is>
       </c>
     </row>
@@ -12818,7 +13006,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>共用研究、突破和投产成果在项目内只计一次；多人分配同一项目总分和提成池，份额合计100%。不同SKU不自动构成新研究项目。</t>
+          <t>共用研究、突破和投产成果在项目内只计一次；多人分配同一项目总报酬和提成池，份额合计100%。不同SKU不自动构成新研究项目。 例如同一研究任务250元，甲乙按已确认贡献60%/40%分配为150元/100元，不是每人250元；独立上架或其他不同交付仍按对应项目另计。</t>
         </is>
       </c>
     </row>
@@ -12874,7 +13062,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>本人设计责任缺陷的补救不另加研究/突破分；新的独立需求或技术问题另确认。原表“3个月质量义务”不作为新增默认承诺，按项目确认责任及支持范围。</t>
+          <t>本人设计责任缺陷的补救不另加研究/突破奖金；新的独立需求或技术问题另确认。原表“3个月质量义务”不作为新增默认承诺，按项目确认责任及支持范围。</t>
         </is>
       </c>
     </row>
@@ -12902,7 +13090,7 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>项目及任务ID、研究问题、技术目标、交付/验证方法、研究总分及节点分配、检查日期、成员份额、突破及投产目标、验收记录、已结算积分。提成另记参数确认和结算记录。</t>
+          <t>项目及任务ID、研究问题、技术目标、交付/验证方法、研究总报酬及节点分配、检查日期、成员份额、突破及投产目标、验收记录、已结算金额。提成另记参数确认和结算记录。 本月应付研究报酬及突破/投产奖金＝已验收累计应付总额减去历史已付金额，只结正差额。</t>
         </is>
       </c>
     </row>
@@ -12936,28 +13124,28 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>统一采用月底统计模式：OA和Ads Change保持原入口，Streamlit只需月度汇总、异常核对及结算。</t>
+          <t>月底按OA、Ads Change及主动记录汇总直接金额，继续使用原有入口。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>黄色列是需要确认的参数，空白不代表0，也不代表放弃奖励。确认后记录适用版本及期间。</t>
+          <t>任务金额已确定；提成比例、期限、成本及成员份额仍须按项目确认。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>本表不把试行建议自动变成合同或实发承诺；固定积分标准与待确认提成参数分开。</t>
+          <t>月度报酬＝本月核定未付任务报酬＋本月突破/投产奖金＋本月现金成果奖；销售提成按约定周期另结。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>来源：桌面原表与本次已确认对话。原表新增的500元、95%、按月份分配等默认项已撤为待确认。</t>
+          <t>固定金额可按后续确认版本调整；原已结算记录保留当时的金额标准。</t>
         </is>
       </c>
     </row>
@@ -12986,18 +13174,22 @@
     <row r="8" ht="85" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>积分单价（元/分）</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
+          <t>计酬单位</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>人民币元</t>
+        </is>
+      </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>历史曾提出5元/分；本次不自动应用。确认适用期间/项目后填数，已结算记录保留原单价。</t>
+          <t>直接使用任务报酬表中的金额，不设置或使用积分换算参数。</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13340,7 @@
     <row r="17" ht="85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>月度任务积分</t>
+          <t>月度任务金额</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -13159,7 +13351,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>月底汇总OA完成并验收任务、Ads Change认领及已确认档位、现有主动页记录。按组/轮次去重，确认未结算积分及补差。</t>
+          <t>月底汇总OA完成并验收任务、Ads Change认领及已确认档位、现有主动页记录。按组/轮次去重，确认未结算金额及补差。</t>
         </is>
       </c>
     </row>
@@ -13190,12 +13382,12 @@
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>公式口径</t>
+          <t>直接金额汇总</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>已核定未付积分×适用已确认单价＋当月已核定现金成果奖；提成按约定周期另结。参数未确认时只统计积分，不输出应付金额。</t>
+          <t>已核定未付任务报酬＋已核定未付研发突破/投产奖金＋已核定未付改善成果奖金。研发研究报酬归任务报酬，不能再加一次；提成按项目约定另结。</t>
         </is>
       </c>
     </row>
@@ -13213,7 +13405,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>确认结算后锁定来源ID、规则版本、数量、倍率、积分、单价及月份。更正通过补差记录，不重发完整任务分。</t>
+          <t>确认结算后锁定来源ID、规则版本、数量、倍率、金额、单价及月份。更正通过补差记录，不重发完整任务报酬。</t>
         </is>
       </c>
     </row>
